--- a/output/10_新人教育カリキュラム_マスター管理表.xlsx
+++ b/output/10_新人教育カリキュラム_マスター管理表.xlsx
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_公会計'!$A$4:$J$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_公営企業会計'!$A$4:$J$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_高齢者・介護保険'!$A$4:$J$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_障害者・障害児'!$A$4:$J$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_障害者・障害児'!$A$4:$J$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_地域福祉'!$A$4:$J$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09_こども・子育て'!$A$4:$J$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10_その他計画'!$A$4:$J$18</definedName>
@@ -2044,22 +2044,22 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
+          <t>1-3ヶ月</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Ⅰ 基礎導入</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>制度知識</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
           <t>食育推進計画</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>1-3ヶ月</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Ⅰ 基礎導入</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>制度知識</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -2094,22 +2094,22 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
+          <t>1-3ヶ月</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Ⅰ 基礎導入</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>制度知識</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
           <t>健康増進計画</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>1-3ヶ月</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Ⅰ 基礎導入</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>制度知識</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -2144,22 +2144,22 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t>4-12ヶ月</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Ⅱ〜Ⅲ</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>業務</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
           <t>健康増進計画</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>4-12ヶ月</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Ⅱ〜Ⅲ</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>業務</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -2194,22 +2194,22 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
+          <t>1-3ヶ月</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Ⅰ 基礎導入</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>制度知識</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
           <t>農業振興計画</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>1-3ヶ月</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Ⅰ 基礎導入</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>制度知識</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -2244,22 +2244,22 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>4-12ヶ月</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Ⅱ〜Ⅲ</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>業務</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
           <t>農業振興計画</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>4-12ヶ月</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Ⅱ〜Ⅲ</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>業務</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -2294,22 +2294,22 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
+          <t>1-3ヶ月</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Ⅰ 基礎導入</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>制度知識</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
           <t>男女共同参画計画</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>1-3ヶ月</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Ⅰ 基礎導入</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>制度知識</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -2344,22 +2344,22 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>4-12ヶ月</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Ⅱ〜Ⅲ</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>業務</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
           <t>男女共同参画計画</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>4-12ヶ月</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Ⅱ〜Ⅲ</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>業務</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -2394,22 +2394,22 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
+          <t>1-3ヶ月</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Ⅰ 基礎導入</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>制度知識</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
           <t>財政計画</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>1-3ヶ月</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Ⅰ 基礎導入</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>制度知識</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -2444,22 +2444,22 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>13-24ヶ月</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>Ⅴ 単独遂行</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>業務</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
           <t>財政計画</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>13-24ヶ月</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Ⅴ 単独遂行</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>業務</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -2494,22 +2494,22 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
+          <t>1-3ヶ月</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Ⅰ 基礎導入</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>制度知識</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
           <t>公共施設等総合管理計画</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>1-3ヶ月</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Ⅰ 基礎導入</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>制度知識</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -2544,22 +2544,22 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
+          <t>13-24ヶ月</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>Ⅴ 単独遂行</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>業務</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
           <t>公共施設等総合管理計画</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>13-24ヶ月</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Ⅴ 単独遂行</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>業務</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -2594,22 +2594,22 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
+          <t>13-24ヶ月</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Ⅴ 単独遂行</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>業務</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
           <t>個別施設計画</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>13-24ヶ月</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Ⅴ 単独遂行</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>業務</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -2644,22 +2644,22 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>4-12ヶ月</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Ⅱ〜Ⅲ</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>営業</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
           <t>その他計画（共通）</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>4-12ヶ月</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Ⅱ〜Ⅲ</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>営業</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -2694,22 +2694,22 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>25-36ヶ月</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Ⅵ 応用・指導</t>
+        </is>
+      </c>
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>営業</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
           <t>その他計画（共通）</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>25-36ヶ月</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Ⅵ 応用・指導</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>営業</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -11897,7 +11897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12680,8 +12680,58 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>25-36ヶ月</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Ⅵ 応用・指導</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>営業</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>統合提案・当事者参画型の商品化</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>3計画一体＋高齢・こども・地域福祉との統合提案の主導／当事者参画（当事者委員・団体ヒアリング・わかりやすい版）を差別化要素とした提案設計／自立支援協議会の運営支援・研修の付帯提案／県・障害福祉圏域単位の案件</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>当事者参画を組み込んだ提案で他社と差別化し、複数計画一体の大型案件を受注できる。</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>受注実績・単価改善</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>自社実績DB／一体策定の事例／当事者団体とのネットワーク</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J18"/>
+  <autoFilter ref="A4:J19"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>

--- a/output/10_新人教育カリキュラム_マスター管理表.xlsx
+++ b/output/10_新人教育カリキュラム_マスター管理表.xlsx
@@ -23,6 +23,10 @@
     <sheet name="13_評価ルーブリック" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="14_教材・参考資料" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="15_年間業務カレンダー" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="16_営業提案レベル定義" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="17_営業提案 深度マトリクス" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="18_テーマ別 提案ネタ台帳" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="19_訪問前 準備チェックリスト" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_月次ロードマップ'!$A$4:$I$40</definedName>
@@ -35,8 +39,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'09_こども・子育て'!$A$4:$J$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'10_その他計画'!$A$4:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'11_共通スキル'!$A$4:$J$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'12_個人別チェックシート'!$A$5:$K$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'12_個人別チェックシート'!$A$5:$K$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'14_教材・参考資料'!$A$4:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'18_テーマ別 提案ネタ台帳'!$A$4:$F$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'19_訪問前 準備チェックリスト'!$A$4:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +51,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,8 +91,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <color rgb="00843C0C"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="30">
+  <fills count="36">
     <fill>
       <patternFill/>
     </fill>
@@ -233,6 +250,36 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F7F7F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00808000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -318,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -458,6 +505,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -825,7 +902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -978,94 +1055,124 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>4. 運用サイクル（推奨）</t>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　16_営業提案レベル定義… 営業提案をどこまで踏み込んでよいか（レベル別）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　17_営業提案 深度マトリクス… 提案素材9種 × L1〜L5 の踏み込み範囲</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　毎月　　… 上長と本人で30分の面談。当月の学習項目と習得目標の達成状況を確認し、翌月の重点を決める。</t>
+          <t xml:space="preserve">　18_テーマ別 提案ネタ台帳… 指針・マニュアル・事例・補助金・起債・関連施策・現行課題の一覧</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　19_訪問前 準備チェックリスト… レベル別に、訪問前に済ませておくこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>4. 運用サイクル（推奨）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　毎月　　… 上長と本人で30分の面談。当月の学習項目と習得目標の達成状況を確認し、翌月の重点を決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　四半期　… 成果物レビューを1件必ず実施し、「確認方法」欄の方法で到達度を確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　半期　　… 12_個人別チェックシートで自己評価と上長評価を突き合わせ、差異の原因を対話する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　年次　　… レベル判定を確定し、次年度の主担当・副担当テーマと育成計画を決定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>5. レベル判定の原則</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・「知っている」ではなく「できた実績があるか」で判定します。判定には必ず具体的な案件名・成果物名を紐づけてください。</t>
+          <t xml:space="preserve">　半期　　… 12_個人別チェックシートで自己評価と上長評価を突き合わせ、差異の原因を対話する。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・1つの項目でL3と判定するには、原則として同種の作業を2案件以上、単独で完遂している必要があります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　・自己評価と上長評価に2段階以上の差がある場合は、必ず面談で認識を合わせてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>6. 更新について</t>
+          <t xml:space="preserve">　年次　　… レベル判定を確定し、次年度の主担当・副担当テーマと育成計画を決定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>5. レベル判定の原則</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・「知っている」ではなく「できた実績があるか」で判定します。判定には必ず具体的な案件名・成果物名を紐づけてください。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・制度改正（基本指針、報酬改定、会計基準、各省ガイドライン等）が生じた場合は、該当テーマシートの学習内容を年1回見直してください。</t>
+          <t xml:space="preserve">　・1つの項目でL3と判定するには、原則として同種の作業を2案件以上、単独で完遂している必要があります。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　・自己評価と上長評価に2段階以上の差がある場合は、必ず面談で認識を合わせてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>6. 更新について</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・制度改正（基本指針、報酬改定、会計基準、各省ガイドライン等）が生じた場合は、該当テーマシートの学習内容を年1回見直してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　・計画の「期」（第○期）は年度の経過とともに進みます。テーマシートの記載は根拠法と期間の考え方を示すもので、具体の期・年度は都度確認してください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="36">
     <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A1:H1"/>
@@ -1073,6 +1180,7 @@
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A41:H41"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A12:H12"/>
@@ -1080,6 +1188,7 @@
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A23:H23"/>
@@ -1088,14 +1197,14 @@
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A38:H38"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3508,7 +3617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4164,12 +4273,12 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>共通評価軸</t>
+          <t>営業提案</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>制度・専門知識</t>
+          <t>① 国の指針・基本方針</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -4199,12 +4308,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>共通評価軸</t>
+          <t>営業提案</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>調査・分析</t>
+          <t>② 作成マニュアル・手引き・ツール</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -4219,7 +4328,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>L3〜L4</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="G22" s="46" t="inlineStr"/>
@@ -4234,17 +4343,17 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>共通評価軸</t>
+          <t>営業提案</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>推計・シミュレーション</t>
+          <t>③ 他自治体事例</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>L1〜L2</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
@@ -4254,7 +4363,7 @@
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>L3〜L4</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="G23" s="46" t="inlineStr"/>
@@ -4269,17 +4378,17 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>共通評価軸</t>
+          <t>営業提案</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>執筆・成果物品質</t>
+          <t>④ 補助金・交付金</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1〜L2</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -4304,17 +4413,17 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>共通評価軸</t>
+          <t>営業提案</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>会議運営・ファシリテーション</t>
+          <t>⑤ 起債・交付税措置・その他財源</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
@@ -4324,7 +4433,7 @@
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>L3〜L4</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="G25" s="46" t="inlineStr"/>
@@ -4339,12 +4448,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>共通評価軸</t>
+          <t>営業提案</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>顧客対応・折衝</t>
+          <t>⑥ 関連施策・関連計画</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -4374,17 +4483,17 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>共通評価軸</t>
+          <t>営業提案</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>営業・提案</t>
+          <t>⑦ 現行計画の課題（進捗評価）</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>L1〜L2</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
@@ -4394,7 +4503,7 @@
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>L3〜L4</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="G27" s="46" t="inlineStr"/>
@@ -4409,17 +4518,17 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>共通評価軸</t>
+          <t>営業提案</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>プロジェクト管理・採算</t>
+          <t>⑧ 都道府県の動き</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1〜L2</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -4444,12 +4553,12 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>共通評価軸</t>
+          <t>営業提案</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>指導・組織貢献</t>
+          <t>⑨ 見積・契約条件</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -4459,12 +4568,12 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>L2〜L3</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L3〜L4</t>
         </is>
       </c>
       <c r="G29" s="46" t="inlineStr"/>
@@ -4473,99 +4582,414 @@
       <c r="J29" s="9" t="inlineStr"/>
       <c r="K29" s="9" t="inlineStr"/>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>共通評価軸</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>制度・専門知識</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="G30" s="46" t="inlineStr"/>
+      <c r="H30" s="46" t="inlineStr"/>
+      <c r="I30" s="6" t="inlineStr"/>
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>共通評価軸</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>調査・分析</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>L3〜L4</t>
+        </is>
+      </c>
+      <c r="G31" s="46" t="inlineStr"/>
+      <c r="H31" s="46" t="inlineStr"/>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="9" t="inlineStr"/>
+      <c r="K31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>共通評価軸</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>推計・シミュレーション</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>L1〜L2</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>L3〜L4</t>
+        </is>
+      </c>
+      <c r="G32" s="46" t="inlineStr"/>
+      <c r="H32" s="46" t="inlineStr"/>
+      <c r="I32" s="6" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr"/>
+      <c r="K32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>共通評価軸</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>執筆・成果物品質</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="G33" s="46" t="inlineStr"/>
+      <c r="H33" s="46" t="inlineStr"/>
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="9" t="inlineStr"/>
+      <c r="K33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>共通評価軸</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>会議運営・ファシリテーション</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>L3〜L4</t>
+        </is>
+      </c>
+      <c r="G34" s="46" t="inlineStr"/>
+      <c r="H34" s="46" t="inlineStr"/>
+      <c r="I34" s="6" t="inlineStr"/>
+      <c r="J34" s="7" t="inlineStr"/>
+      <c r="K34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>共通評価軸</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>顧客対応・折衝</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="G35" s="46" t="inlineStr"/>
+      <c r="H35" s="46" t="inlineStr"/>
+      <c r="I35" s="10" t="inlineStr"/>
+      <c r="J35" s="9" t="inlineStr"/>
+      <c r="K35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>共通評価軸</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>営業・提案</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>L1〜L2</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>L3〜L4</t>
+        </is>
+      </c>
+      <c r="G36" s="46" t="inlineStr"/>
+      <c r="H36" s="46" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr"/>
+      <c r="J36" s="7" t="inlineStr"/>
+      <c r="K36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>共通評価軸</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>プロジェクト管理・採算</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="G37" s="46" t="inlineStr"/>
+      <c r="H37" s="46" t="inlineStr"/>
+      <c r="I37" s="10" t="inlineStr"/>
+      <c r="J37" s="9" t="inlineStr"/>
+      <c r="K37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>共通評価軸</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>指導・組織貢献</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>L1〜L2</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>L2〜L3</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="G38" s="46" t="inlineStr"/>
+      <c r="H38" s="46" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr"/>
+      <c r="J38" s="7" t="inlineStr"/>
+      <c r="K38" s="7" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>総合所見</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="47" t="inlineStr">
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="47" t="inlineStr">
         <is>
           <t>本人コメント（この期間で最も成長した点／課題と感じる点）</t>
         </is>
       </c>
-      <c r="B32" s="48" t="n"/>
-      <c r="C32" s="48" t="n"/>
-      <c r="D32" s="48" t="n"/>
-      <c r="E32" s="48" t="n"/>
-      <c r="F32" s="48" t="n"/>
-      <c r="G32" s="48" t="n"/>
-      <c r="H32" s="48" t="n"/>
-      <c r="I32" s="48" t="n"/>
-      <c r="J32" s="48" t="n"/>
-      <c r="K32" s="48" t="n"/>
-    </row>
-    <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="47" t="inlineStr">
+      <c r="B41" s="48" t="n"/>
+      <c r="C41" s="48" t="n"/>
+      <c r="D41" s="48" t="n"/>
+      <c r="E41" s="48" t="n"/>
+      <c r="F41" s="48" t="n"/>
+      <c r="G41" s="48" t="n"/>
+      <c r="H41" s="48" t="n"/>
+      <c r="I41" s="48" t="n"/>
+      <c r="J41" s="48" t="n"/>
+      <c r="K41" s="48" t="n"/>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="47" t="inlineStr">
         <is>
           <t>上長所見（到達度の総評）</t>
         </is>
       </c>
-      <c r="B33" s="48" t="n"/>
-      <c r="C33" s="48" t="n"/>
-      <c r="D33" s="48" t="n"/>
-      <c r="E33" s="48" t="n"/>
-      <c r="F33" s="48" t="n"/>
-      <c r="G33" s="48" t="n"/>
-      <c r="H33" s="48" t="n"/>
-      <c r="I33" s="48" t="n"/>
-      <c r="J33" s="48" t="n"/>
-      <c r="K33" s="48" t="n"/>
-    </row>
-    <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="47" t="inlineStr">
+      <c r="B42" s="48" t="n"/>
+      <c r="C42" s="48" t="n"/>
+      <c r="D42" s="48" t="n"/>
+      <c r="E42" s="48" t="n"/>
+      <c r="F42" s="48" t="n"/>
+      <c r="G42" s="48" t="n"/>
+      <c r="H42" s="48" t="n"/>
+      <c r="I42" s="48" t="n"/>
+      <c r="J42" s="48" t="n"/>
+      <c r="K42" s="48" t="n"/>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>次期の重点育成テーマ</t>
         </is>
       </c>
-      <c r="B34" s="48" t="n"/>
-      <c r="C34" s="48" t="n"/>
-      <c r="D34" s="48" t="n"/>
-      <c r="E34" s="48" t="n"/>
-      <c r="F34" s="48" t="n"/>
-      <c r="G34" s="48" t="n"/>
-      <c r="H34" s="48" t="n"/>
-      <c r="I34" s="48" t="n"/>
-      <c r="J34" s="48" t="n"/>
-      <c r="K34" s="48" t="n"/>
-    </row>
-    <row r="35" ht="40" customHeight="1">
-      <c r="A35" s="47" t="inlineStr">
+      <c r="B43" s="48" t="n"/>
+      <c r="C43" s="48" t="n"/>
+      <c r="D43" s="48" t="n"/>
+      <c r="E43" s="48" t="n"/>
+      <c r="F43" s="48" t="n"/>
+      <c r="G43" s="48" t="n"/>
+      <c r="H43" s="48" t="n"/>
+      <c r="I43" s="48" t="n"/>
+      <c r="J43" s="48" t="n"/>
+      <c r="K43" s="48" t="n"/>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>次回判定予定日</t>
         </is>
       </c>
-      <c r="B35" s="48" t="n"/>
-      <c r="C35" s="48" t="n"/>
-      <c r="D35" s="48" t="n"/>
-      <c r="E35" s="48" t="n"/>
-      <c r="F35" s="48" t="n"/>
-      <c r="G35" s="48" t="n"/>
-      <c r="H35" s="48" t="n"/>
-      <c r="I35" s="48" t="n"/>
-      <c r="J35" s="48" t="n"/>
-      <c r="K35" s="48" t="n"/>
+      <c r="B44" s="48" t="n"/>
+      <c r="C44" s="48" t="n"/>
+      <c r="D44" s="48" t="n"/>
+      <c r="E44" s="48" t="n"/>
+      <c r="F44" s="48" t="n"/>
+      <c r="G44" s="48" t="n"/>
+      <c r="H44" s="48" t="n"/>
+      <c r="I44" s="48" t="n"/>
+      <c r="J44" s="48" t="n"/>
+      <c r="K44" s="48" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K29"/>
+  <autoFilter ref="A5:K38"/>
   <mergeCells count="12">
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D33:K33"/>
-    <mergeCell ref="D34:K34"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="D44:K44"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:K43"/>
+    <mergeCell ref="D42:K42"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="D35:K35"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="D41:K41"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="D32:K32"/>
-    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A40:K40"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G6:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G6:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"L0,L1,L2,L3,L4,L5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5893,6 +6317,4221 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>営業提案レベル定義（どこまで踏み込むか）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>同じテーマでも、レベルによって「話してよい深さ」と「出してよい提案物」が変わる。背伸びした提案は失注より重い事故（財源の誤案内・官製談合の疑い）を招く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>提案の型</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>何を根拠に話すか</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="inlineStr">
+        <is>
+          <t>提案物（アウトプット）</t>
+        </is>
+      </c>
+      <c r="E4" s="38" t="inlineStr">
+        <is>
+          <t>会う相手</t>
+        </is>
+      </c>
+      <c r="F4" s="38" t="inlineStr">
+        <is>
+          <t>成果の目安</t>
+        </is>
+      </c>
+      <c r="G4" s="38" t="inlineStr">
+        <is>
+          <t>やってはいけないこと</t>
+        </is>
+      </c>
+      <c r="H4" s="38" t="inlineStr">
+        <is>
+          <t>目安
+時期</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>説明する（商品を知ってもらう）</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>自社の商品説明資料／その計画の根拠法・計画期間・所管省庁という一般知識</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>会社案内、商品一覧、実績一覧</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>担当者（先輩に同行）</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>顔と社名を覚えてもらう／次回訪問のアポイントが取れる</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>制度をうろ覚えのまま語る／単価・納期をその場で答える（必ず「持ち帰って確認します」）</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>1〜6ヶ月</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>伝える（国の動きを届ける）</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>国の指針・通知・審議会資料／作成マニュアル・手引き／公表済みの他自治体事例</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>国の動向まとめ1枚、策定年度を逆算したスケジュール表、事例集（出典付き）</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>担当者（単独可）、係長</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>「そろそろ考えないと」と言わせる／次年度の検討テーブルに載る</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>未確定の制度改正を断定する／事例を出典なしで語る／他団体から聞いた未公表情報を持ち込む</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>6〜12ヶ月</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>当てはめる（その団体の課題として示す）</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>L2＋その団体の現行計画・実績データ・決算・経営指標・議会議事録を読み込んだ課題仮説／該当しうる財源（補助金・起債）を最低1つ</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>課題整理メモ1枚、業務内容案、工程表、参考見積、（求められれば）仕様書案</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>係長・課長補佐</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>予算要求に載る（＝翌年度の発注が固まる）</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>財源の要件・補助率・期限を確認せずに「使えます」と断定する／仕様書案に自社しか対応できない条件を書く（官製談合を疑われる）</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>12〜24ヶ月</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>組み立てる（実行案にする）</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>L3＋関連施策・関連計画との連動／複数年の財源スキーム／庁内体制／議会・住民への説明の段取り</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>複数年ロードマップ、財源スキーム表（補助／起債／交付税措置／基金／使用料）、庁内体制案、企画提案書、プレゼン</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>課長・部長／所管の異なる複数課へ同時に</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>複数年・複数計画の一括受注／単価の維持・改善</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>実現できない体制・工程を約束する／他部署の予算獲得を前提に話を進める</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>24〜36ヶ月</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>創る（制度の先を読んでスキームにする）</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>審議会・検討会の議論段階からの先読み／国・都道府県の政策動向／広域・共同のスキーム設計</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>政策提言、広域・共同スキーム案、新商品、都道府県への提案、セミナー・研修</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>部長・副市長／都道府県／複数団体の合同</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>県単位・圏域単位の案件組成／新市場の立ち上げ</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>自社の受注ありきの提言と受け取られる／ある団体から得た情報を他団体の提案に流用する</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>48ヶ月〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>【原則】ひとつ上のレベルの提案物を出すときは、必ず上長のレビューを通すこと。特に財源（補助金・地方債・交付税措置）に関する数値と期限は、当年度の要綱・通知・地方債同意等基準で確認してからでなければ、口頭でも提示しない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C55A11"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>営業提案 深度マトリクス（提案素材 × レベル）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>提案の材料を9つに分解し、レベルごとに「どこまで使うか」を定めたもの。訪問前に自分のレベルの列を読み、超えている材料は上長に同行を依頼する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>提案素材</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>L1 説明する</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>L2 伝える</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="inlineStr">
+        <is>
+          <t>L3 当てはめる</t>
+        </is>
+      </c>
+      <c r="E4" s="38" t="inlineStr">
+        <is>
+          <t>L4 組み立てる</t>
+        </is>
+      </c>
+      <c r="F4" s="38" t="inlineStr">
+        <is>
+          <t>L5 創る</t>
+        </is>
+      </c>
+      <c r="G4" s="38" t="inlineStr">
+        <is>
+          <t>共通の注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="47" t="inlineStr">
+        <is>
+          <t>① 国の指針・基本方針</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>根拠法と所管省庁の名前を挙げ、「国の指針に基づく計画です」と言える。</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>現行指針の重点事項を3つに絞って説明し、次期指針の改正スケジュール（審議会→告示→国の説明会→県の説明会）を示せる。</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>指針の必須記載事項と相手の現行計画を突合し、「この項目が薄い／未記載」と具体的に指摘できる。</t>
+        </is>
+      </c>
+      <c r="E5" s="30" t="inlineStr">
+        <is>
+          <t>次期指針の方向性を先読みし、改正を前提とした業務設計（骨子は告示後に確定、それまでは調査・分析を先行）と工程を提案できる。</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>審議会・検討会の議論段階から論点を読み、指針改正が自治体運営に与える影響を政策提言として整理できる。</t>
+        </is>
+      </c>
+      <c r="G5" s="51" t="inlineStr">
+        <is>
+          <t>指針は期ごとに改正される。必ず最新版の告示・通知を確認し、「改正見込み」と「確定事項」を区別して話す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="49" t="inlineStr">
+        <is>
+          <t>② 作成マニュアル・手引き・ツール</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>該当するマニュアル・手引きの名称を挙げられる。</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>マニュアルが定める作業手順を説明し、自治体が自前でできる範囲／外注が必要な範囲を仕分けられる。</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>国のツール（見える化システム、保険料算定ワークシート、量の見込み算出手引き、更新費用試算ソフト等）の使用を前提に業務範囲を切り分け、工数と見積の根拠として示せる。</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="inlineStr">
+        <is>
+          <t>標準手順に自治体固有の事情（データ不備、体制不足、既存計画との整合）を織り込んだ実施方針を提案できる。</t>
+        </is>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>マニュアルが実務で使いにくい部分を補う独自手法・ツールを商品として提示できる。</t>
+        </is>
+      </c>
+      <c r="G6" s="51" t="inlineStr">
+        <is>
+          <t>「国のツールを使う」＝推計根拠が議会説明に耐えるということ。品質の裏付けとして使う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>③ 他自治体事例</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>自社の受注実績（団体名・業務名）を挙げられる。</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>近隣・同規模・同課題の団体の公表事例を、出典付きで3件示せる。</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>相手の課題に対応する事例を選び、「なぜその団体で機能したか（前提条件）」と自団体との差を説明できる。</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr">
+        <is>
+          <t>複数の事例を組み合わせて自団体向けのモデル案（体制・工程・成果物イメージ）に翻案し、視察・ヒアリングの段取りまで提案できる。</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>自社が支援した事例を先進事例として発信し（セミナー・記事・県の研修）、事例そのものを引き合いの入口にできる。</t>
+        </is>
+      </c>
+      <c r="G7" s="51" t="inlineStr">
+        <is>
+          <t>事例は公表資料のみを使う。ある団体で得た未公表情報を他団体に持ち込まない（信用を一度で失う）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="49" t="inlineStr">
+        <is>
+          <t>④ 補助金・交付金</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>「補助が使える場合があります」と伝え、担当者に確認を促せる。</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>該当しうる補助金・交付金の名称と所管を挙げ、例年の要望調査・内示の時期を伝えられる。</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>補助対象経費・補助率・要望ルート（国直か県経由か）を当年度の要綱で確認した上で、「この業務のこの部分が対象になり得る」と切り分けて提案できる。</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>要望時期から逆算した複数年の実施計画を組み、補助非対象部分を一般財源・起債と組み合わせた財源スキームとして提示できる。</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>補助メニューの新設・拡充を先読みし、要望の前年度から自治体と一緒に仕込む提案ができる。</t>
+        </is>
+      </c>
+      <c r="G8" s="51" t="inlineStr">
+        <is>
+          <t>可否の判断は所管課と県。「使えます」と断定せず「対象になり得るので要綱で確認を」と伝える。要綱は毎年度変わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="47" t="inlineStr">
+        <is>
+          <t>⑤ 起債・交付税措置・その他財源</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>地方債・交付税措置という財源の枠組みがあることを説明できる。</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>該当する地方債メニュー（公営企業債、公営企業会計適用債、公共施設等適正管理推進事業債等）の名称を挙げられる。</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>充当率・交付税措置率と、何より【計画への位置付けが起債の要件であること】を確認し、「計画に書かないと起債できない」という順序で業務の必要性を説明できる。</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="inlineStr">
+        <is>
+          <t>起債・補助・基金・繰入金・使用料改定を組み合わせた財源スキーム表を作り、財政課・企業局を巻き込んだ提案ができる。</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>措置の延長・拡充の動向を踏まえ、適用期限を跨ぐ複数年の投資・財政計画として設計できる。</t>
+        </is>
+      </c>
+      <c r="G9" s="51" t="inlineStr">
+        <is>
+          <t>【最重要】充当率・措置率・対象事業・適用期限は年度で変わる。必ず当年度の地方債計画・地方債同意等基準・総務省通知で確認してから数値を出す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="inlineStr">
+        <is>
+          <t>⑥ 関連施策・関連計画</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>隣接する計画の名前を挙げられる。</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>計画間の上下・並列関係（総合計画→分野別計画、地域福祉計画＝福祉分野の共通事項）を図で説明できる。</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>相手団体の計画期間一覧を作り、同時改定・一体策定が可能な組み合わせと、その効率化（調査の共通化、委員会の合同開催、資料編の共用）を示せる。</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>庁内の複数課に同時提案し、所管が分かれる計画をひとつの業務として束ねる体制・分担案を提示できる。</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>分野を跨ぐ政策課題（人口減少、担い手不足、公共施設）を軸に、計画体系そのものの再編を提案できる。</t>
+        </is>
+      </c>
+      <c r="G10" s="51" t="inlineStr">
+        <is>
+          <t>束ねる提案は自治体側の事務負担軽減が主目的。「安くなる」ではなく「整合が取れ、庁内調整が減る」で語る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="47" t="inlineStr">
+        <is>
+          <t>⑦ 現行計画の課題（進捗評価）</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>現行計画を入手し、計画期間・構成・数値目標の有無を確認できる。</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>数値目標の達成状況を実績データと突合し、未達項目を一覧化できる。</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>未達の原因を構造的に整理し（体制／財源／需要変化／指標設計の問題）、次期計画で手当てすべき論点として提示できる。</t>
+        </is>
+      </c>
+      <c r="E11" s="30" t="inlineStr">
+        <is>
+          <t>課題の解決を業務内容に落とし込み（指標の再設計、実態調査の追加、策定後の体制構築支援）、標準的な策定業務より高い価値の提案ができる。</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>「計画を作る業務」から「課題を解決する業務」へ提案を転換し、策定後の伴走支援・運用支援を商品化できる。</t>
+        </is>
+      </c>
+      <c r="G11" s="51" t="inlineStr">
+        <is>
+          <t>課題の指摘は担当者個人の否定にならないよう、制度・環境要因から入る。前任者批判に聞こえた時点で失注する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="inlineStr">
+        <is>
+          <t>⑧ 都道府県の動き</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>都道府県にも対応する計画（支援計画）があることを知っている。</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>県の支援計画・広域方針の内容と、県の説明会・研修の時期を伝えられる。</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>県の方針が市町村計画に課す制約（圏域設定、施設整備の調整、広域化の枠組み、目標値の考え方）を踏まえた提案ができる。</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>県と市町村の双方に提案し、県主導の枠組み（広域化推進プラン、圏域単位の協議）に自社の業務を接続できる。</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>県の政策形成に関与し（委員・研究会・研修講師）、県単位・圏域単位の案件を組成できる。</t>
+        </is>
+      </c>
+      <c r="G12" s="51" t="inlineStr">
+        <is>
+          <t>県の説明会の直後は市町村の関心が最も高い。県のスケジュールを押さえて訪問時期を合わせる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t>⑨ 見積・契約条件</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>見積は持ち帰り、上長が作成する。</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>過去実績をもとに概算のレンジを伝えられる（確定額は必ず持ち帰る）。</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>業務範囲を明示した参考見積を作り、積算根拠（工数・調査規模・印刷部数・委員会回数）を説明できる。分離発注（調査年度／策定年度）と一括発注の得失を示せる。</t>
+        </is>
+      </c>
+      <c r="E13" s="30" t="inlineStr">
+        <is>
+          <t>複数年契約・複数計画一括の見積を設計し、値引きではなく業務範囲の設計で単価を守れる。</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>テーマ・エリアの価格戦略を設計し、採算ラインと受注確度のバランスを判断できる。</t>
+        </is>
+      </c>
+      <c r="G13" s="51" t="inlineStr">
+        <is>
+          <t>参考見積は複数社から取られる前提。範囲を曖昧にしたまま安い額を出すと、受注後に追加作業を飲まされる。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00843C0C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F111"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>テーマ別 提案ネタ台帳（指針・マニュアル・事例・財源・関連施策・現行課題）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>テーマ列でフィルタして使う。財源（補助金・地方債・交付税措置）は対象経費・率・期限が年度で変わるため、顧客に提示する前に必ず「確認先」欄の当年度資料で裏を取ること。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>素材区分</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>具体名（正式名称）</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="inlineStr">
+        <is>
+          <t>提案での使い方（何を言うか）</t>
+        </is>
+      </c>
+      <c r="E4" s="38" t="inlineStr">
+        <is>
+          <t>使える
+レベル</t>
+        </is>
+      </c>
+      <c r="F4" s="38" t="inlineStr">
+        <is>
+          <t>確認先・更新タイミング</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>指針</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>総務省「統一的な基準による地方公会計マニュアル」（H27策定・H31.3改訂）</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>「作成が要請されている」ことを出発点に、作成の遅れ・活用の遅れを論点化する。台帳整備の手引きは精緻化業務の根拠になる。</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>総務省HP／改訂時に差分を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B6" s="52" t="inlineStr">
+        <is>
+          <t>調査</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>総務省「地方公会計の整備状況等に関する調査」（毎年度公表）</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>自団体の作成・公表・活用の状況が全国・県内でどの位置かを示す。「県内で活用まで進んでいるのは○団体」は担当者に効く。</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>総務省HP／毎年度公表</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>マニュアル</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>「資産評価及び固定資産台帳整備の手引き」（マニュアル所収）</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>取得価額不明資産・再調達価額・備忘価額1円の扱いを根拠に、精緻化業務の必要性を具体的に説明する。</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>マニュアル本編</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B8" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>計画策定・台帳整備は原則として一般財源（総務費）</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>補助がない前提で、「単年度で完璧を目指さず、優先順位を付けて複数年で段階整備する」現実的な提案が刺さる。</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F8" s="54" t="inlineStr">
+        <is>
+          <t>自団体の予算書・決算書</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B9" s="53" t="inlineStr">
+        <is>
+          <t>財源（連動）</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>公共施設等適正管理推進事業債（総務省）</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>固定資産台帳は更新費用試算の基礎データ。台帳が粗いと総合管理計画の試算が甘くなり、起債の裏付けが弱くなる、と連動させて台帳精緻化の必要性を語る。</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F9" s="55" t="inlineStr">
+        <is>
+          <t>当年度の地方債計画・地方債同意等基準／数値は必ず確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>関連施策</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>公共施設等総合管理計画・個別施設計画</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>台帳データの提供・連携を入口に、施設マネジメント業務へ展開する（社内の他テーマへのクロスセル）。</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>自団体の管理計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>関連施策</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計の適用（下水道・簡易水道）</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>資産調査の成果を公会計と公営企業会計の双方で使い回す提案。二重投資の回避は財政課に響く。</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>総務省「公営企業会計の適用に関するマニュアル」</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>関連施策</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>使用料・手数料の見直し／受益者負担の適正化</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>施設別行政コスト計算書を受益者負担見直しの根拠として提示し、活用支援業務につなげる。</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>他団体の受益者負担適正化基準</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>固定資産台帳が毎年度更新されていない（決算後の異動反映が滞る）</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>更新作業の受託だけでなく、所管課からの異動報告様式・年間フローを整備する提案にする。</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>担当者ヒアリング</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>取得価額不明資産・備忘価額1円が大量に残っている</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>資産額が過少計上となり、更新費用試算・有形固定資産減価償却率が実態とずれる。他計画への波及で語る。</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>台帳の実物・公表資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>財務書類の公表が決算から1年以上遅れている／作成しっぱなしで活用されていない</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>早期化の工程改善と、指標分析・住民向け公表資料を業務に含める。</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>自団体HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B16" s="56" t="inlineStr">
+        <is>
+          <t>県の動き</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>県市町村課の説明会・県内統一様式・職員研修</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>県の指導内容に沿った提案。県の研修講師を務めると県内全域への波及効果が大きい。</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>県HP／年度当初</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>指針</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>総務省「公営企業の経営に当たっての留意事項について」（毎年度・公営企業課長通知）</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>その年に国が何を求めているか（経営戦略の改定、広域化、officials化、料金水準の適正化）が凝縮されている。年度初の必読資料で、提案の柱に据える。</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>総務省HP／毎年度発出</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>マニュアル</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>総務省「公営企業会計の適用に関するマニュアル」</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>法適化の作業項目と工程を示し、庁内で発生する作業量を可視化する。「職員だけでは回らない」を数字で見せる。</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>総務省HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>指針</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>総務省「経営戦略策定・改定ガイドライン」</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>「策定して終わりではなく、3〜5年ごとに改定」を根拠に、改定業務を継続受注の柱にする。</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>総務省HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B20" s="52" t="inlineStr">
+        <is>
+          <t>ツール</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>総務省「経営比較分析表」（全団体分が公表）</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>訪問前に必ず作る。経常収支比率・料金回収率・経費回収率・有収率・有形固定資産減価償却率・企業債残高対給水収益比率を類似団体と比較し、課題を一枚で示す。最も費用対効果の高い準備。</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>総務省HP／毎年度更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>マニュアル</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>日本水道協会「水道料金算定要領」／「下水道使用料算定の基本的考え方」</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>総括原価・資産維持費・汚水私費雨水公費の原則を根拠に、改定の必要性を数値で示す。</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>各協会／改訂時に確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>マニュアル</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>水道事業のアセットマネジメント手引き／下水道ストックマネジメント実施に関する手引き</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>更新需要試算と経営戦略の投資試算の整合を論点化する。「別々に作られていて数字が合わない」は頻出。</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>国交省HP（水道は令和6年4月に厚労省から移管）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B23" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計適用債（資産調査・システム導入等の経費に充当。元利償還金に特別交付税措置）</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>法適化の初期費用に財源があることを示し、「予算がないから先送り」を崩す。対象経費・充当率・措置率は当年度の同意等基準で確認する。</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F23" s="55" t="inlineStr">
+        <is>
+          <t>当年度の地方債計画・地方債同意等基準／数値は必ず確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B24" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>経営戦略の策定・改定に要する経費への特別交付税措置</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>「策定費に措置がある」は予算要求の後押しになる。対象範囲・措置率は当年度通知で確認する。</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F24" s="54" t="inlineStr">
+        <is>
+          <t>総務省 公営企業課通知（毎年度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B25" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>広域化等の検討・計画策定に要する経費への財政措置</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>県の広域化推進プラン／下水道広域化・共同化計画に位置付けられた検討を財源付きで提案できる。</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F25" s="55" t="inlineStr">
+        <is>
+          <t>総務省・国交省通知（毎年度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B26" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>企業債（建設改良）／資本費平準化債（下水道）／借換債</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>投資・財政計画の財源試算に組み込む。発行可能額と償還負担のシミュレーションが提案の中身になる。</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F26" s="54" t="inlineStr">
+        <is>
+          <t>地方債同意等基準／当年度版</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B27" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>生活基盤施設耐震化等交付金（水道）／社会資本整備総合交付金・防災安全交付金（下水道）</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>投資計画の財源として位置付ける。交付金の採択要件と計画への記載を結び付ける。</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F27" s="55" t="inlineStr">
+        <is>
+          <t>国交省HP／毎年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B28" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>一般会計繰出金（総務省の繰出基準）</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>基準外繰入が常態化していないかを論点にする。財政課を巻き込む入口になる。</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F28" s="54" t="inlineStr">
+        <is>
+          <t>総務省 繰出基準通知（毎年度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="inlineStr">
+        <is>
+          <t>関連施策</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>ウォーターPPP／PPP-PFI推進アクションプラン</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>官民連携の導入可能性調査へ展開する。国が導入目標を掲げている点が後押しになる。</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>内閣府PPP/PFI推進室</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>経営戦略の投資試算が法定耐用年数の機械的計算のまま（実使用年数を反映していない）</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>更新需要が過大に出て計画が非現実的になっている。精緻化＝改定業務の必要性として提案する。</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>現行の経営戦略</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>収支ギャップの解消策が「料金改定を検討」で止まり実行されていない</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>計画に書いてあるが着手できていない、が最も多いパターン。改定業務そのものを提案する。</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>現行の経営戦略・議会議事録</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B32" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>料金回収率・経費回収率が100%を下回る／有収率が低い</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>独立採算が成立していないことを数値で示す。改定・漏水対策・管路更新の各業務につながる。</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>経営比較分析表</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>技術職員・事務職員が不足し、庁内で作業できない</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>単発の委託ではなく、年間を通じた包括的な会計支援（月次・決算・統計・予算）を提案する。</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>担当者ヒアリング</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B34" s="56" t="inlineStr">
+        <is>
+          <t>県の動き</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>都道府県の水道広域化推進プラン／下水道広域化・共同化計画</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>県の枠組みに市町村の検討を接続する。県主導の案件は複数団体の同時受注につながる。</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>県HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>指針</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>厚労省「介護保険事業に係る保険給付の円滑な実施を確保するための基本的な指針」（期ごとに告示）</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>現行指針の重点事項を整理し、次期指針の改正論点（社会保障審議会介護保険部会）を先読みして提示する。</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>L2〜（先読みはL4〜）</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>厚労省HP・審議会資料／期ごと改正</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B36" s="33" t="inlineStr">
+        <is>
+          <t>マニュアル</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>「介護予防・日常生活圏域ニーズ調査」「在宅介護実態調査」実施の手引き</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>国の標準調査を使う＝全国・県内との比較可能性がある、という品質論点で語る。</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>厚労省HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="inlineStr">
+        <is>
+          <t>ツール</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>地域包括ケア「見える化」システム／第1号保険料算定ワークシート</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>推計の根拠を国のツールに置くことで議会説明に耐える、という説明をする。操作研修の受講実績も提案材料になる。</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>厚労省／期ごとに更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B38" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金／介護保険保険者努力支援交付金（インセンティブ交付金）</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>評価指標に「計画の策定・進捗管理」「見える化システムの活用」「地域ケア会議」等が含まれる。計画の作り込みが交付金額に直結する、という他にない切り口。</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F38" s="54" t="inlineStr">
+        <is>
+          <t>厚労省 評価指標（毎年度公表）／指標の変更を必ず確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B39" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>地域医療介護総合確保基金（介護分）</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>施設整備・介護人材確保の財源。県経由で、計画への位置付けが前提になる。整備計画の提案と結び付ける。</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F39" s="55" t="inlineStr">
+        <is>
+          <t>県の基金事業計画／毎年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B40" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>地域支援事業交付金（総合事業・包括的支援事業・任意事業）</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>調査や体制整備の一部が対象になる場合がある。対象可否は保険者・県に確認する前提で示す。</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F40" s="54" t="inlineStr">
+        <is>
+          <t>厚労省 実施要綱／毎年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>関連施策</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>認知症基本法／認知症施策推進基本計画 → 市町村認知症施策推進計画（努力義務）</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>介護保険事業計画に包含するか別冊にするかの選択肢を示す。新たな計画需要として営業機会になる。</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>内閣府・厚労省</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B42" s="34" t="inlineStr">
+        <is>
+          <t>関連施策</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>高齢者の保健事業と介護予防の一体的実施／データヘルス計画・特定健診等実施計画</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>KDBデータの活用を共通化し、国保部門と介護部門の同時提案につなげる。</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>厚労省</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B43" s="34" t="inlineStr">
+        <is>
+          <t>関連施策</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉計画（上位）、成年後見制度利用促進計画、地域公共交通計画、住生活基本計画</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>同時改定・一体策定の組み合わせを提示する。</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>自団体の計画一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B44" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>サービス見込量と実績の乖離（特に総合事業・地域密着型）</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>推計手法の見直しを業務の付加価値として提案する。乖離率を一覧にして持参すると説得力が出る。</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>現行計画＋介護保険事業状況報告</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B45" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>整備計画（特養・地域密着型）が公募しても応募がなく未整備のまま</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>事業者アンケート・意向調査を業務に追加する提案にする。</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>現行計画・公募結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B46" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>保険料上昇への住民説明が弱い／評価指標が「実施の有無」だけでPDCAが回らない</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>わかりやすい説明資料、指標の再設計を付帯提案する。</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>L3〜L4</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>現行計画・議会議事録</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B47" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>第2層協議体・生活支援コーディネーターが形骸化している</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>計画策定に留まらない体制支援・研修へ展開する。</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>担当者ヒアリング</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B48" s="56" t="inlineStr">
+        <is>
+          <t>県の動き</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>都道府県介護保険事業支援計画（圏域設定・施設整備の調整）／県の説明会・ワークシート研修</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>県の説明会直後は市町村の関心が最も高い。訪問時期を県の日程に合わせる。</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>県HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B49" s="57" t="inlineStr">
+        <is>
+          <t>発注情報</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>広域連合・一部事務組合が保険者の場合</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>介護保険事業計画は広域、高齢者福祉計画は構成市町村、と発注が分かれることがある。両方に提案する。</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>自団体・広域連合HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B50" s="33" t="inlineStr">
+        <is>
+          <t>指針</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>厚労省「障害福祉サービス等及び障害児通所支援等の円滑な実施を確保するための基本的な指針」（期ごと告示）</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>成果目標7項目の考え方が次期にどう変わるかを提示する。目標設定は計画の中核であり、ここを語れると強い。</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>厚労省HP・障害者部会／期ごと改正</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B51" s="33" t="inlineStr">
+        <is>
+          <t>指針</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>国「障害者基本計画（第5次）」</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>障害者計画（理念計画）の分野別体系の根拠として使う。</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>内閣府HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B52" s="33" t="inlineStr">
+        <is>
+          <t>マニュアル</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>地域生活支援拠点等の整備に関する手引き・事例集</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>成果目標の具体化支援（拠点の機能検証・体制設計）へ展開する。</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>厚労省HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B53" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>地域生活支援事業費等補助金（国1/2以内・県1/4以内）</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>相談支援、意思疎通支援、日常生活用具、地域生活支援拠点等の財源。計画への位置付けが前提であることを説明する。</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F53" s="55" t="inlineStr">
+        <is>
+          <t>厚労省 実施要綱／毎年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B54" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>地域生活支援促進事業（発達障害者支援体制整備、医療的ケア児等総合支援、精神障害にも対応した地域包括ケア構築支援、強度行動障害支援者養成 等の個別メニュー）</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>「このメニューを使うには計画への位置付けが要る」という順序で、計画の記載充実の必要性を説明する。</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F54" s="54" t="inlineStr">
+        <is>
+          <t>厚労省 実施要綱／毎年度メニュー改廃あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B55" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>障害福祉サービス等給付費負担金（義務的経費・国1/2）</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>見込量＝給付費＝予算。推計の精度が翌年度の財政に直結する、という品質論点で単価を守る。</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F55" s="55" t="inlineStr">
+        <is>
+          <t>厚労省</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B56" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>社会福祉施設等施設整備費国庫補助金（グループホーム・日中活動系）</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>整備見込との連動。事業所調査の結果を整備計画に反映する提案にする。</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F56" s="54" t="inlineStr">
+        <is>
+          <t>厚労省／県経由</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B57" s="34" t="inlineStr">
+        <is>
+          <t>関連施策</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>障害者差別解消法（令和6年4月から民間事業者の合理的配慮の提供が法的義務）／情報アクセシビリティ・コミュニケーション施策推進法</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>計画への反映に加え、職員研修・事業者向け説明会を付帯提案する。</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>内閣府「基本方針」</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B58" s="34" t="inlineStr">
+        <is>
+          <t>関連施策</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>こども計画（障害児のインクルージョン）、地域福祉計画、バリアフリー基本構想、避難行動要支援者・個別避難計画、特別支援教育推進計画</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>所管が福祉課・こども課・都市計画課・防災課・教育委員会に分かれる。庁内横断の同時提案が効く。</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>自団体の計画一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B59" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>成果目標が国の数値の引き写しで、自団体の実績と乖離している</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>実績に基づく目標設定への転換を提案する。前期の未達要因分析を業務に含める。</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>現行計画＋実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B60" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>地域生活支援拠点が登録型・面的整備の形だけで機能していない／基幹相談支援センターが未設置</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>機能検証と体制設計支援へ。計画策定の枠を超えた業務として単価を上げられる。</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>現行計画・協議会資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B61" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>事業所の偏在（放課後等デイは充足、生活介護・グループホームが不足）</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>事業所調査を業務に追加し、見込量の確保方策の実効性を高める。</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>国保連データ・事業所一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B62" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>医療的ケア児・強度行動障害の実態が把握できていない</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>実態調査を単独業務として切り出して提案できる（計画策定年度以外の受注機会）。</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>担当者ヒアリング</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B63" s="56" t="inlineStr">
+        <is>
+          <t>県の動き</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>都道府県障害福祉計画（圏域調整）／圏域自立支援協議会／県の説明会</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>圏域単位での提案は複数市町村の同時受注につながる。</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>県HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B64" s="33" t="inlineStr">
+        <is>
+          <t>指針</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>厚労省「市町村地域福祉計画策定ガイドライン」（地域共生社会の実現に向けた地域福祉の推進について）</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>「福祉分野の共通事項を定める上位計画」という位置づけを根拠に、他計画との一体策定を提案する。</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>厚労省HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B65" s="33" t="inlineStr">
+        <is>
+          <t>マニュアル</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>厚労省「重層的支援体制整備事業」実施ガイドライン・事例集</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>5事業（包括的相談支援・参加支援・地域づくり・アウトリーチ・多機関協働）の体制設計支援へ展開する。</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>厚労省HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B66" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>重層的支援体制整備事業交付金／同 移行準備事業</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>移行すると介護・障害・こども・困窮の相談支援等の補助が一体的に交付される。移行前に使える移行準備事業とセットで提案するのが定石。</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F66" s="54" t="inlineStr">
+        <is>
+          <t>厚労省 実施要綱／毎年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B67" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>地域自殺対策強化交付金</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>自殺対策計画の策定・改定に充当できる。地域福祉計画に併載する場合、併載編の財源として予算化を後押しできる。</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F67" s="55" t="inlineStr">
+        <is>
+          <t>厚労省・JSCP／県経由・毎年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B68" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>生活困窮者自立相談支援事業費等負担金・補助金／成年後見制度利用促進の体制整備（中核機関）</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>併載する分野の記載と財源を結び付ける。</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F68" s="54" t="inlineStr">
+        <is>
+          <t>厚労省／毎年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B69" s="52" t="inlineStr">
+        <is>
+          <t>ツール</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>いのち支える自殺対策推進センター（JSCP）「地域自殺実態プロファイル」</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>自殺対策計画の重点施策を客観データで決められる。無料で入手でき、提案の具体性が一気に上がる。</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>JSCP／定期更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B70" s="58" t="inlineStr">
+        <is>
+          <t>事例</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>社会福祉協議会の地域福祉活動計画との一体策定（自治体＋社協の共同・連名発注）</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>発注元が2つになり予算を合算できる。社協への同時アプローチが受注確度を上げる。</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>他団体の一体策定事例</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B71" s="34" t="inlineStr">
+        <is>
+          <t>関連施策</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>成年後見制度利用促進基本計画、再犯防止推進計画、自殺対策計画、孤独・孤立対策、避難行動要支援者・個別避難計画、居住支援（住宅セーフティネット）</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>併載編として束ねる。1本あたりの単価は小さいが、まとめると中規模案件になる。</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>各根拠法・各省ガイドライン</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B72" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>理念のみで実行計画がない／担当課が動けていない</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>実行工程・役割分担・年次計画まで書き込む提案にして差別化する。</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>現行計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B73" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>社協の地域福祉活動計画と内容が重複・分断している</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>一体策定または対応表の作成を提案する。</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>両計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B74" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>圏域が計画ごとにバラバラ（日常生活圏域／小学校区／地区社協）</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>圏域の整理そのものを業務に含める。他計画にも波及するため単価を上げやすい。</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>各分野別計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B75" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>重層事業に移行したいが庁内合意が取れない</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>庁内勉強会・業務フロー整理の伴走支援を提案する（計画策定の前段の業務）。</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>担当者ヒアリング</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B76" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>住民座談会が固定メンバーのみ／意見が計画に反映されていない</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>参加設計の見直しとファシリテーションを業務に含める。</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>現行計画・過去の座談会記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B77" s="56" t="inlineStr">
+        <is>
+          <t>県の動き</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>都道府県地域福祉支援計画／県社協の支援／県の重層事業説明会</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>県の方針と説明会の時期を押さえる。</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>県HP・県社協</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B78" s="33" t="inlineStr">
+        <is>
+          <t>指針</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>こども家庭庁「こども大綱」／「市町村こども計画の策定等に関する助言について」</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>こども計画が努力義務であること、統合対象計画（次世代育成支援行動計画、子ども・若者計画、こどもの貧困対策計画、母子保健計画）の整理を提案の柱にする。</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>こども家庭庁HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B79" s="33" t="inlineStr">
+        <is>
+          <t>マニュアル</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>こども家庭庁「市町村子ども・子育て支援事業計画における『量の見込み』の算出等のための手引き」</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>家庭類型・潜在ニーズの算定根拠。中間年見直しの必要性を手引きの記載から説明する。</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>こども家庭庁HP／改訂を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B80" s="33" t="inlineStr">
+        <is>
+          <t>ガイドライン</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>「こども・若者の意見の反映に関するガイドライン」／「こどもの居場所づくりに関する指針」</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>意見聴取の設計・運営、居場所の実態調査を独立した業務として切り出す。計画策定年度以外の受注機会になる。</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>こども家庭庁HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B81" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>子ども・子育て支援交付金（地域子ども・子育て支援事業）</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>量の見込み＝交付金の積算根拠。推計の精度が翌年度の財源に直結する、という品質論点で語る。</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F81" s="55" t="inlineStr">
+        <is>
+          <t>こども家庭庁 実施要綱／毎年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B82" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>地域子供の未来応援交付金</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>こどもの貧困の実態調査・計画策定・支援体制整備に充当できる。調査業務の予算化に直結する最も強いネタのひとつ。要望時期を必ず確認する。</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F82" s="54" t="inlineStr">
+        <is>
+          <t>こども家庭庁／毎年度の要綱・要望調査時期</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B83" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>児童虐待防止対策等総合支援事業費補助金</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>こども家庭センター、子育て世帯訪問支援事業、児童育成支援拠点事業、親子関係形成支援事業の財源。体制構築支援と結び付ける。</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F83" s="55" t="inlineStr">
+        <is>
+          <t>こども家庭庁／毎年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B84" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>ヤングケアラー支援体制強化事業／母子保健関係の国庫補助（産後ケア等）</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>実態調査・研修の財源として提示する。</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F84" s="54" t="inlineStr">
+        <is>
+          <t>こども家庭庁／毎年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B85" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>保育所等整備交付金／子ども・子育て支援施設整備交付金</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>確保方策の裏付けとして、整備計画と財源を結び付ける。</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F85" s="55" t="inlineStr">
+        <is>
+          <t>こども家庭庁</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B86" s="59" t="inlineStr">
+        <is>
+          <t>制度</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>乳児等通園支援事業（こども誰でも通園制度）の給付制度化</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>地域子ども・子育て支援事業に新たに位置付けられるため、量の見込みへの反映が必要になる。中間年見直しを提案する明確な理由になる。</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>こども家庭庁／施行スケジュールを必ず確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B87" s="34" t="inlineStr">
+        <is>
+          <t>関連施策</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>教育振興基本計画（教育委員会）、障害児福祉計画、地域福祉計画、母子保健、子ども・若者計画、公共施設等総合管理計画（幼保再編）</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>所管がこども未来課・保育課・母子保健・教育委員会に分かれる。庁内横断の調整力そのものが提案価値になる。</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>自団体の計画一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B88" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>量の見込みと実績が乖離している（少子化の加速、利用率の変化）</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>中間年見直しの必要性を乖離率で示す。区域別・年齢別の乖離表を作って持参する。</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>現行計画＋実績値</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B89" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>待機児童は解消したが定員割れが始まっている</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>「増やす計画」から「適正化・再編の計画」への転換を提案する。公共施設マネジメントとのクロスセルになる。</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>保育所等関連状況取りまとめ・自団体データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B90" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>こども計画が既存計画の合冊にとどまっている／こどもの意見反映が形式的</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>体系の再設計、こども会議の設計・運営受託を提案する。</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>L3〜L4</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>現行計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B91" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>こども家庭センターが兼務体制で機能していない</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>体制設計支援・業務フロー整理へ展開する。</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>担当者ヒアリング</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B92" s="56" t="inlineStr">
+        <is>
+          <t>県の動き</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>都道府県子ども・子育て支援事業支援計画／社会的養育推進計画</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>県の枠組みと市町村計画の整合を押さえる。</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>県HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B93" s="33" t="inlineStr">
+        <is>
+          <t>指針</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>総務省「公共施設等総合管理計画の策定にあたっての指針」（H26／H30改訂／R3見直し要請）</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>見直し要請事項（個別施設計画の反映、保有量に関する数値目標、脱炭素化、ユニバーサルデザイン化）の充足状況を点検して示す。</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>総務省HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B94" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>公共施設等適正管理推進事業債（集約化・複合化、長寿命化、転用、立地適正化、脱炭素化、UD化、除却）</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>【最強のロジック】総合管理計画および個別施設計画に位置付けられていることが起債の要件。「計画に書いていないと起債できない」という順序で計画策定・改定の必要性を説明する。充当率・交付税措置率・対象事業・適用期限は年度で変わるため、必ず当年度の地方債計画で確認してから提示する。</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F94" s="54" t="inlineStr">
+        <is>
+          <t>当年度の地方債計画・地方債同意等基準／数値と期限は必ず確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B95" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>学校施設環境改善交付金（文科省）／社会資本整備総合交付金・公営住宅等ストック総合改善（国交省）／道路メンテナンス事業補助・防災安全交付金（国交省）</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>いずれも個別施設計画（学校施設長寿命化計画、公営住宅等長寿命化計画、橋梁長寿命化修繕計画）が採択の前提。教育委員会・建築課・土木課への横展開の入口になる。</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F95" s="55" t="inlineStr">
+        <is>
+          <t>各省HP／毎年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B96" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>更新費用試算が総務省ソフトの単価法のままで、固定資産台帳と連動していない</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>台帳連動の再試算を提案する。公会計テーマとのクロスセルが成立する典型例。</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>現行の総合管理計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B97" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>削減目標だけがあり、個別の再編工程・年次計画がない</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>個別施設計画・再編計画の策定へつなげる。</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>現行の総合管理計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B98" s="33" t="inlineStr">
+        <is>
+          <t>指針</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>健康日本21（第三次）／食育推進基本計画／歯科口腔保健の推進に関する基本的事項</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>計画期間が長期化した分、中間評価業務が発生する。改定年度以外の受注機会として押さえる。</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>厚労省・農水省HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B99" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>地域自殺対策強化交付金／健康増進事業費補助／保険者努力支援制度（国保・データヘルス）</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>健康増進計画に併載する自殺対策計画・データヘルス計画の財源として示す。</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F99" s="55" t="inlineStr">
+        <is>
+          <t>厚労省／毎年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B100" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>健康増進・食育・自殺対策・歯科口腔保健・データヘルスが別々に策定され、指標も体系も整合していない</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>一体策定による整合確保と庁内事務負担の軽減を提案する。複数計画の束ね受注になる。</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>自団体の計画一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B101" s="33" t="inlineStr">
+        <is>
+          <t>指針</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>農業振興地域の整備に関する法律（農振整備計画）／農業経営基盤強化促進法「地域計画」（目標地図）</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>地域計画は策定して終わりではなく、随時の変更・更新が継続的に発生する。継続業務として提案する。</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>農水省HP・農業委員会</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B102" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>農山漁村振興交付金／多面的機能支払交付金／中山間地域等直接支払交付金／強い農業づくり総合支援交付金</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>施策の裏付けとして計画に位置付ける。</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F102" s="54" t="inlineStr">
+        <is>
+          <t>農水省／毎年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B103" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>地域計画の目標地図が実態と合っていない／話合いが一度きりで終わっている</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>更新業務と話合いの運営を継続受託する提案にする。</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>自団体・農業委員会</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B104" s="33" t="inlineStr">
+        <is>
+          <t>指針</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>男女共同参画基本計画／女性活躍推進法／配偶者暴力防止法／困難な問題を抱える女性への支援に関する法律</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>3〜4計画の一体策定が主流。法改正に伴う必須記載事項の追加を提案の理由にする。</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>内閣府HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B105" s="53" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>地域女性活躍推進交付金（内閣府）</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>計画策定・実態調査に充当できる場合がある。要望時期を確認した上で提示する。</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F105" s="55" t="inlineStr">
+        <is>
+          <t>内閣府／毎年度の要綱・要望時期</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B106" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>指標が審議会の女性委員比率のみ／DV・困難女性支援の記載が薄い</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>法改正への対応を業務内容に含めて提案する。</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>L3〜</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>現行計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B107" s="34" t="inlineStr">
+        <is>
+          <t>関連施策</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>中期財政計画・財政推計</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>公会計・公共施設・公営企業の試算を統合する上流の業務。単価が高く、他業務の入口にもなる。</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>決算カード・財政状況資料集</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B108" s="35" t="inlineStr">
+        <is>
+          <t>現行課題</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>施設更新費・公営企業繰出金が財政推計に反映されていない</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>統合推計を提案する。財政課との関係構築は全テーマへの波及効果が大きい。</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>L4〜</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>現行の財政推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B109" s="57" t="inlineStr">
+        <is>
+          <t>発注情報</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>自治体HPの計画一覧／総合計画の実施計画／当初予算の主要事業／議会議事録（一般質問での計画への言及）</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>計画期間の終了年度の前年度＝発注年度。担当エリア全団体の全計画を3年先までDB化して優先順位を付ける。</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>L2〜</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>各自治体HP／年1回更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B110" s="53" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>官製談合防止法／公正な調達の確保</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>仕様書案の提供は一般的な業務範囲にとどめ、自社しか対応できない条件は書かない。参考見積は複数社から取られる前提で作る。逸脱は会社と自治体の双方を傷つける。</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>全レベル</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>官製談合防止法・各自治体の契約規則</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B111" s="53" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>守秘義務と情報の扱い</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>ある団体から得た未公表情報を他団体への提案に使わない。公表資料・出典のあるものだけで提案を組む。</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>全レベル</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>契約書の守秘条項・個人情報取扱特記事項</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F111"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6286,6 +10925,518 @@
     <mergeCell ref="C14:G14"/>
     <mergeCell ref="C17:G17"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>訪問前 準備チェックリスト（レベル別）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>自分のレベルまでの項目をすべて満たしてから訪問する。準備が足りないまま訪問した回数だけ、そのお客様での次の機会が遠のく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>準備項目</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>具体的にやること</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="inlineStr">
+        <is>
+          <t>完了の基準</t>
+        </is>
+      </c>
+      <c r="E4" s="38" t="inlineStr">
+        <is>
+          <t>実施
+✓</t>
+        </is>
+      </c>
+      <c r="F4" s="38" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>訪問先の基本情報</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>所管課名・担当者名・役職・過去の取引履歴を社内CRMと名刺で確認する。</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>誰に会うのか、当社と過去にどんな取引があったかを言える。</t>
+        </is>
+      </c>
+      <c r="E5" s="46" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>商品の言語化</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>その計画の根拠法・計画期間・所管省庁を暗記し、商品説明を3分で話せるようにする。</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>資料を見ずに商品説明ができる。</t>
+        </is>
+      </c>
+      <c r="E6" s="46" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>持ち物</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>会社案内、商品一覧、実績一覧、名刺を揃える。</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>同行の先輩から持ち物の確認を受けている。</t>
+        </is>
+      </c>
+      <c r="E7" s="46" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>現行計画の入手と通読</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>自治体HPから現行計画をダウンロードし、目次・計画期間・数値目標の有無・策定体制（委員会名）を確認する。</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>計画の構成と、次の改定がいつかを言える。</t>
+        </is>
+      </c>
+      <c r="E8" s="46" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>国の動向の整理</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>最新の指針・通知・審議会資料を確認し、重点事項を3つに絞った1枚資料を作る。</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>1枚資料が上長のレビューを通っている。</t>
+        </is>
+      </c>
+      <c r="E9" s="46" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>事例の準備</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>近隣・同規模・同課題の団体の公表事例を、出典付きで3件用意する。</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>各事例の出典URLを示せる。</t>
+        </is>
+      </c>
+      <c r="E10" s="46" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>スケジュールの逆算</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>計画期間の終了年度から、調査年度・策定年度・予算要求時期・公告時期を逆算した表を作る。</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>「いつ予算要求すべきか」を相手に示せる。</t>
+        </is>
+      </c>
+      <c r="E11" s="46" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>実績との突合</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>現行計画の数値目標と実績データを突合し、未達項目・乖離率を一覧化する。</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>乖離の一覧表を持参できる。</t>
+        </is>
+      </c>
+      <c r="E12" s="46" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>データの下ごしらえ</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>テーマ別の必須データを作る（公営企業＝経営比較分析表の比較、介護＝見込量と給付実績、こども＝量の見込みと実績、公会計＝財務指標の類似団体比較、公共施設＝更新費用試算の前提）。</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>図表1〜2枚で相手の状況を説明できる。</t>
+        </is>
+      </c>
+      <c r="E13" s="46" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>財源の確認</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>該当しうる補助金・交付金・地方債について、当年度の要綱・通知・地方債同意等基準で対象経費・率・期限・要望時期を確認する。</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>「対象になり得る／要確認」の線引きを正確に説明できる。</t>
+        </is>
+      </c>
+      <c r="E14" s="46" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>議会の確認</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>議会議事録を計画名・施策名で検索し、議員からどんな指摘が出ているかを把握する。</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>議会での指摘事項を1つ以上挙げられる。</t>
+        </is>
+      </c>
+      <c r="E15" s="46" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>提案物の準備</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>課題整理メモ1枚、業務内容案、工程表、参考見積を用意する。</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>上長のレビューを通っている。</t>
+        </is>
+      </c>
+      <c r="E16" s="46" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>庁内マップの作成</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>関連する計画とその所管課・計画期間の一覧を作り、同時提案できる組み合わせを特定する。</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>誰と誰に会うべきかを設計できている。</t>
+        </is>
+      </c>
+      <c r="E17" s="46" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>財源スキームの設計</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>補助・起債・交付税措置・基金・使用料を組み合わせた複数年の財源スキーム表を作る。</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>財政課に説明できる粒度になっている。</t>
+        </is>
+      </c>
+      <c r="E18" s="46" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>実行案の作成</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>複数年ロードマップ、実施体制案、議会・住民への説明の段取りを含む提案書を作る。</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>課長・部長に提示できる完成度になっている。</t>
+        </is>
+      </c>
+      <c r="E19" s="46" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>県の方針の確認</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>都道府県の支援計画・広域方針・説明会日程を確認し、市町村への制約と後押しを整理する。</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>県の方針と矛盾しない提案になっている。</t>
+        </is>
+      </c>
+      <c r="E20" s="46" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>制度の先読み</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>国の審議会・検討会の議事録と資料を継続的に確認し、改正の方向と時期を予測するメモを作る。</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>改正前に提案を仕込める状態になっている。</t>
+        </is>
+      </c>
+      <c r="E21" s="46" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>スキームの設計</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>広域・共同・県主導の枠組みに自社の業務を接続するスキーム案を作る。</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>複数団体・県に提示できる案になっている。</t>
+        </is>
+      </c>
+      <c r="E22" s="46" t="inlineStr"/>
+      <c r="F22" s="9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F22"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="E5:E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,―"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/10_新人教育カリキュラム_マスター管理表.xlsx
+++ b/output/10_新人教育カリキュラム_マスター管理表.xlsx
@@ -27,6 +27,10 @@
     <sheet name="17_営業提案 深度マトリクス" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="18_テーマ別 提案ネタ台帳" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="19_訪問前 準備チェックリスト" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="20_ヒアリング項目_共通" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="21_ヒアリング項目_テーマ別" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="22_トークスクリプト" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="23_訪問記録シート" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_月次ロードマップ'!$A$4:$I$40</definedName>
@@ -43,6 +47,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'14_教材・参考資料'!$A$4:$D$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'18_テーマ別 提案ネタ台帳'!$A$4:$F$111</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'19_訪問前 準備チェックリスト'!$A$4:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'20_ヒアリング項目_共通'!$A$4:$F$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'21_ヒアリング項目_テーマ別'!$A$4:$D$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'22_トークスクリプト'!$A$4:$F$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="23">'23_訪問記録シート'!$A$1:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -51,7 +59,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,8 +110,18 @@
       <color rgb="00843C0C"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <color rgb="00A02020"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -280,8 +298,13 @@
         <fgColor rgb="007030A0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -361,11 +384,44 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -535,6 +591,35 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -902,7 +987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1083,105 +1168,136 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>4. 運用サイクル（推奨）</t>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　20_ヒアリング項目_共通… L1〜L3の場面別に、そのまま聞ける質問文</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　21_ヒアリング項目_テーマ別… テーマごとに押さえるべき質問（L2／L3）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　毎月　　… 上長と本人で30分の面談。当月の学習項目と習得目標の達成状況を確認し、翌月の重点を決める。</t>
+          <t xml:space="preserve">　22_トークスクリプト… L1〜L3の台詞・意図・NG例</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　23_訪問記録シート… 訪問当日に記入する様式（印刷用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>4. 運用サイクル（推奨）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　毎月　　… 上長と本人で30分の面談。当月の学習項目と習得目標の達成状況を確認し、翌月の重点を決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　四半期　… 成果物レビューを1件必ず実施し、「確認方法」欄の方法で到達度を確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　半期　　… 12_個人別チェックシートで自己評価と上長評価を突き合わせ、差異の原因を対話する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　年次　　… レベル判定を確定し、次年度の主担当・副担当テーマと育成計画を決定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>5. レベル判定の原則</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・「知っている」ではなく「できた実績があるか」で判定します。判定には必ず具体的な案件名・成果物名を紐づけてください。</t>
+          <t xml:space="preserve">　半期　　… 12_個人別チェックシートで自己評価と上長評価を突き合わせ、差異の原因を対話する。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・1つの項目でL3と判定するには、原則として同種の作業を2案件以上、単独で完遂している必要があります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　・自己評価と上長評価に2段階以上の差がある場合は、必ず面談で認識を合わせてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>6. 更新について</t>
+          <t xml:space="preserve">　年次　　… レベル判定を確定し、次年度の主担当・副担当テーマと育成計画を決定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>5. レベル判定の原則</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・「知っている」ではなく「できた実績があるか」で判定します。判定には必ず具体的な案件名・成果物名を紐づけてください。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・制度改正（基本指針、報酬改定、会計基準、各省ガイドライン等）が生じた場合は、該当テーマシートの学習内容を年1回見直してください。</t>
+          <t xml:space="preserve">　・1つの項目でL3と判定するには、原則として同種の作業を2案件以上、単独で完遂している必要があります。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　・自己評価と上長評価に2段階以上の差がある場合は、必ず面談で認識を合わせてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>6. 更新について</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・制度改正（基本指針、報酬改定、会計基準、各省ガイドライン等）が生じた場合は、該当テーマシートの学習内容を年1回見直してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　・計画の「期」（第○期）は年度の経過とともに進みます。テーマシートの記載は根拠法と期間の考え方を示すもので、具体の期・年度は都度確認してください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="40">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A45:H45"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
@@ -1192,19 +1308,20 @@
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A40:H40"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11441,6 +11558,3959 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ヒアリング項目（共通・L1〜L3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>そのまま口に出せる形で書いてある。訪問前にこのシートの自分のレベルまでを読み、聞く順番を決めてから行く。◯◯・△△は必ず埋めてから使うこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="60" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="B4" s="60" t="inlineStr">
+        <is>
+          <t>場面</t>
+        </is>
+      </c>
+      <c r="C4" s="60" t="inlineStr">
+        <is>
+          <t>質問文（このまま聞ける形）</t>
+        </is>
+      </c>
+      <c r="D4" s="60" t="inlineStr">
+        <is>
+          <t>聞く目的（何が分かるか）</t>
+        </is>
+      </c>
+      <c r="E4" s="60" t="inlineStr">
+        <is>
+          <t>答えから読み取ること・次の一手</t>
+        </is>
+      </c>
+      <c r="F4" s="60" t="inlineStr">
+        <is>
+          <t>必須
+／任意</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>同行中の記録</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>（質問ではなく記録）所管課名・面談者の氏名・役職・同席者</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>誰が担当で、誰が決めるのかの当たりを付ける。</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>同席者に係長・課長がいれば関心が高い。担当者1人なら情報収集段階。</t>
+        </is>
+      </c>
+      <c r="F5" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>同行中の記録</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>（記録）相手が前のめりになった話題／表情が変わった箇所</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>相手の関心事＝次回の切り口。</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>帰社後すぐ先輩に確認する。「なぜあの話に反応されたのですか」は最良の学習機会。</t>
+        </is>
+      </c>
+      <c r="F6" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>同行中の記録</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>（記録）持ち帰り事項（宿題）と、その期限</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>宿題を落とすと一度で信用を失う。</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>当日中に議事録化し、期限を先輩と共有する。</t>
+        </is>
+      </c>
+      <c r="F7" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>同行中の記録</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>（記録）現行計画の名称・計画期間・策定年度</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>次の発注時期を逆算する起点。</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>帰社後、担当エリアの計画期間DBに登録する。</t>
+        </is>
+      </c>
+      <c r="F8" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>自分で聞いてよい</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>「差し支えなければ、御市の◯◯計画の冊子を1部いただけますでしょうか」</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>現行計画の入手。HPにない資料が手に入ることがある。</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>断られたらHPからダウンロードする。無理に食い下がらない。</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>現状を聞く</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>「現行の◯◯計画は、庁内で作られましたか、それとも委託されましたか」</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>外注の実績と、庁内の内製能力。</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>庁内作成なら「職員の負担」が切り口。委託なら受託先と発注方式を確認する。</t>
+        </is>
+      </c>
+      <c r="F10" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>現状を聞く</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>「前回はどちらの会社さんが受託されましたか」</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>競合と、前回の満足度。</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>自社なら継続の話へ。他社なら「どのあたりが良かったですか」で評価軸を探る。</t>
+        </is>
+      </c>
+      <c r="F11" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>現状を聞く</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>「前回の策定では、どのような調査をされましたか」</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>調査の有無・規模＝業務量と見積の目安。</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>調査を別発注していれば、調査年度と策定年度で2回の受注機会がある。</t>
+        </is>
+      </c>
+      <c r="F12" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>現状を聞く</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>「策定委員会は、どちらの会議体を使われましたか。新しく設置されましたか」</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>会議運営の負担と、既存協議会の活用可否。</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>既存協議会を使うなら委員委嘱の手間が減る＝見積に反映できる。</t>
+        </is>
+      </c>
+      <c r="F13" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>現状を聞く</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>「次期計画について、庁内で何かお話は出ていますか」</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>検討の温度感。</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>「まだ」＝情報提供のフェーズ。「そろそろ」＝L3の準備に入る合図。</t>
+        </is>
+      </c>
+      <c r="F14" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>現状を聞く</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>「いまの計画で、進めにくいと感じておられる点はございますか」</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>課題の入口。自分から指摘せず、相手に言ってもらう。</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>出てきた不満がそのまま次期計画の提案の核になる。メモを正確に取る。</t>
+        </is>
+      </c>
+      <c r="F15" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>現状を聞く</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>「ご担当は何名体制でいらっしゃいますか」</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>内製できる範囲と外注が必要な範囲。</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>1〜2名の兼務なら、調査・集計・会議運営の外注ニーズが高い。</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>現状を聞く</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>「◯◯計画のほかに、同じ時期に改定される計画はございますか」</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>一体・同時策定の可能性。</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>計画期間が近いものがあれば、次回訪問で計画期間一覧を持参する。</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>現状を聞く</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>「関係する他の課はどちらになりますか」</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>庁内横断の糸口（クロスセル）。</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>紹介をお願いできる関係になったら、L3で複数課への同時提案へ。</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>クロージング</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>「次期の指針が固まりましたら、改めてご報告にお伺いしてもよろしいでしょうか」</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>次回訪問の口実を確保する。</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>断られなければ次回のアポは取れたも同然。日付まで決められればなお良い。</t>
+        </is>
+      </c>
+      <c r="F19" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>課題を示す</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>「お伺いする前に現行計画と実績を拝見しました。気づいた点を3つほどお話ししてもよろしいでしょうか」</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>指摘の許可を取る。いきなり課題を並べない。</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>「どうぞ」が出てから話す。渋られたら情報提供に切り替えて撤退する。</t>
+        </is>
+      </c>
+      <c r="F20" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>課題を示す</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>「前期の◯◯について、計画値と実績で差が出ているようですが、要因として思い当たる点はございますか」</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>乖離の背景（体制・需要変化・指標設計）。</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>相手の説明が課題の一次情報。こちらの仮説と突き合わせる。</t>
+        </is>
+      </c>
+      <c r="F21" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>予算化</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>「来年度のご予算では、この業務はどのあたりでお考えでしょうか」</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>予算化の有無と時期。</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>「これから」＝要求書作成前。参考見積を出すべきタイミング。</t>
+        </is>
+      </c>
+      <c r="F22" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>予算化</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>「予算の枠感は、前回と同程度とお考えでしょうか」</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>見積のレンジ。</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>前回額を大きく下回るなら、業務範囲を削る設計に切り替える（値引きしない）。</t>
+        </is>
+      </c>
+      <c r="F23" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>予算化</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>「業務内容の案と参考のお見積をお持ちします。いつ頃までにあるとよろしいでしょうか」</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>提出期限を相手に言わせる＝予算要求スケジュールが分かる。</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>言われた期日の3営業日前に持参する。遅れたら要求書に載らない。</t>
+        </is>
+      </c>
+      <c r="F24" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>発注条件</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>「発注は年度当初のご予定でしょうか。それとも補正でお考えですか」</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>公告時期＝自社の体制確保。</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>年度当初なら1〜3月に公告。年間の受注計画に反映する。</t>
+        </is>
+      </c>
+      <c r="F25" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>発注条件</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>「入札とプロポーザル、どちらの想定でいらっしゃいますか」</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>提案書の要否と勝ち筋。</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>プロポーザルなら評価基準を確認する。入札なら価格勝負になるため採算を先に確認。</t>
+        </is>
+      </c>
+      <c r="F26" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>発注条件</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>「この件は課内でご判断される形でしょうか。それとも部まで上がりますか」</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>決裁ルート＝誰に会うべきか。</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>部長決裁なら、次は課長同席の場を作りにいく。</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>環境確認</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>「議会から、この計画についてご指摘は出ていますか」</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>外圧の有無。議会指摘は予算化の最短ルート。</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>指摘があれば、その論点に応える業務内容を提案に組み込む。</t>
+        </is>
+      </c>
+      <c r="F28" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>環境確認</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>「県からは、次期計画について何か示されていますか」</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>県の制約と後押し。</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>県の説明会資料を持っていなければ、次回持参する（それだけで価値になる）。</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>環境確認</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>「他にもお話を聞かれている会社さんはございますか」</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>競合状況。聞きにくければ「前回はどちらが受託されましたか」に置き換える。</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>複数社が動いていれば、差別化要素（調査設計・体制構築支援）を厚くする。</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>「この業務ですと◯◯交付金が対象になり得ると思うのですが、御市では活用のご検討はされていますか」</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>財源の認知と活用意向。断定せず「なり得る」で聞く。</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>知らなければ、次回までに当年度の要綱を整理して持参する＝訪問理由になる。</t>
+        </is>
+      </c>
+      <c r="F31" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>「◯◯債は計画への位置付けが要件になっていますが、対象事業は計画に書かれていますか」</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>計画と起債の接続。書かれていなければ、計画改定の必要性がそのまま生まれる。</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>「書いていない」＝最も強い提案機会。ただし数値・期限は当年度資料で確認してから話す。</t>
+        </is>
+      </c>
+      <c r="F32" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F32"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F77B4"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ヒアリング項目（テーマ別・L2〜L3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>テーマ列でフィルタして、訪問前に印刷して持参する。L2は現状を押さえる質問、L3は課題と発注条件に踏み込む質問。答えは相手の言葉のまま記録する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="60" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="B4" s="60" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="C4" s="60" t="inlineStr">
+        <is>
+          <t>質問文（このまま聞ける形）</t>
+        </is>
+      </c>
+      <c r="D4" s="60" t="inlineStr">
+        <is>
+          <t>聞く目的・使いどころ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>「財務書類は毎年度作成・公表されていますか。公表はいつ頃になりますか」</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>作成の遅れは最も分かりやすい課題。決算から1年以上空いていれば早期化の提案ができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>「固定資産台帳の更新は、庁内でされていますか、それとも委託でしょうか」</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>毎年度の更新業務は継続受注の柱。庁内対応なら負担軽減の提案へ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>「公会計システムは何をお使いですか。仕訳は日々仕訳と期末一括のどちらでしょうか」</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>作業範囲と工数の見積に直結する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>「取得価額が不明で備忘価額1円のままになっている資産は、どのくらい残っていますか」</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>精緻化業務の入口。件数が多ければ資産額が過少で、更新費用試算にも影響する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>「公有財産台帳と固定資産台帳の突合は実施されていますか」</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>突合していない団体が大半。差異一覧の作成をそのまま業務として提案できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>「借地・指定管理施設・法定外公共物などは、台帳にどう反映されていますか」</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>所有外・管理資産の整理。論点を具体的に挙げられると専門性が伝わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>「財務書類は予算編成や施設マネジメントで使われていますか」</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>「作って終わり」なら活用支援業務へ。指標分析・施設別コスト計算書の提案。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>「総合管理計画の更新費用試算は、固定資産台帳のデータと連動していますか」</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>連動していないケースが多い。公共施設テーマへのクロスセルになる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>「ご担当は何名で、異動後の引継ぎはできていますか」</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>属人化していれば、手順書作成・職員研修を付帯提案できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>「法適用の状況は、全部適用・財務適用・法非適用のどちらでしょうか」</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>法非適用なら法適化支援そのものが提案対象。適用済みなら会計支援・経営戦略へ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>「経営戦略はいつ策定されましたか。改定のご予定はございますか」</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>策定から3〜5年経っていれば改定業務の時期。国も改定を求めている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>「直近の料金（使用料）改定はいつでしたか」</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>10年以上空いていれば改定の必要性が高い。改定履歴は条例の改正履歴で裏が取れる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>「経営戦略の投資試算は、法定耐用年数と実使用年数のどちらで算定されていますか」</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>法定耐用年数のままなら更新需要が過大に出て計画が非現実的。精緻化＝改定の理由になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>「収支ギャップの解消策として料金改定が計画に書かれていますが、実行の目処はいかがですか」</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>「書いてあるが着手できていない」が最多パターン。改定業務そのものを提案できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>「更新需要は、アセットマネジメント（ストックマネジメント）計画と数字が揃っていますか」</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>別々に作られて整合していないケースが多い。整合を取る業務として提案する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>「一般会計からの繰入金に、基準外の繰入はございますか」</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>基準外繰入の常態化は独立採算が崩れている証拠。財政課を巻き込む入口になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>「県の広域化推進プランでは、御市はどの枠組みに位置付けられていますか」</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>県の枠組みを把握していると一段深い話ができる。複数団体への同時提案の糸口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>「技術職員・事務職員の体制は何名でいらっしゃいますか」</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>少人数なら包括的な会計支援（月次・決算・統計・予算）の提案が通りやすい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>「企業債の償還のピークはいつ頃で、発行余力はどのくらいとお考えですか」</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>投資・財政計画の前提。財源試算の提案につながる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>「保険者は御市単独でしょうか、それとも広域連合でしょうか」</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>広域連合なら介護保険事業計画と高齢者福祉計画で発注元が分かれる。両方に提案する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>「ニーズ調査はいつ実施されましたか。次はいつのご予定でしょうか」</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>調査年度は策定年度の前年度。調査だけの発注機会を取りにいける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>「策定委員会は、介護保険運営協議会などの既存の会議体を使われますか」</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>既存協議会の活用可否は見積の前提になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>「前期の見込量と実績で、乖離が大きかったサービスはどれでしょうか」</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>総合事業・地域密着型で乖離が出やすい。乖離率一覧を作って持参すると説得力が出る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>「施設整備の公募は、応募の状況はいかがでしたか」</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>未整備のまま次期に持ち越すケースが多い。事業者意向調査の追加提案につながる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>「次期の保険料は、どのくらいの上昇を見込んでおられますか」</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>上昇幅が大きいほど住民説明の支援ニーズが高い。わかりやすい資料の付帯提案へ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>「保険者機能強化推進交付金の評価で、取れていない項目はどのあたりでしょうか」</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>評価指標に計画の策定・進捗管理が含まれる。計画の作り込みが交付金に直結すると説明できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>「認知症施策推進計画は、事業計画に含める形でしょうか、別冊にされますか」</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>新たな計画需要。別冊なら独立した受注機会になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>「地域包括支援センターは直営と委託のどちらで、何箇所でしょうか」</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>センター評価・体制支援の提案につながる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>「総合事業の見直しは検討されていますか」</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>見直しは体制設計を伴う。策定業務より単価を上げられる領域。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>「障害者計画・障害福祉計画・障害児福祉計画は一体で策定されていますか」</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>一体なら1本の発注、別々なら複数の受注機会。計画期間のずれも確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>「障害者計画の計画期間は何年でしょうか。事業計画と改定時期は揃っていますか」</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>ずれていると次期で揃える提案ができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>「策定は自立支援協議会を使われますか、別に委員会を設置されますか」</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>協議会活用なら当事者参画の設計が要る。情報保障の実務が提案価値になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>「前期の成果目標で、未達になっているのはどの項目でしょうか」</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>未達要因の分析をそのまま業務に組み込める。目標の引き写しからの脱却を提案する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>「地域生活支援拠点は整備済みでしょうか。機能はどのように検証されていますか」</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>登録型で形だけのケースが多い。機能検証・体制設計は策定業務を超える単価が取れる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>「基幹相談支援センターは設置されていますか」</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>未設置なら体制構築支援の提案。設置済みなら相談支援体制の強化へ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>「医療的ケア児や強度行動障害のある方の実態は把握できていますか」</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>未把握が大半。実態調査を単独業務として切り出せる（策定年度以外の受注機会）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>「サービス種別で、地域に不足しているものはどれでしょうか」</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>放課後等デイは充足、生活介護・グループホームが不足という構図が多い。事業所調査の提案へ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>「手帳所持者アンケートは、前回どの範囲・規模で実施されましたか」</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>3障害＋障害児で標本設計が変わる。見積の前提として必ず押さえる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>「調査や会議での情報保障（点字・拡大文字・わかりやすい版）はどうされていますか」</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>対応実績を語れると差別化になる。差別解消法の義務化とも接続できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>「計画は市の単独策定でしょうか、社協の地域福祉活動計画と一体でしょうか」</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>一体なら発注元が2つになり予算を合算できる。社協にも同時にアプローチする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>「重層的支援体制整備事業は実施されていますか。移行準備事業はいかがでしょうか」</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>未実施なら移行支援、実施中なら実施計画の策定・体制強化が提案対象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>「地域福祉計画に併載されている計画はございますか」</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>成年後見・再犯防止・自殺対策など。併載編が増えるほど業務量と単価が上がる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>「重層事業への移行について、庁内の合意状況はいかがですか」</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>合意形成が壁になっている団体が多い。庁内勉強会・フロー整理の伴走支援を提案できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>「圏域の設定は、日常生活圏域や小学校区と揃っていますか」</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>バラバラなことが多い。圏域整理は他計画にも波及するため単価を上げやすい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>「前回の住民座談会は、どのくらいの規模・回数で実施されましたか」</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>回数が見積の主要因。参加者が固定化していれば参加設計の見直しを提案する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>「社会福祉協議会とは、どのような役割分担になりますか」</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>社協との関係性が受注構造を決める。社協側にも顔を出す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>「成年後見の中核機関は設置されていますか」</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>未設置なら利用促進基本計画の策定・体制整備の提案へ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>「自殺対策計画の改定時期はいつでしょうか」</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>地域自殺対策強化交付金を充当できる。財源とセットで提案すると予算化しやすい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>「前計画の進捗評価は、どのように行われていますか」</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>評価の仕組みがなければ、指標設計と年次評価の仕組みづくりを業務に含める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>「子ども・子育て支援事業計画の中間年見直しはご検討されていますか」</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>5年1期の中間年見直しは、改定年度以外の確実な受注機会。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>「こども計画は策定されましたか。どの計画を統合されましたか」</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>未策定なら新規の計画需要。統合済みなら次期改定の時期を押さえる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>「ニーズ調査はいつ実施されましたか。就学前と小学生の両方でしょうか」</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>調査規模＝見積の前提。Web併用の有無も確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>「量の見込みと実績で、乖離が大きいのはどの区域・年齢でしょうか」</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>区域別・年齢別の乖離表を作って持参する。中間見直しの必要性を数字で示せる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>「いまは待機児童と定員割れ、どちらが課題になっていますか」</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>定員割れが始まっていれば「増やす計画」から「適正化の計画」への転換提案ができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>「こども誰でも通園制度の提供体制は、どのように見込まれていますか」</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>新たに量の見込みへの反映が必要。中間見直しを提案する明確な理由になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>「こども家庭センターは設置済みでしょうか。体制は何名でしょうか」</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>兼務で回っていないケースが多い。体制設計・業務フロー整理の提案へ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>「こども・若者の意見反映は、どのような方法で実施されましたか」</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>アンケート止まりが多い。こども会議の設計・運営を独立業務として提案できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>「こどもの貧困の実態調査は実施されていますか」</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>地域子供の未来応援交付金を充当できる可能性がある。財源とセットで提案する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>「保育・母子保健・教育委員会との庁内調整は、どなたが担われていますか」</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>調整の負担が最大の悩み。庁内横断の事務局支援が提案価値になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>「公共施設等総合管理計画の見直しは、国の要請事項の反映まで済んでいますか」</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>個別施設計画の反映・保有量の数値目標・脱炭素・UD化。未反映なら改定の提案ができる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>「個別施設計画は、施設類型ごとに一通り揃っていますか」</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>未策定の類型があれば、そこが単独の受注機会になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>「更新費用試算は何年前のもので、固定資産台帳と連動していますか」</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>古い試算・非連動が大半。再試算は公会計とのクロスセルになる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>「公共施設等適正管理推進事業債の活用実績はございますか」</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>計画への位置付けが起債の要件。書かれていない事業があれば改定の必要性が生まれる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>「健康増進・食育・自殺対策・歯科口腔・データヘルスは一体で策定されていますか」</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>別々なら一体策定による整合確保と事務負担軽減を提案できる（束ね受注）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>「地域計画（農業）の更新や変更は、どなたが担われていますか」</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>策定後の更新が継続的に発生する。農業委員会との関係も確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>「男女共同参画計画は、女性活躍・DV・困難女性支援と一体でしょうか」</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>法改正に伴う必須記載事項の追加が改定理由になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>「財政推計に、施設の更新費や公営企業への繰出金は反映されていますか」</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>未反映が多い。統合推計の提案は財政課との関係構築につながり、全テーマに波及する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:D71"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>トークスクリプト（L1〜L3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>「話す内容」は台詞そのもの。暗記するのではなく、意図を理解したうえで自分の言葉に直して使う。「これはNG」の列が本体 ── ここに書いてある失敗は、取り返すのに年単位かかる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="60" t="inlineStr">
+        <is>
+          <t>Lv</t>
+        </is>
+      </c>
+      <c r="B4" s="60" t="inlineStr">
+        <is>
+          <t>場面</t>
+        </is>
+      </c>
+      <c r="C4" s="60" t="inlineStr">
+        <is>
+          <t>ステップ</t>
+        </is>
+      </c>
+      <c r="D4" s="60" t="inlineStr">
+        <is>
+          <t>話す内容（スクリプト）</t>
+        </is>
+      </c>
+      <c r="E4" s="60" t="inlineStr">
+        <is>
+          <t>意図</t>
+        </is>
+      </c>
+      <c r="F4" s="60" t="inlineStr">
+        <is>
+          <t>これはNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>① 名刺交換・冒頭</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>名乗る</t>
+        </is>
+      </c>
+      <c r="D5" s="63" t="inlineStr">
+        <is>
+          <t>「◯◯株式会社の△△と申します。□□（先輩）と一緒に御市の◯◯計画のお手伝いをさせていただいております。本日は勉強させていただきます。よろしくお願いいたします。」</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>自分の立場を明確にし、同行者として自然に場に入る。</t>
+        </is>
+      </c>
+      <c r="F5" s="64" t="inlineStr">
+        <is>
+          <t>長い自己紹介。自社の説明を始めてしまう（それは先輩の役割）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>② 面談中</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>基本の姿勢</t>
+        </is>
+      </c>
+      <c r="D6" s="65" t="inlineStr">
+        <is>
+          <t>（原則として聞き役に回り、メモを取る。話を振られたら簡潔に答える）</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>同行の目的は受注ではなく、先輩の話し方と相手の反応を観察すること。</t>
+        </is>
+      </c>
+      <c r="F6" s="64" t="inlineStr">
+        <is>
+          <t>沈黙が気になって余計な話を挟む。相手の言葉を遮る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>② 面談中</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>答えられない質問を受けたとき</t>
+        </is>
+      </c>
+      <c r="D7" s="63" t="inlineStr">
+        <is>
+          <t>「申し訳ございません、正確にお答えしたいので、確認のうえご連絡させていただいてもよろしいでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>推測で答えないことが最大の防御。特に金額・納期・制度の可否。</t>
+        </is>
+      </c>
+      <c r="F7" s="64" t="inlineStr">
+        <is>
+          <t>「たぶん◯◯だと思います」。憶測は一度で信用を失う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>② 面談中</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>資料をお願いする</t>
+        </is>
+      </c>
+      <c r="D8" s="65" t="inlineStr">
+        <is>
+          <t>「差し支えなければ、御市の◯◯計画の冊子を1部いただけますでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>現行計画の入手。HPに載っていない資料が手に入ることがある。</t>
+        </is>
+      </c>
+      <c r="F8" s="64" t="inlineStr">
+        <is>
+          <t>断られたのに食い下がる。HPで手に入るものを聞く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>③ 退出</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>締める</t>
+        </is>
+      </c>
+      <c r="D9" s="63" t="inlineStr">
+        <is>
+          <t>「本日はお時間をいただきありがとうございました。◯◯のお話、大変勉強になりました。」</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>相手の話のどこが有益だったかを具体的に言う。</t>
+        </is>
+      </c>
+      <c r="F9" s="64" t="inlineStr">
+        <is>
+          <t>「よろしくお願いします」だけ。何も残らない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>④ 帰社後</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>当日中にやること</t>
+        </is>
+      </c>
+      <c r="D10" s="65" t="inlineStr">
+        <is>
+          <t>（議事録を作成し、宿題と期限を明記して先輩に送る。計画期間DBに現行計画を登録する）</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>記録の速さと正確さがL2に上がる条件。</t>
+        </is>
+      </c>
+      <c r="F10" s="64" t="inlineStr">
+        <is>
+          <t>翌日以降に回す。記憶が曖昧になり、宿題が抜ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>① アポイント（電話）</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>取り次ぎを頼む</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="inlineStr">
+        <is>
+          <t>「お世話になっております。◯◯株式会社の△△と申します。◯◯計画をご担当されている方はいらっしゃいますでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>用件より先に名乗る。担当者名が分かっていれば氏名で指名する。</t>
+        </is>
+      </c>
+      <c r="F11" s="64" t="inlineStr">
+        <is>
+          <t>いきなり売り込みを始める。担当者名を確認せずに電話する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>① アポイント（電話）</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>用件を伝える</t>
+        </is>
+      </c>
+      <c r="D12" s="65" t="inlineStr">
+        <is>
+          <t>「◯◯計画について、国の指針の改正の動きが出てまいりましたので、15分ほどお時間をいただいて情報提供にお伺いできればと思っております。ご都合はいかがでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>①用件を先に ②所要時間を明示 ③「情報提供」と伝え、実際に売り込まない。</t>
+        </is>
+      </c>
+      <c r="F12" s="64" t="inlineStr">
+        <is>
+          <t>「ご挨拶に伺いたい」だけ。用件がないアポは断られるか、行っても話が続かない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>① アポイント（電話）</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>断られたとき</t>
+        </is>
+      </c>
+      <c r="D13" s="63" t="inlineStr">
+        <is>
+          <t>「承知いたしました。それでは資料だけメールでお送りしてもよろしいでしょうか。ご覧いただいてご関心があればご連絡いただければ幸いです。」</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>接点を残す。資料送付は次の電話の口実になる。</t>
+        </is>
+      </c>
+      <c r="F13" s="64" t="inlineStr">
+        <is>
+          <t>食い下がって時間を取らせる。次の機会を自分で潰すことになる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>② 訪問の冒頭</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>枠組みを示す</t>
+        </is>
+      </c>
+      <c r="D14" s="65" t="inlineStr">
+        <is>
+          <t>「本日はお時間をいただきありがとうございます。15分ほどで、◯◯計画に関する国の動きと、他の自治体さんの状況をお伝えできればと思っております。途中でご質問があればいつでも遮ってください。」</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>所要時間と話す内容を先に示すと、相手が安心して聞ける。</t>
+        </is>
+      </c>
+      <c r="F14" s="64" t="inlineStr">
+        <is>
+          <t>世間話を長く続ける。相手の時間を無駄にしている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>③ 現状を聞く</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>許可を取ってから聞く</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>「本題の前に、御市の現在の状況を少しだけ教えていただいてもよろしいでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>質問の許可を取る。尋問にならないための一言。</t>
+        </is>
+      </c>
+      <c r="F15" s="64" t="inlineStr">
+        <is>
+          <t>挨拶の直後から質問を並べる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>③ 現状を聞く</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>基本を押さえる</t>
+        </is>
+      </c>
+      <c r="D16" s="65" t="inlineStr">
+        <is>
+          <t>「現行の◯◯計画は、庁内で作られましたか、それとも委託されましたか。」／「前回はどちらの会社さんが受託されましたか。」／「次期計画について、庁内で何かお話は出ていますか。」</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>内製能力・競合・検討の温度感の3点を最初に押さえる。</t>
+        </is>
+      </c>
+      <c r="F16" s="64" t="inlineStr">
+        <is>
+          <t>答えを聞き流してメモを取らない。次回の訪問で同じことを聞くと信用を失う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>④ 情報を届ける</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>国の動きを伝える</t>
+        </is>
+      </c>
+      <c r="D17" s="63" t="inlineStr">
+        <is>
+          <t>「まず国の動きですが、◯月に△△審議会で□□の議論が始まっておりまして、次期の指針では◯◯が重点になる方向で議論されています。確定は告示後になりますが、（資料を指して）このあたりが御市に関係してくるかと思います。」</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>「議論されている」「確定は告示後」で、未確定と確定を明確に分ける。</t>
+        </is>
+      </c>
+      <c r="F17" s="64" t="inlineStr">
+        <is>
+          <t>「次期の指針では必ず◯◯になります」。未確定の断定は、後で必ず自分に返ってくる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>④ 情報を届ける</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>他自治体の状況を伝える</t>
+        </is>
+      </c>
+      <c r="D18" s="65" t="inlineStr">
+        <is>
+          <t>「近隣ですと、△△市さんが◯年度に□□に取り組まれています。公表されている資料はこちらです。」</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>必ず出典を示す。公表資料のみを使う。</t>
+        </is>
+      </c>
+      <c r="F18" s="64" t="inlineStr">
+        <is>
+          <t>「◯◯市さんは困っているようです」。他団体から聞いた未公表の話は絶対に持ち込まない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>⑤ スケジュールを示す</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>逆算して見せる</t>
+        </is>
+      </c>
+      <c r="D19" s="63" t="inlineStr">
+        <is>
+          <t>「御市の現行計画は令和◯年度までですので、逆算しますと調査が◯年度、策定が◯年度になります。予算要求が◯年度の夏頃かと思いますので、そろそろご検討いただく時期かと存じます。」</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>「いつ動くべきか」を相手の代わりに計算する。ここが情報提供の最大の価値。</t>
+        </is>
+      </c>
+      <c r="F19" s="64" t="inlineStr">
+        <is>
+          <t>スケジュールを示さずに商品説明だけする。相手は動く理由を持てない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>⑥ クロージング</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>次の口実を作る</t>
+        </is>
+      </c>
+      <c r="D20" s="65" t="inlineStr">
+        <is>
+          <t>「本日の内容は資料にまとめてお渡しします。次期の指針が固まりましたら、改めてご報告にお伺いしてもよろしいでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>次回訪問の許可を取って帰る。売り込まないことが次につながる。</t>
+        </is>
+      </c>
+      <c r="F20" s="64" t="inlineStr">
+        <is>
+          <t>この場で見積や受注の話を持ち出す。L2の役割を超えている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>⑦ 帰社後</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>当日中にやること</t>
+        </is>
+      </c>
+      <c r="D21" s="63" t="inlineStr">
+        <is>
+          <t>（訪問記録をCRMに登録し、次アクションと期限を設定する。約束した資料は3営業日以内に送る）</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>約束した資料の送付が最初の信用になる。</t>
+        </is>
+      </c>
+      <c r="F21" s="64" t="inlineStr">
+        <is>
+          <t>資料送付を先延ばしにする。「送ると言って送らない会社」と記憶される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>① 冒頭</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>準備してきたことを示す</t>
+        </is>
+      </c>
+      <c r="D22" s="65" t="inlineStr">
+        <is>
+          <t>「お伺いする前に、御市の現行計画と実績を拝見しました。差し支えなければ、気づいた点を3つほどお話ししてもよろしいでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>指摘の前に許可を取る。「調べてきた」という事実だけで他社と差がつく。</t>
+        </is>
+      </c>
+      <c r="F22" s="64" t="inlineStr">
+        <is>
+          <t>許可を取らずに課題を並べる。相手は身構え、以降の話が入らなくなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>② 課題を示す</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>データで示す（前任者批判にしない）</t>
+        </is>
+      </c>
+      <c r="D23" s="63" t="inlineStr">
+        <is>
+          <t>「◯◯の見込量ですが、計画では△△、実績が□□で、◯%の差が出ています。これは御市に限った話ではなく、多くの団体で同じ傾向が出ておりまして、次期計画では推計の前提を見直す必要があるかと考えております。」</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>①数字で示す ②一般的な傾向だと添える ③次期への提案に着地させる。</t>
+        </is>
+      </c>
+      <c r="F23" s="64" t="inlineStr">
+        <is>
+          <t>「前回の推計が甘かったですね」。担当者個人の否定に聞こえた時点で失注する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>② 課題を示す</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>相手に語ってもらう</t>
+        </is>
+      </c>
+      <c r="D24" s="65" t="inlineStr">
+        <is>
+          <t>「差が出た要因として、思い当たる点はございますか。」</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>こちらの仮説と相手の実感を突き合わせる。相手が語った課題は提案で否定されない。</t>
+        </is>
+      </c>
+      <c r="F24" s="64" t="inlineStr">
+        <is>
+          <t>自分の仮説を押し通す。相手が知っている事情を聞かずに提案を作ると外す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>③ 財源の話</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>補助金は断定しない</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="inlineStr">
+        <is>
+          <t>「この業務ですと、◯◯交付金が対象になり得るかと思います。ただ要綱が毎年度変わりますので、今年度の対象経費は改めて確認させてください。よろしければ、次回までに整理してお持ちします。」</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>「なり得る」で止める。確認して持参することが次回訪問の理由になる。</t>
+        </is>
+      </c>
+      <c r="F25" s="64" t="inlineStr">
+        <is>
+          <t>「◯◯交付金が使えます」。断定して外すと、予算が付かないだけでなく担当者の面目を潰す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>③ 財源の話</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>起債は順序で語る</t>
+        </is>
+      </c>
+      <c r="D26" s="65" t="inlineStr">
+        <is>
+          <t>「◯◯債は、計画に位置付けられていることが要件になっております。逆に申しますと、計画に書かれていない事業は起債の対象にならないということでして、計画の改定と事業の実施は、実はセットで考える必要があるかと思っております。」</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>「計画に書かないと財源が取れない」という順序が、計画策定業務の必要性を最も強く説明する。</t>
+        </is>
+      </c>
+      <c r="F26" s="64" t="inlineStr">
+        <is>
+          <t>充当率・措置率・期限を、当年度資料で確認せずに口に出す。数値の誤りは事故になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>④ 予算化</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>時期を確認する</t>
+        </is>
+      </c>
+      <c r="D27" s="63" t="inlineStr">
+        <is>
+          <t>「来年度のご予算では、この業務はどのあたりでお考えでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>予算要求前かどうかで打ち手が変わる。要求前なら参考見積を出す。</t>
+        </is>
+      </c>
+      <c r="F27" s="64" t="inlineStr">
+        <is>
+          <t>予算の話を避けて雑談で終わる。訪問の目的を果たしていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>④ 予算化</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>見積の提出を申し出る</t>
+        </is>
+      </c>
+      <c r="D28" s="65" t="inlineStr">
+        <is>
+          <t>「業務内容の案と参考のお見積をお持ちします。予算要求の資料としてお使いいただければと思いますが、いつ頃までにあるとよろしいでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>期限を相手に言わせる。相手の要求スケジュールがそのまま分かる。</t>
+        </is>
+      </c>
+      <c r="F28" s="64" t="inlineStr">
+        <is>
+          <t>こちらから「来月中に」と決める。相手の庁内スケジュールに合わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>④ 予算化</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>枠感を確認する</t>
+        </is>
+      </c>
+      <c r="D29" s="63" t="inlineStr">
+        <is>
+          <t>「予算の枠感は、前回と同程度とお考えでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>レンジを掴む。前回を大きく下回るなら、値引きではなく業務範囲を削る設計に切り替える。</t>
+        </is>
+      </c>
+      <c r="F29" s="64" t="inlineStr">
+        <is>
+          <t>その場で値引きを申し出る。一度下げた単価は戻らない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>⑤ 発注条件</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>方式と時期を聞く</t>
+        </is>
+      </c>
+      <c r="D30" s="65" t="inlineStr">
+        <is>
+          <t>「発注は年度当初のご予定でしょうか、それとも補正でお考えですか。」／「入札とプロポーザル、どちらの想定でいらっしゃいますか。」</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>公告時期と勝ち筋を掴み、年間の受注計画と体制確保に反映する。</t>
+        </is>
+      </c>
+      <c r="F30" s="64" t="inlineStr">
+        <is>
+          <t>聞かずに帰り、公告を見落とす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>⑥ 仕様書案を求められたとき</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>線引きを自分から言う</t>
+        </is>
+      </c>
+      <c r="D31" s="63" t="inlineStr">
+        <is>
+          <t>「業務範囲の考え方であればお出しできます。ただ、当社しか対応できないような書き方はいたしませんので、一般的な内容になります。それでよろしければお持ちします。」</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>官製談合を疑われる余地を自分から潰す。この一言が長期の信頼になる。</t>
+        </is>
+      </c>
+      <c r="F31" s="64" t="inlineStr">
+        <is>
+          <t>自社の強みだけを要件に書き込む。相手も自社も守れない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>⑦ 庁内展開</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>他課につなぐ</t>
+        </is>
+      </c>
+      <c r="D32" s="65" t="inlineStr">
+        <is>
+          <t>「◯◯計画とあわせて、△△計画も同じ時期の改定かと思います。ご担当の課をご紹介いただくことは可能でしょうか。」</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>紹介を得られれば、営業コストをかけずに新規テーマに入れる。</t>
+        </is>
+      </c>
+      <c r="F32" s="64" t="inlineStr">
+        <is>
+          <t>紹介を得る前に他課へ直接飛び込む。担当者の顔を潰し、庁内で悪評が立つ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>⑧ クロージング</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>次アクションを確定させる</t>
+        </is>
+      </c>
+      <c r="D33" s="63" t="inlineStr">
+        <is>
+          <t>「それでは、◯月◯日までに業務内容案と参考見積をお持ちします。そのときに、◯◯交付金の今年度の要綱も整理してお持ちします。」</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>「誰が・いつまでに・何を」を口に出して確定させ、その場でメモを見せる。</t>
+        </is>
+      </c>
+      <c r="F33" s="64" t="inlineStr">
+        <is>
+          <t>「またご連絡します」で終える。次が決まっていない訪問は成果ゼロと同じ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>⑨ 反応が薄いとき</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>撤退の仕方</t>
+        </is>
+      </c>
+      <c r="D34" s="65" t="inlineStr">
+        <is>
+          <t>「本日は突っ込んだお話までは難しかったかと思いますので、まずは資料をお渡しして失礼いたします。状況が変わりましたらいつでもお声がけください。」</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>無理に押さない。引き際が良いと、次の年度に呼ばれる。</t>
+        </is>
+      </c>
+      <c r="F34" s="64" t="inlineStr">
+        <is>
+          <t>粘って時間を延ばす。次の訪問が断られる原因になる。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F34"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>訪問記録シート（様式）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>訪問当日中に記入する。温度感と次アクションが空欄の記録は、記録として成立していない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="60" t="inlineStr">
+        <is>
+          <t>ブロック</t>
+        </is>
+      </c>
+      <c r="B4" s="60" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C4" s="60" t="inlineStr">
+        <is>
+          <t>記入の仕方・記入例</t>
+        </is>
+      </c>
+      <c r="D4" s="60" t="inlineStr">
+        <is>
+          <t>記入欄</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="16" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="44" t="inlineStr">
+        <is>
+          <t>基本情報</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>訪問日／時間</t>
+        </is>
+      </c>
+      <c r="C5" s="66" t="inlineStr">
+        <is>
+          <t>例：R◯.◯.◯（◯）14:00〜14:30</t>
+        </is>
+      </c>
+      <c r="D5" s="67" t="n"/>
+      <c r="E5" s="48" t="n"/>
+      <c r="F5" s="48" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="68" t="n"/>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>訪問先（団体名・部課名）</t>
+        </is>
+      </c>
+      <c r="C6" s="66" t="inlineStr">
+        <is>
+          <t>例：◯◯市 福祉部 高齢福祉課</t>
+        </is>
+      </c>
+      <c r="D6" s="67" t="n"/>
+      <c r="E6" s="48" t="n"/>
+      <c r="F6" s="48" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="68" t="n"/>
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>面談者（氏名・役職）</t>
+        </is>
+      </c>
+      <c r="C7" s="66" t="inlineStr">
+        <is>
+          <t>同席者も全員記載する</t>
+        </is>
+      </c>
+      <c r="D7" s="67" t="n"/>
+      <c r="E7" s="48" t="n"/>
+      <c r="F7" s="48" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="68" t="n"/>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>当社出席者／自分のレベル</t>
+        </is>
+      </c>
+      <c r="C8" s="66" t="inlineStr">
+        <is>
+          <t>例：△△（L2）、□□（L4・同行）</t>
+        </is>
+      </c>
+      <c r="D8" s="67" t="n"/>
+      <c r="E8" s="48" t="n"/>
+      <c r="F8" s="48" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="69" t="n"/>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>テーマ／対象計画</t>
+        </is>
+      </c>
+      <c r="C9" s="66" t="inlineStr">
+        <is>
+          <t>例：第◯期介護保険事業計画</t>
+        </is>
+      </c>
+      <c r="D9" s="67" t="n"/>
+      <c r="E9" s="48" t="n"/>
+      <c r="F9" s="48" t="n"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>準備</t>
+        </is>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>事前に確認したもの</t>
+        </is>
+      </c>
+      <c r="C10" s="66" t="inlineStr">
+        <is>
+          <t>現行計画／実績データ／議会議事録／県の資料／経営指標　など該当するものを列挙</t>
+        </is>
+      </c>
+      <c r="D10" s="67" t="n"/>
+      <c r="E10" s="48" t="n"/>
+      <c r="F10" s="48" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="69" t="n"/>
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>本日の目的（訪問前に書く）</t>
+        </is>
+      </c>
+      <c r="C11" s="66" t="inlineStr">
+        <is>
+          <t>例：次期計画の検討状況を確認し、予算要求時期を特定する</t>
+        </is>
+      </c>
+      <c r="D11" s="67" t="n"/>
+      <c r="E11" s="48" t="n"/>
+      <c r="F11" s="48" t="n"/>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>面談内容</t>
+        </is>
+      </c>
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>当社から伝えたこと</t>
+        </is>
+      </c>
+      <c r="C12" s="66" t="inlineStr">
+        <is>
+          <t>国の動向／事例／スケジュール逆算／財源　など実際に話した内容</t>
+        </is>
+      </c>
+      <c r="D12" s="67" t="n"/>
+      <c r="E12" s="48" t="n"/>
+      <c r="F12" s="48" t="n"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="68" t="n"/>
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t>ヒアリング結果（現状）</t>
+        </is>
+      </c>
+      <c r="C13" s="66" t="inlineStr">
+        <is>
+          <t>計画期間・前回の発注方式・受託先・調査の有無・体制・庁内の検討状況</t>
+        </is>
+      </c>
+      <c r="D13" s="67" t="n"/>
+      <c r="E13" s="48" t="n"/>
+      <c r="F13" s="48" t="n"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="68" t="n"/>
+      <c r="B14" s="47" t="inlineStr">
+        <is>
+          <t>ヒアリング結果（課題）</t>
+        </is>
+      </c>
+      <c r="C14" s="66" t="inlineStr">
+        <is>
+          <t>相手が語った困りごと。相手の言葉のまま記録する（要約しすぎない）</t>
+        </is>
+      </c>
+      <c r="D14" s="67" t="n"/>
+      <c r="E14" s="48" t="n"/>
+      <c r="F14" s="48" t="n"/>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="69" t="n"/>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>ヒアリング結果（予算・発注）</t>
+        </is>
+      </c>
+      <c r="C15" s="66" t="inlineStr">
+        <is>
+          <t>予算化の見込み／枠感／発注時期／発注方式／決裁ルート／競合</t>
+        </is>
+      </c>
+      <c r="D15" s="67" t="n"/>
+      <c r="E15" s="48" t="n"/>
+      <c r="F15" s="48" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>温度感</t>
+        </is>
+      </c>
+      <c r="C16" s="66" t="inlineStr">
+        <is>
+          <t>A：今年度中に動く／B：次年度予算で検討／C：様子見／D：当面なし</t>
+        </is>
+      </c>
+      <c r="D16" s="70" t="n"/>
+      <c r="E16" s="48" t="n"/>
+      <c r="F16" s="48" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="69" t="n"/>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>受注確度と時期の見立て</t>
+        </is>
+      </c>
+      <c r="C17" s="66" t="inlineStr">
+        <is>
+          <t>例：B　R◯年度当初発注、プロポーザル想定、想定規模◯◯万円</t>
+        </is>
+      </c>
+      <c r="D17" s="67" t="n"/>
+      <c r="E17" s="48" t="n"/>
+      <c r="F17" s="48" t="n"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>宿題</t>
+        </is>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>当社→先方（内容・期限）</t>
+        </is>
+      </c>
+      <c r="C18" s="66" t="inlineStr">
+        <is>
+          <t>例：◯◯交付金の今年度要綱の整理　◯月◯日まで</t>
+        </is>
+      </c>
+      <c r="D18" s="67" t="n"/>
+      <c r="E18" s="48" t="n"/>
+      <c r="F18" s="48" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="69" t="n"/>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>先方→当社（内容・期限）</t>
+        </is>
+      </c>
+      <c r="C19" s="66" t="inlineStr">
+        <is>
+          <t>例：庁内での検討結果の連絡　◯月中</t>
+        </is>
+      </c>
+      <c r="D19" s="67" t="n"/>
+      <c r="E19" s="48" t="n"/>
+      <c r="F19" s="48" t="n"/>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>次アクション</t>
+        </is>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>次にやること／次回訪問予定</t>
+        </is>
+      </c>
+      <c r="C20" s="66" t="inlineStr">
+        <is>
+          <t>「誰が・いつまでに・何を」を具体的に書く</t>
+        </is>
+      </c>
+      <c r="D20" s="67" t="n"/>
+      <c r="E20" s="48" t="n"/>
+      <c r="F20" s="48" t="n"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>振り返り</t>
+        </is>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>うまくいった点／課題</t>
+        </is>
+      </c>
+      <c r="C21" s="66" t="inlineStr">
+        <is>
+          <t>自分の話し方・質問の順序・準備の過不足を1つずつ書く</t>
+        </is>
+      </c>
+      <c r="D21" s="67" t="n"/>
+      <c r="E21" s="48" t="n"/>
+      <c r="F21" s="48" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="69" t="n"/>
+      <c r="B22" s="47" t="inlineStr">
+        <is>
+          <t>上長コメント</t>
+        </is>
+      </c>
+      <c r="C22" s="66" t="inlineStr">
+        <is>
+          <t>（上長が記入）</t>
+        </is>
+      </c>
+      <c r="D22" s="67" t="n"/>
+      <c r="E22" s="48" t="n"/>
+      <c r="F22" s="48" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D6:F6"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"A：今年度中に動く,B：次年度予算で検討,C：様子見,D：当面なし"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/10_新人教育カリキュラム_マスター管理表.xlsx
+++ b/output/10_新人教育カリキュラム_マスター管理表.xlsx
@@ -31,6 +31,10 @@
     <sheet name="21_ヒアリング項目_テーマ別" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="22_トークスクリプト" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="23_訪問記録シート" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="24_訪問記録CSV_入力シート" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="25_CSV入力規則" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="26_テーマ・タイトル標準リスト" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="選択肢マスタ" sheetId="28" state="hidden" r:id="rId28"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_月次ロードマップ'!$A$4:$I$40</definedName>
@@ -50,7 +54,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'20_ヒアリング項目_共通'!$A$4:$F$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'21_ヒアリング項目_テーマ別'!$A$4:$D$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'22_トークスクリプト'!$A$4:$F$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="23">'23_訪問記録シート'!$A$1:$F$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="23">'23_訪問記録シート'!$A$1:$F$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'24_訪問記録CSV_入力シート'!$A$1:$O$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'25_CSV入力規則'!$A$4:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'26_テーマ・タイトル標準リスト'!$A$4:$D$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -59,7 +66,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,8 +127,20 @@
       <color rgb="00A02020"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -303,6 +322,16 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -421,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -613,14 +642,71 @@
     <xf numFmtId="0" fontId="2" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -987,7 +1073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1192,112 +1278,133 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　23_訪問記録シート… 訪問当日に記入する様式（印刷用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>4. 運用サイクル（推奨）</t>
+          <t xml:space="preserve">　23_訪問記録シート… 訪問当日に記入する様式（CSV15列＋社内記録。印刷用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　24_訪問記録CSV_入力シート… Teams提出用。このシートをCSVで保存する</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　25_CSV入力規則… 15列の必須区分・選択肢・記入例・よくある誤り／備考の書き方</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　毎月　　… 上長と本人で30分の面談。当月の学習項目と習得目標の達成状況を確認し、翌月の重点を決める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　四半期　… 成果物レビューを1件必ず実施し、「確認方法」欄の方法で到達度を確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　半期　　… 12_個人別チェックシートで自己評価と上長評価を突き合わせ、差異の原因を対話する。</t>
+          <t xml:space="preserve">　26_テーマ・タイトル標準リスト… テーマ8区分と標準タイトル、カリキュラムとの対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>4. 運用サイクル（推奨）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　年次　　… レベル判定を確定し、次年度の主担当・副担当テーマと育成計画を決定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>5. レベル判定の原則</t>
+          <t xml:space="preserve">　毎月　　… 上長と本人で30分の面談。当月の学習項目と習得目標の達成状況を確認し、翌月の重点を決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　四半期　… 成果物レビューを1件必ず実施し、「確認方法」欄の方法で到達度を確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　半期　　… 12_個人別チェックシートで自己評価と上長評価を突き合わせ、差異の原因を対話する。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　年次　　… レベル判定を確定し、次年度の主担当・副担当テーマと育成計画を決定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>5. レベル判定の原則</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　・「知っている」ではなく「できた実績があるか」で判定します。判定には必ず具体的な案件名・成果物名を紐づけてください。</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">　・1つの項目でL3と判定するには、原則として同種の作業を2案件以上、単独で完遂している必要があります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　・自己評価と上長評価に2段階以上の差がある場合は、必ず面談で認識を合わせてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>6. 更新について</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　・自己評価と上長評価に2段階以上の差がある場合は、必ず面談で認識を合わせてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>6. 更新について</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　・制度改正（基本指針、報酬改定、会計基準、各省ガイドライン等）が生じた場合は、該当テーマシートの学習内容を年1回見直してください。</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">　・計画の「期」（第○期）は年度の経過とともに進みます。テーマシートの記載は根拠法と期間の考え方を示すもので、具体の期・年度は都度確認してください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="43">
     <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A49:H49"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A45:H45"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A41:H41"/>
     <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
@@ -1306,15 +1413,18 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A42:H42"/>
     <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A47:H47"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A40:H40"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A43:H43"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A13:H13"/>
@@ -15106,15 +15216,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -15127,7 +15237,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>訪問当日中に記入する。温度感と次アクションが空欄の記録は、記録として成立していない。</t>
+          <t>上段がTeams管理用CSVの15列、下段が社内記録（CSVには出さない）。訪問当日中に記入する。1回の訪問で複数テーマを話した場合は、CSVはテーマごとに1行になるため、本シートも1テーマ1枚とする。</t>
         </is>
       </c>
     </row>
@@ -15139,375 +15249,4811 @@
       </c>
       <c r="B4" s="60" t="inlineStr">
         <is>
+          <t>CSV
+列</t>
+        </is>
+      </c>
+      <c r="C4" s="60" t="inlineStr">
+        <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C4" s="60" t="inlineStr">
+      <c r="D4" s="60" t="inlineStr">
         <is>
           <t>記入の仕方・記入例</t>
         </is>
       </c>
-      <c r="D4" s="60" t="inlineStr">
+      <c r="E4" s="60" t="inlineStr">
         <is>
           <t>記入欄</t>
         </is>
       </c>
-      <c r="E4" s="15" t="n"/>
       <c r="F4" s="16" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="44" t="inlineStr">
         <is>
-          <t>基本情報</t>
-        </is>
-      </c>
-      <c r="B5" s="47" t="inlineStr">
-        <is>
-          <t>訪問日／時間</t>
-        </is>
-      </c>
-      <c r="C5" s="66" t="inlineStr">
-        <is>
-          <t>例：R◯.◯.◯（◯）14:00〜14:30</t>
-        </is>
-      </c>
-      <c r="D5" s="67" t="n"/>
-      <c r="E5" s="48" t="n"/>
+          <t>CSV出力項目</t>
+        </is>
+      </c>
+      <c r="B5" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="47" t="inlineStr">
+        <is>
+          <t>入力者</t>
+        </is>
+      </c>
+      <c r="D5" s="66" t="inlineStr">
+        <is>
+          <t>姓のみ。敬称なし　例：相澤</t>
+        </is>
+      </c>
+      <c r="E5" s="67" t="n"/>
       <c r="F5" s="48" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="68" t="n"/>
-      <c r="B6" s="47" t="inlineStr">
-        <is>
-          <t>訪問先（団体名・部課名）</t>
-        </is>
-      </c>
-      <c r="C6" s="66" t="inlineStr">
-        <is>
-          <t>例：◯◯市 福祉部 高齢福祉課</t>
-        </is>
-      </c>
-      <c r="D6" s="67" t="n"/>
-      <c r="E6" s="48" t="n"/>
+      <c r="B6" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>訪問日</t>
+        </is>
+      </c>
+      <c r="D6" s="66" t="inlineStr">
+        <is>
+          <t>yyyy/mm/dd　例：2026/08/19　※不在でも必ず記入</t>
+        </is>
+      </c>
+      <c r="E6" s="67" t="n"/>
       <c r="F6" s="48" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="68" t="n"/>
-      <c r="B7" s="47" t="inlineStr">
-        <is>
-          <t>面談者（氏名・役職）</t>
-        </is>
-      </c>
-      <c r="C7" s="66" t="inlineStr">
-        <is>
-          <t>同席者も全員記載する</t>
-        </is>
-      </c>
-      <c r="D7" s="67" t="n"/>
-      <c r="E7" s="48" t="n"/>
+      <c r="B7" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="D7" s="66" t="inlineStr">
+        <is>
+          <t>都道府県名を選択</t>
+        </is>
+      </c>
+      <c r="E7" s="67" t="n"/>
       <c r="F7" s="48" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="68" t="n"/>
-      <c r="B8" s="47" t="inlineStr">
+      <c r="B8" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>団体名</t>
+        </is>
+      </c>
+      <c r="D8" s="66" t="inlineStr">
+        <is>
+          <t>正式名称　例：二戸地区広域行政事務組合　※「市役所」と書かない</t>
+        </is>
+      </c>
+      <c r="E8" s="67" t="n"/>
+      <c r="F8" s="48" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="68" t="n"/>
+      <c r="B9" s="61" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="47" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="D9" s="66" t="inlineStr">
+        <is>
+          <t>8区分から選択　※シート26で中身との対応を確認</t>
+        </is>
+      </c>
+      <c r="E9" s="67" t="n"/>
+      <c r="F9" s="48" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="68" t="n"/>
+      <c r="B10" s="61" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="D10" s="66" t="inlineStr">
+        <is>
+          <t>標準タイトルから選択（シート26）　例：財務書類作成</t>
+        </is>
+      </c>
+      <c r="E10" s="67" t="n"/>
+      <c r="F10" s="48" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="68" t="n"/>
+      <c r="B11" s="61" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="D11" s="66" t="inlineStr">
+        <is>
+          <t>「課名　役職　氏名」を1行。複数は「／」区切り　※改行禁止</t>
+        </is>
+      </c>
+      <c r="E11" s="67" t="n"/>
+      <c r="F11" s="48" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="68" t="n"/>
+      <c r="B12" s="61" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="47" t="inlineStr">
+        <is>
+          <t>前回策定</t>
+        </is>
+      </c>
+      <c r="D12" s="66" t="inlineStr">
+        <is>
+          <t>委託／自前　※不明なら次回必ず確認する</t>
+        </is>
+      </c>
+      <c r="E12" s="67" t="n"/>
+      <c r="F12" s="48" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="68" t="n"/>
+      <c r="B13" s="61" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="47" t="inlineStr">
+        <is>
+          <t>改定時期</t>
+        </is>
+      </c>
+      <c r="D13" s="66" t="inlineStr">
+        <is>
+          <t>R＋数字（単年）　例：R9　※幅がある場合は最も早い年度</t>
+        </is>
+      </c>
+      <c r="E13" s="67" t="n"/>
+      <c r="F13" s="48" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="68" t="n"/>
+      <c r="B14" s="61" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="47" t="inlineStr">
+        <is>
+          <t>アプローチ時期</t>
+        </is>
+      </c>
+      <c r="D14" s="66" t="inlineStr">
+        <is>
+          <t>今年度／来年度／再来年度　※改定年度の前年度が原則</t>
+        </is>
+      </c>
+      <c r="E14" s="67" t="n"/>
+      <c r="F14" s="48" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="68" t="n"/>
+      <c r="B15" s="61" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" s="47" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="D15" s="66" t="inlineStr">
+        <is>
+          <t>初回訪問／セカンドアプローチ／見積提示／見積＋仕様書</t>
+        </is>
+      </c>
+      <c r="E15" s="67" t="n"/>
+      <c r="F15" s="48" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="68" t="n"/>
+      <c r="B16" s="61" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="47" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="D16" s="66" t="inlineStr">
+        <is>
+          <t>見積提示／自力／他社随契／不在／その他　※「その他」は備考に理由を書く</t>
+        </is>
+      </c>
+      <c r="E16" s="67" t="n"/>
+      <c r="F16" s="48" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="68" t="n"/>
+      <c r="B17" s="61" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" s="47" t="inlineStr">
+        <is>
+          <t>次回アクション</t>
+        </is>
+      </c>
+      <c r="D17" s="66" t="inlineStr">
+        <is>
+          <t>再アプローチ／見積提示／同行依頼、再訪／再訪不要　※空欄にしない</t>
+        </is>
+      </c>
+      <c r="E17" s="67" t="n"/>
+      <c r="F17" s="48" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="68" t="n"/>
+      <c r="B18" s="61" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" s="47" t="inlineStr">
+        <is>
+          <t>契約予定</t>
+        </is>
+      </c>
+      <c r="D18" s="66" t="inlineStr">
+        <is>
+          <t>入札／見積合わせ／随契／プロポ　※分かった時点で入れる</t>
+        </is>
+      </c>
+      <c r="E18" s="67" t="n"/>
+      <c r="F18" s="48" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="69" t="n"/>
+      <c r="B19" s="61" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" s="47" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="D19" s="66" t="inlineStr">
+        <is>
+          <t>［現況］＋［根拠・時期］＋［次の一手］を1行で。改行・インデント禁止（書き方はシート25下部）</t>
+        </is>
+      </c>
+      <c r="E19" s="67" t="n"/>
+      <c r="F19" s="48" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="70" t="inlineStr">
+        <is>
+          <t>社内記録（CSV対象外）</t>
+        </is>
+      </c>
+      <c r="B20" s="71" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C20" s="47" t="inlineStr">
         <is>
           <t>当社出席者／自分のレベル</t>
         </is>
       </c>
-      <c r="C8" s="66" t="inlineStr">
+      <c r="D20" s="66" t="inlineStr">
         <is>
           <t>例：△△（L2）、□□（L4・同行）</t>
         </is>
       </c>
-      <c r="D8" s="67" t="n"/>
-      <c r="E8" s="48" t="n"/>
-      <c r="F8" s="48" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="69" t="n"/>
-      <c r="B9" s="47" t="inlineStr">
-        <is>
-          <t>テーマ／対象計画</t>
-        </is>
-      </c>
-      <c r="C9" s="66" t="inlineStr">
-        <is>
-          <t>例：第◯期介護保険事業計画</t>
-        </is>
-      </c>
-      <c r="D9" s="67" t="n"/>
-      <c r="E9" s="48" t="n"/>
-      <c r="F9" s="48" t="n"/>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>準備</t>
-        </is>
-      </c>
-      <c r="B10" s="47" t="inlineStr">
+      <c r="E20" s="72" t="n"/>
+      <c r="F20" s="48" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="68" t="n"/>
+      <c r="B21" s="71" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C21" s="47" t="inlineStr">
         <is>
           <t>事前に確認したもの</t>
         </is>
       </c>
-      <c r="C10" s="66" t="inlineStr">
-        <is>
-          <t>現行計画／実績データ／議会議事録／県の資料／経営指標　など該当するものを列挙</t>
-        </is>
-      </c>
-      <c r="D10" s="67" t="n"/>
-      <c r="E10" s="48" t="n"/>
-      <c r="F10" s="48" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="69" t="n"/>
-      <c r="B11" s="47" t="inlineStr">
+      <c r="D21" s="66" t="inlineStr">
+        <is>
+          <t>現行計画／実績データ／議会議事録／県の資料／経営指標　など（シート19の準備チェックに対応）</t>
+        </is>
+      </c>
+      <c r="E21" s="72" t="n"/>
+      <c r="F21" s="48" t="n"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="68" t="n"/>
+      <c r="B22" s="71" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C22" s="47" t="inlineStr">
         <is>
           <t>本日の目的（訪問前に書く）</t>
         </is>
       </c>
-      <c r="C11" s="66" t="inlineStr">
+      <c r="D22" s="66" t="inlineStr">
         <is>
           <t>例：次期計画の検討状況を確認し、予算要求時期を特定する</t>
         </is>
       </c>
-      <c r="D11" s="67" t="n"/>
-      <c r="E11" s="48" t="n"/>
-      <c r="F11" s="48" t="n"/>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="44" t="inlineStr">
-        <is>
-          <t>面談内容</t>
-        </is>
-      </c>
-      <c r="B12" s="47" t="inlineStr">
+      <c r="E22" s="72" t="n"/>
+      <c r="F22" s="48" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="68" t="n"/>
+      <c r="B23" s="71" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C23" s="47" t="inlineStr">
         <is>
           <t>当社から伝えたこと</t>
         </is>
       </c>
-      <c r="C12" s="66" t="inlineStr">
+      <c r="D23" s="66" t="inlineStr">
         <is>
           <t>国の動向／事例／スケジュール逆算／財源　など実際に話した内容</t>
         </is>
       </c>
-      <c r="D12" s="67" t="n"/>
-      <c r="E12" s="48" t="n"/>
-      <c r="F12" s="48" t="n"/>
-    </row>
-    <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="68" t="n"/>
-      <c r="B13" s="47" t="inlineStr">
+      <c r="E23" s="72" t="n"/>
+      <c r="F23" s="48" t="n"/>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="68" t="n"/>
+      <c r="B24" s="71" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C24" s="47" t="inlineStr">
         <is>
           <t>ヒアリング結果（現状）</t>
         </is>
       </c>
-      <c r="C13" s="66" t="inlineStr">
-        <is>
-          <t>計画期間・前回の発注方式・受託先・調査の有無・体制・庁内の検討状況</t>
-        </is>
-      </c>
-      <c r="D13" s="67" t="n"/>
-      <c r="E13" s="48" t="n"/>
-      <c r="F13" s="48" t="n"/>
-    </row>
-    <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="68" t="n"/>
-      <c r="B14" s="47" t="inlineStr">
+      <c r="D24" s="66" t="inlineStr">
+        <is>
+          <t>シート20・21の質問に対する答え。相手の言葉のまま記録する（要約しすぎない）</t>
+        </is>
+      </c>
+      <c r="E24" s="72" t="n"/>
+      <c r="F24" s="48" t="n"/>
+    </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="68" t="n"/>
+      <c r="B25" s="71" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C25" s="47" t="inlineStr">
         <is>
           <t>ヒアリング結果（課題）</t>
         </is>
       </c>
-      <c r="C14" s="66" t="inlineStr">
-        <is>
-          <t>相手が語った困りごと。相手の言葉のまま記録する（要約しすぎない）</t>
-        </is>
-      </c>
-      <c r="D14" s="67" t="n"/>
-      <c r="E14" s="48" t="n"/>
-      <c r="F14" s="48" t="n"/>
-    </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="69" t="n"/>
-      <c r="B15" s="47" t="inlineStr">
+      <c r="D25" s="66" t="inlineStr">
+        <is>
+          <t>相手が語った困りごと。ここが次回の提案の核になる</t>
+        </is>
+      </c>
+      <c r="E25" s="72" t="n"/>
+      <c r="F25" s="48" t="n"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="68" t="n"/>
+      <c r="B26" s="71" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C26" s="47" t="inlineStr">
         <is>
           <t>ヒアリング結果（予算・発注）</t>
         </is>
       </c>
-      <c r="C15" s="66" t="inlineStr">
-        <is>
-          <t>予算化の見込み／枠感／発注時期／発注方式／決裁ルート／競合</t>
-        </is>
-      </c>
-      <c r="D15" s="67" t="n"/>
-      <c r="E15" s="48" t="n"/>
-      <c r="F15" s="48" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="44" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-      <c r="B16" s="47" t="inlineStr">
+      <c r="D26" s="66" t="inlineStr">
+        <is>
+          <t>予算化の見込み／枠感／決裁ルート／競合　※金額の枠感はCSVには書かない</t>
+        </is>
+      </c>
+      <c r="E26" s="72" t="n"/>
+      <c r="F26" s="48" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="68" t="n"/>
+      <c r="B27" s="71" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="inlineStr">
         <is>
           <t>温度感</t>
         </is>
       </c>
-      <c r="C16" s="66" t="inlineStr">
+      <c r="D27" s="66" t="inlineStr">
         <is>
           <t>A：今年度中に動く／B：次年度予算で検討／C：様子見／D：当面なし</t>
         </is>
       </c>
-      <c r="D16" s="70" t="n"/>
-      <c r="E16" s="48" t="n"/>
-      <c r="F16" s="48" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="69" t="n"/>
-      <c r="B17" s="47" t="inlineStr">
-        <is>
-          <t>受注確度と時期の見立て</t>
-        </is>
-      </c>
-      <c r="C17" s="66" t="inlineStr">
-        <is>
-          <t>例：B　R◯年度当初発注、プロポーザル想定、想定規模◯◯万円</t>
-        </is>
-      </c>
-      <c r="D17" s="67" t="n"/>
-      <c r="E17" s="48" t="n"/>
-      <c r="F17" s="48" t="n"/>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="44" t="inlineStr">
-        <is>
-          <t>宿題</t>
-        </is>
-      </c>
-      <c r="B18" s="47" t="inlineStr">
-        <is>
-          <t>当社→先方（内容・期限）</t>
-        </is>
-      </c>
-      <c r="C18" s="66" t="inlineStr">
+      <c r="E27" s="72" t="n"/>
+      <c r="F27" s="48" t="n"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="68" t="n"/>
+      <c r="B28" s="71" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C28" s="47" t="inlineStr">
+        <is>
+          <t>温度感の根拠</t>
+        </is>
+      </c>
+      <c r="D28" s="66" t="inlineStr">
+        <is>
+          <t>そう判断した具体的な発言・事実を書く</t>
+        </is>
+      </c>
+      <c r="E28" s="72" t="n"/>
+      <c r="F28" s="48" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="68" t="n"/>
+      <c r="B29" s="71" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C29" s="47" t="inlineStr">
+        <is>
+          <t>宿題　当社→先方（内容・期限）</t>
+        </is>
+      </c>
+      <c r="D29" s="66" t="inlineStr">
         <is>
           <t>例：◯◯交付金の今年度要綱の整理　◯月◯日まで</t>
         </is>
       </c>
-      <c r="D18" s="67" t="n"/>
-      <c r="E18" s="48" t="n"/>
-      <c r="F18" s="48" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="69" t="n"/>
-      <c r="B19" s="47" t="inlineStr">
-        <is>
-          <t>先方→当社（内容・期限）</t>
-        </is>
-      </c>
-      <c r="C19" s="66" t="inlineStr">
+      <c r="E29" s="72" t="n"/>
+      <c r="F29" s="48" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="68" t="n"/>
+      <c r="B30" s="71" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C30" s="47" t="inlineStr">
+        <is>
+          <t>宿題　先方→当社（内容・期限）</t>
+        </is>
+      </c>
+      <c r="D30" s="66" t="inlineStr">
         <is>
           <t>例：庁内での検討結果の連絡　◯月中</t>
         </is>
       </c>
-      <c r="D19" s="67" t="n"/>
-      <c r="E19" s="48" t="n"/>
-      <c r="F19" s="48" t="n"/>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="44" t="inlineStr">
-        <is>
-          <t>次アクション</t>
-        </is>
-      </c>
-      <c r="B20" s="47" t="inlineStr">
-        <is>
-          <t>次にやること／次回訪問予定</t>
-        </is>
-      </c>
-      <c r="C20" s="66" t="inlineStr">
-        <is>
-          <t>「誰が・いつまでに・何を」を具体的に書く</t>
-        </is>
-      </c>
-      <c r="D20" s="67" t="n"/>
-      <c r="E20" s="48" t="n"/>
-      <c r="F20" s="48" t="n"/>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="44" t="inlineStr">
-        <is>
-          <t>振り返り</t>
-        </is>
-      </c>
-      <c r="B21" s="47" t="inlineStr">
-        <is>
-          <t>うまくいった点／課題</t>
-        </is>
-      </c>
-      <c r="C21" s="66" t="inlineStr">
-        <is>
-          <t>自分の話し方・質問の順序・準備の過不足を1つずつ書く</t>
-        </is>
-      </c>
-      <c r="D21" s="67" t="n"/>
-      <c r="E21" s="48" t="n"/>
-      <c r="F21" s="48" t="n"/>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="69" t="n"/>
-      <c r="B22" s="47" t="inlineStr">
+      <c r="E30" s="72" t="n"/>
+      <c r="F30" s="48" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="68" t="n"/>
+      <c r="B31" s="71" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C31" s="47" t="inlineStr">
+        <is>
+          <t>振り返り（うまくいった点／課題）</t>
+        </is>
+      </c>
+      <c r="D31" s="66" t="inlineStr">
+        <is>
+          <t>自分の話し方・質問の順序・準備の過不足を1つずつ</t>
+        </is>
+      </c>
+      <c r="E31" s="72" t="n"/>
+      <c r="F31" s="48" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="69" t="n"/>
+      <c r="B32" s="71" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C32" s="47" t="inlineStr">
         <is>
           <t>上長コメント</t>
         </is>
       </c>
-      <c r="C22" s="66" t="inlineStr">
+      <c r="D32" s="66" t="inlineStr">
         <is>
           <t>（上長が記入）</t>
         </is>
       </c>
-      <c r="D22" s="67" t="n"/>
-      <c r="E22" s="48" t="n"/>
-      <c r="F22" s="48" t="n"/>
+      <c r="E32" s="72" t="n"/>
+      <c r="F32" s="48" t="n"/>
+    </row>
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" s="50" t="inlineStr">
+        <is>
+          <t>【CSVへの転記】上段15項目を、シート24「訪問記録CSV_入力シート」の1行にCSV列番号の順（入力者→訪問日→エリア→団体名→テーマ→結果→次回アクション→前回策定→担当者→改定時期→アプローチ時期→状態→契約予定→備考→タイトル）で貼り付ける。本シートは列番号を並べ替えて記入しやすくしてあるため、転記時は「CSV列」欄の番号で照合すること。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="A5:A9"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D16:F16"/>
+  <mergeCells count="34">
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E8:F8"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A20:A32"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A5:A19"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="D16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"A：今年度中に動く,B：次年度予算で検討,C：様子見,D：当面なし"</formula1>
+  <dataValidations count="10">
+    <dataValidation sqref="E7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$A$2:$A$48</formula1>
+    </dataValidation>
+    <dataValidation sqref="E9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$B$2:$B$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$E$2:$E$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$F$2:$F$16</formula1>
+    </dataValidation>
+    <dataValidation sqref="E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$G$2:$G$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="E15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$H$2:$H$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$C$2:$C$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="E17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$D$2:$D$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="E18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$I$2:$I$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="E27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$J$2:$J$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
+  <pageSetup orientation="portrait" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="64" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>入力者</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>訪問日</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>団体名</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>次回アクション</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>前回策定</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>改定時期</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>アプローチ時期</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>契約予定</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="73" t="n"/>
+      <c r="B2" s="73" t="n"/>
+      <c r="C2" s="73" t="n"/>
+      <c r="D2" s="73" t="n"/>
+      <c r="E2" s="73" t="n"/>
+      <c r="F2" s="73" t="n"/>
+      <c r="G2" s="73" t="n"/>
+      <c r="H2" s="73" t="n"/>
+      <c r="I2" s="73" t="n"/>
+      <c r="J2" s="73" t="n"/>
+      <c r="K2" s="73" t="n"/>
+      <c r="L2" s="73" t="n"/>
+      <c r="M2" s="73" t="n"/>
+      <c r="N2" s="74" t="n"/>
+      <c r="O2" s="73" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="73" t="n"/>
+      <c r="B3" s="73" t="n"/>
+      <c r="C3" s="73" t="n"/>
+      <c r="D3" s="73" t="n"/>
+      <c r="E3" s="73" t="n"/>
+      <c r="F3" s="73" t="n"/>
+      <c r="G3" s="73" t="n"/>
+      <c r="H3" s="73" t="n"/>
+      <c r="I3" s="73" t="n"/>
+      <c r="J3" s="73" t="n"/>
+      <c r="K3" s="73" t="n"/>
+      <c r="L3" s="73" t="n"/>
+      <c r="M3" s="73" t="n"/>
+      <c r="N3" s="74" t="n"/>
+      <c r="O3" s="73" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="73" t="n"/>
+      <c r="B4" s="73" t="n"/>
+      <c r="C4" s="73" t="n"/>
+      <c r="D4" s="73" t="n"/>
+      <c r="E4" s="73" t="n"/>
+      <c r="F4" s="73" t="n"/>
+      <c r="G4" s="73" t="n"/>
+      <c r="H4" s="73" t="n"/>
+      <c r="I4" s="73" t="n"/>
+      <c r="J4" s="73" t="n"/>
+      <c r="K4" s="73" t="n"/>
+      <c r="L4" s="73" t="n"/>
+      <c r="M4" s="73" t="n"/>
+      <c r="N4" s="74" t="n"/>
+      <c r="O4" s="73" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="73" t="n"/>
+      <c r="B5" s="73" t="n"/>
+      <c r="C5" s="73" t="n"/>
+      <c r="D5" s="73" t="n"/>
+      <c r="E5" s="73" t="n"/>
+      <c r="F5" s="73" t="n"/>
+      <c r="G5" s="73" t="n"/>
+      <c r="H5" s="73" t="n"/>
+      <c r="I5" s="73" t="n"/>
+      <c r="J5" s="73" t="n"/>
+      <c r="K5" s="73" t="n"/>
+      <c r="L5" s="73" t="n"/>
+      <c r="M5" s="73" t="n"/>
+      <c r="N5" s="74" t="n"/>
+      <c r="O5" s="73" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="73" t="n"/>
+      <c r="B6" s="73" t="n"/>
+      <c r="C6" s="73" t="n"/>
+      <c r="D6" s="73" t="n"/>
+      <c r="E6" s="73" t="n"/>
+      <c r="F6" s="73" t="n"/>
+      <c r="G6" s="73" t="n"/>
+      <c r="H6" s="73" t="n"/>
+      <c r="I6" s="73" t="n"/>
+      <c r="J6" s="73" t="n"/>
+      <c r="K6" s="73" t="n"/>
+      <c r="L6" s="73" t="n"/>
+      <c r="M6" s="73" t="n"/>
+      <c r="N6" s="74" t="n"/>
+      <c r="O6" s="73" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="73" t="n"/>
+      <c r="B7" s="73" t="n"/>
+      <c r="C7" s="73" t="n"/>
+      <c r="D7" s="73" t="n"/>
+      <c r="E7" s="73" t="n"/>
+      <c r="F7" s="73" t="n"/>
+      <c r="G7" s="73" t="n"/>
+      <c r="H7" s="73" t="n"/>
+      <c r="I7" s="73" t="n"/>
+      <c r="J7" s="73" t="n"/>
+      <c r="K7" s="73" t="n"/>
+      <c r="L7" s="73" t="n"/>
+      <c r="M7" s="73" t="n"/>
+      <c r="N7" s="74" t="n"/>
+      <c r="O7" s="73" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="73" t="n"/>
+      <c r="B8" s="73" t="n"/>
+      <c r="C8" s="73" t="n"/>
+      <c r="D8" s="73" t="n"/>
+      <c r="E8" s="73" t="n"/>
+      <c r="F8" s="73" t="n"/>
+      <c r="G8" s="73" t="n"/>
+      <c r="H8" s="73" t="n"/>
+      <c r="I8" s="73" t="n"/>
+      <c r="J8" s="73" t="n"/>
+      <c r="K8" s="73" t="n"/>
+      <c r="L8" s="73" t="n"/>
+      <c r="M8" s="73" t="n"/>
+      <c r="N8" s="74" t="n"/>
+      <c r="O8" s="73" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="73" t="n"/>
+      <c r="B9" s="73" t="n"/>
+      <c r="C9" s="73" t="n"/>
+      <c r="D9" s="73" t="n"/>
+      <c r="E9" s="73" t="n"/>
+      <c r="F9" s="73" t="n"/>
+      <c r="G9" s="73" t="n"/>
+      <c r="H9" s="73" t="n"/>
+      <c r="I9" s="73" t="n"/>
+      <c r="J9" s="73" t="n"/>
+      <c r="K9" s="73" t="n"/>
+      <c r="L9" s="73" t="n"/>
+      <c r="M9" s="73" t="n"/>
+      <c r="N9" s="74" t="n"/>
+      <c r="O9" s="73" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="73" t="n"/>
+      <c r="B10" s="73" t="n"/>
+      <c r="C10" s="73" t="n"/>
+      <c r="D10" s="73" t="n"/>
+      <c r="E10" s="73" t="n"/>
+      <c r="F10" s="73" t="n"/>
+      <c r="G10" s="73" t="n"/>
+      <c r="H10" s="73" t="n"/>
+      <c r="I10" s="73" t="n"/>
+      <c r="J10" s="73" t="n"/>
+      <c r="K10" s="73" t="n"/>
+      <c r="L10" s="73" t="n"/>
+      <c r="M10" s="73" t="n"/>
+      <c r="N10" s="74" t="n"/>
+      <c r="O10" s="73" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="73" t="n"/>
+      <c r="B11" s="73" t="n"/>
+      <c r="C11" s="73" t="n"/>
+      <c r="D11" s="73" t="n"/>
+      <c r="E11" s="73" t="n"/>
+      <c r="F11" s="73" t="n"/>
+      <c r="G11" s="73" t="n"/>
+      <c r="H11" s="73" t="n"/>
+      <c r="I11" s="73" t="n"/>
+      <c r="J11" s="73" t="n"/>
+      <c r="K11" s="73" t="n"/>
+      <c r="L11" s="73" t="n"/>
+      <c r="M11" s="73" t="n"/>
+      <c r="N11" s="74" t="n"/>
+      <c r="O11" s="73" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="73" t="n"/>
+      <c r="B12" s="73" t="n"/>
+      <c r="C12" s="73" t="n"/>
+      <c r="D12" s="73" t="n"/>
+      <c r="E12" s="73" t="n"/>
+      <c r="F12" s="73" t="n"/>
+      <c r="G12" s="73" t="n"/>
+      <c r="H12" s="73" t="n"/>
+      <c r="I12" s="73" t="n"/>
+      <c r="J12" s="73" t="n"/>
+      <c r="K12" s="73" t="n"/>
+      <c r="L12" s="73" t="n"/>
+      <c r="M12" s="73" t="n"/>
+      <c r="N12" s="74" t="n"/>
+      <c r="O12" s="73" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="73" t="n"/>
+      <c r="B13" s="73" t="n"/>
+      <c r="C13" s="73" t="n"/>
+      <c r="D13" s="73" t="n"/>
+      <c r="E13" s="73" t="n"/>
+      <c r="F13" s="73" t="n"/>
+      <c r="G13" s="73" t="n"/>
+      <c r="H13" s="73" t="n"/>
+      <c r="I13" s="73" t="n"/>
+      <c r="J13" s="73" t="n"/>
+      <c r="K13" s="73" t="n"/>
+      <c r="L13" s="73" t="n"/>
+      <c r="M13" s="73" t="n"/>
+      <c r="N13" s="74" t="n"/>
+      <c r="O13" s="73" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="73" t="n"/>
+      <c r="B14" s="73" t="n"/>
+      <c r="C14" s="73" t="n"/>
+      <c r="D14" s="73" t="n"/>
+      <c r="E14" s="73" t="n"/>
+      <c r="F14" s="73" t="n"/>
+      <c r="G14" s="73" t="n"/>
+      <c r="H14" s="73" t="n"/>
+      <c r="I14" s="73" t="n"/>
+      <c r="J14" s="73" t="n"/>
+      <c r="K14" s="73" t="n"/>
+      <c r="L14" s="73" t="n"/>
+      <c r="M14" s="73" t="n"/>
+      <c r="N14" s="74" t="n"/>
+      <c r="O14" s="73" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="73" t="n"/>
+      <c r="B15" s="73" t="n"/>
+      <c r="C15" s="73" t="n"/>
+      <c r="D15" s="73" t="n"/>
+      <c r="E15" s="73" t="n"/>
+      <c r="F15" s="73" t="n"/>
+      <c r="G15" s="73" t="n"/>
+      <c r="H15" s="73" t="n"/>
+      <c r="I15" s="73" t="n"/>
+      <c r="J15" s="73" t="n"/>
+      <c r="K15" s="73" t="n"/>
+      <c r="L15" s="73" t="n"/>
+      <c r="M15" s="73" t="n"/>
+      <c r="N15" s="74" t="n"/>
+      <c r="O15" s="73" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="73" t="n"/>
+      <c r="B16" s="73" t="n"/>
+      <c r="C16" s="73" t="n"/>
+      <c r="D16" s="73" t="n"/>
+      <c r="E16" s="73" t="n"/>
+      <c r="F16" s="73" t="n"/>
+      <c r="G16" s="73" t="n"/>
+      <c r="H16" s="73" t="n"/>
+      <c r="I16" s="73" t="n"/>
+      <c r="J16" s="73" t="n"/>
+      <c r="K16" s="73" t="n"/>
+      <c r="L16" s="73" t="n"/>
+      <c r="M16" s="73" t="n"/>
+      <c r="N16" s="74" t="n"/>
+      <c r="O16" s="73" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="73" t="n"/>
+      <c r="B17" s="73" t="n"/>
+      <c r="C17" s="73" t="n"/>
+      <c r="D17" s="73" t="n"/>
+      <c r="E17" s="73" t="n"/>
+      <c r="F17" s="73" t="n"/>
+      <c r="G17" s="73" t="n"/>
+      <c r="H17" s="73" t="n"/>
+      <c r="I17" s="73" t="n"/>
+      <c r="J17" s="73" t="n"/>
+      <c r="K17" s="73" t="n"/>
+      <c r="L17" s="73" t="n"/>
+      <c r="M17" s="73" t="n"/>
+      <c r="N17" s="74" t="n"/>
+      <c r="O17" s="73" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="73" t="n"/>
+      <c r="B18" s="73" t="n"/>
+      <c r="C18" s="73" t="n"/>
+      <c r="D18" s="73" t="n"/>
+      <c r="E18" s="73" t="n"/>
+      <c r="F18" s="73" t="n"/>
+      <c r="G18" s="73" t="n"/>
+      <c r="H18" s="73" t="n"/>
+      <c r="I18" s="73" t="n"/>
+      <c r="J18" s="73" t="n"/>
+      <c r="K18" s="73" t="n"/>
+      <c r="L18" s="73" t="n"/>
+      <c r="M18" s="73" t="n"/>
+      <c r="N18" s="74" t="n"/>
+      <c r="O18" s="73" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="73" t="n"/>
+      <c r="B19" s="73" t="n"/>
+      <c r="C19" s="73" t="n"/>
+      <c r="D19" s="73" t="n"/>
+      <c r="E19" s="73" t="n"/>
+      <c r="F19" s="73" t="n"/>
+      <c r="G19" s="73" t="n"/>
+      <c r="H19" s="73" t="n"/>
+      <c r="I19" s="73" t="n"/>
+      <c r="J19" s="73" t="n"/>
+      <c r="K19" s="73" t="n"/>
+      <c r="L19" s="73" t="n"/>
+      <c r="M19" s="73" t="n"/>
+      <c r="N19" s="74" t="n"/>
+      <c r="O19" s="73" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="73" t="n"/>
+      <c r="B20" s="73" t="n"/>
+      <c r="C20" s="73" t="n"/>
+      <c r="D20" s="73" t="n"/>
+      <c r="E20" s="73" t="n"/>
+      <c r="F20" s="73" t="n"/>
+      <c r="G20" s="73" t="n"/>
+      <c r="H20" s="73" t="n"/>
+      <c r="I20" s="73" t="n"/>
+      <c r="J20" s="73" t="n"/>
+      <c r="K20" s="73" t="n"/>
+      <c r="L20" s="73" t="n"/>
+      <c r="M20" s="73" t="n"/>
+      <c r="N20" s="74" t="n"/>
+      <c r="O20" s="73" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="73" t="n"/>
+      <c r="B21" s="73" t="n"/>
+      <c r="C21" s="73" t="n"/>
+      <c r="D21" s="73" t="n"/>
+      <c r="E21" s="73" t="n"/>
+      <c r="F21" s="73" t="n"/>
+      <c r="G21" s="73" t="n"/>
+      <c r="H21" s="73" t="n"/>
+      <c r="I21" s="73" t="n"/>
+      <c r="J21" s="73" t="n"/>
+      <c r="K21" s="73" t="n"/>
+      <c r="L21" s="73" t="n"/>
+      <c r="M21" s="73" t="n"/>
+      <c r="N21" s="74" t="n"/>
+      <c r="O21" s="73" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="73" t="n"/>
+      <c r="B22" s="73" t="n"/>
+      <c r="C22" s="73" t="n"/>
+      <c r="D22" s="73" t="n"/>
+      <c r="E22" s="73" t="n"/>
+      <c r="F22" s="73" t="n"/>
+      <c r="G22" s="73" t="n"/>
+      <c r="H22" s="73" t="n"/>
+      <c r="I22" s="73" t="n"/>
+      <c r="J22" s="73" t="n"/>
+      <c r="K22" s="73" t="n"/>
+      <c r="L22" s="73" t="n"/>
+      <c r="M22" s="73" t="n"/>
+      <c r="N22" s="74" t="n"/>
+      <c r="O22" s="73" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="73" t="n"/>
+      <c r="B23" s="73" t="n"/>
+      <c r="C23" s="73" t="n"/>
+      <c r="D23" s="73" t="n"/>
+      <c r="E23" s="73" t="n"/>
+      <c r="F23" s="73" t="n"/>
+      <c r="G23" s="73" t="n"/>
+      <c r="H23" s="73" t="n"/>
+      <c r="I23" s="73" t="n"/>
+      <c r="J23" s="73" t="n"/>
+      <c r="K23" s="73" t="n"/>
+      <c r="L23" s="73" t="n"/>
+      <c r="M23" s="73" t="n"/>
+      <c r="N23" s="74" t="n"/>
+      <c r="O23" s="73" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="73" t="n"/>
+      <c r="B24" s="73" t="n"/>
+      <c r="C24" s="73" t="n"/>
+      <c r="D24" s="73" t="n"/>
+      <c r="E24" s="73" t="n"/>
+      <c r="F24" s="73" t="n"/>
+      <c r="G24" s="73" t="n"/>
+      <c r="H24" s="73" t="n"/>
+      <c r="I24" s="73" t="n"/>
+      <c r="J24" s="73" t="n"/>
+      <c r="K24" s="73" t="n"/>
+      <c r="L24" s="73" t="n"/>
+      <c r="M24" s="73" t="n"/>
+      <c r="N24" s="74" t="n"/>
+      <c r="O24" s="73" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="73" t="n"/>
+      <c r="B25" s="73" t="n"/>
+      <c r="C25" s="73" t="n"/>
+      <c r="D25" s="73" t="n"/>
+      <c r="E25" s="73" t="n"/>
+      <c r="F25" s="73" t="n"/>
+      <c r="G25" s="73" t="n"/>
+      <c r="H25" s="73" t="n"/>
+      <c r="I25" s="73" t="n"/>
+      <c r="J25" s="73" t="n"/>
+      <c r="K25" s="73" t="n"/>
+      <c r="L25" s="73" t="n"/>
+      <c r="M25" s="73" t="n"/>
+      <c r="N25" s="74" t="n"/>
+      <c r="O25" s="73" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="73" t="n"/>
+      <c r="B26" s="73" t="n"/>
+      <c r="C26" s="73" t="n"/>
+      <c r="D26" s="73" t="n"/>
+      <c r="E26" s="73" t="n"/>
+      <c r="F26" s="73" t="n"/>
+      <c r="G26" s="73" t="n"/>
+      <c r="H26" s="73" t="n"/>
+      <c r="I26" s="73" t="n"/>
+      <c r="J26" s="73" t="n"/>
+      <c r="K26" s="73" t="n"/>
+      <c r="L26" s="73" t="n"/>
+      <c r="M26" s="73" t="n"/>
+      <c r="N26" s="74" t="n"/>
+      <c r="O26" s="73" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="73" t="n"/>
+      <c r="B27" s="73" t="n"/>
+      <c r="C27" s="73" t="n"/>
+      <c r="D27" s="73" t="n"/>
+      <c r="E27" s="73" t="n"/>
+      <c r="F27" s="73" t="n"/>
+      <c r="G27" s="73" t="n"/>
+      <c r="H27" s="73" t="n"/>
+      <c r="I27" s="73" t="n"/>
+      <c r="J27" s="73" t="n"/>
+      <c r="K27" s="73" t="n"/>
+      <c r="L27" s="73" t="n"/>
+      <c r="M27" s="73" t="n"/>
+      <c r="N27" s="74" t="n"/>
+      <c r="O27" s="73" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="73" t="n"/>
+      <c r="B28" s="73" t="n"/>
+      <c r="C28" s="73" t="n"/>
+      <c r="D28" s="73" t="n"/>
+      <c r="E28" s="73" t="n"/>
+      <c r="F28" s="73" t="n"/>
+      <c r="G28" s="73" t="n"/>
+      <c r="H28" s="73" t="n"/>
+      <c r="I28" s="73" t="n"/>
+      <c r="J28" s="73" t="n"/>
+      <c r="K28" s="73" t="n"/>
+      <c r="L28" s="73" t="n"/>
+      <c r="M28" s="73" t="n"/>
+      <c r="N28" s="74" t="n"/>
+      <c r="O28" s="73" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="73" t="n"/>
+      <c r="B29" s="73" t="n"/>
+      <c r="C29" s="73" t="n"/>
+      <c r="D29" s="73" t="n"/>
+      <c r="E29" s="73" t="n"/>
+      <c r="F29" s="73" t="n"/>
+      <c r="G29" s="73" t="n"/>
+      <c r="H29" s="73" t="n"/>
+      <c r="I29" s="73" t="n"/>
+      <c r="J29" s="73" t="n"/>
+      <c r="K29" s="73" t="n"/>
+      <c r="L29" s="73" t="n"/>
+      <c r="M29" s="73" t="n"/>
+      <c r="N29" s="74" t="n"/>
+      <c r="O29" s="73" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="73" t="n"/>
+      <c r="B30" s="73" t="n"/>
+      <c r="C30" s="73" t="n"/>
+      <c r="D30" s="73" t="n"/>
+      <c r="E30" s="73" t="n"/>
+      <c r="F30" s="73" t="n"/>
+      <c r="G30" s="73" t="n"/>
+      <c r="H30" s="73" t="n"/>
+      <c r="I30" s="73" t="n"/>
+      <c r="J30" s="73" t="n"/>
+      <c r="K30" s="73" t="n"/>
+      <c r="L30" s="73" t="n"/>
+      <c r="M30" s="73" t="n"/>
+      <c r="N30" s="74" t="n"/>
+      <c r="O30" s="73" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="73" t="n"/>
+      <c r="B31" s="73" t="n"/>
+      <c r="C31" s="73" t="n"/>
+      <c r="D31" s="73" t="n"/>
+      <c r="E31" s="73" t="n"/>
+      <c r="F31" s="73" t="n"/>
+      <c r="G31" s="73" t="n"/>
+      <c r="H31" s="73" t="n"/>
+      <c r="I31" s="73" t="n"/>
+      <c r="J31" s="73" t="n"/>
+      <c r="K31" s="73" t="n"/>
+      <c r="L31" s="73" t="n"/>
+      <c r="M31" s="73" t="n"/>
+      <c r="N31" s="74" t="n"/>
+      <c r="O31" s="73" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="73" t="n"/>
+      <c r="B32" s="73" t="n"/>
+      <c r="C32" s="73" t="n"/>
+      <c r="D32" s="73" t="n"/>
+      <c r="E32" s="73" t="n"/>
+      <c r="F32" s="73" t="n"/>
+      <c r="G32" s="73" t="n"/>
+      <c r="H32" s="73" t="n"/>
+      <c r="I32" s="73" t="n"/>
+      <c r="J32" s="73" t="n"/>
+      <c r="K32" s="73" t="n"/>
+      <c r="L32" s="73" t="n"/>
+      <c r="M32" s="73" t="n"/>
+      <c r="N32" s="74" t="n"/>
+      <c r="O32" s="73" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="73" t="n"/>
+      <c r="B33" s="73" t="n"/>
+      <c r="C33" s="73" t="n"/>
+      <c r="D33" s="73" t="n"/>
+      <c r="E33" s="73" t="n"/>
+      <c r="F33" s="73" t="n"/>
+      <c r="G33" s="73" t="n"/>
+      <c r="H33" s="73" t="n"/>
+      <c r="I33" s="73" t="n"/>
+      <c r="J33" s="73" t="n"/>
+      <c r="K33" s="73" t="n"/>
+      <c r="L33" s="73" t="n"/>
+      <c r="M33" s="73" t="n"/>
+      <c r="N33" s="74" t="n"/>
+      <c r="O33" s="73" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="73" t="n"/>
+      <c r="B34" s="73" t="n"/>
+      <c r="C34" s="73" t="n"/>
+      <c r="D34" s="73" t="n"/>
+      <c r="E34" s="73" t="n"/>
+      <c r="F34" s="73" t="n"/>
+      <c r="G34" s="73" t="n"/>
+      <c r="H34" s="73" t="n"/>
+      <c r="I34" s="73" t="n"/>
+      <c r="J34" s="73" t="n"/>
+      <c r="K34" s="73" t="n"/>
+      <c r="L34" s="73" t="n"/>
+      <c r="M34" s="73" t="n"/>
+      <c r="N34" s="74" t="n"/>
+      <c r="O34" s="73" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="73" t="n"/>
+      <c r="B35" s="73" t="n"/>
+      <c r="C35" s="73" t="n"/>
+      <c r="D35" s="73" t="n"/>
+      <c r="E35" s="73" t="n"/>
+      <c r="F35" s="73" t="n"/>
+      <c r="G35" s="73" t="n"/>
+      <c r="H35" s="73" t="n"/>
+      <c r="I35" s="73" t="n"/>
+      <c r="J35" s="73" t="n"/>
+      <c r="K35" s="73" t="n"/>
+      <c r="L35" s="73" t="n"/>
+      <c r="M35" s="73" t="n"/>
+      <c r="N35" s="74" t="n"/>
+      <c r="O35" s="73" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="73" t="n"/>
+      <c r="B36" s="73" t="n"/>
+      <c r="C36" s="73" t="n"/>
+      <c r="D36" s="73" t="n"/>
+      <c r="E36" s="73" t="n"/>
+      <c r="F36" s="73" t="n"/>
+      <c r="G36" s="73" t="n"/>
+      <c r="H36" s="73" t="n"/>
+      <c r="I36" s="73" t="n"/>
+      <c r="J36" s="73" t="n"/>
+      <c r="K36" s="73" t="n"/>
+      <c r="L36" s="73" t="n"/>
+      <c r="M36" s="73" t="n"/>
+      <c r="N36" s="74" t="n"/>
+      <c r="O36" s="73" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="73" t="n"/>
+      <c r="B37" s="73" t="n"/>
+      <c r="C37" s="73" t="n"/>
+      <c r="D37" s="73" t="n"/>
+      <c r="E37" s="73" t="n"/>
+      <c r="F37" s="73" t="n"/>
+      <c r="G37" s="73" t="n"/>
+      <c r="H37" s="73" t="n"/>
+      <c r="I37" s="73" t="n"/>
+      <c r="J37" s="73" t="n"/>
+      <c r="K37" s="73" t="n"/>
+      <c r="L37" s="73" t="n"/>
+      <c r="M37" s="73" t="n"/>
+      <c r="N37" s="74" t="n"/>
+      <c r="O37" s="73" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="73" t="n"/>
+      <c r="B38" s="73" t="n"/>
+      <c r="C38" s="73" t="n"/>
+      <c r="D38" s="73" t="n"/>
+      <c r="E38" s="73" t="n"/>
+      <c r="F38" s="73" t="n"/>
+      <c r="G38" s="73" t="n"/>
+      <c r="H38" s="73" t="n"/>
+      <c r="I38" s="73" t="n"/>
+      <c r="J38" s="73" t="n"/>
+      <c r="K38" s="73" t="n"/>
+      <c r="L38" s="73" t="n"/>
+      <c r="M38" s="73" t="n"/>
+      <c r="N38" s="74" t="n"/>
+      <c r="O38" s="73" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="73" t="n"/>
+      <c r="B39" s="73" t="n"/>
+      <c r="C39" s="73" t="n"/>
+      <c r="D39" s="73" t="n"/>
+      <c r="E39" s="73" t="n"/>
+      <c r="F39" s="73" t="n"/>
+      <c r="G39" s="73" t="n"/>
+      <c r="H39" s="73" t="n"/>
+      <c r="I39" s="73" t="n"/>
+      <c r="J39" s="73" t="n"/>
+      <c r="K39" s="73" t="n"/>
+      <c r="L39" s="73" t="n"/>
+      <c r="M39" s="73" t="n"/>
+      <c r="N39" s="74" t="n"/>
+      <c r="O39" s="73" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="73" t="n"/>
+      <c r="B40" s="73" t="n"/>
+      <c r="C40" s="73" t="n"/>
+      <c r="D40" s="73" t="n"/>
+      <c r="E40" s="73" t="n"/>
+      <c r="F40" s="73" t="n"/>
+      <c r="G40" s="73" t="n"/>
+      <c r="H40" s="73" t="n"/>
+      <c r="I40" s="73" t="n"/>
+      <c r="J40" s="73" t="n"/>
+      <c r="K40" s="73" t="n"/>
+      <c r="L40" s="73" t="n"/>
+      <c r="M40" s="73" t="n"/>
+      <c r="N40" s="74" t="n"/>
+      <c r="O40" s="73" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="73" t="n"/>
+      <c r="B41" s="73" t="n"/>
+      <c r="C41" s="73" t="n"/>
+      <c r="D41" s="73" t="n"/>
+      <c r="E41" s="73" t="n"/>
+      <c r="F41" s="73" t="n"/>
+      <c r="G41" s="73" t="n"/>
+      <c r="H41" s="73" t="n"/>
+      <c r="I41" s="73" t="n"/>
+      <c r="J41" s="73" t="n"/>
+      <c r="K41" s="73" t="n"/>
+      <c r="L41" s="73" t="n"/>
+      <c r="M41" s="73" t="n"/>
+      <c r="N41" s="74" t="n"/>
+      <c r="O41" s="73" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="73" t="n"/>
+      <c r="B42" s="73" t="n"/>
+      <c r="C42" s="73" t="n"/>
+      <c r="D42" s="73" t="n"/>
+      <c r="E42" s="73" t="n"/>
+      <c r="F42" s="73" t="n"/>
+      <c r="G42" s="73" t="n"/>
+      <c r="H42" s="73" t="n"/>
+      <c r="I42" s="73" t="n"/>
+      <c r="J42" s="73" t="n"/>
+      <c r="K42" s="73" t="n"/>
+      <c r="L42" s="73" t="n"/>
+      <c r="M42" s="73" t="n"/>
+      <c r="N42" s="74" t="n"/>
+      <c r="O42" s="73" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="73" t="n"/>
+      <c r="B43" s="73" t="n"/>
+      <c r="C43" s="73" t="n"/>
+      <c r="D43" s="73" t="n"/>
+      <c r="E43" s="73" t="n"/>
+      <c r="F43" s="73" t="n"/>
+      <c r="G43" s="73" t="n"/>
+      <c r="H43" s="73" t="n"/>
+      <c r="I43" s="73" t="n"/>
+      <c r="J43" s="73" t="n"/>
+      <c r="K43" s="73" t="n"/>
+      <c r="L43" s="73" t="n"/>
+      <c r="M43" s="73" t="n"/>
+      <c r="N43" s="74" t="n"/>
+      <c r="O43" s="73" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="73" t="n"/>
+      <c r="B44" s="73" t="n"/>
+      <c r="C44" s="73" t="n"/>
+      <c r="D44" s="73" t="n"/>
+      <c r="E44" s="73" t="n"/>
+      <c r="F44" s="73" t="n"/>
+      <c r="G44" s="73" t="n"/>
+      <c r="H44" s="73" t="n"/>
+      <c r="I44" s="73" t="n"/>
+      <c r="J44" s="73" t="n"/>
+      <c r="K44" s="73" t="n"/>
+      <c r="L44" s="73" t="n"/>
+      <c r="M44" s="73" t="n"/>
+      <c r="N44" s="74" t="n"/>
+      <c r="O44" s="73" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="73" t="n"/>
+      <c r="B45" s="73" t="n"/>
+      <c r="C45" s="73" t="n"/>
+      <c r="D45" s="73" t="n"/>
+      <c r="E45" s="73" t="n"/>
+      <c r="F45" s="73" t="n"/>
+      <c r="G45" s="73" t="n"/>
+      <c r="H45" s="73" t="n"/>
+      <c r="I45" s="73" t="n"/>
+      <c r="J45" s="73" t="n"/>
+      <c r="K45" s="73" t="n"/>
+      <c r="L45" s="73" t="n"/>
+      <c r="M45" s="73" t="n"/>
+      <c r="N45" s="74" t="n"/>
+      <c r="O45" s="73" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="73" t="n"/>
+      <c r="B46" s="73" t="n"/>
+      <c r="C46" s="73" t="n"/>
+      <c r="D46" s="73" t="n"/>
+      <c r="E46" s="73" t="n"/>
+      <c r="F46" s="73" t="n"/>
+      <c r="G46" s="73" t="n"/>
+      <c r="H46" s="73" t="n"/>
+      <c r="I46" s="73" t="n"/>
+      <c r="J46" s="73" t="n"/>
+      <c r="K46" s="73" t="n"/>
+      <c r="L46" s="73" t="n"/>
+      <c r="M46" s="73" t="n"/>
+      <c r="N46" s="74" t="n"/>
+      <c r="O46" s="73" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="73" t="n"/>
+      <c r="B47" s="73" t="n"/>
+      <c r="C47" s="73" t="n"/>
+      <c r="D47" s="73" t="n"/>
+      <c r="E47" s="73" t="n"/>
+      <c r="F47" s="73" t="n"/>
+      <c r="G47" s="73" t="n"/>
+      <c r="H47" s="73" t="n"/>
+      <c r="I47" s="73" t="n"/>
+      <c r="J47" s="73" t="n"/>
+      <c r="K47" s="73" t="n"/>
+      <c r="L47" s="73" t="n"/>
+      <c r="M47" s="73" t="n"/>
+      <c r="N47" s="74" t="n"/>
+      <c r="O47" s="73" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="73" t="n"/>
+      <c r="B48" s="73" t="n"/>
+      <c r="C48" s="73" t="n"/>
+      <c r="D48" s="73" t="n"/>
+      <c r="E48" s="73" t="n"/>
+      <c r="F48" s="73" t="n"/>
+      <c r="G48" s="73" t="n"/>
+      <c r="H48" s="73" t="n"/>
+      <c r="I48" s="73" t="n"/>
+      <c r="J48" s="73" t="n"/>
+      <c r="K48" s="73" t="n"/>
+      <c r="L48" s="73" t="n"/>
+      <c r="M48" s="73" t="n"/>
+      <c r="N48" s="74" t="n"/>
+      <c r="O48" s="73" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="73" t="n"/>
+      <c r="B49" s="73" t="n"/>
+      <c r="C49" s="73" t="n"/>
+      <c r="D49" s="73" t="n"/>
+      <c r="E49" s="73" t="n"/>
+      <c r="F49" s="73" t="n"/>
+      <c r="G49" s="73" t="n"/>
+      <c r="H49" s="73" t="n"/>
+      <c r="I49" s="73" t="n"/>
+      <c r="J49" s="73" t="n"/>
+      <c r="K49" s="73" t="n"/>
+      <c r="L49" s="73" t="n"/>
+      <c r="M49" s="73" t="n"/>
+      <c r="N49" s="74" t="n"/>
+      <c r="O49" s="73" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="73" t="n"/>
+      <c r="B50" s="73" t="n"/>
+      <c r="C50" s="73" t="n"/>
+      <c r="D50" s="73" t="n"/>
+      <c r="E50" s="73" t="n"/>
+      <c r="F50" s="73" t="n"/>
+      <c r="G50" s="73" t="n"/>
+      <c r="H50" s="73" t="n"/>
+      <c r="I50" s="73" t="n"/>
+      <c r="J50" s="73" t="n"/>
+      <c r="K50" s="73" t="n"/>
+      <c r="L50" s="73" t="n"/>
+      <c r="M50" s="73" t="n"/>
+      <c r="N50" s="74" t="n"/>
+      <c r="O50" s="73" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="73" t="n"/>
+      <c r="B51" s="73" t="n"/>
+      <c r="C51" s="73" t="n"/>
+      <c r="D51" s="73" t="n"/>
+      <c r="E51" s="73" t="n"/>
+      <c r="F51" s="73" t="n"/>
+      <c r="G51" s="73" t="n"/>
+      <c r="H51" s="73" t="n"/>
+      <c r="I51" s="73" t="n"/>
+      <c r="J51" s="73" t="n"/>
+      <c r="K51" s="73" t="n"/>
+      <c r="L51" s="73" t="n"/>
+      <c r="M51" s="73" t="n"/>
+      <c r="N51" s="74" t="n"/>
+      <c r="O51" s="73" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="73" t="n"/>
+      <c r="B52" s="73" t="n"/>
+      <c r="C52" s="73" t="n"/>
+      <c r="D52" s="73" t="n"/>
+      <c r="E52" s="73" t="n"/>
+      <c r="F52" s="73" t="n"/>
+      <c r="G52" s="73" t="n"/>
+      <c r="H52" s="73" t="n"/>
+      <c r="I52" s="73" t="n"/>
+      <c r="J52" s="73" t="n"/>
+      <c r="K52" s="73" t="n"/>
+      <c r="L52" s="73" t="n"/>
+      <c r="M52" s="73" t="n"/>
+      <c r="N52" s="74" t="n"/>
+      <c r="O52" s="73" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="73" t="n"/>
+      <c r="B53" s="73" t="n"/>
+      <c r="C53" s="73" t="n"/>
+      <c r="D53" s="73" t="n"/>
+      <c r="E53" s="73" t="n"/>
+      <c r="F53" s="73" t="n"/>
+      <c r="G53" s="73" t="n"/>
+      <c r="H53" s="73" t="n"/>
+      <c r="I53" s="73" t="n"/>
+      <c r="J53" s="73" t="n"/>
+      <c r="K53" s="73" t="n"/>
+      <c r="L53" s="73" t="n"/>
+      <c r="M53" s="73" t="n"/>
+      <c r="N53" s="74" t="n"/>
+      <c r="O53" s="73" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="73" t="n"/>
+      <c r="B54" s="73" t="n"/>
+      <c r="C54" s="73" t="n"/>
+      <c r="D54" s="73" t="n"/>
+      <c r="E54" s="73" t="n"/>
+      <c r="F54" s="73" t="n"/>
+      <c r="G54" s="73" t="n"/>
+      <c r="H54" s="73" t="n"/>
+      <c r="I54" s="73" t="n"/>
+      <c r="J54" s="73" t="n"/>
+      <c r="K54" s="73" t="n"/>
+      <c r="L54" s="73" t="n"/>
+      <c r="M54" s="73" t="n"/>
+      <c r="N54" s="74" t="n"/>
+      <c r="O54" s="73" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="73" t="n"/>
+      <c r="B55" s="73" t="n"/>
+      <c r="C55" s="73" t="n"/>
+      <c r="D55" s="73" t="n"/>
+      <c r="E55" s="73" t="n"/>
+      <c r="F55" s="73" t="n"/>
+      <c r="G55" s="73" t="n"/>
+      <c r="H55" s="73" t="n"/>
+      <c r="I55" s="73" t="n"/>
+      <c r="J55" s="73" t="n"/>
+      <c r="K55" s="73" t="n"/>
+      <c r="L55" s="73" t="n"/>
+      <c r="M55" s="73" t="n"/>
+      <c r="N55" s="74" t="n"/>
+      <c r="O55" s="73" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="73" t="n"/>
+      <c r="B56" s="73" t="n"/>
+      <c r="C56" s="73" t="n"/>
+      <c r="D56" s="73" t="n"/>
+      <c r="E56" s="73" t="n"/>
+      <c r="F56" s="73" t="n"/>
+      <c r="G56" s="73" t="n"/>
+      <c r="H56" s="73" t="n"/>
+      <c r="I56" s="73" t="n"/>
+      <c r="J56" s="73" t="n"/>
+      <c r="K56" s="73" t="n"/>
+      <c r="L56" s="73" t="n"/>
+      <c r="M56" s="73" t="n"/>
+      <c r="N56" s="74" t="n"/>
+      <c r="O56" s="73" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="73" t="n"/>
+      <c r="B57" s="73" t="n"/>
+      <c r="C57" s="73" t="n"/>
+      <c r="D57" s="73" t="n"/>
+      <c r="E57" s="73" t="n"/>
+      <c r="F57" s="73" t="n"/>
+      <c r="G57" s="73" t="n"/>
+      <c r="H57" s="73" t="n"/>
+      <c r="I57" s="73" t="n"/>
+      <c r="J57" s="73" t="n"/>
+      <c r="K57" s="73" t="n"/>
+      <c r="L57" s="73" t="n"/>
+      <c r="M57" s="73" t="n"/>
+      <c r="N57" s="74" t="n"/>
+      <c r="O57" s="73" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="73" t="n"/>
+      <c r="B58" s="73" t="n"/>
+      <c r="C58" s="73" t="n"/>
+      <c r="D58" s="73" t="n"/>
+      <c r="E58" s="73" t="n"/>
+      <c r="F58" s="73" t="n"/>
+      <c r="G58" s="73" t="n"/>
+      <c r="H58" s="73" t="n"/>
+      <c r="I58" s="73" t="n"/>
+      <c r="J58" s="73" t="n"/>
+      <c r="K58" s="73" t="n"/>
+      <c r="L58" s="73" t="n"/>
+      <c r="M58" s="73" t="n"/>
+      <c r="N58" s="74" t="n"/>
+      <c r="O58" s="73" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="73" t="n"/>
+      <c r="B59" s="73" t="n"/>
+      <c r="C59" s="73" t="n"/>
+      <c r="D59" s="73" t="n"/>
+      <c r="E59" s="73" t="n"/>
+      <c r="F59" s="73" t="n"/>
+      <c r="G59" s="73" t="n"/>
+      <c r="H59" s="73" t="n"/>
+      <c r="I59" s="73" t="n"/>
+      <c r="J59" s="73" t="n"/>
+      <c r="K59" s="73" t="n"/>
+      <c r="L59" s="73" t="n"/>
+      <c r="M59" s="73" t="n"/>
+      <c r="N59" s="74" t="n"/>
+      <c r="O59" s="73" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="73" t="n"/>
+      <c r="B60" s="73" t="n"/>
+      <c r="C60" s="73" t="n"/>
+      <c r="D60" s="73" t="n"/>
+      <c r="E60" s="73" t="n"/>
+      <c r="F60" s="73" t="n"/>
+      <c r="G60" s="73" t="n"/>
+      <c r="H60" s="73" t="n"/>
+      <c r="I60" s="73" t="n"/>
+      <c r="J60" s="73" t="n"/>
+      <c r="K60" s="73" t="n"/>
+      <c r="L60" s="73" t="n"/>
+      <c r="M60" s="73" t="n"/>
+      <c r="N60" s="74" t="n"/>
+      <c r="O60" s="73" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="73" t="n"/>
+      <c r="B61" s="73" t="n"/>
+      <c r="C61" s="73" t="n"/>
+      <c r="D61" s="73" t="n"/>
+      <c r="E61" s="73" t="n"/>
+      <c r="F61" s="73" t="n"/>
+      <c r="G61" s="73" t="n"/>
+      <c r="H61" s="73" t="n"/>
+      <c r="I61" s="73" t="n"/>
+      <c r="J61" s="73" t="n"/>
+      <c r="K61" s="73" t="n"/>
+      <c r="L61" s="73" t="n"/>
+      <c r="M61" s="73" t="n"/>
+      <c r="N61" s="74" t="n"/>
+      <c r="O61" s="73" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O61"/>
+  <dataValidations count="10">
+    <dataValidation sqref="C2:C61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$A$2:$A$48</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$B$2:$B$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$C$2:$C$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$D$2:$D$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$E$2:$E$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$F$2:$F$16</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$G$2:$G$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$H$2:$H$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$I$2:$I$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=選択肢マスタ!$K$2:$K$39</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00843C0C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="74" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>訪問記録CSV 入力規則（15列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>列構成はTeams管理用CSVのまま変更しない。選択肢は実データ141件で実際に使われている値。「よくある誤り」は現行データを点検して見つかったもの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="60" t="inlineStr">
+        <is>
+          <t>列名</t>
+        </is>
+      </c>
+      <c r="C4" s="60" t="inlineStr">
+        <is>
+          <t>必須区分</t>
+        </is>
+      </c>
+      <c r="D4" s="60" t="inlineStr">
+        <is>
+          <t>入力形式</t>
+        </is>
+      </c>
+      <c r="E4" s="60" t="inlineStr">
+        <is>
+          <t>選択肢</t>
+        </is>
+      </c>
+      <c r="F4" s="60" t="inlineStr">
+        <is>
+          <t>記入例</t>
+        </is>
+      </c>
+      <c r="G4" s="60" t="inlineStr">
+        <is>
+          <t>よくある誤り・注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>入力者</t>
+        </is>
+      </c>
+      <c r="C5" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>姓のみ（敬称なし）</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>相澤</t>
+        </is>
+      </c>
+      <c r="G5" s="51" t="inlineStr">
+        <is>
+          <t>フルネームや「さん」を付けると集計時に別人として数えられる。社内で表記を1つに固定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>訪問日</t>
+        </is>
+      </c>
+      <c r="C6" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>yyyy/mm/dd</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="G6" s="51" t="inlineStr">
+        <is>
+          <t>空欄が現行データに4件。担当者不在でも、電話だけでも、訪問した日は必ず入れる。日付が無い行は活動実績に計上できない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="C7" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>都道府県名（プルダウン）</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>47都道府県</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>岩手県</t>
+        </is>
+      </c>
+      <c r="G7" s="51" t="inlineStr">
+        <is>
+          <t>「東北」「道南」など地域名で書かない。県名は正式表記（「北海道」に“県”を付けない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>団体名</t>
+        </is>
+      </c>
+      <c r="C8" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>正式名称</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>二戸地区広域行政事務組合</t>
+        </is>
+      </c>
+      <c r="G8" s="51" t="inlineStr">
+        <is>
+          <t>「◯◯市役所」と書かない（団体名は「◯◯市」）。組合・病院・広域連合は正式名称で。「◯◯県全市町村」のような一括行は団体別の集計を壊すので、原則1団体1行にする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="C9" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>8区分から選択（プルダウン）</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>公会計／会計支援／経営戦略／経営改善／福祉計画／公共施設マネジメント／社会生活計画／その他計画</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="G9" s="51" t="inlineStr">
+        <is>
+          <t>中身と区分のずれが多い。現行データでは「その他計画」に子ども子育て支援事業計画（4件）・高齢者福祉計画（1件）・固定資産台帳精緻化（1件）が入っている。正しくは順に 福祉計画・福祉計画・公会計。区分はシート26で確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>面談できたら必須</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>5区分から選択（プルダウン）</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>見積提示／自力／他社随契／不在／その他</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>他社随契</t>
+        </is>
+      </c>
+      <c r="G10" s="51" t="inlineStr">
+        <is>
+          <t>「その他」が現行データで最多（37件）。当てはまる区分があるなら必ずそちらを選ぶ。「その他」を選んだ場合は、備考に何があったかを必ず書く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>次回アクション</t>
+        </is>
+      </c>
+      <c r="C11" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>4区分から選択（プルダウン）</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>再アプローチ／見積提示／同行依頼、再訪／再訪不要</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>再アプローチ</t>
+        </is>
+      </c>
+      <c r="G11" s="51" t="inlineStr">
+        <is>
+          <t>空欄が22件。「次に何もしない」場合は空欄ではなく「再訪不要」を選ぶ。空欄は「決めていない」と同義で、フォローが漏れる原因になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>前回策定</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>判明したら必須</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>2区分から選択（プルダウン）</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>委託／自前</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>委託</t>
+        </is>
+      </c>
+      <c r="G12" s="51" t="inlineStr">
+        <is>
+          <t>空欄が67件。自前か委託かは提案の組み立てが変わる最重要情報。分からなければ次回訪問で必ず聞く（シート20のL2の質問「庁内で作られましたか、それとも委託されましたか」）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>判明したら必須</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>「課名　役職　氏名」を1行。複数は「／」で区切る</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>財政課　係長　佐藤様　／　同　主事　鈴木様</t>
+        </is>
+      </c>
+      <c r="G13" s="51" t="inlineStr">
+        <is>
+          <t>【最重要】セル内改行を入れない。現行データで9セルに改行があり、CSVとして開いたときに行が壊れる。また「財政課」「政策推進課（4階）」など課名や場所だけが入っている例が14件ある。課名しか分からない場合も、課名だけを1行で入れる（改行・階数は入れない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>改定時期</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>判明したら必須</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>R＋数字（単年、プルダウン）</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>R6〜R20</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="G14" s="51" t="inlineStr">
+        <is>
+          <t>「～R7」「R17～」のような範囲表記は集計・並べ替えができない。幅がある場合は最も早い年度を入れ、幅の説明は備考に書く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>アプローチ時期</t>
+        </is>
+      </c>
+      <c r="C15" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>3区分から選択（プルダウン）</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>今年度／来年度／再来年度</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>今年度</t>
+        </is>
+      </c>
+      <c r="G15" s="51" t="inlineStr">
+        <is>
+          <t>空欄が52件。改定時期から逆算すれば必ず決まる（改定年度の前年度が予算要求＝アプローチ年度）。ここが埋まっていないと、年間の営業計画が組めない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="C16" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>4区分から選択（プルダウン）</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>初回訪問／セカンドアプローチ／見積提示／見積＋仕様書</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>セカンドアプローチ</t>
+        </is>
+      </c>
+      <c r="G16" s="51" t="inlineStr">
+        <is>
+          <t>空欄が46件。関係の深さを示す唯一の列。訪問のたびに更新する（初回訪問→セカンドアプローチ→見積提示→見積＋仕様書）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>契約予定</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>見込みが立ったら必須</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>4区分から選択（プルダウン）</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>入札／見積合わせ／随契／プロポ</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>随契</t>
+        </is>
+      </c>
+      <c r="G17" s="51" t="inlineStr">
+        <is>
+          <t>空欄が107件と最も欠測が多いが、受注確度と必要な準備（提案書の要否）を決める列。分かった時点で必ず入れる（シート20のL3の質問「入札とプロポーザル、どちらの想定でしょうか」）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="C18" s="62" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>1行・120字程度。改行とインデントを入れない</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>今年度EY新日本随契。R9改定のため、R8夏の予算要求前に参考見積を提示する。</t>
+        </is>
+      </c>
+      <c r="G18" s="51" t="inlineStr">
+        <is>
+          <t>改行・全角スペースでのインデントを入れるとCSVとTeamsの表示が崩れる（現行データに1件）。「セミナー案内」だけでは、誰に何をして次に何をするかが分からない。書き方はシート25下部を参照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="C19" s="61" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>標準リストから選択（シート26。プルダウン・新規追加可）</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>シート26参照</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>財務書類作成</t>
+        </is>
+      </c>
+      <c r="G19" s="51" t="inlineStr">
+        <is>
+          <t>空欄が59件。表記ゆれも多い（「公共施設等総合管理計画」と「〜改定業務」、「台帳精緻化（所有外）」「所有外管理資産」「固定資産台帳精緻化（所有外管理資産）」が併存）。団体名を入れてしまっている行もある。標準リストから選ぶ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>備考の書き方</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="60" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B22" s="60" t="inlineStr">
+        <is>
+          <t>例文</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="60" t="inlineStr"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="16" t="n"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="75" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>［現況］＋［根拠・時期］＋［次の一手］　を1行で。</t>
+        </is>
+      </c>
+      <c r="C23" s="76" t="n"/>
+      <c r="D23" s="76" t="n"/>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>この3点が揃っていれば、書いた本人以外が読んでも次の行動が分かる。</t>
+        </is>
+      </c>
+      <c r="F23" s="76" t="n"/>
+      <c r="G23" s="76" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="77" t="inlineStr">
+        <is>
+          <t>◎ 良い例</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>今年度EY新日本随契。R9改定時期のため、R8夏の予算要求前に参考見積を提示する。</t>
+        </is>
+      </c>
+      <c r="C24" s="76" t="n"/>
+      <c r="D24" s="76" t="n"/>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>現況（他社随契）・根拠（改定年度）・次の一手（いつ何をするか）が1行に収まっている。</t>
+        </is>
+      </c>
+      <c r="F24" s="76" t="n"/>
+      <c r="G24" s="76" t="n"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="77" t="inlineStr">
+        <is>
+          <t>◎ 良い例</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>経営戦略R8〜R17（簡水・特環）、委託先は行政研。料金改定はR12予定だがR10への前倒しを想定。決算統計との不整合解消を会計支援として提案。</t>
+        </is>
+      </c>
+      <c r="C25" s="76" t="n"/>
+      <c r="D25" s="76" t="n"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>計画期間・委託先・時期の前倒し見込み・提案の切り口まで書かれており、そのまま引き継げる。</t>
+        </is>
+      </c>
+      <c r="F25" s="76" t="n"/>
+      <c r="G25" s="76" t="n"/>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="77" t="inlineStr">
+        <is>
+          <t>◎ 良い例</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>自前作成を継続。予算が取れれば委託も検討とのこと。次回は見積書を提出する。</t>
+        </is>
+      </c>
+      <c r="C26" s="76" t="n"/>
+      <c r="D26" s="76" t="n"/>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>「自力」の結果でも、次に何をするかが書かれていれば追える。</t>
+        </is>
+      </c>
+      <c r="F26" s="76" t="n"/>
+      <c r="G26" s="76" t="n"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="75" t="inlineStr">
+        <is>
+          <t>△ 惜しい例</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>所有外セミナー案内</t>
+        </is>
+      </c>
+      <c r="C27" s="76" t="n"/>
+      <c r="D27" s="76" t="n"/>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>何をしたかは分かるが、相手の反応と次の一手が無い。「所有外管理資産セミナーを案内。関心ありとのことで、9月にセミナー後フォロー訪問する」まで書く。</t>
+        </is>
+      </c>
+      <c r="F27" s="76" t="n"/>
+      <c r="G27" s="76" t="n"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="78" t="inlineStr">
+        <is>
+          <t>× 悪い例</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>担当不在</t>
+        </is>
+      </c>
+      <c r="C28" s="76" t="n"/>
+      <c r="D28" s="76" t="n"/>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>結果列に「不在」があるので情報の重複。備考には「次にいつ・誰を訪ねるか」を書く。</t>
+        </is>
+      </c>
+      <c r="F28" s="76" t="n"/>
+      <c r="G28" s="76" t="n"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="78" t="inlineStr">
+        <is>
+          <t>× 悪い例</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>（改行やインデントを含む複数行のメモ）</t>
+        </is>
+      </c>
+      <c r="C29" s="76" t="n"/>
+      <c r="D29" s="76" t="n"/>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>CSVとして開いたときに行が壊れ、Teams上の表示も崩れる。長くなる場合は要点を1行にまとめ、詳細は訪問記録シート（社内用）に書く。</t>
+        </is>
+      </c>
+      <c r="F29" s="76" t="n"/>
+      <c r="G29" s="76" t="n"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="75" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>団体名・担当者名・金額の書き方</t>
+        </is>
+      </c>
+      <c r="C30" s="76" t="n"/>
+      <c r="D30" s="76" t="n"/>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>備考は社内で広く共有される。相手の個人的な事情や、未公表の内部情報は書かない。他団体から聞いた話をそのまま転記しない。</t>
+        </is>
+      </c>
+      <c r="F30" s="76" t="n"/>
+      <c r="G30" s="76" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>現行データ（141件）の入力状況　── 埋めるべき列の優先順位</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="60" t="inlineStr">
+        <is>
+          <t>列名</t>
+        </is>
+      </c>
+      <c r="B33" s="60" t="inlineStr">
+        <is>
+          <t>入力</t>
+        </is>
+      </c>
+      <c r="C33" s="60" t="inlineStr">
+        <is>
+          <t>欠測</t>
+        </is>
+      </c>
+      <c r="D33" s="60" t="inlineStr">
+        <is>
+          <t>欠測率</t>
+        </is>
+      </c>
+      <c r="E33" s="60" t="inlineStr">
+        <is>
+          <t>コメント</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="16" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>入力者</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F34" s="48" t="n"/>
+      <c r="G34" s="48" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>訪問日</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>137</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>不在・電話のみの回で抜けている。</t>
+        </is>
+      </c>
+      <c r="F35" s="48" t="n"/>
+      <c r="G35" s="48" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F36" s="48" t="n"/>
+      <c r="G36" s="48" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>団体名</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>「◯◯県全市町村」の一括行が1件あり、団体別集計から外れる。</t>
+        </is>
+      </c>
+      <c r="F37" s="48" t="n"/>
+      <c r="G37" s="48" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>区分の当てはめ違いが6件以上。</t>
+        </is>
+      </c>
+      <c r="F38" s="48" t="n"/>
+      <c r="G38" s="48" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>「その他」が37件で最多。区分が機能していない。</t>
+        </is>
+      </c>
+      <c r="F39" s="48" t="n"/>
+      <c r="G39" s="48" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>次回アクション</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>119</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>空欄はフォロー漏れに直結する。</t>
+        </is>
+      </c>
+      <c r="F40" s="48" t="n"/>
+      <c r="G40" s="48" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="79" t="inlineStr">
+        <is>
+          <t>前回策定</t>
+        </is>
+      </c>
+      <c r="B41" s="80" t="n">
+        <v>74</v>
+      </c>
+      <c r="C41" s="80" t="n">
+        <v>67</v>
+      </c>
+      <c r="D41" s="81" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>提案の組み立てが変わる最重要情報が半分欠けている。</t>
+        </is>
+      </c>
+      <c r="F41" s="48" t="n"/>
+      <c r="G41" s="48" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>9セルに改行あり（CSVが壊れる）。課名だけの入力が14件。</t>
+        </is>
+      </c>
+      <c r="F42" s="48" t="n"/>
+      <c r="G42" s="48" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="79" t="inlineStr">
+        <is>
+          <t>改定時期</t>
+        </is>
+      </c>
+      <c r="B43" s="80" t="n">
+        <v>83</v>
+      </c>
+      <c r="C43" s="80" t="n">
+        <v>58</v>
+      </c>
+      <c r="D43" s="81" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>範囲表記（～R7、R17～）が3件。</t>
+        </is>
+      </c>
+      <c r="F43" s="48" t="n"/>
+      <c r="G43" s="48" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="79" t="inlineStr">
+        <is>
+          <t>アプローチ時期</t>
+        </is>
+      </c>
+      <c r="B44" s="80" t="n">
+        <v>89</v>
+      </c>
+      <c r="C44" s="80" t="n">
+        <v>52</v>
+      </c>
+      <c r="D44" s="81" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>改定時期から逆算すれば必ず埋まる。</t>
+        </is>
+      </c>
+      <c r="F44" s="48" t="n"/>
+      <c r="G44" s="48" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="79" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B45" s="80" t="n">
+        <v>95</v>
+      </c>
+      <c r="C45" s="80" t="n">
+        <v>46</v>
+      </c>
+      <c r="D45" s="81" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>関係の深さを示す唯一の列。</t>
+        </is>
+      </c>
+      <c r="F45" s="48" t="n"/>
+      <c r="G45" s="48" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="79" t="inlineStr">
+        <is>
+          <t>契約予定</t>
+        </is>
+      </c>
+      <c r="B46" s="80" t="n">
+        <v>34</v>
+      </c>
+      <c r="C46" s="80" t="n">
+        <v>107</v>
+      </c>
+      <c r="D46" s="81" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>最も欠測が多い。受注確度の判断ができない。</t>
+        </is>
+      </c>
+      <c r="F46" s="48" t="n"/>
+      <c r="G46" s="48" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>1件に改行あり。「セミナー案内」のみで次が読めない記述が散見。</t>
+        </is>
+      </c>
+      <c r="F47" s="48" t="n"/>
+      <c r="G47" s="48" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="79" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B48" s="80" t="n">
+        <v>82</v>
+      </c>
+      <c r="C48" s="80" t="n">
+        <v>59</v>
+      </c>
+      <c r="D48" s="81" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>表記ゆれ多数。団体名が入っている行が1件。</t>
+        </is>
+      </c>
+      <c r="F48" s="48" t="n"/>
+      <c r="G48" s="48" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G19"/>
+  <mergeCells count="38">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E38:G38"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>テーマ・タイトル標準リスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CSVの「テーマ」8区分と「タイトル」の標準値。カリキュラム上のテーマと、訪問前に見るヒアリングシートの対応も併記。タイトルはここから選ぶ（表記ゆれを防ぐ）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="60" t="inlineStr">
+        <is>
+          <t>CSVのテーマ</t>
+        </is>
+      </c>
+      <c r="B4" s="60" t="inlineStr">
+        <is>
+          <t>標準タイトル（タイトル列に入れる値）</t>
+        </is>
+      </c>
+      <c r="C4" s="60" t="inlineStr">
+        <is>
+          <t>カリキュラム上のテーマ</t>
+        </is>
+      </c>
+      <c r="D4" s="60" t="inlineStr">
+        <is>
+          <t>訪問前に見るシート</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="82" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>財務書類作成</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>21（公会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="82" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>台帳精緻化（全体）</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>21（公会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="82" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>台帳精緻化（所有外管理資産）</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>21（公会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="82" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>公会計システム導入</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>21（公会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="82" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>財務書類の活用支援・分析</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>21（公会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="82" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>職員研修（公会計）</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>21（公会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="83" t="inlineStr">
+        <is>
+          <t>会計支援</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計 会計支援</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>21（公営企業会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="83" t="inlineStr">
+        <is>
+          <t>会計支援</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計 適用（法適化）支援</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>21（公営企業会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="83" t="inlineStr">
+        <is>
+          <t>会計支援</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>決算・決算統計 作成支援</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>21（公営企業会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="83" t="inlineStr">
+        <is>
+          <t>経営戦略</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>上下水道 経営戦略（策定）</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>21（公営企業会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="83" t="inlineStr">
+        <is>
+          <t>経営戦略</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>上下水道 経営戦略（改定）</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>21（公営企業会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="83" t="inlineStr">
+        <is>
+          <t>経営戦略</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>アセットマネジメント・ストックマネジメント</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>21（公営企業会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="83" t="inlineStr">
+        <is>
+          <t>経営戦略</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>病院事業 経営強化プラン</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>21（公営企業会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="83" t="inlineStr">
+        <is>
+          <t>経営改善</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>料金・使用料改定</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>21（公営企業会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="83" t="inlineStr">
+        <is>
+          <t>経営改善</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>経営分析（経営比較分析表の活用）</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>21（公営企業会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="83" t="inlineStr">
+        <is>
+          <t>経営改善</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>広域化・官民連携 検討支援</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>公営企業会計</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>21（公営企業会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="84" t="inlineStr">
+        <is>
+          <t>福祉計画</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>高齢者福祉計画・介護保険事業計画</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>21（高齢者・介護保険）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="84" t="inlineStr">
+        <is>
+          <t>福祉計画</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>障害者計画・障害福祉計画・障害児福祉計画</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>21（障害者・障害児）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="84" t="inlineStr">
+        <is>
+          <t>福祉計画</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉計画</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>21（地域福祉）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="84" t="inlineStr">
+        <is>
+          <t>福祉計画</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>こども計画</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>21（こども・子育て）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="84" t="inlineStr">
+        <is>
+          <t>福祉計画</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>子ども子育て支援事業計画</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>こども・子育て</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>21（こども・子育て）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="84" t="inlineStr">
+        <is>
+          <t>福祉計画</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>重層的支援体制整備事業 支援</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>21（地域福祉）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="84" t="inlineStr">
+        <is>
+          <t>福祉計画</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>福祉分野 アンケート調査（単独受託）</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>該当分野</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>21（該当テーマ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="85" t="inlineStr">
+        <is>
+          <t>公共施設マネジメント</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>公共施設等総合管理計画</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>21（その他計画）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="85" t="inlineStr">
+        <is>
+          <t>公共施設マネジメント</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>個別施設計画</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>21（その他計画）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="85" t="inlineStr">
+        <is>
+          <t>公共施設マネジメント</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>施設カルテ・施設白書</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>21（その他計画）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="85" t="inlineStr">
+        <is>
+          <t>公共施設マネジメント</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>公共施設 再編・適正配置検討</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>21（その他計画）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="86" t="inlineStr">
+        <is>
+          <t>社会生活計画</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>健康増進計画・食育推進計画</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>21（その他計画）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="86" t="inlineStr">
+        <is>
+          <t>社会生活計画</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>自殺対策計画</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>21（地域福祉）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="86" t="inlineStr">
+        <is>
+          <t>社会生活計画</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>男女共同参画計画</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>21（その他計画）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="86" t="inlineStr">
+        <is>
+          <t>社会生活計画</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>環境基本計画</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>―（社内で教材整備）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="86" t="inlineStr">
+        <is>
+          <t>社会生活計画</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>地域公共交通計画</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>―（社内で教材整備）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="86" t="inlineStr">
+        <is>
+          <t>社会生活計画</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>文化財保存活用地域計画</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>―（社内で教材整備）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="87" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>総合計画</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>21（その他計画）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="87" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>財政計画・中期財政推計</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>21（その他計画）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="87" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>農業振興計画・地域計画</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>21（その他計画）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="87" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>国土強靱化地域計画</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>―（社内で教材整備）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="87" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>その他（上記以外）</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="46" customHeight="1">
+      <c r="A44" s="88" t="inlineStr">
+        <is>
+          <t>【区分の当てはめで迷いやすいもの】こども計画・子ども子育て支援事業計画・高齢者福祉計画は「福祉計画」（「その他計画」ではない）。固定資産台帳精緻化は「公会計」。公営企業の料金改定は「経営改善」、経営戦略の策定・改定は「経営戦略」、日常の会計・決算支援は「会計支援」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="46" customHeight="1">
+      <c r="A45" s="89" t="inlineStr">
+        <is>
+          <t>【要検討：社会生活計画とその他計画の線引き】現行データでは環境系が両方に入っている（環境計画＝社会生活計画／環境基本計画＝その他計画）。本リストは「住民生活に直結する分野別計画（健康・食育・自殺対策・男女共同参画・環境・交通・文化財）を社会生活計画、行政運営に関わる計画（総合計画・財政・農業振興・強靱化）をその他計画」とする案。社内で確定したうえで運用を統一してください。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:D42"/>
+  <mergeCells count="4">
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A44:D44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="90" t="inlineStr">
+        <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="B1" s="90" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="C1" s="90" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="D1" s="90" t="inlineStr">
+        <is>
+          <t>次回アクション</t>
+        </is>
+      </c>
+      <c r="E1" s="90" t="inlineStr">
+        <is>
+          <t>前回策定</t>
+        </is>
+      </c>
+      <c r="F1" s="90" t="inlineStr">
+        <is>
+          <t>改定時期</t>
+        </is>
+      </c>
+      <c r="G1" s="90" t="inlineStr">
+        <is>
+          <t>アプローチ時期</t>
+        </is>
+      </c>
+      <c r="H1" s="90" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="I1" s="90" t="inlineStr">
+        <is>
+          <t>契約予定</t>
+        </is>
+      </c>
+      <c r="J1" s="90" t="inlineStr">
+        <is>
+          <t>温度感</t>
+        </is>
+      </c>
+      <c r="K1" s="90" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="91" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B2" s="91" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="C2" s="91" t="inlineStr">
+        <is>
+          <t>見積提示</t>
+        </is>
+      </c>
+      <c r="D2" s="91" t="inlineStr">
+        <is>
+          <t>再アプローチ</t>
+        </is>
+      </c>
+      <c r="E2" s="91" t="inlineStr">
+        <is>
+          <t>委託</t>
+        </is>
+      </c>
+      <c r="F2" s="91" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="G2" s="91" t="inlineStr">
+        <is>
+          <t>今年度</t>
+        </is>
+      </c>
+      <c r="H2" s="91" t="inlineStr">
+        <is>
+          <t>初回訪問</t>
+        </is>
+      </c>
+      <c r="I2" s="91" t="inlineStr">
+        <is>
+          <t>入札</t>
+        </is>
+      </c>
+      <c r="J2" s="91" t="inlineStr">
+        <is>
+          <t>A：今年度中に動く</t>
+        </is>
+      </c>
+      <c r="K2" s="91" t="inlineStr">
+        <is>
+          <t>財務書類作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="91" t="inlineStr">
+        <is>
+          <t>青森県</t>
+        </is>
+      </c>
+      <c r="B3" s="91" t="inlineStr">
+        <is>
+          <t>会計支援</t>
+        </is>
+      </c>
+      <c r="C3" s="91" t="inlineStr">
+        <is>
+          <t>自力</t>
+        </is>
+      </c>
+      <c r="D3" s="91" t="inlineStr">
+        <is>
+          <t>見積提示</t>
+        </is>
+      </c>
+      <c r="E3" s="91" t="inlineStr">
+        <is>
+          <t>自前</t>
+        </is>
+      </c>
+      <c r="F3" s="91" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="G3" s="91" t="inlineStr">
+        <is>
+          <t>来年度</t>
+        </is>
+      </c>
+      <c r="H3" s="91" t="inlineStr">
+        <is>
+          <t>セカンドアプローチ</t>
+        </is>
+      </c>
+      <c r="I3" s="91" t="inlineStr">
+        <is>
+          <t>見積合わせ</t>
+        </is>
+      </c>
+      <c r="J3" s="91" t="inlineStr">
+        <is>
+          <t>B：次年度予算で検討</t>
+        </is>
+      </c>
+      <c r="K3" s="91" t="inlineStr">
+        <is>
+          <t>台帳精緻化（全体）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="91" t="inlineStr">
+        <is>
+          <t>岩手県</t>
+        </is>
+      </c>
+      <c r="B4" s="91" t="inlineStr">
+        <is>
+          <t>経営戦略</t>
+        </is>
+      </c>
+      <c r="C4" s="91" t="inlineStr">
+        <is>
+          <t>他社随契</t>
+        </is>
+      </c>
+      <c r="D4" s="91" t="inlineStr">
+        <is>
+          <t>同行依頼、再訪</t>
+        </is>
+      </c>
+      <c r="F4" s="91" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="G4" s="91" t="inlineStr">
+        <is>
+          <t>再来年度</t>
+        </is>
+      </c>
+      <c r="H4" s="91" t="inlineStr">
+        <is>
+          <t>見積提示</t>
+        </is>
+      </c>
+      <c r="I4" s="91" t="inlineStr">
+        <is>
+          <t>随契</t>
+        </is>
+      </c>
+      <c r="J4" s="91" t="inlineStr">
+        <is>
+          <t>C：様子見</t>
+        </is>
+      </c>
+      <c r="K4" s="91" t="inlineStr">
+        <is>
+          <t>台帳精緻化（所有外管理資産）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="91" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="B5" s="91" t="inlineStr">
+        <is>
+          <t>経営改善</t>
+        </is>
+      </c>
+      <c r="C5" s="91" t="inlineStr">
+        <is>
+          <t>不在</t>
+        </is>
+      </c>
+      <c r="D5" s="91" t="inlineStr">
+        <is>
+          <t>再訪不要</t>
+        </is>
+      </c>
+      <c r="F5" s="91" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="H5" s="91" t="inlineStr">
+        <is>
+          <t>見積＋仕様書</t>
+        </is>
+      </c>
+      <c r="I5" s="91" t="inlineStr">
+        <is>
+          <t>プロポ</t>
+        </is>
+      </c>
+      <c r="J5" s="91" t="inlineStr">
+        <is>
+          <t>D：当面なし</t>
+        </is>
+      </c>
+      <c r="K5" s="91" t="inlineStr">
+        <is>
+          <t>公会計システム導入</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="91" t="inlineStr">
+        <is>
+          <t>秋田県</t>
+        </is>
+      </c>
+      <c r="B6" s="91" t="inlineStr">
+        <is>
+          <t>福祉計画</t>
+        </is>
+      </c>
+      <c r="C6" s="91" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="F6" s="91" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="K6" s="91" t="inlineStr">
+        <is>
+          <t>財務書類の活用支援・分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="91" t="inlineStr">
+        <is>
+          <t>山形県</t>
+        </is>
+      </c>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>公共施設マネジメント</t>
+        </is>
+      </c>
+      <c r="F7" s="91" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="K7" s="91" t="inlineStr">
+        <is>
+          <t>職員研修（公会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="91" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="B8" s="91" t="inlineStr">
+        <is>
+          <t>社会生活計画</t>
+        </is>
+      </c>
+      <c r="F8" s="91" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="K8" s="91" t="inlineStr">
+        <is>
+          <t>公営企業会計 会計支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="91" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="B9" s="91" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="F9" s="91" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="K9" s="91" t="inlineStr">
+        <is>
+          <t>公営企業会計 適用（法適化）支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="91" t="inlineStr">
+        <is>
+          <t>栃木県</t>
+        </is>
+      </c>
+      <c r="F10" s="91" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="K10" s="91" t="inlineStr">
+        <is>
+          <t>決算・決算統計 作成支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="91" t="inlineStr">
+        <is>
+          <t>群馬県</t>
+        </is>
+      </c>
+      <c r="F11" s="91" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="K11" s="91" t="inlineStr">
+        <is>
+          <t>上下水道 経営戦略（策定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="91" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="F12" s="91" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="K12" s="91" t="inlineStr">
+        <is>
+          <t>上下水道 経営戦略（改定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="91" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="F13" s="91" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="K13" s="91" t="inlineStr">
+        <is>
+          <t>アセットマネジメント・ストックマネジメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="91" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="F14" s="91" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="K14" s="91" t="inlineStr">
+        <is>
+          <t>病院事業 経営強化プラン</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="91" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="F15" s="91" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="K15" s="91" t="inlineStr">
+        <is>
+          <t>料金・使用料改定</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="91" t="inlineStr">
+        <is>
+          <t>新潟県</t>
+        </is>
+      </c>
+      <c r="F16" s="91" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="K16" s="91" t="inlineStr">
+        <is>
+          <t>経営分析（経営比較分析表の活用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="91" t="inlineStr">
+        <is>
+          <t>富山県</t>
+        </is>
+      </c>
+      <c r="K17" s="91" t="inlineStr">
+        <is>
+          <t>広域化・官民連携 検討支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="91" t="inlineStr">
+        <is>
+          <t>石川県</t>
+        </is>
+      </c>
+      <c r="K18" s="91" t="inlineStr">
+        <is>
+          <t>高齢者福祉計画・介護保険事業計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="91" t="inlineStr">
+        <is>
+          <t>福井県</t>
+        </is>
+      </c>
+      <c r="K19" s="91" t="inlineStr">
+        <is>
+          <t>障害者計画・障害福祉計画・障害児福祉計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="91" t="inlineStr">
+        <is>
+          <t>山梨県</t>
+        </is>
+      </c>
+      <c r="K20" s="91" t="inlineStr">
+        <is>
+          <t>地域福祉計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="91" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="K21" s="91" t="inlineStr">
+        <is>
+          <t>こども計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="91" t="inlineStr">
+        <is>
+          <t>岐阜県</t>
+        </is>
+      </c>
+      <c r="K22" s="91" t="inlineStr">
+        <is>
+          <t>子ども子育て支援事業計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="91" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="K23" s="91" t="inlineStr">
+        <is>
+          <t>重層的支援体制整備事業 支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="91" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="K24" s="91" t="inlineStr">
+        <is>
+          <t>福祉分野 アンケート調査（単独受託）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="91" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="K25" s="91" t="inlineStr">
+        <is>
+          <t>公共施設等総合管理計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="91" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="K26" s="91" t="inlineStr">
+        <is>
+          <t>個別施設計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="91" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="K27" s="91" t="inlineStr">
+        <is>
+          <t>施設カルテ・施設白書</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="91" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="K28" s="91" t="inlineStr">
+        <is>
+          <t>公共施設 再編・適正配置検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="91" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="K29" s="91" t="inlineStr">
+        <is>
+          <t>健康増進計画・食育推進計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="91" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="K30" s="91" t="inlineStr">
+        <is>
+          <t>自殺対策計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="91" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="K31" s="91" t="inlineStr">
+        <is>
+          <t>男女共同参画計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="91" t="inlineStr">
+        <is>
+          <t>鳥取県</t>
+        </is>
+      </c>
+      <c r="K32" s="91" t="inlineStr">
+        <is>
+          <t>環境基本計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="91" t="inlineStr">
+        <is>
+          <t>島根県</t>
+        </is>
+      </c>
+      <c r="K33" s="91" t="inlineStr">
+        <is>
+          <t>地域公共交通計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="91" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="K34" s="91" t="inlineStr">
+        <is>
+          <t>文化財保存活用地域計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="91" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="K35" s="91" t="inlineStr">
+        <is>
+          <t>総合計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="91" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="K36" s="91" t="inlineStr">
+        <is>
+          <t>財政計画・中期財政推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="91" t="inlineStr">
+        <is>
+          <t>徳島県</t>
+        </is>
+      </c>
+      <c r="K37" s="91" t="inlineStr">
+        <is>
+          <t>農業振興計画・地域計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="91" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="K38" s="91" t="inlineStr">
+        <is>
+          <t>国土強靱化地域計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="91" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="K39" s="91" t="inlineStr">
+        <is>
+          <t>その他（上記以外）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="91" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="91" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="91" t="inlineStr">
+        <is>
+          <t>佐賀県</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="91" t="inlineStr">
+        <is>
+          <t>長崎県</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="91" t="inlineStr">
+        <is>
+          <t>熊本県</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="91" t="inlineStr">
+        <is>
+          <t>大分県</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="91" t="inlineStr">
+        <is>
+          <t>宮崎県</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="91" t="inlineStr">
+        <is>
+          <t>鹿児島県</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="91" t="inlineStr">
+        <is>
+          <t>沖縄県</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/output/10_新人教育カリキュラム_マスター管理表.xlsx
+++ b/output/10_新人教育カリキュラム_マスター管理表.xlsx
@@ -34,7 +34,9 @@
     <sheet name="24_訪問記録CSV_入力シート" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="25_CSV入力規則" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="26_テーマ・タイトル標準リスト" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="選択肢マスタ" sheetId="28" state="hidden" r:id="rId28"/>
+    <sheet name="27_5分トーク_高齢者(自前先)" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="28_来期営業方針_こども・地域福祉" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="選択肢マスタ" sheetId="30" state="hidden" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_月次ロードマップ'!$A$4:$I$40</definedName>
@@ -58,6 +60,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'24_訪問記録CSV_入力シート'!$A$1:$O$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'25_CSV入力規則'!$A$4:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'26_テーマ・タイトル標準リスト'!$A$4:$D$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="27">'27_5分トーク_高齢者(自前先)'!$A$1:$D$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -66,7 +69,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -139,8 +142,14 @@
       <color rgb="001F3864"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="39">
+  <fills count="41">
     <fill>
       <patternFill/>
     </fill>
@@ -332,6 +341,16 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C55A11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A02020"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -450,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -704,6 +723,33 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1073,7 +1119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1303,98 +1349,112 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　27_5分トーク_高齢者(自前先)… 自前作成先から補正予算を取る5分の台本と想定問答</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　28_来期営業方針_こども・地域福祉… R9年度に向けた2テーマの攻め方</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>4. 運用サイクル（推奨）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　毎月　　… 上長と本人で30分の面談。当月の学習項目と習得目標の達成状況を確認し、翌月の重点を決める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　四半期　… 成果物レビューを1件必ず実施し、「確認方法」欄の方法で到達度を確認する。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　半期　　… 12_個人別チェックシートで自己評価と上長評価を突き合わせ、差異の原因を対話する。</t>
+          <t xml:space="preserve">　毎月　　… 上長と本人で30分の面談。当月の学習項目と習得目標の達成状況を確認し、翌月の重点を決める。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　四半期　… 成果物レビューを1件必ず実施し、「確認方法」欄の方法で到達度を確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　半期　　… 12_個人別チェックシートで自己評価と上長評価を突き合わせ、差異の原因を対話する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　年次　　… レベル判定を確定し、次年度の主担当・副担当テーマと育成計画を決定する。</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>5. レベル判定の原則</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　・「知っている」ではなく「できた実績があるか」で判定します。判定には必ず具体的な案件名・成果物名を紐づけてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　・1つの項目でL3と判定するには、原則として同種の作業を2案件以上、単独で完遂している必要があります。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　・「知っている」ではなく「できた実績があるか」で判定します。判定には必ず具体的な案件名・成果物名を紐づけてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　・1つの項目でL3と判定するには、原則として同種の作業を2案件以上、単独で完遂している必要があります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　・自己評価と上長評価に2段階以上の差がある場合は、必ず面談で認識を合わせてください。</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>6. 更新について</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">　・制度改正（基本指針、報酬改定、会計基準、各省ガイドライン等）が生じた場合は、該当テーマシートの学習内容を年1回見直してください。</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">　・計画の「期」（第○期）は年度の経過とともに進みます。テーマシートの記載は根拠法と期間の考え方を示すもので、具体の期・年度は都度確認してください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="45">
     <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A51:H51"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A49:H49"/>
@@ -1404,10 +1464,12 @@
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="A2:H2"/>
@@ -1422,9 +1484,9 @@
     <mergeCell ref="A40:H40"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A43:H43"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A13:H13"/>
@@ -19212,847 +19274,737 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002CA02C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="84" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>5分トーク｜高齢者・自前作成先からの補正予算獲得</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>対象は第10期（R9〜11年度）介護保険事業計画を自前で作っている自治体。R9年4月からの保険料賦課にはR9年3月議会での条例改正が必要で、そこから逆算すると10月末までに分析が終わっていないとパブリックコメントの期間が取れない。その一点だけを伝える5分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>見出し</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>話す内容（スクリプト）</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>ねらい</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="90" t="inlineStr">
+        <is>
+          <t>0:00–0:30</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>用件を告げ、5分だけもらう</t>
+        </is>
+      </c>
+      <c r="C5" s="63" t="inlineStr">
+        <is>
+          <t>「◯◯町の高齢福祉課様でいらっしゃいますね。◯◯株式会社の△△と申します。第10期の介護保険事業計画の件で、5分だけお時間をいただけますでしょうか。御町ではご自身で作られていると伺っておりまして、この時期にお伝えしておいたほうがよいことが2点ございます。」</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>「自前で作っている」ことを知っている＝下調べ済みだと最初に伝える。売り込みではなく「時期の話」として入る。5分と明示すると断られにくい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="91" t="inlineStr">
+        <is>
+          <t>0:30–1:30</t>
+        </is>
+      </c>
+      <c r="B6" s="49" t="inlineStr">
+        <is>
+          <t>進捗を3問だけ聞く</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="inlineStr">
+        <is>
+          <t>「①ニーズ調査と在宅介護実態調査の集計は、もうお済みでしょうか。」
+「②保険料の算定は、どなたがご担当される予定でしょうか。」
+「③3月議会での条例改正に向けて、パブリックコメントはいつ頃を想定されていますか。」</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>この3問で自前完遂の可否がほぼ判定できる。①が未了、②が未定、③が「これから考える」なら高い確率で間に合わない。詰問にならないよう、3問で止めて次へ進む。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="90" t="inlineStr">
+        <is>
+          <t>1:30–3:00</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>逆算して見せる（本題）</t>
+        </is>
+      </c>
+      <c r="C7" s="63" t="inlineStr">
+        <is>
+          <t>「第10期の保険料は、R9年4月から賦課するためにR9年3月議会での条例改正が要ります。そこから逆算しますと──2月下旬に議案上程、その前に1〜2月でパブリックコメント（30日程度）、その前の12〜1月で保険料の確定と計画素案、11月に給付費推計とサービス見込量、10月までに現状分析。つまり10月末までに分析が終わっていないと、パブコメの期間が取れなくなります。」</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>計画策定業務ではなく「条例改正の期限」から話す。ここは自治体側が動かせない制約なので、こちらの都合ではなく相手の制約として受け取ってもらえる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="91" t="inlineStr">
+        <is>
+          <t>3:00–4:00</t>
+        </is>
+      </c>
+      <c r="B8" s="49" t="inlineStr">
+        <is>
+          <t>部分委託という逃げ道を示す</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="inlineStr">
+        <is>
+          <t>「全部をお預けいただく必要はありません。いちばん時間がかかるのは保険料の算定と給付費推計で、ここは見える化システムと厚労省のワークシートを使った作業です。ここだけをお預かりして、計画本文は御町で書いていただく、という切り分けができます。この形なら金額も抑えられますので、12月補正で十分間に合います。」</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>全部委託は補正で通りにくい（金額が大きい・査定に耐えない）。「作れない」ではなく「時間がかかる工程だけ外に出す」と提示すると、担当者の面目も立つ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="90" t="inlineStr">
+        <is>
+          <t>4:00–5:00</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>次を決めて帰る</t>
+        </is>
+      </c>
+      <c r="C9" s="63" t="inlineStr">
+        <is>
+          <t>「12月補正ですと、財政課へのご要求はおおむね11月上旬かと思います。10月中に、業務の切り分け案と参考のお見積をお持ちします。いつ頃までにあるとよろしいでしょうか。」</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>提出期限を相手に言わせる。相手の庁内スケジュールがそのまま分かり、次回訪問の理由も確定する。「検討します」で終わらせない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="92" t="inlineStr">
+        <is>
+          <t>想定問答</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="60" t="inlineStr">
+        <is>
+          <t>想定される反応</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>切り返し</t>
+        </is>
+      </c>
+      <c r="C12" s="60" t="inlineStr">
+        <is>
+          <t>補足・注意</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t>「予算がないので今年度は無理です」</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>「補正でも難しいようでしたら、まず調査・集計の部分だけ、既定予算の範囲でお受けする形もあります。本体は次年度当初でも、分析が先に終わっていれば間に合います。」</t>
+        </is>
+      </c>
+      <c r="C13" s="79" t="inlineStr">
+        <is>
+          <t>少額随意契約の範囲（金額は自治体の契約規則による）で先行着手し、本体を補正または当初に回す二段構え。金額の線引きは必ず当該自治体の契約規則で確認してから話す。</t>
+        </is>
+      </c>
+      <c r="D13" s="93" t="n"/>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="47" t="inlineStr">
+        <is>
+          <t>「自前でやれます」</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr">
+        <is>
+          <t>「承知しました。無理にお預けいただく話ではありません。ただ保険料の算定だけは、算定後の検算をセカンドオピニオンとしてお使いいただく形もございます。3年間の保険料に直結しますので、二重にご確認いただく価値はあるかと思います。」</t>
+        </is>
+      </c>
+      <c r="C14" s="79" t="inlineStr">
+        <is>
+          <t>自前を否定しない。否定した瞬間に担当者の面目を潰し、次年度以降も入れなくなる。検算・レビューという小さな入口を残す。</t>
+        </is>
+      </c>
+      <c r="D14" s="93" t="n"/>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>「もう他社にお願いしています」</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr">
+        <is>
+          <t>「失礼しました。差し支えなければ、業務の範囲はどこまででしょうか。調査だけのご契約でしたら、保険料の算定と計画本文が残っているかもしれません。」</t>
+        </is>
+      </c>
+      <c r="C15" s="79" t="inlineStr">
+        <is>
+          <t>調査のみ・アンケートのみの分離発注は多い。範囲を確認せずに引き下がらない。ただし食い下がらず、1往復で判断する。</t>
+        </is>
+      </c>
+      <c r="D15" s="93" t="n"/>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="47" t="inlineStr">
+        <is>
+          <t>「国の基本指針がまだ固まっていない」</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>「おっしゃるとおりです。ですので、指針を待つ部分（骨子・成果目標）と、待たなくてよい部分（アンケート集計・現状分析・人口推計）を分けて、待たなくてよい部分から先に進めておくご提案です。」</t>
+        </is>
+      </c>
+      <c r="C16" s="79" t="inlineStr">
+        <is>
+          <t>指針待ちは着手しない理由として最も多い。工程を二分して見せることが唯一の崩し方。</t>
+        </is>
+      </c>
+      <c r="D16" s="93" t="n"/>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="47" t="inlineStr">
+        <is>
+          <t>「議会を通るか分かりません」</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>「見積は要求のための資料としてお使いください。通らなければ次年度当初でご検討いただければ結構です。資料が無いと要求そのものができませんので、まずお持ちします。」</t>
+        </is>
+      </c>
+      <c r="C17" s="79" t="inlineStr">
+        <is>
+          <t>補正の可否を断定しない。「見積＝要求資料」と位置づけると、断る理由がなくなる。</t>
+        </is>
+      </c>
+      <c r="D17" s="93" t="n"/>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="47" t="inlineStr">
+        <is>
+          <t>「担当が異動したばかりで分からない」</t>
+        </is>
+      </c>
+      <c r="B18" s="63" t="inlineStr">
+        <is>
+          <t>「でしたら、前期の計画と実績の突合だけ、こちらで整理してお持ちしましょうか。次期に何を直すべきかが1枚で分かる形にします。」</t>
+        </is>
+      </c>
+      <c r="C18" s="79" t="inlineStr">
+        <is>
+          <t>異動直後は最大の機会。資料を作って持参するだけで、以後の相談相手になれる。</t>
+        </is>
+      </c>
+      <c r="D18" s="93" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t>この5分でやってはいけないこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="64" t="inlineStr">
+        <is>
+          <t>・「このままでは間に合いませんよ」と脅す ── 担当者の面目を潰した時点で、以後どの案件にも入れなくなる。</t>
+        </is>
+      </c>
+      <c r="B21" s="48" t="n"/>
+      <c r="C21" s="48" t="n"/>
+      <c r="D21" s="48" t="n"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="64" t="inlineStr">
+        <is>
+          <t>・保険料の上昇率を推測で口に出す ── 推計前の数字は、外れたときに議会・住民への説明を壊す。</t>
+        </is>
+      </c>
+      <c r="B22" s="48" t="n"/>
+      <c r="C22" s="48" t="n"/>
+      <c r="D22" s="48" t="n"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="64" t="inlineStr">
+        <is>
+          <t>・「補正で必ず取れます」と断定する ── 予算の可否は財政課と議会が決める。こちらは資料を用意する側。</t>
+        </is>
+      </c>
+      <c r="B23" s="48" t="n"/>
+      <c r="C23" s="48" t="n"/>
+      <c r="D23" s="48" t="n"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="64" t="inlineStr">
+        <is>
+          <t>・5分と言って10分話す ── 次のアポが取れなくなる。話し切れなければ「続きは資料でお持ちします」で切る。</t>
+        </is>
+      </c>
+      <c r="B24" s="48" t="n"/>
+      <c r="C24" s="48" t="n"/>
+      <c r="D24" s="48" t="n"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="64" t="inlineStr">
+        <is>
+          <t>・他団体の進捗を引き合いに出す ── 「△△町さんはもう委託されています」は、未公表情報の持ち込みになる。</t>
+        </is>
+      </c>
+      <c r="B25" s="48" t="n"/>
+      <c r="C25" s="48" t="n"/>
+      <c r="D25" s="48" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D6336C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="108" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="90" t="inlineStr">
-        <is>
-          <t>エリア</t>
-        </is>
-      </c>
-      <c r="B1" s="90" t="inlineStr">
-        <is>
-          <t>テーマ</t>
-        </is>
-      </c>
-      <c r="C1" s="90" t="inlineStr">
-        <is>
-          <t>結果</t>
-        </is>
-      </c>
-      <c r="D1" s="90" t="inlineStr">
-        <is>
-          <t>次回アクション</t>
-        </is>
-      </c>
-      <c r="E1" s="90" t="inlineStr">
-        <is>
-          <t>前回策定</t>
-        </is>
-      </c>
-      <c r="F1" s="90" t="inlineStr">
-        <is>
-          <t>改定時期</t>
-        </is>
-      </c>
-      <c r="G1" s="90" t="inlineStr">
-        <is>
-          <t>アプローチ時期</t>
-        </is>
-      </c>
-      <c r="H1" s="90" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="I1" s="90" t="inlineStr">
-        <is>
-          <t>契約予定</t>
-        </is>
-      </c>
-      <c r="J1" s="90" t="inlineStr">
-        <is>
-          <t>温度感</t>
-        </is>
-      </c>
-      <c r="K1" s="90" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="91" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="B2" s="91" t="inlineStr">
-        <is>
-          <t>公会計</t>
-        </is>
-      </c>
-      <c r="C2" s="91" t="inlineStr">
-        <is>
-          <t>見積提示</t>
-        </is>
-      </c>
-      <c r="D2" s="91" t="inlineStr">
-        <is>
-          <t>再アプローチ</t>
-        </is>
-      </c>
-      <c r="E2" s="91" t="inlineStr">
-        <is>
-          <t>委託</t>
-        </is>
-      </c>
-      <c r="F2" s="91" t="inlineStr">
-        <is>
-          <t>R6</t>
-        </is>
-      </c>
-      <c r="G2" s="91" t="inlineStr">
-        <is>
-          <t>今年度</t>
-        </is>
-      </c>
-      <c r="H2" s="91" t="inlineStr">
-        <is>
-          <t>初回訪問</t>
-        </is>
-      </c>
-      <c r="I2" s="91" t="inlineStr">
-        <is>
-          <t>入札</t>
-        </is>
-      </c>
-      <c r="J2" s="91" t="inlineStr">
-        <is>
-          <t>A：今年度中に動く</t>
-        </is>
-      </c>
-      <c r="K2" s="91" t="inlineStr">
-        <is>
-          <t>財務書類作成</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="91" t="inlineStr">
-        <is>
-          <t>青森県</t>
-        </is>
-      </c>
-      <c r="B3" s="91" t="inlineStr">
-        <is>
-          <t>会計支援</t>
-        </is>
-      </c>
-      <c r="C3" s="91" t="inlineStr">
-        <is>
-          <t>自力</t>
-        </is>
-      </c>
-      <c r="D3" s="91" t="inlineStr">
-        <is>
-          <t>見積提示</t>
-        </is>
-      </c>
-      <c r="E3" s="91" t="inlineStr">
-        <is>
-          <t>自前</t>
-        </is>
-      </c>
-      <c r="F3" s="91" t="inlineStr">
-        <is>
-          <t>R7</t>
-        </is>
-      </c>
-      <c r="G3" s="91" t="inlineStr">
-        <is>
-          <t>来年度</t>
-        </is>
-      </c>
-      <c r="H3" s="91" t="inlineStr">
-        <is>
-          <t>セカンドアプローチ</t>
-        </is>
-      </c>
-      <c r="I3" s="91" t="inlineStr">
-        <is>
-          <t>見積合わせ</t>
-        </is>
-      </c>
-      <c r="J3" s="91" t="inlineStr">
-        <is>
-          <t>B：次年度予算で検討</t>
-        </is>
-      </c>
-      <c r="K3" s="91" t="inlineStr">
-        <is>
-          <t>台帳精緻化（全体）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="91" t="inlineStr">
-        <is>
-          <t>岩手県</t>
-        </is>
-      </c>
-      <c r="B4" s="91" t="inlineStr">
-        <is>
-          <t>経営戦略</t>
-        </is>
-      </c>
-      <c r="C4" s="91" t="inlineStr">
-        <is>
-          <t>他社随契</t>
-        </is>
-      </c>
-      <c r="D4" s="91" t="inlineStr">
-        <is>
-          <t>同行依頼、再訪</t>
-        </is>
-      </c>
-      <c r="F4" s="91" t="inlineStr">
-        <is>
-          <t>R8</t>
-        </is>
-      </c>
-      <c r="G4" s="91" t="inlineStr">
-        <is>
-          <t>再来年度</t>
-        </is>
-      </c>
-      <c r="H4" s="91" t="inlineStr">
-        <is>
-          <t>見積提示</t>
-        </is>
-      </c>
-      <c r="I4" s="91" t="inlineStr">
-        <is>
-          <t>随契</t>
-        </is>
-      </c>
-      <c r="J4" s="91" t="inlineStr">
-        <is>
-          <t>C：様子見</t>
-        </is>
-      </c>
-      <c r="K4" s="91" t="inlineStr">
-        <is>
-          <t>台帳精緻化（所有外管理資産）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="91" t="inlineStr">
-        <is>
-          <t>宮城県</t>
-        </is>
-      </c>
-      <c r="B5" s="91" t="inlineStr">
-        <is>
-          <t>経営改善</t>
-        </is>
-      </c>
-      <c r="C5" s="91" t="inlineStr">
-        <is>
-          <t>不在</t>
-        </is>
-      </c>
-      <c r="D5" s="91" t="inlineStr">
-        <is>
-          <t>再訪不要</t>
-        </is>
-      </c>
-      <c r="F5" s="91" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="H5" s="91" t="inlineStr">
-        <is>
-          <t>見積＋仕様書</t>
-        </is>
-      </c>
-      <c r="I5" s="91" t="inlineStr">
-        <is>
-          <t>プロポ</t>
-        </is>
-      </c>
-      <c r="J5" s="91" t="inlineStr">
-        <is>
-          <t>D：当面なし</t>
-        </is>
-      </c>
-      <c r="K5" s="91" t="inlineStr">
-        <is>
-          <t>公会計システム導入</t>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>来期（R9年度）営業方針｜こども計画／地域福祉計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>どちらも努力義務の計画で、待っていても発注は生まれない。こどもは「制度が変わったので直さざるを得ない」、地域福祉は「束ねれば手間が減る」が崩し方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="95" t="inlineStr">
+        <is>
+          <t>こども計画・子ども子育て支援事業計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>見出し</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="91" t="inlineStr">
-        <is>
-          <t>秋田県</t>
-        </is>
-      </c>
-      <c r="B6" s="91" t="inlineStr">
-        <is>
-          <t>福祉計画</t>
-        </is>
-      </c>
-      <c r="C6" s="91" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="F6" s="91" t="inlineStr">
-        <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="K6" s="91" t="inlineStr">
-        <is>
-          <t>財務書類の活用支援・分析</t>
+      <c r="A6" s="52" t="inlineStr">
+        <is>
+          <t>現状認識</t>
+        </is>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>「国や道の強制力しだい」で様子見が多数派</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>訪問記録を見ると、こども計画について「子ども・子育て支援事業計画の改定タイミングで、国や県の温度感を見ながら判断する」「中間見直しは自前」という回答が複数の団体で並んでいる。努力義務であるため、待っていても発注は生まれない。待ちの姿勢を崩す材料を持ち込むのが来期の仕事。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="91" t="inlineStr">
-        <is>
-          <t>山形県</t>
-        </is>
-      </c>
-      <c r="B7" s="91" t="inlineStr">
-        <is>
-          <t>公共施設マネジメント</t>
-        </is>
-      </c>
-      <c r="F7" s="91" t="inlineStr">
-        <is>
-          <t>R11</t>
-        </is>
-      </c>
-      <c r="K7" s="91" t="inlineStr">
-        <is>
-          <t>職員研修（公会計）</t>
+      <c r="A7" s="53" t="inlineStr">
+        <is>
+          <t>狙い目①</t>
+        </is>
+      </c>
+      <c r="B7" s="49" t="inlineStr">
+        <is>
+          <t>第3期事業計画（R7〜11年度）の中間年の見直し</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>5年計画の中間年に、量の見込みと実績の乖離を踏まえて見直す。少子化の加速と利用率の変化で、第3期策定時の見込みから外れている団体が多い。区域別・年齢別の乖離率を一覧にして持参すると、見直しの必要性が数字で伝わる。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="91" t="inlineStr">
-        <is>
-          <t>福島県</t>
-        </is>
-      </c>
-      <c r="B8" s="91" t="inlineStr">
-        <is>
-          <t>社会生活計画</t>
-        </is>
-      </c>
-      <c r="F8" s="91" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
-      <c r="K8" s="91" t="inlineStr">
-        <is>
-          <t>公営企業会計 会計支援</t>
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>狙い目②</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>こども誰でも通園制度（乳児等通園支援事業）の反映</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>地域子ども・子育て支援事業に新たに位置付けられたため、量の見込みへの反映が必要になる。「制度が変わったので計画を直さなければならない」は、担当者が庁内を説得しやすい理由になる。中間見直しを提案する最も明確な入口。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="91" t="inlineStr">
-        <is>
-          <t>茨城県</t>
-        </is>
-      </c>
-      <c r="B9" s="91" t="inlineStr">
-        <is>
-          <t>その他計画</t>
-        </is>
-      </c>
-      <c r="F9" s="91" t="inlineStr">
-        <is>
-          <t>R13</t>
-        </is>
-      </c>
-      <c r="K9" s="91" t="inlineStr">
-        <is>
-          <t>公営企業会計 適用（法適化）支援</t>
+      <c r="A9" s="53" t="inlineStr">
+        <is>
+          <t>狙い目③</t>
+        </is>
+      </c>
+      <c r="B9" s="49" t="inlineStr">
+        <is>
+          <t>こども計画の新規策定（未策定団体）</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>こども基本法に基づく努力義務。子ども・若者計画、こどもの貧困対策計画、母子保健計画を統合できる。「別々に作っている計画を1本にまとめれば、次からの改定の手間が減る」という、事務負担の軽減を軸に話す。安くなるからではない。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="91" t="inlineStr">
-        <is>
-          <t>栃木県</t>
-        </is>
-      </c>
-      <c r="F10" s="91" t="inlineStr">
-        <is>
-          <t>R14</t>
-        </is>
-      </c>
-      <c r="K10" s="91" t="inlineStr">
-        <is>
-          <t>決算・決算統計 作成支援</t>
+      <c r="A10" s="96" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>地域子供の未来応援交付金／ヤングケアラー支援体制強化事業</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>こどもの貧困の実態調査・計画策定・支援体制整備に充当できる。調査業務の予算化に直結する。要綱と要望時期は毎年度変わるため、当年度資料で確認してから提示すること。「対象になり得るので要綱で確認を」で止め、断定しない。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="91" t="inlineStr">
-        <is>
-          <t>群馬県</t>
-        </is>
-      </c>
-      <c r="F11" s="91" t="inlineStr">
-        <is>
-          <t>R15</t>
-        </is>
-      </c>
-      <c r="K11" s="91" t="inlineStr">
-        <is>
-          <t>上下水道 経営戦略（策定）</t>
+      <c r="A11" s="56" t="inlineStr">
+        <is>
+          <t>提案の型</t>
+        </is>
+      </c>
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>調査と計画を分けて、二段で取る</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>実態調査（貧困・ヤングケアラー・こどもの意見聴取）を単独業務として先に受け、その結果を持って計画本体につなげる。調査は交付金が使え、金額も抑えられるため通りやすい。こども会議の設計・運営は策定年度以外でも受注できる。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="91" t="inlineStr">
-        <is>
-          <t>埼玉県</t>
-        </is>
-      </c>
-      <c r="F12" s="91" t="inlineStr">
-        <is>
-          <t>R16</t>
-        </is>
-      </c>
-      <c r="K12" s="91" t="inlineStr">
-        <is>
-          <t>上下水道 経営戦略（改定）</t>
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>接触先</t>
+        </is>
+      </c>
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>こども未来課・子育て支援課だけでは足りない</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>保育、母子保健（健康推進課）、教育委員会（放課後児童クラブ）に所管が分かれている。庁内横断の調整そのものが担当者の最大の負担なので、「関係課をまとめた進め方の案」を持っていくと提案価値になる。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="91" t="inlineStr">
-        <is>
-          <t>千葉県</t>
-        </is>
-      </c>
-      <c r="F13" s="91" t="inlineStr">
-        <is>
-          <t>R17</t>
-        </is>
-      </c>
-      <c r="K13" s="91" t="inlineStr">
-        <is>
-          <t>アセットマネジメント・ストックマネジメント</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="91" t="inlineStr">
-        <is>
-          <t>東京都</t>
-        </is>
-      </c>
-      <c r="F14" s="91" t="inlineStr">
-        <is>
-          <t>R18</t>
-        </is>
-      </c>
-      <c r="K14" s="91" t="inlineStr">
-        <is>
-          <t>病院事業 経営強化プラン</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="91" t="inlineStr">
-        <is>
-          <t>神奈川県</t>
-        </is>
-      </c>
-      <c r="F15" s="91" t="inlineStr">
-        <is>
-          <t>R19</t>
-        </is>
-      </c>
-      <c r="K15" s="91" t="inlineStr">
-        <is>
-          <t>料金・使用料改定</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="91" t="inlineStr">
-        <is>
-          <t>新潟県</t>
-        </is>
-      </c>
-      <c r="F16" s="91" t="inlineStr">
-        <is>
-          <t>R20</t>
-        </is>
-      </c>
-      <c r="K16" s="91" t="inlineStr">
-        <is>
-          <t>経営分析（経営比較分析表の活用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="91" t="inlineStr">
-        <is>
-          <t>富山県</t>
-        </is>
-      </c>
-      <c r="K17" s="91" t="inlineStr">
-        <is>
-          <t>広域化・官民連携 検討支援</t>
+      <c r="A13" s="59" t="inlineStr">
+        <is>
+          <t>タイムライン</t>
+        </is>
+      </c>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>R8年度中に予算化まで持ち込む</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R9年度当初予算での発注を狙うなら、R8年8〜10月に情報提供と参考見積、11〜12月に査定対応、1〜3月に公告。中間見直しを補正で狙う場合は、9月補正はすでに間に合わないため12月補正（要求は11月上旬）を目標にする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="97" t="inlineStr">
+        <is>
+          <t>地域福祉計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B17" s="39" t="inlineStr">
+        <is>
+          <t>見出し</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="inlineStr">
+        <is>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="91" t="inlineStr">
-        <is>
-          <t>石川県</t>
-        </is>
-      </c>
-      <c r="K18" s="91" t="inlineStr">
-        <is>
-          <t>高齢者福祉計画・介護保険事業計画</t>
+      <c r="A18" s="52" t="inlineStr">
+        <is>
+          <t>現状認識</t>
+        </is>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>単発で取ると小さい。束ねて初めて中規模案件になる</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉計画そのものは金額が大きくない。併載できる計画と、社協の地域福祉活動計画を合わせて初めて採算に乗る。訪問記録にも「複数計画を地域福祉計画で一本化したい」という団体が実在しており、需要側の要望とも一致する。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="91" t="inlineStr">
-        <is>
-          <t>福井県</t>
-        </is>
-      </c>
-      <c r="K19" s="91" t="inlineStr">
-        <is>
-          <t>障害者計画・障害福祉計画・障害児福祉計画</t>
+      <c r="A19" s="53" t="inlineStr">
+        <is>
+          <t>狙い目①</t>
+        </is>
+      </c>
+      <c r="B19" s="49" t="inlineStr">
+        <is>
+          <t>成年後見制度利用促進基本計画の改定期</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>国の第二期基本計画が令和8年度で終期を迎え、第三期に移る。これに合わせて市町村計画を改定する団体が出るため、来期の有力な入口になる。中核機関が未設置の団体では、計画策定と体制整備をあわせて提案できる。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="91" t="inlineStr">
-        <is>
-          <t>山梨県</t>
-        </is>
-      </c>
-      <c r="K20" s="91" t="inlineStr">
-        <is>
-          <t>地域福祉計画</t>
+      <c r="A20" s="53" t="inlineStr">
+        <is>
+          <t>狙い目②</t>
+        </is>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>重層的支援体制整備事業</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>未実施の団体には移行準備事業、実施済みの団体には実施計画の策定と体制強化。移行すると介護・障害・こども・困窮の相談支援等の補助が一体的に交付される点が説得材料になる。ただし最大の壁は庁内合意なので、計画の前段として庁内勉強会・業務フロー整理の伴走を提案する。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="91" t="inlineStr">
-        <is>
-          <t>長野県</t>
-        </is>
-      </c>
-      <c r="K21" s="91" t="inlineStr">
-        <is>
-          <t>こども計画</t>
+      <c r="A21" s="53" t="inlineStr">
+        <is>
+          <t>狙い目③</t>
+        </is>
+      </c>
+      <c r="B21" s="49" t="inlineStr">
+        <is>
+          <t>自殺対策計画（地域自殺対策強化交付金）</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>策定が義務であり、交付金を計画の策定・改定に充当できる。地域福祉計画に併載する形にすれば、財源のある計画が本体を引っ張る構図が作れる。JSCPの地域自殺実態プロファイルを使えば、重点施策を客観データで組める。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="91" t="inlineStr">
-        <is>
-          <t>岐阜県</t>
-        </is>
-      </c>
-      <c r="K22" s="91" t="inlineStr">
-        <is>
-          <t>子ども子育て支援事業計画</t>
+      <c r="A22" s="56" t="inlineStr">
+        <is>
+          <t>提案の型</t>
+        </is>
+      </c>
+      <c r="B22" s="47" t="inlineStr">
+        <is>
+          <t>自治体と社会福祉協議会の両方に当たる</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉計画（自治体）と地域福祉活動計画（社協）を一体で策定すると、発注元が2つになり予算を合算できる。社協は自治体より意思決定が早いことが多く、社協側から自治体を動かせる場合もある。どちらか一方だけを訪問している状態は、機会を半分捨てている。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="91" t="inlineStr">
-        <is>
-          <t>静岡県</t>
-        </is>
-      </c>
-      <c r="K23" s="91" t="inlineStr">
-        <is>
-          <t>重層的支援体制整備事業 支援</t>
+      <c r="A23" s="56" t="inlineStr">
+        <is>
+          <t>提案の型</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>併載計画の一覧を作って持参する</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>成年後見・再犯防止・自殺対策・孤独孤立・生活困窮・避難行動要支援者・居住支援。担当自治体それぞれについて、どの計画がいつ切れるかを一覧にして見せる。「バラバラに作ると毎年どれかの改定が来るが、束ねれば数年に一度で済む」が最も効く言い方。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="91" t="inlineStr">
-        <is>
-          <t>愛知県</t>
-        </is>
-      </c>
-      <c r="K24" s="91" t="inlineStr">
-        <is>
-          <t>福祉分野 アンケート調査（単独受託）</t>
+      <c r="A24" s="98" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="B24" s="47" t="inlineStr">
+        <is>
+          <t>圏域と進捗評価が実務の争点になる</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>圏域が計画ごとにバラバラ（日常生活圏域／小学校区／地区社協）な団体が多く、整理そのものを業務に含められる。また前計画の進捗評価の仕組みが無い団体が大半なので、指標設計と年次評価の仕組みづくりを提案に入れると、他社の標準的な策定業務と差がつく。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="91" t="inlineStr">
-        <is>
-          <t>三重県</t>
-        </is>
-      </c>
-      <c r="K25" s="91" t="inlineStr">
-        <is>
-          <t>公共施設等総合管理計画</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="91" t="inlineStr">
-        <is>
-          <t>滋賀県</t>
-        </is>
-      </c>
-      <c r="K26" s="91" t="inlineStr">
-        <is>
-          <t>個別施設計画</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="91" t="inlineStr">
-        <is>
-          <t>京都府</t>
-        </is>
-      </c>
-      <c r="K27" s="91" t="inlineStr">
-        <is>
-          <t>施設カルテ・施設白書</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="91" t="inlineStr">
-        <is>
-          <t>大阪府</t>
-        </is>
-      </c>
-      <c r="K28" s="91" t="inlineStr">
-        <is>
-          <t>公共施設 再編・適正配置検討</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="91" t="inlineStr">
-        <is>
-          <t>兵庫県</t>
-        </is>
-      </c>
-      <c r="K29" s="91" t="inlineStr">
-        <is>
-          <t>健康増進計画・食育推進計画</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="91" t="inlineStr">
-        <is>
-          <t>奈良県</t>
-        </is>
-      </c>
-      <c r="K30" s="91" t="inlineStr">
-        <is>
-          <t>自殺対策計画</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="91" t="inlineStr">
-        <is>
-          <t>和歌山県</t>
-        </is>
-      </c>
-      <c r="K31" s="91" t="inlineStr">
-        <is>
-          <t>男女共同参画計画</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="91" t="inlineStr">
-        <is>
-          <t>鳥取県</t>
-        </is>
-      </c>
-      <c r="K32" s="91" t="inlineStr">
-        <is>
-          <t>環境基本計画</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="91" t="inlineStr">
-        <is>
-          <t>島根県</t>
-        </is>
-      </c>
-      <c r="K33" s="91" t="inlineStr">
-        <is>
-          <t>地域公共交通計画</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="91" t="inlineStr">
-        <is>
-          <t>岡山県</t>
-        </is>
-      </c>
-      <c r="K34" s="91" t="inlineStr">
-        <is>
-          <t>文化財保存活用地域計画</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="91" t="inlineStr">
-        <is>
-          <t>広島県</t>
-        </is>
-      </c>
-      <c r="K35" s="91" t="inlineStr">
-        <is>
-          <t>総合計画</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="91" t="inlineStr">
-        <is>
-          <t>山口県</t>
-        </is>
-      </c>
-      <c r="K36" s="91" t="inlineStr">
-        <is>
-          <t>財政計画・中期財政推計</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="91" t="inlineStr">
-        <is>
-          <t>徳島県</t>
-        </is>
-      </c>
-      <c r="K37" s="91" t="inlineStr">
-        <is>
-          <t>農業振興計画・地域計画</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="91" t="inlineStr">
-        <is>
-          <t>香川県</t>
-        </is>
-      </c>
-      <c r="K38" s="91" t="inlineStr">
-        <is>
-          <t>国土強靱化地域計画</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="91" t="inlineStr">
-        <is>
-          <t>愛媛県</t>
-        </is>
-      </c>
-      <c r="K39" s="91" t="inlineStr">
-        <is>
-          <t>その他（上記以外）</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="91" t="inlineStr">
-        <is>
-          <t>高知県</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="91" t="inlineStr">
-        <is>
-          <t>福岡県</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="91" t="inlineStr">
-        <is>
-          <t>佐賀県</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="91" t="inlineStr">
-        <is>
-          <t>長崎県</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="91" t="inlineStr">
-        <is>
-          <t>熊本県</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="91" t="inlineStr">
-        <is>
-          <t>大分県</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="91" t="inlineStr">
-        <is>
-          <t>宮崎県</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="91" t="inlineStr">
-        <is>
-          <t>鹿児島県</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="91" t="inlineStr">
-        <is>
-          <t>沖縄県</t>
+      <c r="A25" s="59" t="inlineStr">
+        <is>
+          <t>タイムライン</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>R8年8〜10月が勝負</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉計画は複数課・社協との調整が要るため、予算要求の準備に時間がかかる。R8年8〜10月に併載計画の一覧と一体策定案を提示し、11〜12月の査定を越える。社協への接触は自治体と同時期に始める。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A16:C16"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21768,6 +21720,854 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="99" t="inlineStr">
+        <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="B1" s="99" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="C1" s="99" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="D1" s="99" t="inlineStr">
+        <is>
+          <t>次回アクション</t>
+        </is>
+      </c>
+      <c r="E1" s="99" t="inlineStr">
+        <is>
+          <t>前回策定</t>
+        </is>
+      </c>
+      <c r="F1" s="99" t="inlineStr">
+        <is>
+          <t>改定時期</t>
+        </is>
+      </c>
+      <c r="G1" s="99" t="inlineStr">
+        <is>
+          <t>アプローチ時期</t>
+        </is>
+      </c>
+      <c r="H1" s="99" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="I1" s="99" t="inlineStr">
+        <is>
+          <t>契約予定</t>
+        </is>
+      </c>
+      <c r="J1" s="99" t="inlineStr">
+        <is>
+          <t>温度感</t>
+        </is>
+      </c>
+      <c r="K1" s="99" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="100" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="B2" s="100" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="C2" s="100" t="inlineStr">
+        <is>
+          <t>見積提示</t>
+        </is>
+      </c>
+      <c r="D2" s="100" t="inlineStr">
+        <is>
+          <t>再アプローチ</t>
+        </is>
+      </c>
+      <c r="E2" s="100" t="inlineStr">
+        <is>
+          <t>委託</t>
+        </is>
+      </c>
+      <c r="F2" s="100" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="G2" s="100" t="inlineStr">
+        <is>
+          <t>今年度</t>
+        </is>
+      </c>
+      <c r="H2" s="100" t="inlineStr">
+        <is>
+          <t>初回訪問</t>
+        </is>
+      </c>
+      <c r="I2" s="100" t="inlineStr">
+        <is>
+          <t>入札</t>
+        </is>
+      </c>
+      <c r="J2" s="100" t="inlineStr">
+        <is>
+          <t>A：今年度中に動く</t>
+        </is>
+      </c>
+      <c r="K2" s="100" t="inlineStr">
+        <is>
+          <t>財務書類作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="100" t="inlineStr">
+        <is>
+          <t>青森県</t>
+        </is>
+      </c>
+      <c r="B3" s="100" t="inlineStr">
+        <is>
+          <t>会計支援</t>
+        </is>
+      </c>
+      <c r="C3" s="100" t="inlineStr">
+        <is>
+          <t>自力</t>
+        </is>
+      </c>
+      <c r="D3" s="100" t="inlineStr">
+        <is>
+          <t>見積提示</t>
+        </is>
+      </c>
+      <c r="E3" s="100" t="inlineStr">
+        <is>
+          <t>自前</t>
+        </is>
+      </c>
+      <c r="F3" s="100" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="G3" s="100" t="inlineStr">
+        <is>
+          <t>来年度</t>
+        </is>
+      </c>
+      <c r="H3" s="100" t="inlineStr">
+        <is>
+          <t>セカンドアプローチ</t>
+        </is>
+      </c>
+      <c r="I3" s="100" t="inlineStr">
+        <is>
+          <t>見積合わせ</t>
+        </is>
+      </c>
+      <c r="J3" s="100" t="inlineStr">
+        <is>
+          <t>B：次年度予算で検討</t>
+        </is>
+      </c>
+      <c r="K3" s="100" t="inlineStr">
+        <is>
+          <t>台帳精緻化（全体）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="100" t="inlineStr">
+        <is>
+          <t>岩手県</t>
+        </is>
+      </c>
+      <c r="B4" s="100" t="inlineStr">
+        <is>
+          <t>経営戦略</t>
+        </is>
+      </c>
+      <c r="C4" s="100" t="inlineStr">
+        <is>
+          <t>他社随契</t>
+        </is>
+      </c>
+      <c r="D4" s="100" t="inlineStr">
+        <is>
+          <t>同行依頼、再訪</t>
+        </is>
+      </c>
+      <c r="F4" s="100" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="G4" s="100" t="inlineStr">
+        <is>
+          <t>再来年度</t>
+        </is>
+      </c>
+      <c r="H4" s="100" t="inlineStr">
+        <is>
+          <t>見積提示</t>
+        </is>
+      </c>
+      <c r="I4" s="100" t="inlineStr">
+        <is>
+          <t>随契</t>
+        </is>
+      </c>
+      <c r="J4" s="100" t="inlineStr">
+        <is>
+          <t>C：様子見</t>
+        </is>
+      </c>
+      <c r="K4" s="100" t="inlineStr">
+        <is>
+          <t>台帳精緻化（所有外管理資産）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="100" t="inlineStr">
+        <is>
+          <t>宮城県</t>
+        </is>
+      </c>
+      <c r="B5" s="100" t="inlineStr">
+        <is>
+          <t>経営改善</t>
+        </is>
+      </c>
+      <c r="C5" s="100" t="inlineStr">
+        <is>
+          <t>不在</t>
+        </is>
+      </c>
+      <c r="D5" s="100" t="inlineStr">
+        <is>
+          <t>再訪不要</t>
+        </is>
+      </c>
+      <c r="F5" s="100" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="H5" s="100" t="inlineStr">
+        <is>
+          <t>見積＋仕様書</t>
+        </is>
+      </c>
+      <c r="I5" s="100" t="inlineStr">
+        <is>
+          <t>プロポ</t>
+        </is>
+      </c>
+      <c r="J5" s="100" t="inlineStr">
+        <is>
+          <t>D：当面なし</t>
+        </is>
+      </c>
+      <c r="K5" s="100" t="inlineStr">
+        <is>
+          <t>公会計システム導入</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="100" t="inlineStr">
+        <is>
+          <t>秋田県</t>
+        </is>
+      </c>
+      <c r="B6" s="100" t="inlineStr">
+        <is>
+          <t>福祉計画</t>
+        </is>
+      </c>
+      <c r="C6" s="100" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="F6" s="100" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="K6" s="100" t="inlineStr">
+        <is>
+          <t>財務書類の活用支援・分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="100" t="inlineStr">
+        <is>
+          <t>山形県</t>
+        </is>
+      </c>
+      <c r="B7" s="100" t="inlineStr">
+        <is>
+          <t>公共施設マネジメント</t>
+        </is>
+      </c>
+      <c r="F7" s="100" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="K7" s="100" t="inlineStr">
+        <is>
+          <t>職員研修（公会計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="100" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="B8" s="100" t="inlineStr">
+        <is>
+          <t>社会生活計画</t>
+        </is>
+      </c>
+      <c r="F8" s="100" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="K8" s="100" t="inlineStr">
+        <is>
+          <t>公営企業会計 会計支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="100" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="B9" s="100" t="inlineStr">
+        <is>
+          <t>その他計画</t>
+        </is>
+      </c>
+      <c r="F9" s="100" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="K9" s="100" t="inlineStr">
+        <is>
+          <t>公営企業会計 適用（法適化）支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="100" t="inlineStr">
+        <is>
+          <t>栃木県</t>
+        </is>
+      </c>
+      <c r="F10" s="100" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="K10" s="100" t="inlineStr">
+        <is>
+          <t>決算・決算統計 作成支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="100" t="inlineStr">
+        <is>
+          <t>群馬県</t>
+        </is>
+      </c>
+      <c r="F11" s="100" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="K11" s="100" t="inlineStr">
+        <is>
+          <t>上下水道 経営戦略（策定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="100" t="inlineStr">
+        <is>
+          <t>埼玉県</t>
+        </is>
+      </c>
+      <c r="F12" s="100" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="K12" s="100" t="inlineStr">
+        <is>
+          <t>上下水道 経営戦略（改定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="100" t="inlineStr">
+        <is>
+          <t>千葉県</t>
+        </is>
+      </c>
+      <c r="F13" s="100" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="K13" s="100" t="inlineStr">
+        <is>
+          <t>アセットマネジメント・ストックマネジメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="100" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="F14" s="100" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="K14" s="100" t="inlineStr">
+        <is>
+          <t>病院事業 経営強化プラン</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="100" t="inlineStr">
+        <is>
+          <t>神奈川県</t>
+        </is>
+      </c>
+      <c r="F15" s="100" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="K15" s="100" t="inlineStr">
+        <is>
+          <t>料金・使用料改定</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="100" t="inlineStr">
+        <is>
+          <t>新潟県</t>
+        </is>
+      </c>
+      <c r="F16" s="100" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="K16" s="100" t="inlineStr">
+        <is>
+          <t>経営分析（経営比較分析表の活用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="100" t="inlineStr">
+        <is>
+          <t>富山県</t>
+        </is>
+      </c>
+      <c r="K17" s="100" t="inlineStr">
+        <is>
+          <t>広域化・官民連携 検討支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="100" t="inlineStr">
+        <is>
+          <t>石川県</t>
+        </is>
+      </c>
+      <c r="K18" s="100" t="inlineStr">
+        <is>
+          <t>高齢者福祉計画・介護保険事業計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="100" t="inlineStr">
+        <is>
+          <t>福井県</t>
+        </is>
+      </c>
+      <c r="K19" s="100" t="inlineStr">
+        <is>
+          <t>障害者計画・障害福祉計画・障害児福祉計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="100" t="inlineStr">
+        <is>
+          <t>山梨県</t>
+        </is>
+      </c>
+      <c r="K20" s="100" t="inlineStr">
+        <is>
+          <t>地域福祉計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="100" t="inlineStr">
+        <is>
+          <t>長野県</t>
+        </is>
+      </c>
+      <c r="K21" s="100" t="inlineStr">
+        <is>
+          <t>こども計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="100" t="inlineStr">
+        <is>
+          <t>岐阜県</t>
+        </is>
+      </c>
+      <c r="K22" s="100" t="inlineStr">
+        <is>
+          <t>子ども子育て支援事業計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="100" t="inlineStr">
+        <is>
+          <t>静岡県</t>
+        </is>
+      </c>
+      <c r="K23" s="100" t="inlineStr">
+        <is>
+          <t>重層的支援体制整備事業 支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="100" t="inlineStr">
+        <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="K24" s="100" t="inlineStr">
+        <is>
+          <t>福祉分野 アンケート調査（単独受託）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="100" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="K25" s="100" t="inlineStr">
+        <is>
+          <t>公共施設等総合管理計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="100" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="K26" s="100" t="inlineStr">
+        <is>
+          <t>個別施設計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="100" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="K27" s="100" t="inlineStr">
+        <is>
+          <t>施設カルテ・施設白書</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="100" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="K28" s="100" t="inlineStr">
+        <is>
+          <t>公共施設 再編・適正配置検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="100" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="K29" s="100" t="inlineStr">
+        <is>
+          <t>健康増進計画・食育推進計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="100" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="K30" s="100" t="inlineStr">
+        <is>
+          <t>自殺対策計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="100" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="K31" s="100" t="inlineStr">
+        <is>
+          <t>男女共同参画計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="100" t="inlineStr">
+        <is>
+          <t>鳥取県</t>
+        </is>
+      </c>
+      <c r="K32" s="100" t="inlineStr">
+        <is>
+          <t>環境基本計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="100" t="inlineStr">
+        <is>
+          <t>島根県</t>
+        </is>
+      </c>
+      <c r="K33" s="100" t="inlineStr">
+        <is>
+          <t>地域公共交通計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="100" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="K34" s="100" t="inlineStr">
+        <is>
+          <t>文化財保存活用地域計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="100" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="K35" s="100" t="inlineStr">
+        <is>
+          <t>総合計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="100" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="K36" s="100" t="inlineStr">
+        <is>
+          <t>財政計画・中期財政推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="100" t="inlineStr">
+        <is>
+          <t>徳島県</t>
+        </is>
+      </c>
+      <c r="K37" s="100" t="inlineStr">
+        <is>
+          <t>農業振興計画・地域計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="100" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="K38" s="100" t="inlineStr">
+        <is>
+          <t>国土強靱化地域計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="100" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="K39" s="100" t="inlineStr">
+        <is>
+          <t>その他（上記以外）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="100" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="100" t="inlineStr">
+        <is>
+          <t>福岡県</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="100" t="inlineStr">
+        <is>
+          <t>佐賀県</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="100" t="inlineStr">
+        <is>
+          <t>長崎県</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="100" t="inlineStr">
+        <is>
+          <t>熊本県</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="100" t="inlineStr">
+        <is>
+          <t>大分県</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="100" t="inlineStr">
+        <is>
+          <t>宮崎県</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="100" t="inlineStr">
+        <is>
+          <t>鹿児島県</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="100" t="inlineStr">
+        <is>
+          <t>沖縄県</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/10_新人教育カリキュラム_マスター管理表.xlsx
+++ b/output/10_新人教育カリキュラム_マスター管理表.xlsx
@@ -34,9 +34,10 @@
     <sheet name="24_訪問記録CSV_入力シート" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="25_CSV入力規則" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="26_テーマ・タイトル標準リスト" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="27_5分トーク_高齢者(自前先)" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="28_来期営業方針_こども・地域福祉" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="選択肢マスタ" sheetId="30" state="hidden" r:id="rId30"/>
+    <sheet name="27_5分トーク集" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="28_5分トーク_想定問答とNG" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="29_来期営業方針_こども・地域福祉" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="選択肢マスタ" sheetId="31" state="hidden" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_月次ロードマップ'!$A$4:$I$40</definedName>
@@ -60,7 +61,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'24_訪問記録CSV_入力シート'!$A$1:$O$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'25_CSV入力規則'!$A$4:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'26_テーマ・タイトル標準リスト'!$A$4:$D$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="27">'27_5分トーク_高齢者(自前先)'!$A$1:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'27_5分トーク集'!$A$13:$E$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'28_5分トーク_想定問答とNG'!$A$5:$D$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -69,7 +71,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -141,12 +143,6 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="41">
@@ -469,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -724,20 +720,26 @@
     <xf numFmtId="0" fontId="12" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1119,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1352,104 +1354,112 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　27_5分トーク_高齢者(自前先)… 自前作成先から補正予算を取る5分の台本と想定問答</t>
+          <t xml:space="preserve">　27_5分トーク集… 5ケースの台本（高齢者の補正予算／所有外／公共施設／他社随契／不在時）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　28_来期営業方針_こども・地域福祉… R9年度に向けた2テーマの攻め方</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+          <t xml:space="preserve">　28_5分トーク_想定問答とNG… 断られ方の型と切り返し、言ってはいけないこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　29_来期営業方針_こども・地域福祉… R9年度に向けた2テーマの攻め方</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>4. 運用サイクル（推奨）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　毎月　　… 上長と本人で30分の面談。当月の学習項目と習得目標の達成状況を確認し、翌月の重点を決める。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　四半期　… 成果物レビューを1件必ず実施し、「確認方法」欄の方法で到達度を確認する。</t>
+          <t xml:space="preserve">　毎月　　… 上長と本人で30分の面談。当月の学習項目と習得目標の達成状況を確認し、翌月の重点を決める。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　半期　　… 12_個人別チェックシートで自己評価と上長評価を突き合わせ、差異の原因を対話する。</t>
+          <t xml:space="preserve">　四半期　… 成果物レビューを1件必ず実施し、「確認方法」欄の方法で到達度を確認する。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　半期　　… 12_個人別チェックシートで自己評価と上長評価を突き合わせ、差異の原因を対話する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　年次　　… レベル判定を確定し、次年度の主担当・副担当テーマと育成計画を決定する。</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>5. レベル判定の原則</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　・「知っている」ではなく「できた実績があるか」で判定します。判定には必ず具体的な案件名・成果物名を紐づけてください。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・1つの項目でL3と判定するには、原則として同種の作業を2案件以上、単独で完遂している必要があります。</t>
+          <t xml:space="preserve">　・「知っている」ではなく「できた実績があるか」で判定します。判定には必ず具体的な案件名・成果物名を紐づけてください。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　・1つの項目でL3と判定するには、原則として同種の作業を2案件以上、単独で完遂している必要があります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　・自己評価と上長評価に2段階以上の差がある場合は、必ず面談で認識を合わせてください。</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>6. 更新について</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　・制度改正（基本指針、報酬改定、会計基準、各省ガイドライン等）が生じた場合は、該当テーマシートの学習内容を年1回見直してください。</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　・制度改正（基本指針、報酬改定、会計基準、各省ガイドライン等）が生じた場合は、該当テーマシートの学習内容を年1回見直してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　・計画の「期」（第○期）は年度の経過とともに進みます。テーマシートの記載は根拠法と期間の考え方を示すもので、具体の期・年度は都度確認してください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="46">
     <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A15:H15"/>
@@ -1457,7 +1467,6 @@
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A49:H49"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A45:H45"/>
     <mergeCell ref="A6:H6"/>
@@ -1465,6 +1474,7 @@
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A46:H46"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A12:H12"/>
@@ -1486,12 +1496,12 @@
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A44:H44"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
@@ -19276,734 +19286,1752 @@
   <sheetPr>
     <tabColor rgb="002CA02C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="84" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="76" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5分トーク｜高齢者・自前作成先からの補正予算獲得</t>
+          <t>5分トーク集（L2〜L3）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>対象は第10期（R9〜11年度）介護保険事業計画を自前で作っている自治体。R9年4月からの保険料賦課にはR9年3月議会での条例改正が必要で、そこから逆算すると10月末までに分析が終わっていないとパブリックコメントの期間が取れない。その一点だけを伝える5分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+          <t>訪問記録141件の分布に合わせて5ケース。台詞は暗記するものではなく、意図を理解したうえで自分の言葉に直して使う。◯◯・△△は訪問前に必ず埋める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="90" t="inlineStr">
+        <is>
+          <t>ケース一覧 ── この5分で伝えることは1ケースにつき1つだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="60" t="inlineStr"/>
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="C5" s="60" t="inlineStr">
+        <is>
+          <t>ケース</t>
+        </is>
+      </c>
+      <c r="D5" s="60" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="E5" s="60" t="inlineStr">
+        <is>
+          <t>この5分の軸（伝えることは1つ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>自前作成先からの補正予算獲得</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>第10期（R9〜11年度）介護保険事業計画を自前で作っている自治体</t>
+        </is>
+      </c>
+      <c r="E6" s="91" t="inlineStr">
+        <is>
+          <t>R9年4月から保険料を賦課するにはR9年3月議会での条例改正が必要。逆算すると10月末までに分析が終わっていないとパブリックコメントの期間が取れない。自治体側が動かせない制約なので、こちらの都合ではなく相手の制約として話せる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>公会計</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>所有外管理資産（セミナー案内後のフォロー）</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>財務書類は作成済みで、固定資産台帳の精緻化が手つかずの自治体。セミナーを案内した先。</t>
+        </is>
+      </c>
+      <c r="E7" s="91" t="inlineStr">
+        <is>
+          <t>台帳の資産額が実態より少ないと、有形固定資産減価償却率がずれ、総合管理計画の更新費用試算の前提が崩れ、起債・交付金の裏付けも弱くなる。台帳は公会計だけの話ではなく、施設と財源の話につながっている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>公共施設マネジメント</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>総合管理計画の改定（起債要件から入る）</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>公共施設等総合管理計画の改定時期がR9〜R10に来る自治体</t>
+        </is>
+      </c>
+      <c r="E8" s="91" t="inlineStr">
+        <is>
+          <t>公共施設等適正管理推進事業債は、総合管理計画に基づく事業であることが要件。裏を返せば、計画に書かれていない事業は起債の対象にならない。計画改定は「作り直し」ではなく「財源を使えるようにする作業」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>会計支援・経営戦略ほか</t>
+        </is>
+      </c>
+      <c r="C9" s="47" t="inlineStr">
+        <is>
+          <t>他社随契先への切り込み</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>現在ほかの会社と随意契約している自治体。訪問記録では他社随契20件のうち7件が「再訪不要」で打ち切られているが、改定時期はR9〜R14と先の団体が多い。</t>
+        </is>
+      </c>
+      <c r="E9" s="91" t="inlineStr">
+        <is>
+          <t>随意契約は「変える理由がない」から続いている。変えさせようとするのではなく、契約範囲に入っていない隣の業務を取る。そして改定年度の前年度に必ず戻る。随契が切れる機会は、担当者の交代と改定年度しかない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>全テーマ共通</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>担当者が不在だったときの3分</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>訪問先で担当者が不在だった場合。訪問記録では不在が15件あり、すべて「再アプローチ」としているが、備考に再訪日まで書けている記録は一部にとどまる。</t>
+        </is>
+      </c>
+      <c r="E10" s="91" t="inlineStr">
+        <is>
+          <t>不在は失敗ではなく、次を作る機会。受付で3つ確認し、1枚置いて帰る。何も置かずに帰ると、訪問した事実が相手側に何も残らない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="90" t="inlineStr">
+        <is>
+          <t>スクリプト</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="60" t="inlineStr"/>
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>見出し</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr">
         <is>
           <t>話す内容（スクリプト）</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>ねらい</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="90" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B14" s="93" t="inlineStr">
         <is>
           <t>0:00–0:30</t>
         </is>
       </c>
-      <c r="B5" s="47" t="inlineStr">
+      <c r="C14" s="47" t="inlineStr">
         <is>
           <t>用件を告げ、5分だけもらう</t>
         </is>
       </c>
-      <c r="C5" s="63" t="inlineStr">
+      <c r="D14" s="63" t="inlineStr">
         <is>
           <t>「◯◯町の高齢福祉課様でいらっしゃいますね。◯◯株式会社の△△と申します。第10期の介護保険事業計画の件で、5分だけお時間をいただけますでしょうか。御町ではご自身で作られていると伺っておりまして、この時期にお伝えしておいたほうがよいことが2点ございます。」</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>「自前で作っている」ことを知っている＝下調べ済みだと最初に伝える。売り込みではなく「時期の話」として入る。5分と明示すると断られにくい。</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="91" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B15" s="93" t="inlineStr">
         <is>
           <t>0:30–1:30</t>
         </is>
       </c>
-      <c r="B6" s="49" t="inlineStr">
+      <c r="C15" s="47" t="inlineStr">
         <is>
           <t>進捗を3問だけ聞く</t>
         </is>
       </c>
-      <c r="C6" s="65" t="inlineStr">
+      <c r="D15" s="63" t="inlineStr">
         <is>
           <t>「①ニーズ調査と在宅介護実態調査の集計は、もうお済みでしょうか。」
 「②保険料の算定は、どなたがご担当される予定でしょうか。」
 「③3月議会での条例改正に向けて、パブリックコメントはいつ頃を想定されていますか。」</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>この3問で自前完遂の可否がほぼ判定できる。①が未了、②が未定、③が「これから考える」なら高い確率で間に合わない。詰問にならないよう、3問で止めて次へ進む。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="90" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>この3問で自前完遂の可否がほぼ判定できる。①が未了、②が未定、③が「これから考える」なら高い確率で間に合わない。詰問にならないよう3問で止める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B16" s="93" t="inlineStr">
         <is>
           <t>1:30–3:00</t>
         </is>
       </c>
-      <c r="B7" s="47" t="inlineStr">
+      <c r="C16" s="47" t="inlineStr">
         <is>
           <t>逆算して見せる（本題）</t>
         </is>
       </c>
-      <c r="C7" s="63" t="inlineStr">
+      <c r="D16" s="63" t="inlineStr">
         <is>
           <t>「第10期の保険料は、R9年4月から賦課するためにR9年3月議会での条例改正が要ります。そこから逆算しますと──2月下旬に議案上程、その前に1〜2月でパブリックコメント（30日程度）、その前の12〜1月で保険料の確定と計画素案、11月に給付費推計とサービス見込量、10月までに現状分析。つまり10月末までに分析が終わっていないと、パブコメの期間が取れなくなります。」</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>計画策定業務ではなく「条例改正の期限」から話す。ここは自治体側が動かせない制約なので、こちらの都合ではなく相手の制約として受け取ってもらえる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="91" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>計画策定業務ではなく「条例改正の期限」から話す。自治体側が動かせない制約なので、こちらの都合ではなく相手の制約として受け取ってもらえる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B17" s="93" t="inlineStr">
         <is>
           <t>3:00–4:00</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>部分委託という逃げ道を示す</t>
         </is>
       </c>
-      <c r="C8" s="65" t="inlineStr">
+      <c r="D17" s="63" t="inlineStr">
         <is>
           <t>「全部をお預けいただく必要はありません。いちばん時間がかかるのは保険料の算定と給付費推計で、ここは見える化システムと厚労省のワークシートを使った作業です。ここだけをお預かりして、計画本文は御町で書いていただく、という切り分けができます。この形なら金額も抑えられますので、12月補正で十分間に合います。」</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>全部委託は補正で通りにくい（金額が大きい・査定に耐えない）。「作れない」ではなく「時間がかかる工程だけ外に出す」と提示すると、担当者の面目も立つ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="90" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>全部委託は補正で通りにくい（金額が大きく査定に耐えない）。「作れない」ではなく「時間がかかる工程だけ外に出す」と提示すると、担当者の面目も立つ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B18" s="93" t="inlineStr">
         <is>
           <t>4:00–5:00</t>
         </is>
       </c>
-      <c r="B9" s="47" t="inlineStr">
+      <c r="C18" s="47" t="inlineStr">
         <is>
           <t>次を決めて帰る</t>
         </is>
       </c>
-      <c r="C9" s="63" t="inlineStr">
+      <c r="D18" s="63" t="inlineStr">
         <is>
           <t>「12月補正ですと、財政課へのご要求はおおむね11月上旬かと思います。10月中に、業務の切り分け案と参考のお見積をお持ちします。いつ頃までにあるとよろしいでしょうか。」</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>提出期限を相手に言わせる。相手の庁内スケジュールがそのまま分かり、次回訪問の理由も確定する。「検討します」で終わらせない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="92" t="inlineStr">
-        <is>
-          <t>想定問答</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="60" t="inlineStr">
-        <is>
-          <t>想定される反応</t>
-        </is>
-      </c>
-      <c r="B12" s="60" t="inlineStr">
-        <is>
-          <t>切り返し</t>
-        </is>
-      </c>
-      <c r="C12" s="60" t="inlineStr">
-        <is>
-          <t>補足・注意</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="n"/>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="47" t="inlineStr">
-        <is>
-          <t>「予算がないので今年度は無理です」</t>
-        </is>
-      </c>
-      <c r="B13" s="63" t="inlineStr">
-        <is>
-          <t>「補正でも難しいようでしたら、まず調査・集計の部分だけ、既定予算の範囲でお受けする形もあります。本体は次年度当初でも、分析が先に終わっていれば間に合います。」</t>
-        </is>
-      </c>
-      <c r="C13" s="79" t="inlineStr">
-        <is>
-          <t>少額随意契約の範囲（金額は自治体の契約規則による）で先行着手し、本体を補正または当初に回す二段構え。金額の線引きは必ず当該自治体の契約規則で確認してから話す。</t>
-        </is>
-      </c>
-      <c r="D13" s="93" t="n"/>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="47" t="inlineStr">
-        <is>
-          <t>「自前でやれます」</t>
-        </is>
-      </c>
-      <c r="B14" s="63" t="inlineStr">
-        <is>
-          <t>「承知しました。無理にお預けいただく話ではありません。ただ保険料の算定だけは、算定後の検算をセカンドオピニオンとしてお使いいただく形もございます。3年間の保険料に直結しますので、二重にご確認いただく価値はあるかと思います。」</t>
-        </is>
-      </c>
-      <c r="C14" s="79" t="inlineStr">
-        <is>
-          <t>自前を否定しない。否定した瞬間に担当者の面目を潰し、次年度以降も入れなくなる。検算・レビューという小さな入口を残す。</t>
-        </is>
-      </c>
-      <c r="D14" s="93" t="n"/>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="47" t="inlineStr">
-        <is>
-          <t>「もう他社にお願いしています」</t>
-        </is>
-      </c>
-      <c r="B15" s="63" t="inlineStr">
-        <is>
-          <t>「失礼しました。差し支えなければ、業務の範囲はどこまででしょうか。調査だけのご契約でしたら、保険料の算定と計画本文が残っているかもしれません。」</t>
-        </is>
-      </c>
-      <c r="C15" s="79" t="inlineStr">
-        <is>
-          <t>調査のみ・アンケートのみの分離発注は多い。範囲を確認せずに引き下がらない。ただし食い下がらず、1往復で判断する。</t>
-        </is>
-      </c>
-      <c r="D15" s="93" t="n"/>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="47" t="inlineStr">
-        <is>
-          <t>「国の基本指針がまだ固まっていない」</t>
-        </is>
-      </c>
-      <c r="B16" s="63" t="inlineStr">
-        <is>
-          <t>「おっしゃるとおりです。ですので、指針を待つ部分（骨子・成果目標）と、待たなくてよい部分（アンケート集計・現状分析・人口推計）を分けて、待たなくてよい部分から先に進めておくご提案です。」</t>
-        </is>
-      </c>
-      <c r="C16" s="79" t="inlineStr">
-        <is>
-          <t>指針待ちは着手しない理由として最も多い。工程を二分して見せることが唯一の崩し方。</t>
-        </is>
-      </c>
-      <c r="D16" s="93" t="n"/>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="47" t="inlineStr">
-        <is>
-          <t>「議会を通るか分かりません」</t>
-        </is>
-      </c>
-      <c r="B17" s="63" t="inlineStr">
-        <is>
-          <t>「見積は要求のための資料としてお使いください。通らなければ次年度当初でご検討いただければ結構です。資料が無いと要求そのものができませんので、まずお持ちします。」</t>
-        </is>
-      </c>
-      <c r="C17" s="79" t="inlineStr">
-        <is>
-          <t>補正の可否を断定しない。「見積＝要求資料」と位置づけると、断る理由がなくなる。</t>
-        </is>
-      </c>
-      <c r="D17" s="93" t="n"/>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="47" t="inlineStr">
-        <is>
-          <t>「担当が異動したばかりで分からない」</t>
-        </is>
-      </c>
-      <c r="B18" s="63" t="inlineStr">
-        <is>
-          <t>「でしたら、前期の計画と実績の突合だけ、こちらで整理してお持ちしましょうか。次期に何を直すべきかが1枚で分かる形にします。」</t>
-        </is>
-      </c>
-      <c r="C18" s="79" t="inlineStr">
-        <is>
-          <t>異動直後は最大の機会。資料を作って持参するだけで、以後の相談相手になれる。</t>
-        </is>
-      </c>
-      <c r="D18" s="93" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="94" t="inlineStr">
-        <is>
-          <t>この5分でやってはいけないこと</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="64" t="inlineStr">
-        <is>
-          <t>・「このままでは間に合いませんよ」と脅す ── 担当者の面目を潰した時点で、以後どの案件にも入れなくなる。</t>
-        </is>
-      </c>
-      <c r="B21" s="48" t="n"/>
-      <c r="C21" s="48" t="n"/>
-      <c r="D21" s="48" t="n"/>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="64" t="inlineStr">
-        <is>
-          <t>・保険料の上昇率を推測で口に出す ── 推計前の数字は、外れたときに議会・住民への説明を壊す。</t>
-        </is>
-      </c>
-      <c r="B22" s="48" t="n"/>
-      <c r="C22" s="48" t="n"/>
-      <c r="D22" s="48" t="n"/>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="64" t="inlineStr">
-        <is>
-          <t>・「補正で必ず取れます」と断定する ── 予算の可否は財政課と議会が決める。こちらは資料を用意する側。</t>
-        </is>
-      </c>
-      <c r="B23" s="48" t="n"/>
-      <c r="C23" s="48" t="n"/>
-      <c r="D23" s="48" t="n"/>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="64" t="inlineStr">
-        <is>
-          <t>・5分と言って10分話す ── 次のアポが取れなくなる。話し切れなければ「続きは資料でお持ちします」で切る。</t>
-        </is>
-      </c>
-      <c r="B24" s="48" t="n"/>
-      <c r="C24" s="48" t="n"/>
-      <c r="D24" s="48" t="n"/>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="64" t="inlineStr">
-        <is>
-          <t>・他団体の進捗を引き合いに出す ── 「△△町さんはもう委託されています」は、未公表情報の持ち込みになる。</t>
-        </is>
-      </c>
-      <c r="B25" s="48" t="n"/>
-      <c r="C25" s="48" t="n"/>
-      <c r="D25" s="48" t="n"/>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>提出期限を相手に言わせる。相手の庁内スケジュールが分かり、次回訪問の理由も確定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="92" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B19" s="93" t="inlineStr">
+        <is>
+          <t>0:00–0:30</t>
+        </is>
+      </c>
+      <c r="C19" s="47" t="inlineStr">
+        <is>
+          <t>セミナーを口実に入る</t>
+        </is>
+      </c>
+      <c r="D19" s="63" t="inlineStr">
+        <is>
+          <t>「先日ご案内いたしました所有外管理資産のセミナーの件で伺いました。ご参加は難しかったかと存じますので、要点だけ5分でお伝えできればと思っております。」</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>セミナーは案内して終わりにしない。参加の有無にかかわらず内容を届けに行くのが本来のフォロー。訪問記録では「セミナー案内」で止まっている記録が多く、ここが取りこぼしになっている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="92" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B20" s="93" t="inlineStr">
+        <is>
+          <t>0:30–1:30</t>
+        </is>
+      </c>
+      <c r="C20" s="47" t="inlineStr">
+        <is>
+          <t>台帳の実態を3問だけ聞く</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>「①固定資産台帳の更新は、毎年度されていますでしょうか。」
+「②公有財産台帳との突合は、これまでにされたことはございますか。」
+「③借地の上に建っている施設や、指定管理でお願いしている施設は、台帳にどう入っていますか。」</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>③が即答できなければ所有外の整理は未着手。3問目で「うちはどうなっているだろう」と相手自身に思わせるのが目的で、答えを引き出すこと自体は目的ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="92" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B21" s="93" t="inlineStr">
+        <is>
+          <t>1:30–3:00</t>
+        </is>
+      </c>
+      <c r="C21" s="47" t="inlineStr">
+        <is>
+          <t>論点を具体名で並べる</t>
+        </is>
+      </c>
+      <c r="D21" s="63" t="inlineStr">
+        <is>
+          <t>「所有外管理資産と申しましても、中身はいくつかに分かれます。借地の上の建物、指定管理施設、無償で譲り受けた資産、法定外公共物──里道や水路ですね、共有や区分所有のもの、リース資産、PFIの施設。それから逆に、所有はしているが管理を他に委ねているもの。まず、どれが御市に当てはまるかを一覧にするところからです。」</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>抽象的な「精緻化」では動かない。具体名を並べると「うちにもある」と気づいてもらえる。ここで相手が挙げた資産が、そのまま提案の対象になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="92" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B22" s="93" t="inlineStr">
+        <is>
+          <t>3:00–4:00</t>
+        </is>
+      </c>
+      <c r="C22" s="47" t="inlineStr">
+        <is>
+          <t>影響の連鎖を見せる</t>
+        </is>
+      </c>
+      <c r="D22" s="63" t="inlineStr">
+        <is>
+          <t>「台帳の資産額が実態より少ないと、有形固定資産減価償却率が実態とずれます。その数字は公共施設等総合管理計画の更新費用試算の前提になっていて、さらに起債や交付金の裏付けにもなります。台帳は公会計だけの話ではなく、施設と財源の話につながっているとお考えいただければと思います。」</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>公会計担当だけの問題にしない。財政課・管財課を巻き込む理由になり、公共施設マネジメントへのクロスセルの入口にもなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="92" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B23" s="93" t="inlineStr">
+        <is>
+          <t>4:00–5:00</t>
+        </is>
+      </c>
+      <c r="C23" s="47" t="inlineStr">
+        <is>
+          <t>段階整備を提案して次を決める</t>
+        </is>
+      </c>
+      <c r="D23" s="63" t="inlineStr">
+        <is>
+          <t>「一度に全部やる必要はありません。金額の大きいものと、所管課が特定できるものから、複数年に分けて整理する進め方をご提案しています。まず現状の台帳を拝見して、どこから手を付けるべきかの整理表をお持ちします。」</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>「全部やる＝高い」で止まらせない。整理表の持参が次回訪問の理由になり、複数年契約の入口にもなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="92" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B24" s="93" t="inlineStr">
+        <is>
+          <t>0:00–0:30</t>
+        </is>
+      </c>
+      <c r="C24" s="47" t="inlineStr">
+        <is>
+          <t>改定時期から入る</t>
+        </is>
+      </c>
+      <c r="D24" s="63" t="inlineStr">
+        <is>
+          <t>「公共施設等総合管理計画の件で伺いました。御町の計画はR◯年度までと拝見しましたので、そろそろ改定のご検討時期かと存じます。5分だけお時間をいただけますでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>計画期間を調べてから行く。「R◯年度まで」と言えるだけで、他社との差がつく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="92" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B25" s="93" t="inlineStr">
+        <is>
+          <t>0:30–1:30</t>
+        </is>
+      </c>
+      <c r="C25" s="47" t="inlineStr">
+        <is>
+          <t>充足状況を3問だけ聞く</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="inlineStr">
+        <is>
+          <t>「①国の見直し要請の内容──個別施設計画の反映、保有量の数値目標、脱炭素化、ユニバーサルデザイン化ですが、現行計画に入っていますでしょうか。」
+「②個別施設計画は、施設類型ごとに一通り揃っていますか。」
+「③更新費用の試算は、いつのデータで作られたものでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>3問とも「たぶん入っている」「揃っていないかもしれない」で返ってくることが多い。その曖昧さ自体が、点検表を持参する理由になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="92" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B26" s="93" t="inlineStr">
+        <is>
+          <t>1:30–3:00</t>
+        </is>
+      </c>
+      <c r="C26" s="47" t="inlineStr">
+        <is>
+          <t>起債の要件から必要性を語る</t>
+        </is>
+      </c>
+      <c r="D26" s="63" t="inlineStr">
+        <is>
+          <t>「公共施設等適正管理推進事業債は、総合管理計画に基づく事業であることが要件になっています。裏を返しますと、計画に書かれていない事業は起債の対象になりません。これから集約化や長寿命化を進められるのであれば、その事業が計画に位置付けられているかどうかが、そのまま財源を使えるかどうかになります。」</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>計画改定を「作り直し」ではなく「財源を使えるようにする作業」として提示する。充当率・交付税措置率・適用期限は必ず当年度の地方債計画で確認してから話す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="92" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B27" s="93" t="inlineStr">
+        <is>
+          <t>3:00–4:00</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="inlineStr">
+        <is>
+          <t>3点セットで提案する</t>
+        </is>
+      </c>
+      <c r="D27" s="63" t="inlineStr">
+        <is>
+          <t>「総合管理計画だけを改定しても、個別施設計画が古いままですと整合が取れません。また更新費用の試算は、固定資産台帳と連動させると精度が上がります。総合管理計画・個別施設計画・台帳の3つをどう組み合わせるかで、ご提案の形が変わってまいります。」</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>単発の改定業務で終わらせない。台帳を持ち出すことで公会計テーマとのクロスセルになる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="92" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B28" s="93" t="inlineStr">
+        <is>
+          <t>4:00–5:00</t>
+        </is>
+      </c>
+      <c r="C28" s="47" t="inlineStr">
+        <is>
+          <t>点検表を約束して帰る</t>
+        </is>
+      </c>
+      <c r="D28" s="63" t="inlineStr">
+        <is>
+          <t>「現行計画を拝見して、国の要請事項がどこまで反映されているかの点検表をお持ちします。改定の要否をご判断いただく材料になるかと思います。いつ頃までにあるとよろしいでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>点検表は公表資料だけで作れて、相手にとって価値がある。最も費用対効果の高い置き土産。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="92" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B29" s="93" t="inlineStr">
+        <is>
+          <t>0:00–0:30</t>
+        </is>
+      </c>
+      <c r="C29" s="47" t="inlineStr">
+        <is>
+          <t>随契を前提に、切り替えを迫らずに入る</t>
+        </is>
+      </c>
+      <c r="D29" s="63" t="inlineStr">
+        <is>
+          <t>「◯◯の件は、現在お願いされている会社さんがいらっしゃると伺っております。切り替えのお願いに参ったわけではございません。ただ、ご契約の範囲に入っていない部分でお役に立てることがあるかと思いまして、5分だけお時間をいただけますでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>最初に「切り替えの話ではない」と言い切る。ここで警戒を解けるかどうかが、この5分の成否を決める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="92" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B30" s="93" t="inlineStr">
+        <is>
+          <t>0:30–1:30</t>
+        </is>
+      </c>
+      <c r="C30" s="47" t="inlineStr">
+        <is>
+          <t>契約範囲を3問で確かめる</t>
+        </is>
+      </c>
+      <c r="D30" s="63" t="inlineStr">
+        <is>
+          <t>「①現在のご契約は、どこまでの範囲でしょうか。」
+「②経営戦略の改定や料金の見直しは、同じところにお願いされていますか。」
+「③次の改定は、R◯年度でよろしかったでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>①で範囲外が見つかれば今日の商談になり、③で改定年度が分かれば数年後の商談になる。どちらかは必ず取れる質問構成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="92" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B31" s="93" t="inlineStr">
+        <is>
+          <t>1:30–3:00</t>
+        </is>
+      </c>
+      <c r="C31" s="47" t="inlineStr">
+        <is>
+          <t>隣の業務を示す</t>
+        </is>
+      </c>
+      <c r="D31" s="63" t="inlineStr">
+        <is>
+          <t>「会計のご支援と経営戦略は、別のご発注になっている団体が多くございます。財務書類の作成と固定資産台帳の精緻化も同じです。総合管理計画と個別施設計画も分かれることが多いです。いまご契約に入っていない部分について、比較のための材料としてご覧いただければと思います。」</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>現受託者の仕事を評価も批判もしない。「範囲」という事実だけを扱う。ここで他社批判に踏み込むと、担当者の判断を否定することになり一度で終わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="92" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B32" s="93" t="inlineStr">
+        <is>
+          <t>3:00–4:00</t>
+        </is>
+      </c>
+      <c r="C32" s="47" t="inlineStr">
+        <is>
+          <t>参考見積を比較材料として置く</t>
+        </is>
+      </c>
+      <c r="D32" s="63" t="inlineStr">
+        <is>
+          <t>「もしよろしければ、その部分の参考のお見積をお持ちします。ご発注いただかなくても、次回のご契約の際に金額の目安としてお使いいただければ結構です。」</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>随契先がある団体で見積を受け取ってもらう唯一の名目が「比較材料」。受け取ってもらえれば、次の契約時に必ず思い出される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="92" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B33" s="93" t="inlineStr">
+        <is>
+          <t>4:00–5:00</t>
+        </is>
+      </c>
+      <c r="C33" s="47" t="inlineStr">
+        <is>
+          <t>改定年度の前年度に戻る約束をする</t>
+        </is>
+      </c>
+      <c r="D33" s="63" t="inlineStr">
+        <is>
+          <t>「次の改定がR◯年度でしたら、その前年度にまた伺わせてください。ご担当が代わられるタイミングでも、もう一度ご相談いただけますと幸いです。」</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>随契が切れる唯一の機会は担当者交代と改定年度。訪問記録に「再訪不要」と書いて切ると、その機会を自ら捨てることになる。改定時期が先でも「再アプローチ」とし、備考に再訪する年度を書く。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="92" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B34" s="93" t="inlineStr">
+        <is>
+          <t>0:00–0:30</t>
+        </is>
+      </c>
+      <c r="C34" s="47" t="inlineStr">
+        <is>
+          <t>受付で3つ確認する</t>
+        </is>
+      </c>
+      <c r="D34" s="63" t="inlineStr">
+        <is>
+          <t>「①◯◯のご担当は△△様でお間違いないでしょうか。」
+「②お戻りのお時間、あるいは在席されやすい曜日・時間帯はございますか。」
+「③改めて伺いたいのですが、◯月頃でご都合のよい時期はございますでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>この3つを聞くだけで、次回の訪問が当てずっぽうでなくなる。同じ時間帯に何度も行って不在を繰り返すのが、最も無駄な時間の使い方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="92" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B35" s="93" t="inlineStr">
+        <is>
+          <t>0:30–1:30</t>
+        </is>
+      </c>
+      <c r="C35" s="47" t="inlineStr">
+        <is>
+          <t>置いていく資料を渡す</t>
+        </is>
+      </c>
+      <c r="D35" s="63" t="inlineStr">
+        <is>
+          <t>「△△様にお渡しいただけますでしょうか。ご覧いただいて、ご関心がありましたらご連絡いただければ幸いです。」</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>置く資料は4つの条件を満たすこと──1枚であること、宛名が入っていること、次にいつ伺うかが書いてあること、連絡先があること。宛名を手書きで入れるだけで、机上で捨てられにくくなる。カタログだけを置かない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="92" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B36" s="93" t="inlineStr">
+        <is>
+          <t>1:30–2:30</t>
+        </is>
+      </c>
+      <c r="C36" s="47" t="inlineStr">
+        <is>
+          <t>名刺に一言添える</t>
+        </is>
+      </c>
+      <c r="D36" s="63" t="inlineStr">
+        <is>
+          <t>（名刺の裏に「◯月に改めて伺います」と手書きで添えて、資料に留める）</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>名刺だけでは用件が残らない。一言あるだけで、次に訪ねたときの入口になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="92" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B37" s="93" t="inlineStr">
+        <is>
+          <t>2:30–3:00</t>
+        </is>
+      </c>
+      <c r="C37" s="47" t="inlineStr">
+        <is>
+          <t>その場で記録する</t>
+        </is>
+      </c>
+      <c r="D37" s="63" t="inlineStr">
+        <is>
+          <t>（受付で確認した担当者名・在席しやすい時間帯・次回訪問の目安を、庁舎を出る前にメモする）</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>帰社してからでは細部を忘れる。特に担当者の氏名の漢字は、その場で確認しておく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="92" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B38" s="93" t="inlineStr">
+        <is>
+          <t>帰社後・当日中</t>
+        </is>
+      </c>
+      <c r="C38" s="47" t="inlineStr">
+        <is>
+          <t>訪問記録に次が読める形で残す</t>
+        </is>
+      </c>
+      <c r="D38" s="63" t="inlineStr">
+        <is>
+          <t>（結果＝不在／次回アクション＝再アプローチ／備考に「◯月◯日再訪」と日付まで書く）</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>備考が「担当不在」だけで終わっている記録は、書いた本人以外には追えない。訪問記録の中には再訪日を具体的に書けているものがあり、そうした記録はそのまま引き継げる。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+  <autoFilter ref="A13:E38"/>
+  <mergeCells count="4">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00D6336C"/>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="108" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>来期（R9年度）営業方針｜こども計画／地域福祉計画</t>
+          <t>5分トーク 想定問答・やってはいけないこと</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>どちらも努力義務の計画で、待っていても発注は生まれない。こどもは「制度が変わったので直さざるを得ない」、地域福祉は「束ねれば手間が減る」が崩し方。</t>
+          <t>断られ方には型がある。切り返しを持っていないと、その場で引くか、言ってはいけないことを言うかのどちらかになる。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="95" t="inlineStr">
-        <is>
-          <t>こども計画・子ども子育て支援事業計画</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>想定問答</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="40" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B5" s="40" t="inlineStr">
-        <is>
-          <t>見出し</t>
-        </is>
-      </c>
-      <c r="C5" s="40" t="inlineStr">
-        <is>
-          <t>内容</t>
+      <c r="A5" s="60" t="inlineStr"/>
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t>想定される反応</t>
+        </is>
+      </c>
+      <c r="C5" s="60" t="inlineStr">
+        <is>
+          <t>切り返し</t>
+        </is>
+      </c>
+      <c r="D5" s="60" t="inlineStr">
+        <is>
+          <t>補足・注意</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="52" t="inlineStr">
-        <is>
-          <t>現状認識</t>
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B6" s="47" t="inlineStr">
         <is>
-          <t>「国や道の強制力しだい」で様子見が多数派</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>訪問記録を見ると、こども計画について「子ども・子育て支援事業計画の改定タイミングで、国や県の温度感を見ながら判断する」「中間見直しは自前」という回答が複数の団体で並んでいる。努力義務であるため、待っていても発注は生まれない。待ちの姿勢を崩す材料を持ち込むのが来期の仕事。</t>
+          <t>「予算がないので今年度は無理です」</t>
+        </is>
+      </c>
+      <c r="C6" s="63" t="inlineStr">
+        <is>
+          <t>「補正でも難しいようでしたら、まず調査・集計の部分だけ、既定予算の範囲でお受けする形もあります。本体は次年度当初でも、分析が先に終わっていれば間に合います。」</t>
+        </is>
+      </c>
+      <c r="D6" s="79" t="inlineStr">
+        <is>
+          <t>少額随意契約の範囲（金額は自治体の契約規則による）で先行着手し、本体を補正または当初に回す二段構え。金額の線引きは必ず当該自治体の契約規則で確認してから話す。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="53" t="inlineStr">
-        <is>
-          <t>狙い目①</t>
-        </is>
-      </c>
-      <c r="B7" s="49" t="inlineStr">
-        <is>
-          <t>第3期事業計画（R7〜11年度）の中間年の見直し</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>5年計画の中間年に、量の見込みと実績の乖離を踏まえて見直す。少子化の加速と利用率の変化で、第3期策定時の見込みから外れている団体が多い。区域別・年齢別の乖離率を一覧にして持参すると、見直しの必要性が数字で伝わる。</t>
+      <c r="A7" s="56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>「自前でやれます」</t>
+        </is>
+      </c>
+      <c r="C7" s="63" t="inlineStr">
+        <is>
+          <t>「承知しました。無理にお預けいただく話ではありません。ただ保険料の算定だけは、算定後の検算をセカンドオピニオンとしてお使いいただく形もございます。3年間の保険料に直結しますので、二重にご確認いただく価値はあるかと思います。」</t>
+        </is>
+      </c>
+      <c r="D7" s="79" t="inlineStr">
+        <is>
+          <t>自前を否定しない。否定した瞬間に担当者の面目を潰し、次年度以降も入れなくなる。検算・レビューという小さな入口を残す。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="53" t="inlineStr">
-        <is>
-          <t>狙い目②</t>
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B8" s="47" t="inlineStr">
         <is>
-          <t>こども誰でも通園制度（乳児等通園支援事業）の反映</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>地域子ども・子育て支援事業に新たに位置付けられたため、量の見込みへの反映が必要になる。「制度が変わったので計画を直さなければならない」は、担当者が庁内を説得しやすい理由になる。中間見直しを提案する最も明確な入口。</t>
+          <t>「もう他社にお願いしています」</t>
+        </is>
+      </c>
+      <c r="C8" s="63" t="inlineStr">
+        <is>
+          <t>「失礼しました。差し支えなければ、業務の範囲はどこまででしょうか。調査だけのご契約でしたら、保険料の算定と計画本文が残っているかもしれません。」</t>
+        </is>
+      </c>
+      <c r="D8" s="79" t="inlineStr">
+        <is>
+          <t>調査のみ・アンケートのみの分離発注は多い。範囲を確認せずに引き下がらない。ただし1往復で判断する。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="53" t="inlineStr">
-        <is>
-          <t>狙い目③</t>
-        </is>
-      </c>
-      <c r="B9" s="49" t="inlineStr">
-        <is>
-          <t>こども計画の新規策定（未策定団体）</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>こども基本法に基づく努力義務。子ども・若者計画、こどもの貧困対策計画、母子保健計画を統合できる。「別々に作っている計画を1本にまとめれば、次からの改定の手間が減る」という、事務負担の軽減を軸に話す。安くなるからではない。</t>
+      <c r="A9" s="56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>「国の基本指針がまだ固まっていない」</t>
+        </is>
+      </c>
+      <c r="C9" s="63" t="inlineStr">
+        <is>
+          <t>「おっしゃるとおりです。ですので、指針を待つ部分（骨子・成果目標）と、待たなくてよい部分（アンケート集計・現状分析・人口推計）を分けて、待たなくてよい部分から先に進めておくご提案です。」</t>
+        </is>
+      </c>
+      <c r="D9" s="79" t="inlineStr">
+        <is>
+          <t>指針待ちは着手しない理由として最も多い。工程を二分して見せることが唯一の崩し方。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="96" t="inlineStr">
-        <is>
-          <t>財源</t>
+      <c r="A10" s="56" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B10" s="47" t="inlineStr">
         <is>
-          <t>地域子供の未来応援交付金／ヤングケアラー支援体制強化事業</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>こどもの貧困の実態調査・計画策定・支援体制整備に充当できる。調査業務の予算化に直結する。要綱と要望時期は毎年度変わるため、当年度資料で確認してから提示すること。「対象になり得るので要綱で確認を」で止め、断定しない。</t>
+          <t>「議会を通るか分かりません」</t>
+        </is>
+      </c>
+      <c r="C10" s="63" t="inlineStr">
+        <is>
+          <t>「見積は要求のための資料としてお使いください。通らなければ次年度当初でご検討いただければ結構です。資料が無いと要求そのものができませんので、まずお持ちします。」</t>
+        </is>
+      </c>
+      <c r="D10" s="79" t="inlineStr">
+        <is>
+          <t>補正の可否を断定しない。「見積＝要求資料」と位置づけると、断る理由がなくなる。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="56" t="inlineStr">
         <is>
-          <t>提案の型</t>
-        </is>
-      </c>
-      <c r="B11" s="49" t="inlineStr">
-        <is>
-          <t>調査と計画を分けて、二段で取る</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>実態調査（貧困・ヤングケアラー・こどもの意見聴取）を単独業務として先に受け、その結果を持って計画本体につなげる。調査は交付金が使え、金額も抑えられるため通りやすい。こども会議の設計・運営は策定年度以外でも受注できる。</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>「担当が異動したばかりで分からない」</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>「でしたら、前期の計画と実績の突合だけ、こちらで整理してお持ちしましょうか。次期に何を直すべきかが1枚で分かる形にします。」</t>
+        </is>
+      </c>
+      <c r="D11" s="79" t="inlineStr">
+        <is>
+          <t>異動直後は最大の機会。資料を作って持参するだけで、以後の相談相手になれる。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
-        <is>
-          <t>接触先</t>
+      <c r="A12" s="56" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B12" s="47" t="inlineStr">
         <is>
-          <t>こども未来課・子育て支援課だけでは足りない</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>保育、母子保健（健康推進課）、教育委員会（放課後児童クラブ）に所管が分かれている。庁内横断の調整そのものが担当者の最大の負担なので、「関係課をまとめた進め方の案」を持っていくと提案価値になる。</t>
+          <t>「まだ財務書類の作成で手一杯です」</t>
+        </is>
+      </c>
+      <c r="C12" s="63" t="inlineStr">
+        <is>
+          <t>「でしたら台帳の整備は来年度以降で結構です。ただ、どこから手を付けるべきかの整理だけ先にしておくと、来年度のご要求を具体的に書けるようになります。」</t>
+        </is>
+      </c>
+      <c r="D12" s="79" t="inlineStr">
+        <is>
+          <t>着手時期を譲り、整理だけ先行させる。予算要求の材料を提供する立場に回る。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="59" t="inlineStr">
-        <is>
-          <t>タイムライン</t>
-        </is>
-      </c>
-      <c r="B13" s="49" t="inlineStr">
-        <is>
-          <t>R8年度中に予算化まで持ち込む</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R9年度当初予算での発注を狙うなら、R8年8〜10月に情報提供と参考見積、11〜12月に査定対応、1〜3月に公告。中間見直しを補正で狙う場合は、9月補正はすでに間に合わないため12月補正（要求は11月上旬）を目標にする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="97" t="inlineStr">
-        <is>
-          <t>地域福祉計画</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="39" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>見出し</t>
-        </is>
-      </c>
-      <c r="C17" s="39" t="inlineStr">
-        <is>
-          <t>内容</t>
+      <c r="A13" s="56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t>「所有外というのは何を指すのですか」</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>「団体によって使われ方が違いますので、まず御市で何を指すかをそろえるところからです。所有していないが管理しているもの、所有しているが管理を委ねているもの、その両方を含めて整理するのが一般的です。」</t>
+        </is>
+      </c>
+      <c r="D13" s="79" t="inlineStr">
+        <is>
+          <t>定義が現場で揺れている。用語をそろえる作業そのものが業務になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" s="47" t="inlineStr">
+        <is>
+          <t>「台帳は業者にお願いしています」</t>
+        </is>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
+        <is>
+          <t>「ご契約の範囲は、毎年度の更新まででしょうか。更新と精緻化は別の作業ですので、精緻化の部分が残っていることがあります。」</t>
+        </is>
+      </c>
+      <c r="D14" s="79" t="inlineStr">
+        <is>
+          <t>更新の委託と精緻化は別業務。範囲を確認せずに引き下がらない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>「予算がありません」</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>「単年度で全部という前提ですと、確かに大きくなります。3か年に分けて、初年度は影響の大きいところだけ、という形であれば要求しやすいかと思います。」</t>
+        </is>
+      </c>
+      <c r="D15" s="79" t="inlineStr">
+        <is>
+          <t>段階整備は金額を下げる話ではなく、要求を通しやすくする話として伝える。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>「改定の予定はありません」</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>「承知しました。それでは点検表だけお持ちします。要請事項が反映されていない項目があれば、そのときにご判断いただければと思います。」</t>
+        </is>
+      </c>
+      <c r="D16" s="79" t="inlineStr">
+        <is>
+          <t>改定予定なしの団体こそ点検表が効く。未反映が見つかれば、それが改定の理由になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>「個別施設計画は他社にお願いしています」</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>「でしたら、総合管理計画と個別施設計画の整合を取る部分でお役に立てるかもしれません。両方が別々に作られていて数字が合っていない団体は少なくありません。」</t>
+        </is>
+      </c>
+      <c r="D17" s="79" t="inlineStr">
+        <is>
+          <t>他社の成果物を批判せず、「整合」という別の業務として立てる。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="52" t="inlineStr">
-        <is>
-          <t>現状認識</t>
+      <c r="A18" s="56" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B18" s="47" t="inlineStr">
         <is>
-          <t>単発で取ると小さい。束ねて初めて中規模案件になる</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>地域福祉計画そのものは金額が大きくない。併載できる計画と、社協の地域福祉活動計画を合わせて初めて採算に乗る。訪問記録にも「複数計画を地域福祉計画で一本化したい」という団体が実在しており、需要側の要望とも一致する。</t>
+          <t>「更新費用は総務省のソフトで試算しました」</t>
+        </is>
+      </c>
+      <c r="C18" s="63" t="inlineStr">
+        <is>
+          <t>「単価法での試算ですと、実際の施設の規模や構造が反映されません。固定資産台帳と連動させると、施設ごとの数字になります。」</t>
+        </is>
+      </c>
+      <c r="D18" s="79" t="inlineStr">
+        <is>
+          <t>台帳連動の再試算は公会計とのクロスセル。ここが最も単価を上げやすい。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="53" t="inlineStr">
-        <is>
-          <t>狙い目①</t>
-        </is>
-      </c>
-      <c r="B19" s="49" t="inlineStr">
-        <is>
-          <t>成年後見制度利用促進基本計画の改定期</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>国の第二期基本計画が令和8年度で終期を迎え、第三期に移る。これに合わせて市町村計画を改定する団体が出るため、来期の有力な入口になる。中核機関が未設置の団体では、計画策定と体制整備をあわせて提案できる。</t>
+      <c r="A19" s="56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>「予算が取れません」</t>
+        </is>
+      </c>
+      <c r="C19" s="63" t="inlineStr">
+        <is>
+          <t>「起債の要件にかかわる部分ですので、財政課の方とご一緒にお話しできる機会があれば、そちらでもご説明します。」</t>
+        </is>
+      </c>
+      <c r="D19" s="79" t="inlineStr">
+        <is>
+          <t>財政課を巻き込む。施設所管課だけでは予算が動かないことが多い。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="53" t="inlineStr">
-        <is>
-          <t>狙い目②</t>
+      <c r="A20" s="56" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="B20" s="47" t="inlineStr">
         <is>
-          <t>重層的支援体制整備事業</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>未実施の団体には移行準備事業、実施済みの団体には実施計画の策定と体制強化。移行すると介護・障害・こども・困窮の相談支援等の補助が一体的に交付される点が説得材料になる。ただし最大の壁は庁内合意なので、計画の前段として庁内勉強会・業務フロー整理の伴走を提案する。</t>
+          <t>「今のところで満足しています」</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>「承知しました。無理にお切り替えいただく話ではございません。範囲に入っていない部分だけ、資料をお渡しして失礼いたします。」</t>
+        </is>
+      </c>
+      <c r="D20" s="79" t="inlineStr">
+        <is>
+          <t>満足を否定しない。引き際が良いと、次の改定年度に呼ばれる。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="inlineStr">
-        <is>
-          <t>狙い目③</t>
-        </is>
-      </c>
-      <c r="B21" s="49" t="inlineStr">
-        <is>
-          <t>自殺対策計画（地域自殺対策強化交付金）</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>策定が義務であり、交付金を計画の策定・改定に充当できる。地域福祉計画に併載する形にすれば、財源のある計画が本体を引っ張る構図が作れる。JSCPの地域自殺実態プロファイルを使えば、重点施策を客観データで組める。</t>
+      <c r="A21" s="56" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B21" s="47" t="inlineStr">
+        <is>
+          <t>「見積だけもらっても困ります」</t>
+        </is>
+      </c>
+      <c r="C21" s="63" t="inlineStr">
+        <is>
+          <t>「ご発注のご判断材料としてではなく、庁内で金額の妥当性をご説明される際の材料としてお使いいただければと思います。」</t>
+        </is>
+      </c>
+      <c r="D21" s="79" t="inlineStr">
+        <is>
+          <t>「比較材料」という位置づけなら受け取ってもらえる。押しつけない。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="56" t="inlineStr">
         <is>
-          <t>提案の型</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B22" s="47" t="inlineStr">
         <is>
-          <t>自治体と社会福祉協議会の両方に当たる</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>地域福祉計画（自治体）と地域福祉活動計画（社協）を一体で策定すると、発注元が2つになり予算を合算できる。社協は自治体より意思決定が早いことが多く、社協側から自治体を動かせる場合もある。どちらか一方だけを訪問している状態は、機会を半分捨てている。</t>
+          <t>「他社の批判はしないでほしい」</t>
+        </is>
+      </c>
+      <c r="C22" s="63" t="inlineStr">
+        <is>
+          <t>「もちろんいたしません。ご契約の範囲のお話だけさせてください。」</t>
+        </is>
+      </c>
+      <c r="D22" s="79" t="inlineStr">
+        <is>
+          <t>そもそも批判しない。この一言で信頼が生まれる。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="56" t="inlineStr">
         <is>
-          <t>提案の型</t>
-        </is>
-      </c>
-      <c r="B23" s="49" t="inlineStr">
-        <is>
-          <t>併載計画の一覧を作って持参する</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>成年後見・再犯防止・自殺対策・孤独孤立・生活困窮・避難行動要支援者・居住支援。担当自治体それぞれについて、どの計画がいつ切れるかを一覧にして見せる。「バラバラに作ると毎年どれかの改定が来るが、束ねれば数年に一度で済む」が最も効く言い方。</t>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B23" s="47" t="inlineStr">
+        <is>
+          <t>「担当が代わったら連絡します」</t>
+        </is>
+      </c>
+      <c r="C23" s="63" t="inlineStr">
+        <is>
+          <t>「ありがとうございます。R◯年度の改定の前年度に、こちらからも一度伺わせてください。」</t>
+        </is>
+      </c>
+      <c r="D23" s="79" t="inlineStr">
+        <is>
+          <t>相手の言葉を記録に残し、必ずこちらから戻る。待っていても連絡は来ない。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="98" t="inlineStr">
-        <is>
-          <t>注意</t>
+      <c r="A24" s="56" t="inlineStr">
+        <is>
+          <t>E</t>
         </is>
       </c>
       <c r="B24" s="47" t="inlineStr">
         <is>
-          <t>圏域と進捗評価が実務の争点になる</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>圏域が計画ごとにバラバラ（日常生活圏域／小学校区／地区社協）な団体が多く、整理そのものを業務に含められる。また前計画の進捗評価の仕組みが無い団体が大半なので、指標設計と年次評価の仕組みづくりを提案に入れると、他社の標準的な策定業務と差がつく。</t>
+          <t>不在が続いて会えない</t>
+        </is>
+      </c>
+      <c r="C24" s="63" t="inlineStr">
+        <is>
+          <t>受付で聞いた在席しやすい曜日・時間帯に合わせる。それでも会えなければ、資料送付とあわせて電話でアポイントを取る形に切り替える。</t>
+        </is>
+      </c>
+      <c r="D24" s="79" t="inlineStr">
+        <is>
+          <t>訪問の回数ではなく、会えた回数が成果。同じやり方を繰り返さない。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="59" t="inlineStr">
-        <is>
-          <t>タイムライン</t>
-        </is>
-      </c>
-      <c r="B25" s="49" t="inlineStr">
-        <is>
-          <t>R8年8〜10月が勝負</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>地域福祉計画は複数課・社協との調整が要るため、予算要求の準備に時間がかかる。R8年8〜10月に併載計画の一覧と一体策定案を提示し、11〜12月の査定を越える。社協への接触は自治体と同時期に始める。</t>
-        </is>
-      </c>
+      <c r="A25" s="56" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B25" s="47" t="inlineStr">
+        <is>
+          <t>資料を置いてよいか分からない</t>
+        </is>
+      </c>
+      <c r="C25" s="63" t="inlineStr">
+        <is>
+          <t>「△△様にお渡しいただけますでしょうか」と受付に確認する。断られたら持ち帰り、郵送かメールにする。</t>
+        </is>
+      </c>
+      <c r="D25" s="79" t="inlineStr">
+        <is>
+          <t>無理に置いていかない。受付での印象は担当者に伝わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="56" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B26" s="47" t="inlineStr">
+        <is>
+          <t>次回の時期を聞きにくい</t>
+        </is>
+      </c>
+      <c r="C26" s="63" t="inlineStr">
+        <is>
+          <t>「◯月頃にまた伺ってもよろしいでしょうか」と月単位で聞く。日付を詰めない。</t>
+        </is>
+      </c>
+      <c r="D26" s="79" t="inlineStr">
+        <is>
+          <t>受付は日程を決める権限を持たない。月単位なら答えやすい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="94" t="inlineStr">
+        <is>
+          <t>やってはいけないこと ── ここに書いた失敗は取り返すのに年単位かかる</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="95" t="inlineStr"/>
+      <c r="B29" s="95" t="inlineStr">
+        <is>
+          <t>ケース</t>
+        </is>
+      </c>
+      <c r="C29" s="95" t="inlineStr">
+        <is>
+          <t>やってはいけないこと</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="n"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B30" s="96" t="inlineStr">
+        <is>
+          <t>自前作成先からの補正予算獲得</t>
+        </is>
+      </c>
+      <c r="C30" s="64" t="inlineStr">
+        <is>
+          <t>「このままでは間に合いませんよ」と脅す ── 担当者の面目を潰した時点で、以後どの案件にも入れなくなる。</t>
+        </is>
+      </c>
+      <c r="D30" s="64" t="n"/>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="61" t="inlineStr"/>
+      <c r="B31" s="96" t="inlineStr"/>
+      <c r="C31" s="64" t="inlineStr">
+        <is>
+          <t>保険料の上昇率を推測で口に出す ── 推計前の数字は、外れたときに議会・住民への説明を壊す。</t>
+        </is>
+      </c>
+      <c r="D31" s="64" t="n"/>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="61" t="inlineStr"/>
+      <c r="B32" s="96" t="inlineStr"/>
+      <c r="C32" s="64" t="inlineStr">
+        <is>
+          <t>「補正で必ず取れます」と断定する ── 予算の可否は財政課と議会が決める。こちらは資料を用意する側。</t>
+        </is>
+      </c>
+      <c r="D32" s="64" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="61" t="inlineStr"/>
+      <c r="B33" s="96" t="inlineStr"/>
+      <c r="C33" s="64" t="inlineStr">
+        <is>
+          <t>5分と言って10分話す ── 次のアポが取れなくなる。話し切れなければ「続きは資料でお持ちします」で切る。</t>
+        </is>
+      </c>
+      <c r="D33" s="64" t="n"/>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="61" t="inlineStr"/>
+      <c r="B34" s="96" t="inlineStr"/>
+      <c r="C34" s="64" t="inlineStr">
+        <is>
+          <t>他団体の進捗を引き合いに出す ── 「△△町さんはもう委託されています」は未公表情報の持ち込みになる。</t>
+        </is>
+      </c>
+      <c r="D34" s="64" t="n"/>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="61" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="96" t="inlineStr">
+        <is>
+          <t>所有外管理資産（セミナー案内後のフォロー）</t>
+        </is>
+      </c>
+      <c r="C35" s="64" t="inlineStr">
+        <is>
+          <t>「台帳が間違っています」と言う ── 精緻化されていないことと誤りは違う。担当者の否定になる。</t>
+        </is>
+      </c>
+      <c r="D35" s="64" t="n"/>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="61" t="inlineStr"/>
+      <c r="B36" s="96" t="inlineStr"/>
+      <c r="C36" s="64" t="inlineStr">
+        <is>
+          <t>精緻化の効果を金額で断定する ── 資産額がいくら増えるかは調べてみないと分からない。</t>
+        </is>
+      </c>
+      <c r="D36" s="64" t="n"/>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="61" t="inlineStr"/>
+      <c r="B37" s="96" t="inlineStr"/>
+      <c r="C37" s="64" t="inlineStr">
+        <is>
+          <t>セミナーに来なかったことを責める・確認する ── 案内が担当者まで届いていないことも多い。</t>
+        </is>
+      </c>
+      <c r="D37" s="64" t="n"/>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="61" t="inlineStr"/>
+      <c r="B38" s="96" t="inlineStr"/>
+      <c r="C38" s="64" t="inlineStr">
+        <is>
+          <t>公会計の話だけで終える ── 財政課・管財課につながる話に広げないと、単発の小さな受注で終わる。</t>
+        </is>
+      </c>
+      <c r="D38" s="64" t="n"/>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="61" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B39" s="96" t="inlineStr">
+        <is>
+          <t>総合管理計画の改定（起債要件から入る）</t>
+        </is>
+      </c>
+      <c r="C39" s="64" t="inlineStr">
+        <is>
+          <t>起債の充当率・措置率・適用期限を、当年度資料で確認せずに口に出す ── 数値の誤りはそのまま事故になる。</t>
+        </is>
+      </c>
+      <c r="D39" s="64" t="n"/>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="61" t="inlineStr"/>
+      <c r="B40" s="96" t="inlineStr"/>
+      <c r="C40" s="64" t="inlineStr">
+        <is>
+          <t>「この計画は要件を満たしていません」と断定する ── 判断するのは総務省と県であって、当社ではない。</t>
+        </is>
+      </c>
+      <c r="D40" s="64" t="n"/>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="61" t="inlineStr"/>
+      <c r="B41" s="96" t="inlineStr"/>
+      <c r="C41" s="64" t="inlineStr">
+        <is>
+          <t>他社が作った計画を批判する ── その計画を選んだのは目の前の担当者。</t>
+        </is>
+      </c>
+      <c r="D41" s="64" t="n"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="61" t="inlineStr"/>
+      <c r="B42" s="96" t="inlineStr"/>
+      <c r="C42" s="64" t="inlineStr">
+        <is>
+          <t>「起債が使えなくなります」と脅す ── 事実に基づかない不安の煽りは、後で必ず信用を失う。</t>
+        </is>
+      </c>
+      <c r="D42" s="64" t="n"/>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="61" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B43" s="96" t="inlineStr">
+        <is>
+          <t>他社随契先への切り込み</t>
+        </is>
+      </c>
+      <c r="C43" s="64" t="inlineStr">
+        <is>
+          <t>現受託者の成果物を批判する ── その会社を選んだのは目の前の担当者。否定は担当者への否定になる。</t>
+        </is>
+      </c>
+      <c r="D43" s="64" t="n"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="61" t="inlineStr"/>
+      <c r="B44" s="96" t="inlineStr"/>
+      <c r="C44" s="64" t="inlineStr">
+        <is>
+          <t>「随意契約は競争性がない」と制度論を持ち出す ── 契約方式は自治体が決めること。</t>
+        </is>
+      </c>
+      <c r="D44" s="64" t="n"/>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="61" t="inlineStr"/>
+      <c r="B45" s="96" t="inlineStr"/>
+      <c r="C45" s="64" t="inlineStr">
+        <is>
+          <t>訪問記録に「再訪不要」と書いて切る ── 改定時期が先なら「再アプローチ」とし、備考に再訪年度を書く。</t>
+        </is>
+      </c>
+      <c r="D45" s="64" t="n"/>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="61" t="inlineStr"/>
+      <c r="B46" s="96" t="inlineStr"/>
+      <c r="C46" s="64" t="inlineStr">
+        <is>
+          <t>現受託者の契約金額を聞き出そうとする ── 聞き方によっては相手を困らせる。公表資料で調べる。</t>
+        </is>
+      </c>
+      <c r="D46" s="64" t="n"/>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="61" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B47" s="96" t="inlineStr">
+        <is>
+          <t>担当者が不在だったときの3分</t>
+        </is>
+      </c>
+      <c r="C47" s="64" t="inlineStr">
+        <is>
+          <t>何も置かずに帰る ── 訪問した事実が相手側に何も残らず、その日の移動時間がすべて無駄になる。</t>
+        </is>
+      </c>
+      <c r="D47" s="64" t="n"/>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="61" t="inlineStr"/>
+      <c r="B48" s="96" t="inlineStr"/>
+      <c r="C48" s="64" t="inlineStr">
+        <is>
+          <t>備考に「担当不在」とだけ書く ── 次に何をするかが読めない記録は、記録として成立していない。</t>
+        </is>
+      </c>
+      <c r="D48" s="64" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="61" t="inlineStr"/>
+      <c r="B49" s="96" t="inlineStr"/>
+      <c r="C49" s="64" t="inlineStr">
+        <is>
+          <t>次回アクションを空欄にする ── 空欄は「決めていない」と同義で、そのままフォローが漏れる。</t>
+        </is>
+      </c>
+      <c r="D49" s="64" t="n"/>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="61" t="inlineStr"/>
+      <c r="B50" s="96" t="inlineStr"/>
+      <c r="C50" s="64" t="inlineStr">
+        <is>
+          <t>在席時間を確認せず、同じ曜日・時間帯に繰り返し訪問する ── 不在が続く原因はたいていこれ。</t>
+        </is>
+      </c>
+      <c r="D50" s="64" t="n"/>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="61" t="inlineStr"/>
+      <c r="B51" s="96" t="inlineStr"/>
+      <c r="C51" s="64" t="inlineStr">
+        <is>
+          <t>受付で担当者の携帯番号や不在の理由を聞き出そうとする ── 相手を困らせる。</t>
+        </is>
+      </c>
+      <c r="D51" s="64" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A16:C16"/>
+  <autoFilter ref="A5:D26"/>
+  <mergeCells count="27">
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="C49:D49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21727,6 +22755,366 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00D6336C"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="108" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>来期（R9年度）営業方針｜こども計画／地域福祉計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>どちらも努力義務の計画で、待っていても発注は生まれない。こどもは「制度が変わったので直さざるを得ない」、地域福祉は「束ねれば手間が減る」が崩し方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="97" t="inlineStr">
+        <is>
+          <t>こども計画・子ども子育て支援事業計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>見出し</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="52" t="inlineStr">
+        <is>
+          <t>現状認識</t>
+        </is>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>「国や道の強制力しだい」で様子見が多数派</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>訪問記録を見ると、こども計画について「子ども・子育て支援事業計画の改定タイミングで、国や県の温度感を見ながら判断する」「中間見直しは自前」という回答が複数の団体で並んでいる。努力義務であるため、待っていても発注は生まれない。待ちの姿勢を崩す材料を持ち込むのが来期の仕事。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="53" t="inlineStr">
+        <is>
+          <t>狙い目①</t>
+        </is>
+      </c>
+      <c r="B7" s="49" t="inlineStr">
+        <is>
+          <t>第3期事業計画（R7〜11年度）の中間年の見直し</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>5年計画の中間年に、量の見込みと実績の乖離を踏まえて見直す。少子化の加速と利用率の変化で、第3期策定時の見込みから外れている団体が多い。区域別・年齢別の乖離率を一覧にして持参すると、見直しの必要性が数字で伝わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>狙い目②</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>こども誰でも通園制度（乳児等通園支援事業）の反映</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>地域子ども・子育て支援事業に新たに位置付けられたため、量の見込みへの反映が必要になる。「制度が変わったので計画を直さなければならない」は、担当者が庁内を説得しやすい理由になる。中間見直しを提案する最も明確な入口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="53" t="inlineStr">
+        <is>
+          <t>狙い目③</t>
+        </is>
+      </c>
+      <c r="B9" s="49" t="inlineStr">
+        <is>
+          <t>こども計画の新規策定（未策定団体）</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>こども基本法に基づく努力義務。子ども・若者計画、こどもの貧困対策計画、母子保健計画を統合できる。「別々に作っている計画を1本にまとめれば、次からの改定の手間が減る」という、事務負担の軽減を軸に話す。安くなるからではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="98" t="inlineStr">
+        <is>
+          <t>財源</t>
+        </is>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>地域子供の未来応援交付金／ヤングケアラー支援体制強化事業</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>こどもの貧困の実態調査・計画策定・支援体制整備に充当できる。調査業務の予算化に直結する。要綱と要望時期は毎年度変わるため、当年度資料で確認してから提示すること。「対象になり得るので要綱で確認を」で止め、断定しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="56" t="inlineStr">
+        <is>
+          <t>提案の型</t>
+        </is>
+      </c>
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>調査と計画を分けて、二段で取る</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>実態調査（貧困・ヤングケアラー・こどもの意見聴取）を単独業務として先に受け、その結果を持って計画本体につなげる。調査は交付金が使え、金額も抑えられるため通りやすい。こども会議の設計・運営は策定年度以外でも受注できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>接触先</t>
+        </is>
+      </c>
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>こども未来課・子育て支援課だけでは足りない</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>保育、母子保健（健康推進課）、教育委員会（放課後児童クラブ）に所管が分かれている。庁内横断の調整そのものが担当者の最大の負担なので、「関係課をまとめた進め方の案」を持っていくと提案価値になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="59" t="inlineStr">
+        <is>
+          <t>タイムライン</t>
+        </is>
+      </c>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>R8年度中に予算化まで持ち込む</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R9年度当初予算での発注を狙うなら、R8年8〜10月に情報提供と参考見積、11〜12月に査定対応、1〜3月に公告。中間見直しを補正で狙う場合は、9月補正はすでに間に合わないため12月補正（要求は11月上旬）を目標にする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="99" t="inlineStr">
+        <is>
+          <t>地域福祉計画</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B17" s="39" t="inlineStr">
+        <is>
+          <t>見出し</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="52" t="inlineStr">
+        <is>
+          <t>現状認識</t>
+        </is>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>単発で取ると小さい。束ねて初めて中規模案件になる</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉計画そのものは金額が大きくない。併載できる計画と、社協の地域福祉活動計画を合わせて初めて採算に乗る。訪問記録にも「複数計画を地域福祉計画で一本化したい」という団体が実在しており、需要側の要望とも一致する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="53" t="inlineStr">
+        <is>
+          <t>狙い目①</t>
+        </is>
+      </c>
+      <c r="B19" s="49" t="inlineStr">
+        <is>
+          <t>成年後見制度利用促進基本計画の改定期</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>国の第二期基本計画が令和8年度で終期を迎え、第三期に移る。これに合わせて市町村計画を改定する団体が出るため、来期の有力な入口になる。中核機関が未設置の団体では、計画策定と体制整備をあわせて提案できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="53" t="inlineStr">
+        <is>
+          <t>狙い目②</t>
+        </is>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>重層的支援体制整備事業</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>未実施の団体には移行準備事業、実施済みの団体には実施計画の策定と体制強化。移行すると介護・障害・こども・困窮の相談支援等の補助が一体的に交付される点が説得材料になる。ただし最大の壁は庁内合意なので、計画の前段として庁内勉強会・業務フロー整理の伴走を提案する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="53" t="inlineStr">
+        <is>
+          <t>狙い目③</t>
+        </is>
+      </c>
+      <c r="B21" s="49" t="inlineStr">
+        <is>
+          <t>自殺対策計画（地域自殺対策強化交付金）</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>策定が義務であり、交付金を計画の策定・改定に充当できる。地域福祉計画に併載する形にすれば、財源のある計画が本体を引っ張る構図が作れる。JSCPの地域自殺実態プロファイルを使えば、重点施策を客観データで組める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="56" t="inlineStr">
+        <is>
+          <t>提案の型</t>
+        </is>
+      </c>
+      <c r="B22" s="47" t="inlineStr">
+        <is>
+          <t>自治体と社会福祉協議会の両方に当たる</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉計画（自治体）と地域福祉活動計画（社協）を一体で策定すると、発注元が2つになり予算を合算できる。社協は自治体より意思決定が早いことが多く、社協側から自治体を動かせる場合もある。どちらか一方だけを訪問している状態は、機会を半分捨てている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="56" t="inlineStr">
+        <is>
+          <t>提案の型</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>併載計画の一覧を作って持参する</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>成年後見・再犯防止・自殺対策・孤独孤立・生活困窮・避難行動要支援者・居住支援。担当自治体それぞれについて、どの計画がいつ切れるかを一覧にして見せる。「バラバラに作ると毎年どれかの改定が来るが、束ねれば数年に一度で済む」が最も効く言い方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="100" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="B24" s="47" t="inlineStr">
+        <is>
+          <t>圏域と進捗評価が実務の争点になる</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>圏域が計画ごとにバラバラ（日常生活圏域／小学校区／地区社協）な団体が多く、整理そのものを業務に含められる。また前計画の進捗評価の仕組みが無い団体が大半なので、指標設計と年次評価の仕組みづくりを提案に入れると、他社の標準的な策定業務と差がつく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="59" t="inlineStr">
+        <is>
+          <t>タイムライン</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>R8年8〜10月が勝負</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>地域福祉計画は複数課・社協との調整が要るため、予算要求の準備に時間がかかる。R8年8〜10月に併載計画の一覧と一体策定案を提示し、11〜12月の査定を越える。社協への接触は自治体と同時期に始める。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A16:C16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -21747,821 +23135,821 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="101" t="inlineStr">
         <is>
           <t>エリア</t>
         </is>
       </c>
-      <c r="B1" s="99" t="inlineStr">
+      <c r="B1" s="101" t="inlineStr">
         <is>
           <t>テーマ</t>
         </is>
       </c>
-      <c r="C1" s="99" t="inlineStr">
+      <c r="C1" s="101" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
-      <c r="D1" s="99" t="inlineStr">
+      <c r="D1" s="101" t="inlineStr">
         <is>
           <t>次回アクション</t>
         </is>
       </c>
-      <c r="E1" s="99" t="inlineStr">
+      <c r="E1" s="101" t="inlineStr">
         <is>
           <t>前回策定</t>
         </is>
       </c>
-      <c r="F1" s="99" t="inlineStr">
+      <c r="F1" s="101" t="inlineStr">
         <is>
           <t>改定時期</t>
         </is>
       </c>
-      <c r="G1" s="99" t="inlineStr">
+      <c r="G1" s="101" t="inlineStr">
         <is>
           <t>アプローチ時期</t>
         </is>
       </c>
-      <c r="H1" s="99" t="inlineStr">
+      <c r="H1" s="101" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="I1" s="99" t="inlineStr">
+      <c r="I1" s="101" t="inlineStr">
         <is>
           <t>契約予定</t>
         </is>
       </c>
-      <c r="J1" s="99" t="inlineStr">
+      <c r="J1" s="101" t="inlineStr">
         <is>
           <t>温度感</t>
         </is>
       </c>
-      <c r="K1" s="99" t="inlineStr">
+      <c r="K1" s="101" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="100" t="inlineStr">
+      <c r="A2" s="102" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="B2" s="100" t="inlineStr">
+      <c r="B2" s="102" t="inlineStr">
         <is>
           <t>公会計</t>
         </is>
       </c>
-      <c r="C2" s="100" t="inlineStr">
+      <c r="C2" s="102" t="inlineStr">
         <is>
           <t>見積提示</t>
         </is>
       </c>
-      <c r="D2" s="100" t="inlineStr">
+      <c r="D2" s="102" t="inlineStr">
         <is>
           <t>再アプローチ</t>
         </is>
       </c>
-      <c r="E2" s="100" t="inlineStr">
+      <c r="E2" s="102" t="inlineStr">
         <is>
           <t>委託</t>
         </is>
       </c>
-      <c r="F2" s="100" t="inlineStr">
+      <c r="F2" s="102" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="G2" s="100" t="inlineStr">
+      <c r="G2" s="102" t="inlineStr">
         <is>
           <t>今年度</t>
         </is>
       </c>
-      <c r="H2" s="100" t="inlineStr">
+      <c r="H2" s="102" t="inlineStr">
         <is>
           <t>初回訪問</t>
         </is>
       </c>
-      <c r="I2" s="100" t="inlineStr">
+      <c r="I2" s="102" t="inlineStr">
         <is>
           <t>入札</t>
         </is>
       </c>
-      <c r="J2" s="100" t="inlineStr">
+      <c r="J2" s="102" t="inlineStr">
         <is>
           <t>A：今年度中に動く</t>
         </is>
       </c>
-      <c r="K2" s="100" t="inlineStr">
+      <c r="K2" s="102" t="inlineStr">
         <is>
           <t>財務書類作成</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="100" t="inlineStr">
+      <c r="A3" s="102" t="inlineStr">
         <is>
           <t>青森県</t>
         </is>
       </c>
-      <c r="B3" s="100" t="inlineStr">
+      <c r="B3" s="102" t="inlineStr">
         <is>
           <t>会計支援</t>
         </is>
       </c>
-      <c r="C3" s="100" t="inlineStr">
+      <c r="C3" s="102" t="inlineStr">
         <is>
           <t>自力</t>
         </is>
       </c>
-      <c r="D3" s="100" t="inlineStr">
+      <c r="D3" s="102" t="inlineStr">
         <is>
           <t>見積提示</t>
         </is>
       </c>
-      <c r="E3" s="100" t="inlineStr">
+      <c r="E3" s="102" t="inlineStr">
         <is>
           <t>自前</t>
         </is>
       </c>
-      <c r="F3" s="100" t="inlineStr">
+      <c r="F3" s="102" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="G3" s="100" t="inlineStr">
+      <c r="G3" s="102" t="inlineStr">
         <is>
           <t>来年度</t>
         </is>
       </c>
-      <c r="H3" s="100" t="inlineStr">
+      <c r="H3" s="102" t="inlineStr">
         <is>
           <t>セカンドアプローチ</t>
         </is>
       </c>
-      <c r="I3" s="100" t="inlineStr">
+      <c r="I3" s="102" t="inlineStr">
         <is>
           <t>見積合わせ</t>
         </is>
       </c>
-      <c r="J3" s="100" t="inlineStr">
+      <c r="J3" s="102" t="inlineStr">
         <is>
           <t>B：次年度予算で検討</t>
         </is>
       </c>
-      <c r="K3" s="100" t="inlineStr">
+      <c r="K3" s="102" t="inlineStr">
         <is>
           <t>台帳精緻化（全体）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="100" t="inlineStr">
+      <c r="A4" s="102" t="inlineStr">
         <is>
           <t>岩手県</t>
         </is>
       </c>
-      <c r="B4" s="100" t="inlineStr">
+      <c r="B4" s="102" t="inlineStr">
         <is>
           <t>経営戦略</t>
         </is>
       </c>
-      <c r="C4" s="100" t="inlineStr">
+      <c r="C4" s="102" t="inlineStr">
         <is>
           <t>他社随契</t>
         </is>
       </c>
-      <c r="D4" s="100" t="inlineStr">
+      <c r="D4" s="102" t="inlineStr">
         <is>
           <t>同行依頼、再訪</t>
         </is>
       </c>
-      <c r="F4" s="100" t="inlineStr">
+      <c r="F4" s="102" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="G4" s="100" t="inlineStr">
+      <c r="G4" s="102" t="inlineStr">
         <is>
           <t>再来年度</t>
         </is>
       </c>
-      <c r="H4" s="100" t="inlineStr">
+      <c r="H4" s="102" t="inlineStr">
         <is>
           <t>見積提示</t>
         </is>
       </c>
-      <c r="I4" s="100" t="inlineStr">
+      <c r="I4" s="102" t="inlineStr">
         <is>
           <t>随契</t>
         </is>
       </c>
-      <c r="J4" s="100" t="inlineStr">
+      <c r="J4" s="102" t="inlineStr">
         <is>
           <t>C：様子見</t>
         </is>
       </c>
-      <c r="K4" s="100" t="inlineStr">
+      <c r="K4" s="102" t="inlineStr">
         <is>
           <t>台帳精緻化（所有外管理資産）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="100" t="inlineStr">
+      <c r="A5" s="102" t="inlineStr">
         <is>
           <t>宮城県</t>
         </is>
       </c>
-      <c r="B5" s="100" t="inlineStr">
+      <c r="B5" s="102" t="inlineStr">
         <is>
           <t>経営改善</t>
         </is>
       </c>
-      <c r="C5" s="100" t="inlineStr">
+      <c r="C5" s="102" t="inlineStr">
         <is>
           <t>不在</t>
         </is>
       </c>
-      <c r="D5" s="100" t="inlineStr">
+      <c r="D5" s="102" t="inlineStr">
         <is>
           <t>再訪不要</t>
         </is>
       </c>
-      <c r="F5" s="100" t="inlineStr">
+      <c r="F5" s="102" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="H5" s="100" t="inlineStr">
+      <c r="H5" s="102" t="inlineStr">
         <is>
           <t>見積＋仕様書</t>
         </is>
       </c>
-      <c r="I5" s="100" t="inlineStr">
+      <c r="I5" s="102" t="inlineStr">
         <is>
           <t>プロポ</t>
         </is>
       </c>
-      <c r="J5" s="100" t="inlineStr">
+      <c r="J5" s="102" t="inlineStr">
         <is>
           <t>D：当面なし</t>
         </is>
       </c>
-      <c r="K5" s="100" t="inlineStr">
+      <c r="K5" s="102" t="inlineStr">
         <is>
           <t>公会計システム導入</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="100" t="inlineStr">
+      <c r="A6" s="102" t="inlineStr">
         <is>
           <t>秋田県</t>
         </is>
       </c>
-      <c r="B6" s="100" t="inlineStr">
+      <c r="B6" s="102" t="inlineStr">
         <is>
           <t>福祉計画</t>
         </is>
       </c>
-      <c r="C6" s="100" t="inlineStr">
+      <c r="C6" s="102" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F6" s="100" t="inlineStr">
+      <c r="F6" s="102" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="K6" s="100" t="inlineStr">
+      <c r="K6" s="102" t="inlineStr">
         <is>
           <t>財務書類の活用支援・分析</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="100" t="inlineStr">
+      <c r="A7" s="102" t="inlineStr">
         <is>
           <t>山形県</t>
         </is>
       </c>
-      <c r="B7" s="100" t="inlineStr">
+      <c r="B7" s="102" t="inlineStr">
         <is>
           <t>公共施設マネジメント</t>
         </is>
       </c>
-      <c r="F7" s="100" t="inlineStr">
+      <c r="F7" s="102" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="K7" s="100" t="inlineStr">
+      <c r="K7" s="102" t="inlineStr">
         <is>
           <t>職員研修（公会計）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="100" t="inlineStr">
+      <c r="A8" s="102" t="inlineStr">
         <is>
           <t>福島県</t>
         </is>
       </c>
-      <c r="B8" s="100" t="inlineStr">
+      <c r="B8" s="102" t="inlineStr">
         <is>
           <t>社会生活計画</t>
         </is>
       </c>
-      <c r="F8" s="100" t="inlineStr">
+      <c r="F8" s="102" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="K8" s="100" t="inlineStr">
+      <c r="K8" s="102" t="inlineStr">
         <is>
           <t>公営企業会計 会計支援</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="100" t="inlineStr">
+      <c r="A9" s="102" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="B9" s="100" t="inlineStr">
+      <c r="B9" s="102" t="inlineStr">
         <is>
           <t>その他計画</t>
         </is>
       </c>
-      <c r="F9" s="100" t="inlineStr">
+      <c r="F9" s="102" t="inlineStr">
         <is>
           <t>R13</t>
         </is>
       </c>
-      <c r="K9" s="100" t="inlineStr">
+      <c r="K9" s="102" t="inlineStr">
         <is>
           <t>公営企業会計 適用（法適化）支援</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="100" t="inlineStr">
+      <c r="A10" s="102" t="inlineStr">
         <is>
           <t>栃木県</t>
         </is>
       </c>
-      <c r="F10" s="100" t="inlineStr">
+      <c r="F10" s="102" t="inlineStr">
         <is>
           <t>R14</t>
         </is>
       </c>
-      <c r="K10" s="100" t="inlineStr">
+      <c r="K10" s="102" t="inlineStr">
         <is>
           <t>決算・決算統計 作成支援</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="100" t="inlineStr">
+      <c r="A11" s="102" t="inlineStr">
         <is>
           <t>群馬県</t>
         </is>
       </c>
-      <c r="F11" s="100" t="inlineStr">
+      <c r="F11" s="102" t="inlineStr">
         <is>
           <t>R15</t>
         </is>
       </c>
-      <c r="K11" s="100" t="inlineStr">
+      <c r="K11" s="102" t="inlineStr">
         <is>
           <t>上下水道 経営戦略（策定）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="100" t="inlineStr">
+      <c r="A12" s="102" t="inlineStr">
         <is>
           <t>埼玉県</t>
         </is>
       </c>
-      <c r="F12" s="100" t="inlineStr">
+      <c r="F12" s="102" t="inlineStr">
         <is>
           <t>R16</t>
         </is>
       </c>
-      <c r="K12" s="100" t="inlineStr">
+      <c r="K12" s="102" t="inlineStr">
         <is>
           <t>上下水道 経営戦略（改定）</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="100" t="inlineStr">
+      <c r="A13" s="102" t="inlineStr">
         <is>
           <t>千葉県</t>
         </is>
       </c>
-      <c r="F13" s="100" t="inlineStr">
+      <c r="F13" s="102" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="K13" s="100" t="inlineStr">
+      <c r="K13" s="102" t="inlineStr">
         <is>
           <t>アセットマネジメント・ストックマネジメント</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="100" t="inlineStr">
+      <c r="A14" s="102" t="inlineStr">
         <is>
           <t>東京都</t>
         </is>
       </c>
-      <c r="F14" s="100" t="inlineStr">
+      <c r="F14" s="102" t="inlineStr">
         <is>
           <t>R18</t>
         </is>
       </c>
-      <c r="K14" s="100" t="inlineStr">
+      <c r="K14" s="102" t="inlineStr">
         <is>
           <t>病院事業 経営強化プラン</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="100" t="inlineStr">
+      <c r="A15" s="102" t="inlineStr">
         <is>
           <t>神奈川県</t>
         </is>
       </c>
-      <c r="F15" s="100" t="inlineStr">
+      <c r="F15" s="102" t="inlineStr">
         <is>
           <t>R19</t>
         </is>
       </c>
-      <c r="K15" s="100" t="inlineStr">
+      <c r="K15" s="102" t="inlineStr">
         <is>
           <t>料金・使用料改定</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="100" t="inlineStr">
+      <c r="A16" s="102" t="inlineStr">
         <is>
           <t>新潟県</t>
         </is>
       </c>
-      <c r="F16" s="100" t="inlineStr">
+      <c r="F16" s="102" t="inlineStr">
         <is>
           <t>R20</t>
         </is>
       </c>
-      <c r="K16" s="100" t="inlineStr">
+      <c r="K16" s="102" t="inlineStr">
         <is>
           <t>経営分析（経営比較分析表の活用）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="100" t="inlineStr">
+      <c r="A17" s="102" t="inlineStr">
         <is>
           <t>富山県</t>
         </is>
       </c>
-      <c r="K17" s="100" t="inlineStr">
+      <c r="K17" s="102" t="inlineStr">
         <is>
           <t>広域化・官民連携 検討支援</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="100" t="inlineStr">
+      <c r="A18" s="102" t="inlineStr">
         <is>
           <t>石川県</t>
         </is>
       </c>
-      <c r="K18" s="100" t="inlineStr">
+      <c r="K18" s="102" t="inlineStr">
         <is>
           <t>高齢者福祉計画・介護保険事業計画</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="100" t="inlineStr">
+      <c r="A19" s="102" t="inlineStr">
         <is>
           <t>福井県</t>
         </is>
       </c>
-      <c r="K19" s="100" t="inlineStr">
+      <c r="K19" s="102" t="inlineStr">
         <is>
           <t>障害者計画・障害福祉計画・障害児福祉計画</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="100" t="inlineStr">
+      <c r="A20" s="102" t="inlineStr">
         <is>
           <t>山梨県</t>
         </is>
       </c>
-      <c r="K20" s="100" t="inlineStr">
+      <c r="K20" s="102" t="inlineStr">
         <is>
           <t>地域福祉計画</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="100" t="inlineStr">
+      <c r="A21" s="102" t="inlineStr">
         <is>
           <t>長野県</t>
         </is>
       </c>
-      <c r="K21" s="100" t="inlineStr">
+      <c r="K21" s="102" t="inlineStr">
         <is>
           <t>こども計画</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="100" t="inlineStr">
+      <c r="A22" s="102" t="inlineStr">
         <is>
           <t>岐阜県</t>
         </is>
       </c>
-      <c r="K22" s="100" t="inlineStr">
+      <c r="K22" s="102" t="inlineStr">
         <is>
           <t>子ども子育て支援事業計画</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="100" t="inlineStr">
+      <c r="A23" s="102" t="inlineStr">
         <is>
           <t>静岡県</t>
         </is>
       </c>
-      <c r="K23" s="100" t="inlineStr">
+      <c r="K23" s="102" t="inlineStr">
         <is>
           <t>重層的支援体制整備事業 支援</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="100" t="inlineStr">
+      <c r="A24" s="102" t="inlineStr">
         <is>
           <t>愛知県</t>
         </is>
       </c>
-      <c r="K24" s="100" t="inlineStr">
+      <c r="K24" s="102" t="inlineStr">
         <is>
           <t>福祉分野 アンケート調査（単独受託）</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="100" t="inlineStr">
+      <c r="A25" s="102" t="inlineStr">
         <is>
           <t>三重県</t>
         </is>
       </c>
-      <c r="K25" s="100" t="inlineStr">
+      <c r="K25" s="102" t="inlineStr">
         <is>
           <t>公共施設等総合管理計画</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="100" t="inlineStr">
+      <c r="A26" s="102" t="inlineStr">
         <is>
           <t>滋賀県</t>
         </is>
       </c>
-      <c r="K26" s="100" t="inlineStr">
+      <c r="K26" s="102" t="inlineStr">
         <is>
           <t>個別施設計画</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="100" t="inlineStr">
+      <c r="A27" s="102" t="inlineStr">
         <is>
           <t>京都府</t>
         </is>
       </c>
-      <c r="K27" s="100" t="inlineStr">
+      <c r="K27" s="102" t="inlineStr">
         <is>
           <t>施設カルテ・施設白書</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="100" t="inlineStr">
+      <c r="A28" s="102" t="inlineStr">
         <is>
           <t>大阪府</t>
         </is>
       </c>
-      <c r="K28" s="100" t="inlineStr">
+      <c r="K28" s="102" t="inlineStr">
         <is>
           <t>公共施設 再編・適正配置検討</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="100" t="inlineStr">
+      <c r="A29" s="102" t="inlineStr">
         <is>
           <t>兵庫県</t>
         </is>
       </c>
-      <c r="K29" s="100" t="inlineStr">
+      <c r="K29" s="102" t="inlineStr">
         <is>
           <t>健康増進計画・食育推進計画</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="100" t="inlineStr">
+      <c r="A30" s="102" t="inlineStr">
         <is>
           <t>奈良県</t>
         </is>
       </c>
-      <c r="K30" s="100" t="inlineStr">
+      <c r="K30" s="102" t="inlineStr">
         <is>
           <t>自殺対策計画</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="100" t="inlineStr">
+      <c r="A31" s="102" t="inlineStr">
         <is>
           <t>和歌山県</t>
         </is>
       </c>
-      <c r="K31" s="100" t="inlineStr">
+      <c r="K31" s="102" t="inlineStr">
         <is>
           <t>男女共同参画計画</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="100" t="inlineStr">
+      <c r="A32" s="102" t="inlineStr">
         <is>
           <t>鳥取県</t>
         </is>
       </c>
-      <c r="K32" s="100" t="inlineStr">
+      <c r="K32" s="102" t="inlineStr">
         <is>
           <t>環境基本計画</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="100" t="inlineStr">
+      <c r="A33" s="102" t="inlineStr">
         <is>
           <t>島根県</t>
         </is>
       </c>
-      <c r="K33" s="100" t="inlineStr">
+      <c r="K33" s="102" t="inlineStr">
         <is>
           <t>地域公共交通計画</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="100" t="inlineStr">
+      <c r="A34" s="102" t="inlineStr">
         <is>
           <t>岡山県</t>
         </is>
       </c>
-      <c r="K34" s="100" t="inlineStr">
+      <c r="K34" s="102" t="inlineStr">
         <is>
           <t>文化財保存活用地域計画</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="100" t="inlineStr">
+      <c r="A35" s="102" t="inlineStr">
         <is>
           <t>広島県</t>
         </is>
       </c>
-      <c r="K35" s="100" t="inlineStr">
+      <c r="K35" s="102" t="inlineStr">
         <is>
           <t>総合計画</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="100" t="inlineStr">
+      <c r="A36" s="102" t="inlineStr">
         <is>
           <t>山口県</t>
         </is>
       </c>
-      <c r="K36" s="100" t="inlineStr">
+      <c r="K36" s="102" t="inlineStr">
         <is>
           <t>財政計画・中期財政推計</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="100" t="inlineStr">
+      <c r="A37" s="102" t="inlineStr">
         <is>
           <t>徳島県</t>
         </is>
       </c>
-      <c r="K37" s="100" t="inlineStr">
+      <c r="K37" s="102" t="inlineStr">
         <is>
           <t>農業振興計画・地域計画</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="100" t="inlineStr">
+      <c r="A38" s="102" t="inlineStr">
         <is>
           <t>香川県</t>
         </is>
       </c>
-      <c r="K38" s="100" t="inlineStr">
+      <c r="K38" s="102" t="inlineStr">
         <is>
           <t>国土強靱化地域計画</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="100" t="inlineStr">
+      <c r="A39" s="102" t="inlineStr">
         <is>
           <t>愛媛県</t>
         </is>
       </c>
-      <c r="K39" s="100" t="inlineStr">
+      <c r="K39" s="102" t="inlineStr">
         <is>
           <t>その他（上記以外）</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="100" t="inlineStr">
+      <c r="A40" s="102" t="inlineStr">
         <is>
           <t>高知県</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="100" t="inlineStr">
+      <c r="A41" s="102" t="inlineStr">
         <is>
           <t>福岡県</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="100" t="inlineStr">
+      <c r="A42" s="102" t="inlineStr">
         <is>
           <t>佐賀県</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="100" t="inlineStr">
+      <c r="A43" s="102" t="inlineStr">
         <is>
           <t>長崎県</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="100" t="inlineStr">
+      <c r="A44" s="102" t="inlineStr">
         <is>
           <t>熊本県</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="100" t="inlineStr">
+      <c r="A45" s="102" t="inlineStr">
         <is>
           <t>大分県</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="100" t="inlineStr">
+      <c r="A46" s="102" t="inlineStr">
         <is>
           <t>宮崎県</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="100" t="inlineStr">
+      <c r="A47" s="102" t="inlineStr">
         <is>
           <t>鹿児島県</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="100" t="inlineStr">
+      <c r="A48" s="102" t="inlineStr">
         <is>
           <t>沖縄県</t>
         </is>

--- a/output/10_新人教育カリキュラム_マスター管理表.xlsx
+++ b/output/10_新人教育カリキュラム_マスター管理表.xlsx
@@ -36,8 +36,9 @@
     <sheet name="26_テーマ・タイトル標準リスト" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="27_5分トーク集" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="28_5分トーク_想定問答とNG" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="29_来期営業方針_こども・地域福祉" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="選択肢マスタ" sheetId="31" state="hidden" r:id="rId31"/>
+    <sheet name="29_営業方針_今期補正と来期獲得" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="30_5分社内研修" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="選択肢マスタ" sheetId="32" state="hidden" r:id="rId32"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_月次ロードマップ'!$A$4:$I$40</definedName>
@@ -61,8 +62,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'24_訪問記録CSV_入力シート'!$A$1:$O$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'25_CSV入力規則'!$A$4:$G$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'26_テーマ・タイトル標準リスト'!$A$4:$D$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'27_5分トーク集'!$A$13:$E$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'28_5分トーク_想定問答とNG'!$A$5:$D$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'27_5分トーク集'!$A$14:$E$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'28_5分トーク_想定問答とNG'!$A$5:$D$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="30">'30_5分社内研修'!$A$1:$F$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -71,7 +73,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -143,6 +145,12 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="41">
@@ -465,7 +473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -741,16 +749,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1121,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1368,107 +1385,113 @@
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　29_来期営業方針_こども・地域福祉… R9年度に向けた2テーマの攻め方</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+          <t xml:space="preserve">　29_営業方針_今期補正と来期獲得… A 高齢者介護・障がいの補正／B 地域福祉・こどもの来期獲得</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　30_5分社内研修… A補正編・B来期編の5分台本と、週次5分シリーズ8回</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>4. 運用サイクル（推奨）</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　毎月　　… 上長と本人で30分の面談。当月の学習項目と習得目標の達成状況を確認し、翌月の重点を決める。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　四半期　… 成果物レビューを1件必ず実施し、「確認方法」欄の方法で到達度を確認する。</t>
+          <t xml:space="preserve">　毎月　　… 上長と本人で30分の面談。当月の学習項目と習得目標の達成状況を確認し、翌月の重点を決める。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　半期　　… 12_個人別チェックシートで自己評価と上長評価を突き合わせ、差異の原因を対話する。</t>
+          <t xml:space="preserve">　四半期　… 成果物レビューを1件必ず実施し、「確認方法」欄の方法で到達度を確認する。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　半期　　… 12_個人別チェックシートで自己評価と上長評価を突き合わせ、差異の原因を対話する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　年次　　… レベル判定を確定し、次年度の主担当・副担当テーマと育成計画を決定する。</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>5. レベル判定の原則</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　・「知っている」ではなく「できた実績があるか」で判定します。判定には必ず具体的な案件名・成果物名を紐づけてください。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　・1つの項目でL3と判定するには、原則として同種の作業を2案件以上、単独で完遂している必要があります。</t>
+          <t xml:space="preserve">　・「知っている」ではなく「できた実績があるか」で判定します。判定には必ず具体的な案件名・成果物名を紐づけてください。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　・1つの項目でL3と判定するには、原則として同種の作業を2案件以上、単独で完遂している必要があります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　・自己評価と上長評価に2段階以上の差がある場合は、必ず面談で認識を合わせてください。</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>6. 更新について</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　・制度改正（基本指針、報酬改定、会計基準、各省ガイドライン等）が生じた場合は、該当テーマシートの学習内容を年1回見直してください。</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">　・制度改正（基本指針、報酬改定、会計基準、各省ガイドライン等）が生じた場合は、該当テーマシートの学習内容を年1回見直してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　・計画の「期」（第○期）は年度の経過とともに進みます。テーマシートの記載は根拠法と期間の考え方を示すもので、具体の期・年度は都度確認してください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="47">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A39:H39"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A49:H49"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A45:H45"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A25:H25"/>
@@ -1479,7 +1502,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="A2:H2"/>
@@ -1493,15 +1515,18 @@
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A40:H40"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A53:H53"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A43:H43"/>
     <mergeCell ref="A52:H52"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
@@ -19288,12 +19313,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="76" customWidth="1" min="5" max="5"/>
   </cols>
@@ -19323,12 +19348,12 @@
       <c r="A5" s="60" t="inlineStr"/>
       <c r="B5" s="60" t="inlineStr">
         <is>
-          <t>テーマ</t>
+          <t>軸</t>
         </is>
       </c>
       <c r="C5" s="60" t="inlineStr">
         <is>
-          <t>ケース</t>
+          <t>テーマ／ケース</t>
         </is>
       </c>
       <c r="D5" s="60" t="inlineStr">
@@ -19350,12 +19375,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>高齢者・介護保険</t>
+          <t>A 補正</t>
         </is>
       </c>
       <c r="C6" s="47" t="inlineStr">
         <is>
-          <t>自前作成先からの補正予算獲得</t>
+          <t>高齢者・介護保険／自前作成先からの補正予算獲得</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -19372,165 +19397,165 @@
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>公会計</t>
+          <t>A 補正</t>
         </is>
       </c>
       <c r="C7" s="47" t="inlineStr">
         <is>
-          <t>所有外管理資産（セミナー案内後のフォロー）</t>
+          <t>障害者・障害児／障がい3計画の補正（高齢者と重なる年）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>財務書類は作成済みで、固定資産台帳の精緻化が手つかずの自治体。セミナーを案内した先。</t>
+          <t>第8期障害福祉計画・第4期障害児福祉計画（R9〜11年度）を自前で作っている自治体。高齢者の第10期と策定年度が重なり、小規模団体では同じ課・同じ担当者が両方を持っている。</t>
         </is>
       </c>
       <c r="E7" s="91" t="inlineStr">
         <is>
-          <t>台帳の資産額が実態より少ないと、有形固定資産減価償却率がずれ、総合管理計画の更新費用試算の前提が崩れ、起債・交付金の裏付けも弱くなる。台帳は公会計だけの話ではなく、施設と財源の話につながっている。</t>
+          <t>障害福祉計画には保険料のような議決の期限がないため、高齢者が優先されて後回しになりやすい。ただし県の障害福祉計画が市町村の見込量を集約するため、県への提出時期が実質の期限になる。「期限がない」と思われているものに、実質の期限を示すのが障がい特有の切り口。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>公共施設マネジメント</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="C8" s="47" t="inlineStr">
         <is>
-          <t>総合管理計画の改定（起債要件から入る）</t>
+          <t>公会計／所有外管理資産（セミナー案内後のフォロー）</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>公共施設等総合管理計画の改定時期がR9〜R10に来る自治体</t>
+          <t>財務書類は作成済みで、固定資産台帳の精緻化が手つかずの自治体。セミナーを案内した先。</t>
         </is>
       </c>
       <c r="E8" s="91" t="inlineStr">
         <is>
-          <t>公共施設等適正管理推進事業債は、総合管理計画に基づく事業であることが要件。裏を返せば、計画に書かれていない事業は起債の対象にならない。計画改定は「作り直し」ではなく「財源を使えるようにする作業」。</t>
+          <t>台帳の資産額が実態より少ないと、有形固定資産減価償却率がずれ、総合管理計画の更新費用試算の前提が崩れ、起債・交付金の裏付けも弱くなる。台帳は公会計だけの話ではなく、施設と財源の話につながっている。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>会計支援・経営戦略ほか</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="C9" s="47" t="inlineStr">
         <is>
-          <t>他社随契先への切り込み</t>
+          <t>公共施設マネジメント／総合管理計画の改定（起債要件から入る）</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>現在ほかの会社と随意契約している自治体。訪問記録では他社随契20件のうち7件が「再訪不要」で打ち切られているが、改定時期はR9〜R14と先の団体が多い。</t>
+          <t>公共施設等総合管理計画の改定時期がR9〜R10に来る自治体</t>
         </is>
       </c>
       <c r="E9" s="91" t="inlineStr">
         <is>
-          <t>随意契約は「変える理由がない」から続いている。変えさせようとするのではなく、契約範囲に入っていない隣の業務を取る。そして改定年度の前年度に必ず戻る。随契が切れる機会は、担当者の交代と改定年度しかない。</t>
+          <t>公共施設等適正管理推進事業債は、総合管理計画に基づく事業であることが要件。裏を返せば、計画に書かれていない事業は起債の対象にならない。計画改定は「作り直し」ではなく「財源を使えるようにする作業」。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="37" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>会計支援・経営戦略ほか／他社随契先への切り込み</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>現在ほかの会社と随意契約している自治体。訪問記録では他社随契20件のうち7件が「再訪不要」で打ち切られているが、改定時期はR9〜R14と先の団体が多い。</t>
+        </is>
+      </c>
+      <c r="E10" s="91" t="inlineStr">
+        <is>
+          <t>随意契約は「変える理由がない」から続いている。変えさせようとするのではなく、契約範囲に入っていない隣の業務を取る。そして改定年度の前年度に必ず戻る。随契が切れる機会は、担当者の交代と改定年度しかない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="37" t="inlineStr">
+        <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>全テーマ共通</t>
-        </is>
-      </c>
-      <c r="C10" s="47" t="inlineStr">
-        <is>
-          <t>担当者が不在だったときの3分</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
+        <is>
+          <t>全テーマ共通／担当者が不在だったときの3分</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>訪問先で担当者が不在だった場合。訪問記録では不在が15件あり、すべて「再アプローチ」としているが、備考に再訪日まで書けている記録は一部にとどまる。</t>
         </is>
       </c>
-      <c r="E10" s="91" t="inlineStr">
+      <c r="E11" s="91" t="inlineStr">
         <is>
           <t>不在は失敗ではなく、次を作る機会。受付で3つ確認し、1枚置いて帰る。何も置かずに帰ると、訪問した事実が相手側に何も残らない。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="90" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="90" t="inlineStr">
         <is>
           <t>スクリプト</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="60" t="inlineStr"/>
-      <c r="B13" s="60" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="60" t="inlineStr"/>
+      <c r="B14" s="60" t="inlineStr">
         <is>
           <t>時間</t>
         </is>
       </c>
-      <c r="C13" s="60" t="inlineStr">
+      <c r="C14" s="60" t="inlineStr">
         <is>
           <t>見出し</t>
         </is>
       </c>
-      <c r="D13" s="60" t="inlineStr">
+      <c r="D14" s="60" t="inlineStr">
         <is>
           <t>話す内容（スクリプト）</t>
         </is>
       </c>
-      <c r="E13" s="60" t="inlineStr">
+      <c r="E14" s="60" t="inlineStr">
         <is>
           <t>ねらい</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="92" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B14" s="93" t="inlineStr">
-        <is>
-          <t>0:00–0:30</t>
-        </is>
-      </c>
-      <c r="C14" s="47" t="inlineStr">
-        <is>
-          <t>用件を告げ、5分だけもらう</t>
-        </is>
-      </c>
-      <c r="D14" s="63" t="inlineStr">
-        <is>
-          <t>「◯◯町の高齢福祉課様でいらっしゃいますね。◯◯株式会社の△△と申します。第10期の介護保険事業計画の件で、5分だけお時間をいただけますでしょうか。御町ではご自身で作られていると伺っておりまして、この時期にお伝えしておいたほうがよいことが2点ございます。」</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>「自前で作っている」ことを知っている＝下調べ済みだと最初に伝える。売り込みではなく「時期の話」として入る。5分と明示すると断られにくい。</t>
         </is>
       </c>
     </row>
@@ -19542,51 +19567,51 @@
       </c>
       <c r="B15" s="93" t="inlineStr">
         <is>
+          <t>0:00–0:30</t>
+        </is>
+      </c>
+      <c r="C15" s="47" t="inlineStr">
+        <is>
+          <t>用件を告げ、5分だけもらう</t>
+        </is>
+      </c>
+      <c r="D15" s="63" t="inlineStr">
+        <is>
+          <t>「◯◯町の高齢福祉課様でいらっしゃいますね。◯◯株式会社の△△と申します。第10期の介護保険事業計画の件で、5分だけお時間をいただけますでしょうか。御町ではご自身で作られていると伺っておりまして、この時期にお伝えしておいたほうがよいことが2点ございます。」</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>「自前で作っている」ことを知っている＝下調べ済みだと最初に伝える。売り込みではなく「時期の話」として入る。5分と明示すると断られにくい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B16" s="93" t="inlineStr">
+        <is>
           <t>0:30–1:30</t>
         </is>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C16" s="47" t="inlineStr">
         <is>
           <t>進捗を3問だけ聞く</t>
         </is>
       </c>
-      <c r="D15" s="63" t="inlineStr">
+      <c r="D16" s="63" t="inlineStr">
         <is>
           <t>「①ニーズ調査と在宅介護実態調査の集計は、もうお済みでしょうか。」
 「②保険料の算定は、どなたがご担当される予定でしょうか。」
 「③3月議会での条例改正に向けて、パブリックコメントはいつ頃を想定されていますか。」</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>この3問で自前完遂の可否がほぼ判定できる。①が未了、②が未定、③が「これから考える」なら高い確率で間に合わない。詰問にならないよう3問で止める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="92" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B16" s="93" t="inlineStr">
-        <is>
-          <t>1:30–3:00</t>
-        </is>
-      </c>
-      <c r="C16" s="47" t="inlineStr">
-        <is>
-          <t>逆算して見せる（本題）</t>
-        </is>
-      </c>
-      <c r="D16" s="63" t="inlineStr">
-        <is>
-          <t>「第10期の保険料は、R9年4月から賦課するためにR9年3月議会での条例改正が要ります。そこから逆算しますと──2月下旬に議案上程、その前に1〜2月でパブリックコメント（30日程度）、その前の12〜1月で保険料の確定と計画素案、11月に給付費推計とサービス見込量、10月までに現状分析。つまり10月末までに分析が終わっていないと、パブコメの期間が取れなくなります。」</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>計画策定業務ではなく「条例改正の期限」から話す。自治体側が動かせない制約なので、こちらの都合ではなく相手の制約として受け取ってもらえる。</t>
         </is>
       </c>
     </row>
@@ -19598,22 +19623,22 @@
       </c>
       <c r="B17" s="93" t="inlineStr">
         <is>
-          <t>3:00–4:00</t>
+          <t>1:30–3:00</t>
         </is>
       </c>
       <c r="C17" s="47" t="inlineStr">
         <is>
-          <t>部分委託という逃げ道を示す</t>
+          <t>逆算して見せる（本題）</t>
         </is>
       </c>
       <c r="D17" s="63" t="inlineStr">
         <is>
-          <t>「全部をお預けいただく必要はありません。いちばん時間がかかるのは保険料の算定と給付費推計で、ここは見える化システムと厚労省のワークシートを使った作業です。ここだけをお預かりして、計画本文は御町で書いていただく、という切り分けができます。この形なら金額も抑えられますので、12月補正で十分間に合います。」</t>
+          <t>「第10期の保険料は、R9年4月から賦課するためにR9年3月議会での条例改正が要ります。そこから逆算しますと──2月下旬に議案上程、その前に1〜2月でパブリックコメント（30日程度）、その前の12〜1月で保険料の確定と計画素案、11月に給付費推計とサービス見込量、10月までに現状分析。つまり10月末までに分析が終わっていないと、パブコメの期間が取れなくなります。」</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>全部委託は補正で通りにくい（金額が大きく査定に耐えない）。「作れない」ではなく「時間がかかる工程だけ外に出す」と提示すると、担当者の面目も立つ。</t>
+          <t>計画策定業務ではなく「条例改正の期限」から話す。自治体側が動かせない制約なので、こちらの都合ではなく相手の制約として受け取ってもらえる。</t>
         </is>
       </c>
     </row>
@@ -19625,580 +19650,744 @@
       </c>
       <c r="B18" s="93" t="inlineStr">
         <is>
-          <t>4:00–5:00</t>
+          <t>3:00–4:00</t>
         </is>
       </c>
       <c r="C18" s="47" t="inlineStr">
         <is>
-          <t>次を決めて帰る</t>
+          <t>部分委託という逃げ道を示す</t>
         </is>
       </c>
       <c r="D18" s="63" t="inlineStr">
         <is>
-          <t>「12月補正ですと、財政課へのご要求はおおむね11月上旬かと思います。10月中に、業務の切り分け案と参考のお見積をお持ちします。いつ頃までにあるとよろしいでしょうか。」</t>
+          <t>「全部をお預けいただく必要はありません。いちばん時間がかかるのは保険料の算定と給付費推計で、ここは見える化システムと厚労省のワークシートを使った作業です。ここだけをお預かりして、計画本文は御町で書いていただく、という切り分けができます。この形なら金額も抑えられますので、12月補正で十分間に合います。」</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>提出期限を相手に言わせる。相手の庁内スケジュールが分かり、次回訪問の理由も確定する。</t>
+          <t>全部委託は補正で通りにくい（金額が大きく査定に耐えない）。「作れない」ではなく「時間がかかる工程だけ外に出す」と提示すると、担当者の面目も立つ。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B19" s="93" t="inlineStr">
         <is>
-          <t>0:00–0:30</t>
+          <t>4:00–5:00</t>
         </is>
       </c>
       <c r="C19" s="47" t="inlineStr">
         <is>
-          <t>セミナーを口実に入る</t>
+          <t>次を決めて帰る</t>
         </is>
       </c>
       <c r="D19" s="63" t="inlineStr">
         <is>
-          <t>「先日ご案内いたしました所有外管理資産のセミナーの件で伺いました。ご参加は難しかったかと存じますので、要点だけ5分でお伝えできればと思っております。」</t>
+          <t>「12月補正ですと、財政課へのご要求はおおむね11月上旬かと思います。10月中に、業務の切り分け案と参考のお見積をお持ちします。いつ頃までにあるとよろしいでしょうか。」</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>セミナーは案内して終わりにしない。参加の有無にかかわらず内容を届けに行くのが本来のフォロー。訪問記録では「セミナー案内」で止まっている記録が多く、ここが取りこぼしになっている。</t>
+          <t>提出期限を相手に言わせる。相手の庁内スケジュールが分かり、次回訪問の理由も確定する。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="92" t="inlineStr">
         <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B20" s="93" t="inlineStr">
+        <is>
+          <t>0:00–0:30</t>
+        </is>
+      </c>
+      <c r="C20" s="47" t="inlineStr">
+        <is>
+          <t>高齢者と重なっていることから入る</t>
+        </is>
+      </c>
+      <c r="D20" s="63" t="inlineStr">
+        <is>
+          <t>「第8期の障害福祉計画と第4期の障害児福祉計画の件で伺いました。今年度は高齢者の第10期と重なる年ですので、ご負担が集中されているのではないかと思いまして。5分だけお時間をいただけますでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>「大変ですね」と同情から入らない。「重なっている」という事実から入る。担当者が自分からは言いにくいことを、こちらから先に言う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="92" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B21" s="93" t="inlineStr">
+        <is>
+          <t>0:30–1:30</t>
+        </is>
+      </c>
+      <c r="C21" s="47" t="inlineStr">
+        <is>
+          <t>残っているものを3問だけ聞く</t>
+        </is>
+      </c>
+      <c r="D21" s="63" t="inlineStr">
+        <is>
+          <t>「①手帳をお持ちの方へのアンケートは、もう実施されましたでしょうか。」
+「②前期の成果目標の達成状況の評価は、お済みでしょうか。」
+「③県への見込量のご提出は、いつ頃までとご案内が来ていますでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>③が実質の期限。ここを押さえている担当者は多くなく、答えられなければ、それ自体がこちらの持ち込む課題になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="92" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B22" s="93" t="inlineStr">
+        <is>
+          <t>1:30–3:00</t>
+        </is>
+      </c>
+      <c r="C22" s="47" t="inlineStr">
+        <is>
+          <t>期限の構造を示す（本題）</t>
+        </is>
+      </c>
+      <c r="D22" s="63" t="inlineStr">
+        <is>
+          <t>「障害福祉計画には保険料のような議決の期限がございませんので、高齢者が優先されて後回しになりやすいところかと思います。ただ、県の障害福祉計画が市町村の見込量を集約しますので、県へのご提出が実質の期限になります。そこから逆算しますと、年内に成果目標と見込量が固まっている必要があります。」</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>「期限がない」と思われているものに、実質の期限を示す。県の提出時期は団体・県により違うため、断定せず「ご案内が来ていますか」と確認する形で扱う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="92" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B23" s="93" t="inlineStr">
+        <is>
+          <t>3:00–4:00</t>
+        </is>
+      </c>
+      <c r="C23" s="47" t="inlineStr">
+        <is>
+          <t>負担の大きいところだけ切り出す</t>
+        </is>
+      </c>
+      <c r="D23" s="63" t="inlineStr">
+        <is>
+          <t>「全部をお預けいただく必要はありません。時間がかかるのは成果目標の設定と見込量の推計で、前期の実績と国保連のデータを使った作業です。ここだけをお預かりして、障害者計画の理念の部分は御市で書いていただく形にできます。高齢者と重なる年ですので、負担の大きいところだけ外に出すという考え方です。」</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>3計画一体だと分量が大きく、全部委託は査定に耐えない。「重なっているから一部だけ」は、庁内で説明しやすい理由になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="92" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B24" s="93" t="inlineStr">
+        <is>
+          <t>4:00–5:00</t>
+        </is>
+      </c>
+      <c r="C24" s="47" t="inlineStr">
+        <is>
+          <t>高齢者と分けて見積を出す約束をする</t>
+        </is>
+      </c>
+      <c r="D24" s="63" t="inlineStr">
+        <is>
+          <t>「12月補正でしたら、財政課へのご要求は11月上旬かと思います。10月中に、高齢者と障がいを分けた切り分け案と参考のお見積をお持ちします。いつ頃までにあるとよろしいでしょうか。」</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>高齢者と障がいを1本にまとめると金額が膨らみ、査定で落ちる。分けて出し、通しやすい方から通す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="92" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B20" s="93" t="inlineStr">
+      <c r="B25" s="93" t="inlineStr">
+        <is>
+          <t>0:00–0:30</t>
+        </is>
+      </c>
+      <c r="C25" s="47" t="inlineStr">
+        <is>
+          <t>セミナーを口実に入る</t>
+        </is>
+      </c>
+      <c r="D25" s="63" t="inlineStr">
+        <is>
+          <t>「先日ご案内いたしました所有外管理資産のセミナーの件で伺いました。ご参加は難しかったかと存じますので、要点だけ5分でお伝えできればと思っております。」</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>セミナーは案内して終わりにしない。参加の有無にかかわらず内容を届けに行くのが本来のフォロー。訪問記録では「セミナー案内」で止まっている記録が多く、ここが取りこぼしになっている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="92" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B26" s="93" t="inlineStr">
         <is>
           <t>0:30–1:30</t>
         </is>
       </c>
-      <c r="C20" s="47" t="inlineStr">
+      <c r="C26" s="47" t="inlineStr">
         <is>
           <t>台帳の実態を3問だけ聞く</t>
         </is>
       </c>
-      <c r="D20" s="63" t="inlineStr">
+      <c r="D26" s="63" t="inlineStr">
         <is>
           <t>「①固定資産台帳の更新は、毎年度されていますでしょうか。」
 「②公有財産台帳との突合は、これまでにされたことはございますか。」
 「③借地の上に建っている施設や、指定管理でお願いしている施設は、台帳にどう入っていますか。」</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>③が即答できなければ所有外の整理は未着手。3問目で「うちはどうなっているだろう」と相手自身に思わせるのが目的で、答えを引き出すこと自体は目的ではない。</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="92" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="92" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B21" s="93" t="inlineStr">
+      <c r="B27" s="93" t="inlineStr">
         <is>
           <t>1:30–3:00</t>
         </is>
       </c>
-      <c r="C21" s="47" t="inlineStr">
+      <c r="C27" s="47" t="inlineStr">
         <is>
           <t>論点を具体名で並べる</t>
         </is>
       </c>
-      <c r="D21" s="63" t="inlineStr">
+      <c r="D27" s="63" t="inlineStr">
         <is>
           <t>「所有外管理資産と申しましても、中身はいくつかに分かれます。借地の上の建物、指定管理施設、無償で譲り受けた資産、法定外公共物──里道や水路ですね、共有や区分所有のもの、リース資産、PFIの施設。それから逆に、所有はしているが管理を他に委ねているもの。まず、どれが御市に当てはまるかを一覧にするところからです。」</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>抽象的な「精緻化」では動かない。具体名を並べると「うちにもある」と気づいてもらえる。ここで相手が挙げた資産が、そのまま提案の対象になる。</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="92" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="92" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B22" s="93" t="inlineStr">
+      <c r="B28" s="93" t="inlineStr">
         <is>
           <t>3:00–4:00</t>
         </is>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C28" s="47" t="inlineStr">
         <is>
           <t>影響の連鎖を見せる</t>
         </is>
       </c>
-      <c r="D22" s="63" t="inlineStr">
+      <c r="D28" s="63" t="inlineStr">
         <is>
           <t>「台帳の資産額が実態より少ないと、有形固定資産減価償却率が実態とずれます。その数字は公共施設等総合管理計画の更新費用試算の前提になっていて、さらに起債や交付金の裏付けにもなります。台帳は公会計だけの話ではなく、施設と財源の話につながっているとお考えいただければと思います。」</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>公会計担当だけの問題にしない。財政課・管財課を巻き込む理由になり、公共施設マネジメントへのクロスセルの入口にもなる。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="92" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="92" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B23" s="93" t="inlineStr">
+      <c r="B29" s="93" t="inlineStr">
         <is>
           <t>4:00–5:00</t>
         </is>
       </c>
-      <c r="C23" s="47" t="inlineStr">
+      <c r="C29" s="47" t="inlineStr">
         <is>
           <t>段階整備を提案して次を決める</t>
         </is>
       </c>
-      <c r="D23" s="63" t="inlineStr">
+      <c r="D29" s="63" t="inlineStr">
         <is>
           <t>「一度に全部やる必要はありません。金額の大きいものと、所管課が特定できるものから、複数年に分けて整理する進め方をご提案しています。まず現状の台帳を拝見して、どこから手を付けるべきかの整理表をお持ちします。」</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>「全部やる＝高い」で止まらせない。整理表の持参が次回訪問の理由になり、複数年契約の入口にもなる。</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="92" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="92" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B24" s="93" t="inlineStr">
+      <c r="B30" s="93" t="inlineStr">
         <is>
           <t>0:00–0:30</t>
         </is>
       </c>
-      <c r="C24" s="47" t="inlineStr">
+      <c r="C30" s="47" t="inlineStr">
         <is>
           <t>改定時期から入る</t>
         </is>
       </c>
-      <c r="D24" s="63" t="inlineStr">
+      <c r="D30" s="63" t="inlineStr">
         <is>
           <t>「公共施設等総合管理計画の件で伺いました。御町の計画はR◯年度までと拝見しましたので、そろそろ改定のご検討時期かと存じます。5分だけお時間をいただけますでしょうか。」</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>計画期間を調べてから行く。「R◯年度まで」と言えるだけで、他社との差がつく。</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="92" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="92" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B25" s="93" t="inlineStr">
+      <c r="B31" s="93" t="inlineStr">
         <is>
           <t>0:30–1:30</t>
         </is>
       </c>
-      <c r="C25" s="47" t="inlineStr">
+      <c r="C31" s="47" t="inlineStr">
         <is>
           <t>充足状況を3問だけ聞く</t>
         </is>
       </c>
-      <c r="D25" s="63" t="inlineStr">
+      <c r="D31" s="63" t="inlineStr">
         <is>
           <t>「①国の見直し要請の内容──個別施設計画の反映、保有量の数値目標、脱炭素化、ユニバーサルデザイン化ですが、現行計画に入っていますでしょうか。」
 「②個別施設計画は、施設類型ごとに一通り揃っていますか。」
 「③更新費用の試算は、いつのデータで作られたものでしょうか。」</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>3問とも「たぶん入っている」「揃っていないかもしれない」で返ってくることが多い。その曖昧さ自体が、点検表を持参する理由になる。</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="92" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="92" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B26" s="93" t="inlineStr">
+      <c r="B32" s="93" t="inlineStr">
         <is>
           <t>1:30–3:00</t>
         </is>
       </c>
-      <c r="C26" s="47" t="inlineStr">
+      <c r="C32" s="47" t="inlineStr">
         <is>
           <t>起債の要件から必要性を語る</t>
         </is>
       </c>
-      <c r="D26" s="63" t="inlineStr">
+      <c r="D32" s="63" t="inlineStr">
         <is>
           <t>「公共施設等適正管理推進事業債は、総合管理計画に基づく事業であることが要件になっています。裏を返しますと、計画に書かれていない事業は起債の対象になりません。これから集約化や長寿命化を進められるのであれば、その事業が計画に位置付けられているかどうかが、そのまま財源を使えるかどうかになります。」</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>計画改定を「作り直し」ではなく「財源を使えるようにする作業」として提示する。充当率・交付税措置率・適用期限は必ず当年度の地方債計画で確認してから話す。</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="92" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="92" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B27" s="93" t="inlineStr">
+      <c r="B33" s="93" t="inlineStr">
         <is>
           <t>3:00–4:00</t>
         </is>
       </c>
-      <c r="C27" s="47" t="inlineStr">
+      <c r="C33" s="47" t="inlineStr">
         <is>
           <t>3点セットで提案する</t>
         </is>
       </c>
-      <c r="D27" s="63" t="inlineStr">
+      <c r="D33" s="63" t="inlineStr">
         <is>
           <t>「総合管理計画だけを改定しても、個別施設計画が古いままですと整合が取れません。また更新費用の試算は、固定資産台帳と連動させると精度が上がります。総合管理計画・個別施設計画・台帳の3つをどう組み合わせるかで、ご提案の形が変わってまいります。」</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>単発の改定業務で終わらせない。台帳を持ち出すことで公会計テーマとのクロスセルになる。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="92" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="92" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B28" s="93" t="inlineStr">
+      <c r="B34" s="93" t="inlineStr">
         <is>
           <t>4:00–5:00</t>
         </is>
       </c>
-      <c r="C28" s="47" t="inlineStr">
+      <c r="C34" s="47" t="inlineStr">
         <is>
           <t>点検表を約束して帰る</t>
         </is>
       </c>
-      <c r="D28" s="63" t="inlineStr">
+      <c r="D34" s="63" t="inlineStr">
         <is>
           <t>「現行計画を拝見して、国の要請事項がどこまで反映されているかの点検表をお持ちします。改定の要否をご判断いただく材料になるかと思います。いつ頃までにあるとよろしいでしょうか。」</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>点検表は公表資料だけで作れて、相手にとって価値がある。最も費用対効果の高い置き土産。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="92" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="92" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B29" s="93" t="inlineStr">
+      <c r="B35" s="93" t="inlineStr">
         <is>
           <t>0:00–0:30</t>
         </is>
       </c>
-      <c r="C29" s="47" t="inlineStr">
+      <c r="C35" s="47" t="inlineStr">
         <is>
           <t>随契を前提に、切り替えを迫らずに入る</t>
         </is>
       </c>
-      <c r="D29" s="63" t="inlineStr">
+      <c r="D35" s="63" t="inlineStr">
         <is>
           <t>「◯◯の件は、現在お願いされている会社さんがいらっしゃると伺っております。切り替えのお願いに参ったわけではございません。ただ、ご契約の範囲に入っていない部分でお役に立てることがあるかと思いまして、5分だけお時間をいただけますでしょうか。」</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>最初に「切り替えの話ではない」と言い切る。ここで警戒を解けるかどうかが、この5分の成否を決める。</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="92" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="92" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B30" s="93" t="inlineStr">
+      <c r="B36" s="93" t="inlineStr">
         <is>
           <t>0:30–1:30</t>
         </is>
       </c>
-      <c r="C30" s="47" t="inlineStr">
+      <c r="C36" s="47" t="inlineStr">
         <is>
           <t>契約範囲を3問で確かめる</t>
         </is>
       </c>
-      <c r="D30" s="63" t="inlineStr">
+      <c r="D36" s="63" t="inlineStr">
         <is>
           <t>「①現在のご契約は、どこまでの範囲でしょうか。」
 「②経営戦略の改定や料金の見直しは、同じところにお願いされていますか。」
 「③次の改定は、R◯年度でよろしかったでしょうか。」</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>①で範囲外が見つかれば今日の商談になり、③で改定年度が分かれば数年後の商談になる。どちらかは必ず取れる質問構成。</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="92" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="92" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B31" s="93" t="inlineStr">
+      <c r="B37" s="93" t="inlineStr">
         <is>
           <t>1:30–3:00</t>
         </is>
       </c>
-      <c r="C31" s="47" t="inlineStr">
+      <c r="C37" s="47" t="inlineStr">
         <is>
           <t>隣の業務を示す</t>
         </is>
       </c>
-      <c r="D31" s="63" t="inlineStr">
+      <c r="D37" s="63" t="inlineStr">
         <is>
           <t>「会計のご支援と経営戦略は、別のご発注になっている団体が多くございます。財務書類の作成と固定資産台帳の精緻化も同じです。総合管理計画と個別施設計画も分かれることが多いです。いまご契約に入っていない部分について、比較のための材料としてご覧いただければと思います。」</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>現受託者の仕事を評価も批判もしない。「範囲」という事実だけを扱う。ここで他社批判に踏み込むと、担当者の判断を否定することになり一度で終わる。</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="92" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="92" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B32" s="93" t="inlineStr">
+      <c r="B38" s="93" t="inlineStr">
         <is>
           <t>3:00–4:00</t>
         </is>
       </c>
-      <c r="C32" s="47" t="inlineStr">
+      <c r="C38" s="47" t="inlineStr">
         <is>
           <t>参考見積を比較材料として置く</t>
         </is>
       </c>
-      <c r="D32" s="63" t="inlineStr">
+      <c r="D38" s="63" t="inlineStr">
         <is>
           <t>「もしよろしければ、その部分の参考のお見積をお持ちします。ご発注いただかなくても、次回のご契約の際に金額の目安としてお使いいただければ結構です。」</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>随契先がある団体で見積を受け取ってもらう唯一の名目が「比較材料」。受け取ってもらえれば、次の契約時に必ず思い出される。</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="92" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="92" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B33" s="93" t="inlineStr">
+      <c r="B39" s="93" t="inlineStr">
         <is>
           <t>4:00–5:00</t>
         </is>
       </c>
-      <c r="C33" s="47" t="inlineStr">
+      <c r="C39" s="47" t="inlineStr">
         <is>
           <t>改定年度の前年度に戻る約束をする</t>
         </is>
       </c>
-      <c r="D33" s="63" t="inlineStr">
+      <c r="D39" s="63" t="inlineStr">
         <is>
           <t>「次の改定がR◯年度でしたら、その前年度にまた伺わせてください。ご担当が代わられるタイミングでも、もう一度ご相談いただけますと幸いです。」</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>随契が切れる唯一の機会は担当者交代と改定年度。訪問記録に「再訪不要」と書いて切ると、その機会を自ら捨てることになる。改定時期が先でも「再アプローチ」とし、備考に再訪する年度を書く。</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="92" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="92" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B34" s="93" t="inlineStr">
+      <c r="B40" s="93" t="inlineStr">
         <is>
           <t>0:00–0:30</t>
         </is>
       </c>
-      <c r="C34" s="47" t="inlineStr">
+      <c r="C40" s="47" t="inlineStr">
         <is>
           <t>受付で3つ確認する</t>
         </is>
       </c>
-      <c r="D34" s="63" t="inlineStr">
+      <c r="D40" s="63" t="inlineStr">
         <is>
           <t>「①◯◯のご担当は△△様でお間違いないでしょうか。」
 「②お戻りのお時間、あるいは在席されやすい曜日・時間帯はございますか。」
 「③改めて伺いたいのですが、◯月頃でご都合のよい時期はございますでしょうか。」</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>この3つを聞くだけで、次回の訪問が当てずっぽうでなくなる。同じ時間帯に何度も行って不在を繰り返すのが、最も無駄な時間の使い方。</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="92" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="92" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B35" s="93" t="inlineStr">
+      <c r="B41" s="93" t="inlineStr">
         <is>
           <t>0:30–1:30</t>
         </is>
       </c>
-      <c r="C35" s="47" t="inlineStr">
+      <c r="C41" s="47" t="inlineStr">
         <is>
           <t>置いていく資料を渡す</t>
         </is>
       </c>
-      <c r="D35" s="63" t="inlineStr">
+      <c r="D41" s="63" t="inlineStr">
         <is>
           <t>「△△様にお渡しいただけますでしょうか。ご覧いただいて、ご関心がありましたらご連絡いただければ幸いです。」</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>置く資料は4つの条件を満たすこと──1枚であること、宛名が入っていること、次にいつ伺うかが書いてあること、連絡先があること。宛名を手書きで入れるだけで、机上で捨てられにくくなる。カタログだけを置かない。</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="92" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="92" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B36" s="93" t="inlineStr">
+      <c r="B42" s="93" t="inlineStr">
         <is>
           <t>1:30–2:30</t>
         </is>
       </c>
-      <c r="C36" s="47" t="inlineStr">
+      <c r="C42" s="47" t="inlineStr">
         <is>
           <t>名刺に一言添える</t>
         </is>
       </c>
-      <c r="D36" s="63" t="inlineStr">
+      <c r="D42" s="63" t="inlineStr">
         <is>
           <t>（名刺の裏に「◯月に改めて伺います」と手書きで添えて、資料に留める）</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>名刺だけでは用件が残らない。一言あるだけで、次に訪ねたときの入口になる。</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="92" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="92" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B37" s="93" t="inlineStr">
+      <c r="B43" s="93" t="inlineStr">
         <is>
           <t>2:30–3:00</t>
         </is>
       </c>
-      <c r="C37" s="47" t="inlineStr">
+      <c r="C43" s="47" t="inlineStr">
         <is>
           <t>その場で記録する</t>
         </is>
       </c>
-      <c r="D37" s="63" t="inlineStr">
+      <c r="D43" s="63" t="inlineStr">
         <is>
           <t>（受付で確認した担当者名・在席しやすい時間帯・次回訪問の目安を、庁舎を出る前にメモする）</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>帰社してからでは細部を忘れる。特に担当者の氏名の漢字は、その場で確認しておく。</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="92" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="92" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B38" s="93" t="inlineStr">
+      <c r="B44" s="93" t="inlineStr">
         <is>
           <t>帰社後・当日中</t>
         </is>
       </c>
-      <c r="C38" s="47" t="inlineStr">
+      <c r="C44" s="47" t="inlineStr">
         <is>
           <t>訪問記録に次が読める形で残す</t>
         </is>
       </c>
-      <c r="D38" s="63" t="inlineStr">
+      <c r="D44" s="63" t="inlineStr">
         <is>
           <t>（結果＝不在／次回アクション＝再アプローチ／備考に「◯月◯日再訪」と日付まで書く）</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>備考が「担当不在」だけで終わっている記録は、書いた本人以外には追えない。訪問記録の中には再訪日を具体的に書けているものがあり、そうした記録はそのまま引き継げる。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A13:E38"/>
+  <autoFilter ref="A14:E44"/>
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20211,7 +20400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -20394,73 +20583,73 @@
     <row r="12">
       <c r="A12" s="56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B12" s="47" t="inlineStr">
         <is>
-          <t>「まだ財務書類の作成で手一杯です」</t>
+          <t>「高齢者を先にやっているので、障がいは後で」</t>
         </is>
       </c>
       <c r="C12" s="63" t="inlineStr">
         <is>
-          <t>「でしたら台帳の整備は来年度以降で結構です。ただ、どこから手を付けるべきかの整理だけ先にしておくと、来年度のご要求を具体的に書けるようになります。」</t>
+          <t>「その順番で差し支えないかと思います。ただ、調査だけは先に走らせておきませんと、年明けに集計が間に合わなくなります。調査部分だけ先にご検討いただけますでしょうか。」</t>
         </is>
       </c>
       <c r="D12" s="79" t="inlineStr">
         <is>
-          <t>着手時期を譲り、整理だけ先行させる。予算要求の材料を提供する立場に回る。</t>
+          <t>順番を否定しない。調査だけ先行させれば、本体の受注につながる。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B13" s="47" t="inlineStr">
         <is>
-          <t>「所有外というのは何を指すのですか」</t>
+          <t>「県からまだ何も来ていません」</t>
         </is>
       </c>
       <c r="C13" s="63" t="inlineStr">
         <is>
-          <t>「団体によって使われ方が違いますので、まず御市で何を指すかをそろえるところからです。所有していないが管理しているもの、所有しているが管理を委ねているもの、その両方を含めて整理するのが一般的です。」</t>
+          <t>「例年ですと◯月頃かと存じます。ご案内が来てから動きますと時間が足りませんので、先に進められる部分だけ整理しておきませんか。」</t>
         </is>
       </c>
       <c r="D13" s="79" t="inlineStr">
         <is>
-          <t>定義が現場で揺れている。用語をそろえる作業そのものが業務になる。</t>
+          <t>県の提出時期は県により違う。断定せず「例年ですと」で止め、必ず県の資料で確認する。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B14" s="47" t="inlineStr">
         <is>
-          <t>「台帳は業者にお願いしています」</t>
+          <t>「3計画とも自前でやります」</t>
         </is>
       </c>
       <c r="C14" s="63" t="inlineStr">
         <is>
-          <t>「ご契約の範囲は、毎年度の更新まででしょうか。更新と精緻化は別の作業ですので、精緻化の部分が残っていることがあります。」</t>
+          <t>「承知しました。でしたら、成果目標の設定だけ、こちらでレビューさせていただく形もございます。国の目標をそのまま置かれている団体が多いのですが、実績と離れていると次の期に評価が難しくなりますので。」</t>
         </is>
       </c>
       <c r="D14" s="79" t="inlineStr">
         <is>
-          <t>更新の委託と精緻化は別業務。範囲を確認せずに引き下がらない。</t>
+          <t>自前を否定しない。成果目標のレビューという小さな入口を残す。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B15" s="47" t="inlineStr">
@@ -20470,350 +20659,390 @@
       </c>
       <c r="C15" s="63" t="inlineStr">
         <is>
-          <t>「単年度で全部という前提ですと、確かに大きくなります。3か年に分けて、初年度は影響の大きいところだけ、という形であれば要求しやすいかと思います。」</t>
+          <t>「高齢者と障がいを分けてお出ししますので、金額の小さい方からご要求いただく形でも結構です。」</t>
         </is>
       </c>
       <c r="D15" s="79" t="inlineStr">
         <is>
-          <t>段階整備は金額を下げる話ではなく、要求を通しやすくする話として伝える。</t>
+          <t>分けて出すこと自体が、予算が取れない団体への回答になる。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B16" s="47" t="inlineStr">
         <is>
-          <t>「改定の予定はありません」</t>
+          <t>「まだ財務書類の作成で手一杯です」</t>
         </is>
       </c>
       <c r="C16" s="63" t="inlineStr">
         <is>
-          <t>「承知しました。それでは点検表だけお持ちします。要請事項が反映されていない項目があれば、そのときにご判断いただければと思います。」</t>
+          <t>「でしたら台帳の整備は来年度以降で結構です。ただ、どこから手を付けるべきかの整理だけ先にしておくと、来年度のご要求を具体的に書けるようになります。」</t>
         </is>
       </c>
       <c r="D16" s="79" t="inlineStr">
         <is>
-          <t>改定予定なしの団体こそ点検表が効く。未反映が見つかれば、それが改定の理由になる。</t>
+          <t>着手時期を譲り、整理だけ先行させる。予算要求の材料を提供する立場に回る。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B17" s="47" t="inlineStr">
         <is>
-          <t>「個別施設計画は他社にお願いしています」</t>
+          <t>「所有外というのは何を指すのですか」</t>
         </is>
       </c>
       <c r="C17" s="63" t="inlineStr">
         <is>
-          <t>「でしたら、総合管理計画と個別施設計画の整合を取る部分でお役に立てるかもしれません。両方が別々に作られていて数字が合っていない団体は少なくありません。」</t>
+          <t>「団体によって使われ方が違いますので、まず御市で何を指すかをそろえるところからです。所有していないが管理しているもの、所有しているが管理を委ねているもの、その両方を含めて整理するのが一般的です。」</t>
         </is>
       </c>
       <c r="D17" s="79" t="inlineStr">
         <is>
-          <t>他社の成果物を批判せず、「整合」という別の業務として立てる。</t>
+          <t>定義が現場で揺れている。用語をそろえる作業そのものが業務になる。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B18" s="47" t="inlineStr">
         <is>
-          <t>「更新費用は総務省のソフトで試算しました」</t>
+          <t>「台帳は業者にお願いしています」</t>
         </is>
       </c>
       <c r="C18" s="63" t="inlineStr">
         <is>
-          <t>「単価法での試算ですと、実際の施設の規模や構造が反映されません。固定資産台帳と連動させると、施設ごとの数字になります。」</t>
+          <t>「ご契約の範囲は、毎年度の更新まででしょうか。更新と精緻化は別の作業ですので、精緻化の部分が残っていることがあります。」</t>
         </is>
       </c>
       <c r="D18" s="79" t="inlineStr">
         <is>
-          <t>台帳連動の再試算は公会計とのクロスセル。ここが最も単価を上げやすい。</t>
+          <t>更新の委託と精緻化は別業務。範囲を確認せずに引き下がらない。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B19" s="47" t="inlineStr">
         <is>
-          <t>「予算が取れません」</t>
+          <t>「予算がありません」</t>
         </is>
       </c>
       <c r="C19" s="63" t="inlineStr">
         <is>
-          <t>「起債の要件にかかわる部分ですので、財政課の方とご一緒にお話しできる機会があれば、そちらでもご説明します。」</t>
+          <t>「単年度で全部という前提ですと、確かに大きくなります。3か年に分けて、初年度は影響の大きいところだけ、という形であれば要求しやすいかと思います。」</t>
         </is>
       </c>
       <c r="D19" s="79" t="inlineStr">
         <is>
-          <t>財政課を巻き込む。施設所管課だけでは予算が動かないことが多い。</t>
+          <t>段階整備は金額を下げる話ではなく、要求を通しやすくする話として伝える。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="56" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B20" s="47" t="inlineStr">
         <is>
-          <t>「今のところで満足しています」</t>
+          <t>「改定の予定はありません」</t>
         </is>
       </c>
       <c r="C20" s="63" t="inlineStr">
         <is>
-          <t>「承知しました。無理にお切り替えいただく話ではございません。範囲に入っていない部分だけ、資料をお渡しして失礼いたします。」</t>
+          <t>「承知しました。それでは点検表だけお持ちします。要請事項が反映されていない項目があれば、そのときにご判断いただければと思います。」</t>
         </is>
       </c>
       <c r="D20" s="79" t="inlineStr">
         <is>
-          <t>満足を否定しない。引き際が良いと、次の改定年度に呼ばれる。</t>
+          <t>改定予定なしの団体こそ点検表が効く。未反映が見つかれば、それが改定の理由になる。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="56" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B21" s="47" t="inlineStr">
         <is>
-          <t>「見積だけもらっても困ります」</t>
+          <t>「個別施設計画は他社にお願いしています」</t>
         </is>
       </c>
       <c r="C21" s="63" t="inlineStr">
         <is>
-          <t>「ご発注のご判断材料としてではなく、庁内で金額の妥当性をご説明される際の材料としてお使いいただければと思います。」</t>
+          <t>「でしたら、総合管理計画と個別施設計画の整合を取る部分でお役に立てるかもしれません。両方が別々に作られていて数字が合っていない団体は少なくありません。」</t>
         </is>
       </c>
       <c r="D21" s="79" t="inlineStr">
         <is>
-          <t>「比較材料」という位置づけなら受け取ってもらえる。押しつけない。</t>
+          <t>他社の成果物を批判せず、「整合」という別の業務として立てる。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="56" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B22" s="47" t="inlineStr">
         <is>
-          <t>「他社の批判はしないでほしい」</t>
+          <t>「更新費用は総務省のソフトで試算しました」</t>
         </is>
       </c>
       <c r="C22" s="63" t="inlineStr">
         <is>
-          <t>「もちろんいたしません。ご契約の範囲のお話だけさせてください。」</t>
+          <t>「単価法での試算ですと、実際の施設の規模や構造が反映されません。固定資産台帳と連動させると、施設ごとの数字になります。」</t>
         </is>
       </c>
       <c r="D22" s="79" t="inlineStr">
         <is>
-          <t>そもそも批判しない。この一言で信頼が生まれる。</t>
+          <t>台帳連動の再試算は公会計とのクロスセル。ここが最も単価を上げやすい。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="56" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B23" s="47" t="inlineStr">
         <is>
-          <t>「担当が代わったら連絡します」</t>
+          <t>「予算が取れません」</t>
         </is>
       </c>
       <c r="C23" s="63" t="inlineStr">
         <is>
-          <t>「ありがとうございます。R◯年度の改定の前年度に、こちらからも一度伺わせてください。」</t>
+          <t>「起債の要件にかかわる部分ですので、財政課の方とご一緒にお話しできる機会があれば、そちらでもご説明します。」</t>
         </is>
       </c>
       <c r="D23" s="79" t="inlineStr">
         <is>
-          <t>相手の言葉を記録に残し、必ずこちらから戻る。待っていても連絡は来ない。</t>
+          <t>財政課を巻き込む。施設所管課だけでは予算が動かないことが多い。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="56" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B24" s="47" t="inlineStr">
         <is>
-          <t>不在が続いて会えない</t>
+          <t>「今のところで満足しています」</t>
         </is>
       </c>
       <c r="C24" s="63" t="inlineStr">
         <is>
-          <t>受付で聞いた在席しやすい曜日・時間帯に合わせる。それでも会えなければ、資料送付とあわせて電話でアポイントを取る形に切り替える。</t>
+          <t>「承知しました。無理にお切り替えいただく話ではございません。範囲に入っていない部分だけ、資料をお渡しして失礼いたします。」</t>
         </is>
       </c>
       <c r="D24" s="79" t="inlineStr">
         <is>
-          <t>訪問の回数ではなく、会えた回数が成果。同じやり方を繰り返さない。</t>
+          <t>満足を否定しない。引き際が良いと、次の改定年度に呼ばれる。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="56" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B25" s="47" t="inlineStr">
         <is>
-          <t>資料を置いてよいか分からない</t>
+          <t>「見積だけもらっても困ります」</t>
         </is>
       </c>
       <c r="C25" s="63" t="inlineStr">
         <is>
-          <t>「△△様にお渡しいただけますでしょうか」と受付に確認する。断られたら持ち帰り、郵送かメールにする。</t>
+          <t>「ご発注のご判断材料としてではなく、庁内で金額の妥当性をご説明される際の材料としてお使いいただければと思います。」</t>
         </is>
       </c>
       <c r="D25" s="79" t="inlineStr">
         <is>
-          <t>無理に置いていかない。受付での印象は担当者に伝わる。</t>
+          <t>「比較材料」という位置づけなら受け取ってもらえる。押しつけない。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="56" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B26" s="47" t="inlineStr">
+        <is>
+          <t>「他社の批判はしないでほしい」</t>
+        </is>
+      </c>
+      <c r="C26" s="63" t="inlineStr">
+        <is>
+          <t>「もちろんいたしません。ご契約の範囲のお話だけさせてください。」</t>
+        </is>
+      </c>
+      <c r="D26" s="79" t="inlineStr">
+        <is>
+          <t>そもそも批判しない。この一言で信頼が生まれる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="56" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B27" s="47" t="inlineStr">
+        <is>
+          <t>「担当が代わったら連絡します」</t>
+        </is>
+      </c>
+      <c r="C27" s="63" t="inlineStr">
+        <is>
+          <t>「ありがとうございます。R◯年度の改定の前年度に、こちらからも一度伺わせてください。」</t>
+        </is>
+      </c>
+      <c r="D27" s="79" t="inlineStr">
+        <is>
+          <t>相手の言葉を記録に残し、必ずこちらから戻る。待っていても連絡は来ない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="56" t="inlineStr">
+        <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B26" s="47" t="inlineStr">
+      <c r="B28" s="47" t="inlineStr">
+        <is>
+          <t>不在が続いて会えない</t>
+        </is>
+      </c>
+      <c r="C28" s="63" t="inlineStr">
+        <is>
+          <t>受付で聞いた在席しやすい曜日・時間帯に合わせる。それでも会えなければ、資料送付とあわせて電話でアポイントを取る形に切り替える。</t>
+        </is>
+      </c>
+      <c r="D28" s="79" t="inlineStr">
+        <is>
+          <t>訪問の回数ではなく、会えた回数が成果。同じやり方を繰り返さない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="56" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B29" s="47" t="inlineStr">
+        <is>
+          <t>資料を置いてよいか分からない</t>
+        </is>
+      </c>
+      <c r="C29" s="63" t="inlineStr">
+        <is>
+          <t>「△△様にお渡しいただけますでしょうか」と受付に確認する。断られたら持ち帰り、郵送かメールにする。</t>
+        </is>
+      </c>
+      <c r="D29" s="79" t="inlineStr">
+        <is>
+          <t>無理に置いていかない。受付での印象は担当者に伝わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="56" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B30" s="47" t="inlineStr">
         <is>
           <t>次回の時期を聞きにくい</t>
         </is>
       </c>
-      <c r="C26" s="63" t="inlineStr">
+      <c r="C30" s="63" t="inlineStr">
         <is>
           <t>「◯月頃にまた伺ってもよろしいでしょうか」と月単位で聞く。日付を詰めない。</t>
         </is>
       </c>
-      <c r="D26" s="79" t="inlineStr">
+      <c r="D30" s="79" t="inlineStr">
         <is>
           <t>受付は日程を決める権限を持たない。月単位なら答えやすい。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="94" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="94" t="inlineStr">
         <is>
           <t>やってはいけないこと ── ここに書いた失敗は取り返すのに年単位かかる</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="95" t="inlineStr"/>
-      <c r="B29" s="95" t="inlineStr">
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="95" t="inlineStr"/>
+      <c r="B33" s="95" t="inlineStr">
         <is>
           <t>ケース</t>
         </is>
       </c>
-      <c r="C29" s="95" t="inlineStr">
+      <c r="C33" s="95" t="inlineStr">
         <is>
           <t>やってはいけないこと</t>
         </is>
       </c>
-      <c r="D29" s="16" t="n"/>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="61" t="inlineStr">
+      <c r="D33" s="16" t="n"/>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="61" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B30" s="96" t="inlineStr">
+      <c r="B34" s="96" t="inlineStr">
         <is>
           <t>自前作成先からの補正予算獲得</t>
         </is>
       </c>
-      <c r="C30" s="64" t="inlineStr">
+      <c r="C34" s="64" t="inlineStr">
         <is>
           <t>「このままでは間に合いませんよ」と脅す ── 担当者の面目を潰した時点で、以後どの案件にも入れなくなる。</t>
         </is>
       </c>
-      <c r="D30" s="64" t="n"/>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="61" t="inlineStr"/>
-      <c r="B31" s="96" t="inlineStr"/>
-      <c r="C31" s="64" t="inlineStr">
+      <c r="D34" s="64" t="n"/>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="61" t="inlineStr"/>
+      <c r="B35" s="96" t="inlineStr"/>
+      <c r="C35" s="64" t="inlineStr">
         <is>
           <t>保険料の上昇率を推測で口に出す ── 推計前の数字は、外れたときに議会・住民への説明を壊す。</t>
-        </is>
-      </c>
-      <c r="D31" s="64" t="n"/>
-    </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="61" t="inlineStr"/>
-      <c r="B32" s="96" t="inlineStr"/>
-      <c r="C32" s="64" t="inlineStr">
-        <is>
-          <t>「補正で必ず取れます」と断定する ── 予算の可否は財政課と議会が決める。こちらは資料を用意する側。</t>
-        </is>
-      </c>
-      <c r="D32" s="64" t="n"/>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="61" t="inlineStr"/>
-      <c r="B33" s="96" t="inlineStr"/>
-      <c r="C33" s="64" t="inlineStr">
-        <is>
-          <t>5分と言って10分話す ── 次のアポが取れなくなる。話し切れなければ「続きは資料でお持ちします」で切る。</t>
-        </is>
-      </c>
-      <c r="D33" s="64" t="n"/>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="61" t="inlineStr"/>
-      <c r="B34" s="96" t="inlineStr"/>
-      <c r="C34" s="64" t="inlineStr">
-        <is>
-          <t>他団体の進捗を引き合いに出す ── 「△△町さんはもう委託されています」は未公表情報の持ち込みになる。</t>
-        </is>
-      </c>
-      <c r="D34" s="64" t="n"/>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="61" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B35" s="96" t="inlineStr">
-        <is>
-          <t>所有外管理資産（セミナー案内後のフォロー）</t>
-        </is>
-      </c>
-      <c r="C35" s="64" t="inlineStr">
-        <is>
-          <t>「台帳が間違っています」と言う ── 精緻化されていないことと誤りは違う。担当者の否定になる。</t>
         </is>
       </c>
       <c r="D35" s="64" t="n"/>
@@ -20823,7 +21052,7 @@
       <c r="B36" s="96" t="inlineStr"/>
       <c r="C36" s="64" t="inlineStr">
         <is>
-          <t>精緻化の効果を金額で断定する ── 資産額がいくら増えるかは調べてみないと分からない。</t>
+          <t>「補正で必ず取れます」と断定する ── 予算の可否は財政課と議会が決める。こちらは資料を用意する側。</t>
         </is>
       </c>
       <c r="D36" s="64" t="n"/>
@@ -20833,7 +21062,7 @@
       <c r="B37" s="96" t="inlineStr"/>
       <c r="C37" s="64" t="inlineStr">
         <is>
-          <t>セミナーに来なかったことを責める・確認する ── 案内が担当者まで届いていないことも多い。</t>
+          <t>5分と言って10分話す ── 次のアポが取れなくなる。話し切れなければ「続きは資料でお持ちします」で切る。</t>
         </is>
       </c>
       <c r="D37" s="64" t="n"/>
@@ -20843,7 +21072,7 @@
       <c r="B38" s="96" t="inlineStr"/>
       <c r="C38" s="64" t="inlineStr">
         <is>
-          <t>公会計の話だけで終える ── 財政課・管財課につながる話に広げないと、単発の小さな受注で終わる。</t>
+          <t>他団体の進捗を引き合いに出す ── 「△△町さんはもう委託されています」は未公表情報の持ち込みになる。</t>
         </is>
       </c>
       <c r="D38" s="64" t="n"/>
@@ -20851,17 +21080,17 @@
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B39" s="96" t="inlineStr">
         <is>
-          <t>総合管理計画の改定（起債要件から入る）</t>
+          <t>障がい3計画の補正（高齢者と重なる年）</t>
         </is>
       </c>
       <c r="C39" s="64" t="inlineStr">
         <is>
-          <t>起債の充当率・措置率・適用期限を、当年度資料で確認せずに口に出す ── 数値の誤りはそのまま事故になる。</t>
+          <t>高齢者と障がいをまとめて1本の見積にする ── 金額が膨らみ、査定で両方とも落ちる。</t>
         </is>
       </c>
       <c r="D39" s="64" t="n"/>
@@ -20871,7 +21100,7 @@
       <c r="B40" s="96" t="inlineStr"/>
       <c r="C40" s="64" t="inlineStr">
         <is>
-          <t>「この計画は要件を満たしていません」と断定する ── 判断するのは総務省と県であって、当社ではない。</t>
+          <t>「障がいは後回しにされていますね」と言う ── 事実でも、担当者への批判に聞こえる。</t>
         </is>
       </c>
       <c r="D40" s="64" t="n"/>
@@ -20881,7 +21110,7 @@
       <c r="B41" s="96" t="inlineStr"/>
       <c r="C41" s="64" t="inlineStr">
         <is>
-          <t>他社が作った計画を批判する ── その計画を選んだのは目の前の担当者。</t>
+          <t>県への提出期限を推測で断定する ── 県により違う。必ず県の資料か担当者への確認で押さえる。</t>
         </is>
       </c>
       <c r="D41" s="64" t="n"/>
@@ -20891,7 +21120,7 @@
       <c r="B42" s="96" t="inlineStr"/>
       <c r="C42" s="64" t="inlineStr">
         <is>
-          <t>「起債が使えなくなります」と脅す ── 事実に基づかない不安の煽りは、後で必ず信用を失う。</t>
+          <t>成果目標を国の数値のまま提案する ── 実績と離れた目標は、次の期の評価で必ず問題になる。</t>
         </is>
       </c>
       <c r="D42" s="64" t="n"/>
@@ -20899,17 +21128,17 @@
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="61" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B43" s="96" t="inlineStr">
         <is>
-          <t>他社随契先への切り込み</t>
+          <t>所有外管理資産（セミナー案内後のフォロー）</t>
         </is>
       </c>
       <c r="C43" s="64" t="inlineStr">
         <is>
-          <t>現受託者の成果物を批判する ── その会社を選んだのは目の前の担当者。否定は担当者への否定になる。</t>
+          <t>「台帳が間違っています」と言う ── 精緻化されていないことと誤りは違う。担当者の否定になる。</t>
         </is>
       </c>
       <c r="D43" s="64" t="n"/>
@@ -20919,7 +21148,7 @@
       <c r="B44" s="96" t="inlineStr"/>
       <c r="C44" s="64" t="inlineStr">
         <is>
-          <t>「随意契約は競争性がない」と制度論を持ち出す ── 契約方式は自治体が決めること。</t>
+          <t>精緻化の効果を金額で断定する ── 資産額がいくら増えるかは調べてみないと分からない。</t>
         </is>
       </c>
       <c r="D44" s="64" t="n"/>
@@ -20929,7 +21158,7 @@
       <c r="B45" s="96" t="inlineStr"/>
       <c r="C45" s="64" t="inlineStr">
         <is>
-          <t>訪問記録に「再訪不要」と書いて切る ── 改定時期が先なら「再アプローチ」とし、備考に再訪年度を書く。</t>
+          <t>セミナーに来なかったことを責める・確認する ── 案内が担当者まで届いていないことも多い。</t>
         </is>
       </c>
       <c r="D45" s="64" t="n"/>
@@ -20939,7 +21168,7 @@
       <c r="B46" s="96" t="inlineStr"/>
       <c r="C46" s="64" t="inlineStr">
         <is>
-          <t>現受託者の契約金額を聞き出そうとする ── 聞き方によっては相手を困らせる。公表資料で調べる。</t>
+          <t>公会計の話だけで終える ── 財政課・管財課につながる話に広げないと、単発の小さな受注で終わる。</t>
         </is>
       </c>
       <c r="D46" s="64" t="n"/>
@@ -20947,17 +21176,17 @@
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="61" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B47" s="96" t="inlineStr">
         <is>
-          <t>担当者が不在だったときの3分</t>
+          <t>総合管理計画の改定（起債要件から入る）</t>
         </is>
       </c>
       <c r="C47" s="64" t="inlineStr">
         <is>
-          <t>何も置かずに帰る ── 訪問した事実が相手側に何も残らず、その日の移動時間がすべて無駄になる。</t>
+          <t>起債の充当率・措置率・適用期限を、当年度資料で確認せずに口に出す ── 数値の誤りはそのまま事故になる。</t>
         </is>
       </c>
       <c r="D47" s="64" t="n"/>
@@ -20967,7 +21196,7 @@
       <c r="B48" s="96" t="inlineStr"/>
       <c r="C48" s="64" t="inlineStr">
         <is>
-          <t>備考に「担当不在」とだけ書く ── 次に何をするかが読めない記録は、記録として成立していない。</t>
+          <t>「この計画は要件を満たしていません」と断定する ── 判断するのは総務省と県であって、当社ではない。</t>
         </is>
       </c>
       <c r="D48" s="64" t="n"/>
@@ -20977,7 +21206,7 @@
       <c r="B49" s="96" t="inlineStr"/>
       <c r="C49" s="64" t="inlineStr">
         <is>
-          <t>次回アクションを空欄にする ── 空欄は「決めていない」と同義で、そのままフォローが漏れる。</t>
+          <t>他社が作った計画を批判する ── その計画を選んだのは目の前の担当者。</t>
         </is>
       </c>
       <c r="D49" s="64" t="n"/>
@@ -20987,50 +21216,150 @@
       <c r="B50" s="96" t="inlineStr"/>
       <c r="C50" s="64" t="inlineStr">
         <is>
+          <t>「起債が使えなくなります」と脅す ── 事実に基づかない不安の煽りは、後で必ず信用を失う。</t>
+        </is>
+      </c>
+      <c r="D50" s="64" t="n"/>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="61" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B51" s="96" t="inlineStr">
+        <is>
+          <t>他社随契先への切り込み</t>
+        </is>
+      </c>
+      <c r="C51" s="64" t="inlineStr">
+        <is>
+          <t>現受託者の成果物を批判する ── その会社を選んだのは目の前の担当者。否定は担当者への否定になる。</t>
+        </is>
+      </c>
+      <c r="D51" s="64" t="n"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="61" t="inlineStr"/>
+      <c r="B52" s="96" t="inlineStr"/>
+      <c r="C52" s="64" t="inlineStr">
+        <is>
+          <t>「随意契約は競争性がない」と制度論を持ち出す ── 契約方式は自治体が決めること。</t>
+        </is>
+      </c>
+      <c r="D52" s="64" t="n"/>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="61" t="inlineStr"/>
+      <c r="B53" s="96" t="inlineStr"/>
+      <c r="C53" s="64" t="inlineStr">
+        <is>
+          <t>訪問記録に「再訪不要」と書いて切る ── 改定時期が先なら「再アプローチ」とし、備考に再訪年度を書く。</t>
+        </is>
+      </c>
+      <c r="D53" s="64" t="n"/>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="61" t="inlineStr"/>
+      <c r="B54" s="96" t="inlineStr"/>
+      <c r="C54" s="64" t="inlineStr">
+        <is>
+          <t>現受託者の契約金額を聞き出そうとする ── 聞き方によっては相手を困らせる。公表資料で調べる。</t>
+        </is>
+      </c>
+      <c r="D54" s="64" t="n"/>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="61" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B55" s="96" t="inlineStr">
+        <is>
+          <t>担当者が不在だったときの3分</t>
+        </is>
+      </c>
+      <c r="C55" s="64" t="inlineStr">
+        <is>
+          <t>何も置かずに帰る ── 訪問した事実が相手側に何も残らず、その日の移動時間がすべて無駄になる。</t>
+        </is>
+      </c>
+      <c r="D55" s="64" t="n"/>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="61" t="inlineStr"/>
+      <c r="B56" s="96" t="inlineStr"/>
+      <c r="C56" s="64" t="inlineStr">
+        <is>
+          <t>備考に「担当不在」とだけ書く ── 次に何をするかが読めない記録は、記録として成立していない。</t>
+        </is>
+      </c>
+      <c r="D56" s="64" t="n"/>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="61" t="inlineStr"/>
+      <c r="B57" s="96" t="inlineStr"/>
+      <c r="C57" s="64" t="inlineStr">
+        <is>
+          <t>次回アクションを空欄にする ── 空欄は「決めていない」と同義で、そのままフォローが漏れる。</t>
+        </is>
+      </c>
+      <c r="D57" s="64" t="n"/>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="61" t="inlineStr"/>
+      <c r="B58" s="96" t="inlineStr"/>
+      <c r="C58" s="64" t="inlineStr">
+        <is>
           <t>在席時間を確認せず、同じ曜日・時間帯に繰り返し訪問する ── 不在が続く原因はたいていこれ。</t>
         </is>
       </c>
-      <c r="D50" s="64" t="n"/>
-    </row>
-    <row r="51" ht="26" customHeight="1">
-      <c r="A51" s="61" t="inlineStr"/>
-      <c r="B51" s="96" t="inlineStr"/>
-      <c r="C51" s="64" t="inlineStr">
+      <c r="D58" s="64" t="n"/>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="61" t="inlineStr"/>
+      <c r="B59" s="96" t="inlineStr"/>
+      <c r="C59" s="64" t="inlineStr">
         <is>
           <t>受付で担当者の携帯番号や不在の理由を聞き出そうとする ── 相手を困らせる。</t>
         </is>
       </c>
-      <c r="D51" s="64" t="n"/>
+      <c r="D59" s="64" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:D26"/>
-  <mergeCells count="27">
+  <autoFilter ref="A5:D30"/>
+  <mergeCells count="31">
     <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C58:D58"/>
     <mergeCell ref="C45:D45"/>
-    <mergeCell ref="A28:D28"/>
     <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C29:D29"/>
     <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C54:D54"/>
     <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C55:D55"/>
     <mergeCell ref="C50:D50"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C59:D59"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C46:D46"/>
     <mergeCell ref="C51:D51"/>
     <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C52:D52"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C32:D32"/>
     <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C57:D57"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="A32:D32"/>
     <mergeCell ref="C49:D49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22759,360 +23088,1552 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="108" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="104" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>来期（R9年度）営業方針｜こども計画／地域福祉計画</t>
+          <t>営業方針｜A 今期の補正に向けた提案営業／B 来期案件獲得のための営業</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>どちらも努力義務の計画で、待っていても発注は生まれない。こどもは「制度が変わったので直さざるを得ない」、地域福祉は「束ねれば手間が減る」が崩し方。</t>
+          <t>Aは高齢者介護と障がい計画。どちらもR8年度が策定年度で、狙う枠は12月補正（要求は11月上旬）。Bは地域福祉計画とこども計画。R9年度当初での発注を狙うなら動くのは8〜10月。</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="97" t="inlineStr">
-        <is>
-          <t>こども計画・子ども子育て支援事業計画</t>
+      <c r="A4" s="90" t="inlineStr">
+        <is>
+          <t>A　今期の補正に向けた提案営業　── 高齢者介護（第10期）／障がい3計画（第8期・第4期）</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>見出し</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="52" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B6" s="52" t="inlineStr">
         <is>
           <t>現状認識</t>
         </is>
       </c>
-      <c r="B6" s="47" t="inlineStr">
-        <is>
-          <t>「国や道の強制力しだい」で様子見が多数派</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>訪問記録を見ると、こども計画について「子ども・子育て支援事業計画の改定タイミングで、国や県の温度感を見ながら判断する」「中間見直しは自前」という回答が複数の団体で並んでいる。努力義務であるため、待っていても発注は生まれない。待ちの姿勢を崩す材料を持ち込むのが来期の仕事。</t>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>R8年度は高齢者と障がいの策定年度が重なっている</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>高齢者は第10期（R9〜11年度）、障がいは第8期障害福祉計画・第4期障害児福祉計画（同R9〜11年度）。どちらもR8年度が策定年度で、小規模団体では同じ課・同じ担当者が両方を持っている。自前で始めたものの、秋口で手が止まる団体が出るのがこの時期。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="53" t="inlineStr">
-        <is>
-          <t>狙い目①</t>
-        </is>
-      </c>
-      <c r="B7" s="49" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B7" s="97" t="inlineStr">
+        <is>
+          <t>枠</t>
+        </is>
+      </c>
+      <c r="C7" s="49" t="inlineStr">
+        <is>
+          <t>狙うのは12月補正。9月補正はすでに間に合わない</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>9月議会に上程する議案は8月中に固まっている。今から狙えるのは12月補正で、財政課への要求はおおむね11月上旬。逆算すると10月中に見積を出しておく必要がある。ここを外すと、残るのは次年度当初だけになる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B8" s="56" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>全部委託ではなく部分委託で出す</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>補正は金額が大きいと査定に耐えない。時間がかかる工程だけを切り出して出す。金額を下げることが目的ではなく、庁内で説明しやすくすることが目的だと伝える。切り出しの例：推計・算定だけ／調査集計だけ／計画書の編集・印刷だけ／パブコメ実務だけ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="49" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B9" s="56" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C9" s="49" t="inlineStr">
+        <is>
+          <t>高齢者と障がいは必ず分けて見積を出す</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>同じ課が両方を持っていても、1本にまとめると金額が膨らみ、査定で両方とも落ちる。分けて出し、通しやすい方から通す。片方が通れば、翌年度にもう片方が通りやすくなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="47" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>R9年3月議会での保険料条例改正が動かせない期限</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>R9年4月から保険料を賦課するにはR9年3月議会での条例改正が必要。2月下旬の議案上程 ← 1〜2月のパブリックコメント（30日程度）← 12〜1月の保険料確定と素案 ←11月の給付費推計とサービス見込量 ← 10月末までの現状分析。つまり10月末までに分析が終わっていないと、パブコメの期間が取れない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>見極め</t>
+        </is>
+      </c>
+      <c r="C11" s="49" t="inlineStr">
+        <is>
+          <t>残っているものを3問で判定する</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>①ニーズ調査・在宅介護実態調査の集計は済んだか ②保険料の算定は誰が担当する予定か ③パブリックコメントはいつ頃を想定しているか。①が未了、②が未定、③が「これから」なら、自前完遂は高い確率で間に合わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="47" t="inlineStr">
+        <is>
+          <t>高齢者・介護保険</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>切り出し</t>
+        </is>
+      </c>
+      <c r="C12" s="47" t="inlineStr">
+        <is>
+          <t>保険料算定と給付費推計だけを預かる</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>見える化システムと厚労省ワークシートを使う工程で、最も時間がかかり、かつ3年間の保険料に直結するため誤りが許されない。計画本文は庁内で書いてもらう前提にすると、金額も説明もまとまる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+      <c r="C13" s="49" t="inlineStr">
+        <is>
+          <t>議決の期限がない分、県への提出時期が実質の期限</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>障害福祉計画には保険料のような議決期限がないため、高齢者が優先されて後回しになりやすい。ただし県の障害福祉計画が市町村の見込量を集約するため、県への提出時期が実質の期限になる。そこから逆算すると、年内に成果目標と見込量が固まっている必要がある。提出時期は県により異なるため、断定せず「ご案内が来ていますか」と確認する形で扱う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="47" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>見極め</t>
+        </is>
+      </c>
+      <c r="C14" s="47" t="inlineStr">
+        <is>
+          <t>残っているものを3問で判定する</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>①手帳所持者アンケートは実施済みか ②前期の成果目標の達成状況の評価は済んでいるか ③県への見込量の提出はいつまでと案内が来ているか。③を押さえている担当者は多くなく、答えられなければ、それ自体が持ち込む課題になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="49" t="inlineStr">
+        <is>
+          <t>障害者・障害児</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>切り出し</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>成果目標の設定と見込量の推計だけを預かる</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>前期の実績と国保連データを使う工程で、3計画一体だと分量が大きい。障害者計画（理念計画）の部分は庁内で書いてもらう。「高齢者と重なる年だから、負担の大きいところだけ外に出す」は庁内で説明しやすい理由になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="47" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B16" s="59" t="inlineStr">
+        <is>
+          <t>逃げ道</t>
+        </is>
+      </c>
+      <c r="C16" s="47" t="inlineStr">
+        <is>
+          <t>補正が通らなかった場合の二段構え</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>既定予算の範囲（少額随意契約の限度額は自治体の契約規則による）で調査・集計だけ先行させ、本体は次年度当初に回す。分析が先に終わっていれば、年度をまたいでも間に合う。金額の線引きは必ず当該自治体の契約規則で確認してから話す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="98" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B17" s="99" t="inlineStr">
+        <is>
+          <t>やらないこと</t>
+        </is>
+      </c>
+      <c r="C17" s="98" t="inlineStr">
+        <is>
+          <t>脅さない・断定しない・まとめない</t>
+        </is>
+      </c>
+      <c r="D17" s="79" t="inlineStr">
+        <is>
+          <t>「このままでは間に合いません」と脅すと担当者の面目を潰す。保険料の上昇率や補正の可否を断定しない。高齢者と障がいをまとめて1本の見積にしない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="100" t="inlineStr">
+        <is>
+          <t>B　来期案件獲得のための営業　── 地域福祉計画／こども計画（R9年度当初予算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>見出し</t>
+        </is>
+      </c>
+      <c r="D21" s="40" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="47" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B22" s="97" t="inlineStr">
+        <is>
+          <t>時期</t>
+        </is>
+      </c>
+      <c r="C22" s="47" t="inlineStr">
+        <is>
+          <t>R8年8〜10月が勝負。ここを外すと1年待つ</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>R9年度当初予算での発注を狙うなら、8〜10月に情報提供と参考見積、11〜12月に査定対応、1〜3月に公告という流れになる。予算要求書が固まってから訪問しても、その年度には載らない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B23" s="56" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="inlineStr">
+        <is>
+          <t>参考見積は「要求のための資料」として渡す</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>受注の判断材料としてではなく、担当者が庁内で要求を起こすための資料として位置づける。この言い方であれば、発注を約束できない段階でも受け取ってもらえる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="47" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B24" s="52" t="inlineStr">
+        <is>
+          <t>現状認識</t>
+        </is>
+      </c>
+      <c r="C24" s="47" t="inlineStr">
+        <is>
+          <t>単発では小さい。束ねて初めて中規模案件になる</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>地域福祉計画そのものは金額が大きくない。併載できる計画と社協の地域福祉活動計画を合わせて初めて採算に乗る。訪問記録にも「複数計画を地域福祉計画で一本化したい」という団体が実在しており、需要側の要望とも一致する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B25" s="53" t="inlineStr">
+        <is>
+          <t>狙い目</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="inlineStr">
+        <is>
+          <t>成年後見制度利用促進基本計画の改定期</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>国の第二期基本計画が令和8年度で終期を迎え、第三期に移る。これに合わせて市町村計画を改定する団体が出るため、来期の有力な入口になる。中核機関が未設置の団体では、計画策定と体制整備をあわせて提案できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="47" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B26" s="53" t="inlineStr">
+        <is>
+          <t>狙い目</t>
+        </is>
+      </c>
+      <c r="C26" s="47" t="inlineStr">
+        <is>
+          <t>重層的支援体制整備事業</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>未実施の団体には移行準備事業、実施済みの団体には実施計画の策定と体制強化。移行すると介護・障害・こども・困窮の相談支援等の補助が一体的に交付される点が説得材料になる。最大の壁は庁内合意なので、計画の前段として庁内勉強会・業務フロー整理の伴走を提案する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="49" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B27" s="53" t="inlineStr">
+        <is>
+          <t>狙い目</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="inlineStr">
+        <is>
+          <t>自殺対策計画（地域自殺対策強化交付金）</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>策定が義務であり、交付金を計画の策定・改定に充当できる。地域福祉計画に併載すれば、財源のある計画が本体を引っ張る構図が作れる。JSCPの地域自殺実態プロファイルを使えば、重点施策を客観データで組める。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="47" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B28" s="56" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C28" s="47" t="inlineStr">
+        <is>
+          <t>自治体と社会福祉協議会の両方に当たる</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>一体で策定すると発注元が2つになり予算を合算できる。社協は自治体より意思決定が早いことが多く、社協側から自治体を動かせる場合もある。どちらか一方だけを訪問している状態は、機会を半分捨てている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="49" t="inlineStr">
+        <is>
+          <t>地域福祉</t>
+        </is>
+      </c>
+      <c r="B29" s="59" t="inlineStr">
+        <is>
+          <t>持参物</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="inlineStr">
+        <is>
+          <t>併載計画がいつ切れるかの一覧</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>成年後見・再犯防止・自殺対策・孤独孤立・生活困窮・避難行動要支援者・居住支援。担当自治体ごとに一覧を作って見せる。「バラバラに作ると毎年どれかの改定が来るが、束ねれば数年に一度で済む」が最も効く言い方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="47" t="inlineStr">
+        <is>
+          <t>こども</t>
+        </is>
+      </c>
+      <c r="B30" s="52" t="inlineStr">
+        <is>
+          <t>現状認識</t>
+        </is>
+      </c>
+      <c r="C30" s="47" t="inlineStr">
+        <is>
+          <t>「国や県の強制力しだい」で様子見が多数派</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>訪問記録では「子ども・子育て支援事業計画の改定タイミングで、国や県の温度感を見ながら判断する」「中間見直しは自前」という回答が複数の団体で並んでいる。努力義務であるため、待っていても発注は生まれない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="49" t="inlineStr">
+        <is>
+          <t>こども</t>
+        </is>
+      </c>
+      <c r="B31" s="53" t="inlineStr">
+        <is>
+          <t>狙い目</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="inlineStr">
+        <is>
+          <t>こども誰でも通園制度の量の見込みへの反映</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>地域子ども・子育て支援事業に新たに位置付けられたため、量の見込みへの反映が必要になる。「制度が変わったので計画を直さなければならない」は、担当者が庁内を説得しやすい理由になる。中間見直しを提案する最も明確な入口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="47" t="inlineStr">
+        <is>
+          <t>こども</t>
+        </is>
+      </c>
+      <c r="B32" s="53" t="inlineStr">
+        <is>
+          <t>狙い目</t>
+        </is>
+      </c>
+      <c r="C32" s="47" t="inlineStr">
         <is>
           <t>第3期事業計画（R7〜11年度）の中間年の見直し</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>5年計画の中間年に、量の見込みと実績の乖離を踏まえて見直す。少子化の加速と利用率の変化で、第3期策定時の見込みから外れている団体が多い。区域別・年齢別の乖離率を一覧にして持参すると、見直しの必要性が数字で伝わる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="53" t="inlineStr">
-        <is>
-          <t>狙い目②</t>
-        </is>
-      </c>
-      <c r="B8" s="47" t="inlineStr">
-        <is>
-          <t>こども誰でも通園制度（乳児等通園支援事業）の反映</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>地域子ども・子育て支援事業に新たに位置付けられたため、量の見込みへの反映が必要になる。「制度が変わったので計画を直さなければならない」は、担当者が庁内を説得しやすい理由になる。中間見直しを提案する最も明確な入口。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="53" t="inlineStr">
-        <is>
-          <t>狙い目③</t>
-        </is>
-      </c>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>少子化の加速と利用率の変化で、第3期策定時の見込みから外れている団体が多い。区域別・年齢別の乖離率を一覧にして持参すると、見直しの必要性が数字で伝わる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="49" t="inlineStr">
+        <is>
+          <t>こども</t>
+        </is>
+      </c>
+      <c r="B33" s="53" t="inlineStr">
+        <is>
+          <t>狙い目</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="inlineStr">
         <is>
           <t>こども計画の新規策定（未策定団体）</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>こども基本法に基づく努力義務。子ども・若者計画、こどもの貧困対策計画、母子保健計画を統合できる。「別々に作っている計画を1本にまとめれば、次からの改定の手間が減る」という、事務負担の軽減を軸に話す。安くなるからではない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="98" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>子ども・若者計画、こどもの貧困対策計画、母子保健計画を統合できる。「別々に作っている計画を1本にまとめれば、次からの改定の手間が減る」という事務負担の軽減を軸に話す。安くなるからではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="47" t="inlineStr">
+        <is>
+          <t>こども</t>
+        </is>
+      </c>
+      <c r="B34" s="34" t="inlineStr">
+        <is>
+          <t>接触先</t>
+        </is>
+      </c>
+      <c r="C34" s="47" t="inlineStr">
+        <is>
+          <t>こども未来課だけでは足りない</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>保育、母子保健（健康推進課）、教育委員会（放課後児童クラブ）に所管が分かれている。庁内横断の調整そのものが担当者の最大の負担なので、「関係課をまとめた進め方の案」を持っていくと提案価値になる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="49" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B35" s="97" t="inlineStr">
         <is>
           <t>財源</t>
         </is>
       </c>
-      <c r="B10" s="47" t="inlineStr">
-        <is>
-          <t>地域子供の未来応援交付金／ヤングケアラー支援体制強化事業</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>こどもの貧困の実態調査・計画策定・支援体制整備に充当できる。調査業務の予算化に直結する。要綱と要望時期は毎年度変わるため、当年度資料で確認してから提示すること。「対象になり得るので要綱で確認を」で止め、断定しない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="56" t="inlineStr">
-        <is>
-          <t>提案の型</t>
-        </is>
-      </c>
-      <c r="B11" s="49" t="inlineStr">
-        <is>
-          <t>調査と計画を分けて、二段で取る</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>実態調査（貧困・ヤングケアラー・こどもの意見聴取）を単独業務として先に受け、その結果を持って計画本体につなげる。調査は交付金が使え、金額も抑えられるため通りやすい。こども会議の設計・運営は策定年度以外でも受注できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="34" t="inlineStr">
-        <is>
-          <t>接触先</t>
-        </is>
-      </c>
-      <c r="B12" s="47" t="inlineStr">
-        <is>
-          <t>こども未来課・子育て支援課だけでは足りない</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>保育、母子保健（健康推進課）、教育委員会（放課後児童クラブ）に所管が分かれている。庁内横断の調整そのものが担当者の最大の負担なので、「関係課をまとめた進め方の案」を持っていくと提案価値になる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="59" t="inlineStr">
-        <is>
-          <t>タイムライン</t>
-        </is>
-      </c>
-      <c r="B13" s="49" t="inlineStr">
-        <is>
-          <t>R8年度中に予算化まで持ち込む</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R9年度当初予算での発注を狙うなら、R8年8〜10月に情報提供と参考見積、11〜12月に査定対応、1〜3月に公告。中間見直しを補正で狙う場合は、9月補正はすでに間に合わないため12月補正（要求は11月上旬）を目標にする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="99" t="inlineStr">
-        <is>
-          <t>地域福祉計画</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="39" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>見出し</t>
-        </is>
-      </c>
-      <c r="C17" s="39" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="52" t="inlineStr">
-        <is>
-          <t>現状認識</t>
-        </is>
-      </c>
-      <c r="B18" s="47" t="inlineStr">
-        <is>
-          <t>単発で取ると小さい。束ねて初めて中規模案件になる</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>地域福祉計画そのものは金額が大きくない。併載できる計画と、社協の地域福祉活動計画を合わせて初めて採算に乗る。訪問記録にも「複数計画を地域福祉計画で一本化したい」という団体が実在しており、需要側の要望とも一致する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="53" t="inlineStr">
-        <is>
-          <t>狙い目①</t>
-        </is>
-      </c>
-      <c r="B19" s="49" t="inlineStr">
-        <is>
-          <t>成年後見制度利用促進基本計画の改定期</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>国の第二期基本計画が令和8年度で終期を迎え、第三期に移る。これに合わせて市町村計画を改定する団体が出るため、来期の有力な入口になる。中核機関が未設置の団体では、計画策定と体制整備をあわせて提案できる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="53" t="inlineStr">
-        <is>
-          <t>狙い目②</t>
-        </is>
-      </c>
-      <c r="B20" s="47" t="inlineStr">
-        <is>
-          <t>重層的支援体制整備事業</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>未実施の団体には移行準備事業、実施済みの団体には実施計画の策定と体制強化。移行すると介護・障害・こども・困窮の相談支援等の補助が一体的に交付される点が説得材料になる。ただし最大の壁は庁内合意なので、計画の前段として庁内勉強会・業務フロー整理の伴走を提案する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="53" t="inlineStr">
-        <is>
-          <t>狙い目③</t>
-        </is>
-      </c>
-      <c r="B21" s="49" t="inlineStr">
-        <is>
-          <t>自殺対策計画（地域自殺対策強化交付金）</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>策定が義務であり、交付金を計画の策定・改定に充当できる。地域福祉計画に併載する形にすれば、財源のある計画が本体を引っ張る構図が作れる。JSCPの地域自殺実態プロファイルを使えば、重点施策を客観データで組める。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="56" t="inlineStr">
-        <is>
-          <t>提案の型</t>
-        </is>
-      </c>
-      <c r="B22" s="47" t="inlineStr">
-        <is>
-          <t>自治体と社会福祉協議会の両方に当たる</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>地域福祉計画（自治体）と地域福祉活動計画（社協）を一体で策定すると、発注元が2つになり予算を合算できる。社協は自治体より意思決定が早いことが多く、社協側から自治体を動かせる場合もある。どちらか一方だけを訪問している状態は、機会を半分捨てている。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="56" t="inlineStr">
-        <is>
-          <t>提案の型</t>
-        </is>
-      </c>
-      <c r="B23" s="49" t="inlineStr">
-        <is>
-          <t>併載計画の一覧を作って持参する</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>成年後見・再犯防止・自殺対策・孤独孤立・生活困窮・避難行動要支援者・居住支援。担当自治体それぞれについて、どの計画がいつ切れるかを一覧にして見せる。「バラバラに作ると毎年どれかの改定が来るが、束ねれば数年に一度で済む」が最も効く言い方。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="100" t="inlineStr">
-        <is>
-          <t>注意</t>
-        </is>
-      </c>
-      <c r="B24" s="47" t="inlineStr">
-        <is>
-          <t>圏域と進捗評価が実務の争点になる</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>圏域が計画ごとにバラバラ（日常生活圏域／小学校区／地区社協）な団体が多く、整理そのものを業務に含められる。また前計画の進捗評価の仕組みが無い団体が大半なので、指標設計と年次評価の仕組みづくりを提案に入れると、他社の標準的な策定業務と差がつく。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="59" t="inlineStr">
-        <is>
-          <t>タイムライン</t>
-        </is>
-      </c>
-      <c r="B25" s="49" t="inlineStr">
-        <is>
-          <t>R8年8〜10月が勝負</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>地域福祉計画は複数課・社協との調整が要るため、予算要求の準備に時間がかかる。R8年8〜10月に併載計画の一覧と一体策定案を提示し、11〜12月の査定を越える。社協への接触は自治体と同時期に始める。</t>
+      <c r="C35" s="49" t="inlineStr">
+        <is>
+          <t>調査を先に、交付金とセットで取る</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>こども＝地域子供の未来応援交付金（こどもの貧困の実態調査）、ヤングケアラー支援体制強化事業。地域福祉＝重層事業交付金・移行準備事業、地域自殺対策強化交付金。調査は交付金が使え金額も抑えられるため、計画本体より先に通りやすい。要綱と要望時期は毎年度変わるため、当年度資料で確認してから提示し、断定しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="98" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B36" s="99" t="inlineStr">
+        <is>
+          <t>やらないこと</t>
+        </is>
+      </c>
+      <c r="C36" s="98" t="inlineStr">
+        <is>
+          <t>努力義務を理由に引かない</t>
+        </is>
+      </c>
+      <c r="D36" s="79" t="inlineStr">
+        <is>
+          <t>「努力義務なので」と相手に言わせる前に、直さざるを得ない理由（制度変更・財源・改定期）を先に出す。交付金を「使えます」と断定しない。社協に当たらずに自治体だけで完結させない。庁内横断が要る計画で、1つの課だけに話して終わらせない。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007F4FBF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="86" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>社内研修（5分）｜A 補正編／B 来期編</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>5分は「説明3分＋演習2分」で組む。A編（補正）は今期の期限が迫っているため先に、B編（来期）は後に回す。講師は持ち回りにして、教える側の学習機会にする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="90" t="inlineStr">
+        <is>
+          <t>① A 補正編 5分台本　── 高齢者介護／障がい計画（今期・12月補正）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="inlineStr">
+        <is>
+          <t>見出し</t>
+        </is>
+      </c>
+      <c r="C5" s="60" t="inlineStr">
+        <is>
+          <t>話す内容（台本）</t>
+        </is>
+      </c>
+      <c r="D5" s="60" t="inlineStr">
+        <is>
+          <t>押さえどころ</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="16" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="101" t="inlineStr">
+        <is>
+          <t>0:00–0:30</t>
+        </is>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>いま何が起きているか</t>
+        </is>
+      </c>
+      <c r="C6" s="63" t="inlineStr">
+        <is>
+          <t>「今年度は、高齢者の第10期と、障がいの第8期・第4期の策定年度が重なっています。小さい団体ほど、同じ課の同じ担当者が両方を持っています。自前で始めたものの、秋口で手が止まる先が必ず出ます。そこが今日の話です。」</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>「計画を売る」ではなく「重なっている年」という事実から入る。この認識を全員が持つだけで、訪問先の選び方が変わる。</t>
+        </is>
+      </c>
+      <c r="E6" s="48" t="n"/>
+      <c r="F6" s="48" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="101" t="inlineStr">
+        <is>
+          <t>0:30–1:30</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>狙う枠は12月補正。ひとつだけ</t>
+        </is>
+      </c>
+      <c r="C7" s="63" t="inlineStr">
+        <is>
+          <t>「9月補正はもう間に合いません。議案は8月中に固まっています。いま狙えるのは12月補正で、財政課への要求は11月上旬です。逆算すると、10月中に見積を出しておく必要があります。あと1か月です。」</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>枠を1つに絞る。複数の可能性を並べると、動く時期が曖昧になる。</t>
+        </is>
+      </c>
+      <c r="E7" s="48" t="n"/>
+      <c r="F7" s="48" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="101" t="inlineStr">
+        <is>
+          <t>1:30–2:30</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>期限の構造を、テーマごとに1文で言えるようにする</t>
+        </is>
+      </c>
+      <c r="C8" s="63" t="inlineStr">
+        <is>
+          <t>「高齢者は、R9年4月から保険料を賦課するのにR9年3月議会での条例改正が要る。逆算して10月末までに分析が終わっていないとパブコメの期間が取れない。障がいは議決の期限がないぶん後回しにされますが、県が市町村の見込量を集約するので、県への提出時期が実質の期限になります。」</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>この2文を全員が言えるようにする。これが相手の制約であり、こちらの都合ではないから話せる唯一の材料。</t>
+        </is>
+      </c>
+      <c r="E8" s="48" t="n"/>
+      <c r="F8" s="48" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="101" t="inlineStr">
+        <is>
+          <t>2:30–3:30</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>全部委託では通らない。切り出して出す</t>
+        </is>
+      </c>
+      <c r="C9" s="63" t="inlineStr">
+        <is>
+          <t>「補正は金額が大きいと査定に耐えません。時間がかかる工程だけ切り出します。高齢者なら保険料算定と給付費推計、障がいなら成果目標の設定と見込量の推計。そして高齢者と障がいは必ず分けて見積を出してください。1本にまとめると金額が膨らんで、査定で両方とも落ちます。」</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>「分けて出す」は今日いちばん持ち帰ってほしい実務。同じ課だからまとめたくなるが、そこで落ちる。</t>
+        </is>
+      </c>
+      <c r="E9" s="48" t="n"/>
+      <c r="F9" s="48" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="101" t="inlineStr">
+        <is>
+          <t>3:30–4:30</t>
+        </is>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>断られたときの逃げ道を先に持っておく</t>
+        </is>
+      </c>
+      <c r="C10" s="63" t="inlineStr">
+        <is>
+          <t>「予算がないと言われたら、調査・集計だけ既定予算の範囲で先行させて、本体は次年度当初に回す形を出してください。分析が先に終わっていれば間に合います。金額の線引きは自治体の契約規則によりますので、必ず確認してから話すこと。」</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>断られてから考えると引くだけになる。逃げ道を先に用意しておくと、その場で切り返せる。</t>
+        </is>
+      </c>
+      <c r="E10" s="48" t="n"/>
+      <c r="F10" s="48" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="101" t="inlineStr">
+        <is>
+          <t>4:30–5:00</t>
+        </is>
+      </c>
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>今週やること</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>「担当エリアで、高齢者と障がいを自前で作っている先を洗い出してください。そのうち9月中に訪問できる先に印を付けて、来週の朝礼で共有します。」</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>研修を「聞いて終わり」にしない。今週の行動を1つだけ指定して締める。</t>
+        </is>
+      </c>
+      <c r="E11" s="48" t="n"/>
+      <c r="F11" s="48" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="100" t="inlineStr">
+        <is>
+          <t>② B 来期編 5分台本　── 地域福祉計画／こども計画（R9年度当初予算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="60" t="inlineStr">
+        <is>
+          <t>時間</t>
+        </is>
+      </c>
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t>見出し</t>
+        </is>
+      </c>
+      <c r="C14" s="60" t="inlineStr">
+        <is>
+          <t>話す内容（台本）</t>
+        </is>
+      </c>
+      <c r="D14" s="60" t="inlineStr">
+        <is>
+          <t>押さえどころ</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="16" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="101" t="inlineStr">
+        <is>
+          <t>0:00–0:30</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>いつまでに何をするか</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>「来期の案件、地域福祉計画とこども計画の話です。R9年度の当初予算で取るなら、動くのは8月から10月です。11月から12月が査定、1月から3月が公告。予算要求書が固まってから訪問しても、その年度には載りません。」</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>先に期限を言う。「来期」と言った瞬間に先延ばしになるので、実際の作業は今月からだと最初に示す。</t>
+        </is>
+      </c>
+      <c r="E15" s="48" t="n"/>
+      <c r="F15" s="48" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="101" t="inlineStr">
+        <is>
+          <t>0:30–1:30</t>
+        </is>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>この2つは待っていても発注が生まれない</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>「どちらも努力義務の計画です。訪問記録を見ると、こども計画は『国や県の温度感を見ながら判断する』という回答が並んでいます。待ちの姿勢を崩す材料をこちらから持ち込まないと、来期も同じ回答が返ってきます。」</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>「努力義務だからやらない」と相手に言わせる前に、直さざるを得ない理由を先に出す、という順番を共有する。</t>
+        </is>
+      </c>
+      <c r="E16" s="48" t="n"/>
+      <c r="F16" s="48" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="101" t="inlineStr">
+        <is>
+          <t>1:30–2:30</t>
+        </is>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>地域福祉は束ねる</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>「地域福祉計画は単発では金額が小さく、採算に乗りません。併載できる計画──成年後見、再犯防止、自殺対策、孤独孤立──と、社協の地域福祉活動計画を束ねて初めて中規模になります。とくに成年後見は国の第二期が令和8年度で終期を迎えるので、来期の入口になります。持っていくのは、担当自治体の併載計画がいつ切れるかの一覧です。」</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>束ねる理由は「安くなる」ではなく「毎年どれかの改定が来る状態を、数年に一度にできる」。言い方を全員でそろえる。</t>
+        </is>
+      </c>
+      <c r="E17" s="48" t="n"/>
+      <c r="F17" s="48" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="101" t="inlineStr">
+        <is>
+          <t>2:30–3:30</t>
+        </is>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t>こどもは制度変更を理由にする</t>
+        </is>
+      </c>
+      <c r="C18" s="63" t="inlineStr">
+        <is>
+          <t>「こどもは、こども誰でも通園制度が地域子ども・子育て支援事業に位置付けられたことで、量の見込みへの反映が要ります。これが『制度が変わったので直さざるを得ない』という、担当者が庁内を説得できる唯一の理由です。持っていくのは、区域別・年齢別の量の見込みと実績の乖離率の一覧です。」</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>こども側の切り口は制度変更ひとつに絞る。複数並べると、どれも動かす力を持たなくなる。</t>
+        </is>
+      </c>
+      <c r="E18" s="48" t="n"/>
+      <c r="F18" s="48" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="101" t="inlineStr">
+        <is>
+          <t>3:30–4:30</t>
+        </is>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t>調査を先に、交付金とセットで取る</t>
+        </is>
+      </c>
+      <c r="C19" s="63" t="inlineStr">
+        <is>
+          <t>「計画本体は金額が大きく、来期の当初でも通らないことがあります。実態調査を先に単独で受けてください。こどもの貧困やヤングケアラーの調査は交付金が使える場合があり、金額も抑えられるので通りやすい。ただし要綱は毎年度変わりますので、『対象になり得るので確認を』で止めて、断定しないこと。」</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>二段で取る型を共有する。断定禁止はここでも繰り返す。</t>
+        </is>
+      </c>
+      <c r="E19" s="48" t="n"/>
+      <c r="F19" s="48" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="101" t="inlineStr">
+        <is>
+          <t>4:30–5:00</t>
+        </is>
+      </c>
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>今週やること</t>
+        </is>
+      </c>
+      <c r="C20" s="63" t="inlineStr">
+        <is>
+          <t>「担当エリアの地域福祉計画とこども計画について、計画期間の終期と併載計画を一覧にしてください。10月までに訪問する先を、来週の朝礼で共有します。」</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>こちらも行動を1つだけ指定する。一覧が作れていない状態で訪問しても、L2止まりの話しかできない。</t>
+        </is>
+      </c>
+      <c r="E20" s="48" t="n"/>
+      <c r="F20" s="48" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="102" t="inlineStr">
+        <is>
+          <t>③ 週次5分研修シリーズ（A編4回 → B編4回・約2か月で一巡）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="60" t="inlineStr">
+        <is>
+          <t>軸</t>
+        </is>
+      </c>
+      <c r="B23" s="60" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="C23" s="60" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="D23" s="60" t="inlineStr">
+        <is>
+          <t>伝えること（1回に1つだけ）</t>
+        </is>
+      </c>
+      <c r="E23" s="60" t="inlineStr">
+        <is>
+          <t>使う教材</t>
+        </is>
+      </c>
+      <c r="F23" s="60" t="inlineStr">
+        <is>
+          <t>その場の演習（2分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="92" t="inlineStr">
+        <is>
+          <t>A 補正</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>第1回</t>
+        </is>
+      </c>
+      <c r="C24" s="47" t="inlineStr">
+        <is>
+          <t>重なっている年を理解する</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>R8年度は高齢者・第10期と障がい・第8期／第4期の策定年度が重なる。同じ課が両方を持っている。</t>
+        </is>
+      </c>
+      <c r="E24" s="96" t="inlineStr">
+        <is>
+          <t>29_営業方針（A）／27_5分トーク集 A・F</t>
+        </is>
+      </c>
+      <c r="F24" s="91" t="inlineStr">
+        <is>
+          <t>担当エリアで高齢者・障がいを自前で作っている先を、その場で3件挙げる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="92" t="inlineStr">
+        <is>
+          <t>A 補正</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>第2回</t>
+        </is>
+      </c>
+      <c r="C25" s="47" t="inlineStr">
+        <is>
+          <t>期限の構造を言えるようにする</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>高齢者＝R9年3月議会の条例改正から逆算して10月末。障がい＝県への見込量提出が実質の期限。</t>
+        </is>
+      </c>
+      <c r="E25" s="96" t="inlineStr">
+        <is>
+          <t>29_営業方針（A・期限）／27_5分トーク集 A・F の1:30–3:00</t>
+        </is>
+      </c>
+      <c r="F25" s="91" t="inlineStr">
+        <is>
+          <t>2人1組で、高齢者と障がいの期限を1文ずつ、相手役に説明する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="92" t="inlineStr">
+        <is>
+          <t>A 補正</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>第3回</t>
+        </is>
+      </c>
+      <c r="C26" s="47" t="inlineStr">
+        <is>
+          <t>部分委託の切り分けを作る</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>全部委託は査定に耐えない。高齢者は保険料算定と給付費推計、障がいは成果目標と見込量だけを切り出す。</t>
+        </is>
+      </c>
+      <c r="E26" s="96" t="inlineStr">
+        <is>
+          <t>29_営業方針（A・切り出し）／16・17_営業提案の深度</t>
+        </is>
+      </c>
+      <c r="F26" s="91" t="inlineStr">
+        <is>
+          <t>訪問予定の1件について、切り出す工程と切り出さない工程をその場で書き分ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="92" t="inlineStr">
+        <is>
+          <t>A 補正</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>第4回</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="inlineStr">
+        <is>
+          <t>12月補正の段取りと断られ方</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>要求は11月上旬、逆算して10月中に見積。高齢者と障がいは必ず分けて出す。</t>
+        </is>
+      </c>
+      <c r="E27" s="96" t="inlineStr">
+        <is>
+          <t>28_想定問答とNG（A・F）／19_訪問前 準備チェックリスト</t>
+        </is>
+      </c>
+      <c r="F27" s="91" t="inlineStr">
+        <is>
+          <t>「予算がない」「自前でやれる」への切り返しを、1人ずつ声に出す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="103" t="inlineStr">
+        <is>
+          <t>B 来期</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>第5回</t>
+        </is>
+      </c>
+      <c r="C28" s="47" t="inlineStr">
+        <is>
+          <t>来期は8〜10月が勝負</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>R9年度当初での発注は、8〜10月に情報提供と参考見積、11〜12月が査定、1〜3月が公告。</t>
+        </is>
+      </c>
+      <c r="E28" s="96" t="inlineStr">
+        <is>
+          <t>29_営業方針（B・時期）／15_年間業務カレンダー</t>
+        </is>
+      </c>
+      <c r="F28" s="91" t="inlineStr">
+        <is>
+          <t>担当エリアの地域福祉・こどもについて、計画期間の終期を3件挙げる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="103" t="inlineStr">
+        <is>
+          <t>B 来期</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>第6回</t>
+        </is>
+      </c>
+      <c r="C29" s="47" t="inlineStr">
+        <is>
+          <t>地域福祉は束ねる</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>単発では採算に乗らない。併載計画と社協の活動計画を束ねて初めて中規模案件になる。</t>
+        </is>
+      </c>
+      <c r="E29" s="96" t="inlineStr">
+        <is>
+          <t>29_営業方針（B・地域福祉）／18_提案ネタ台帳（地域福祉）</t>
+        </is>
+      </c>
+      <c r="F29" s="91" t="inlineStr">
+        <is>
+          <t>担当自治体を1件選び、併載できる計画を思いつく限り挙げる（成年後見・再犯防止・自殺対策ほか）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="103" t="inlineStr">
+        <is>
+          <t>B 来期</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>第7回</t>
+        </is>
+      </c>
+      <c r="C30" s="47" t="inlineStr">
+        <is>
+          <t>こどもは制度変更を理由にする</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>こども誰でも通園制度の反映が「直さざるを得ない理由」になる。中間見直しの最も明確な入口。</t>
+        </is>
+      </c>
+      <c r="E30" s="96" t="inlineStr">
+        <is>
+          <t>29_営業方針（B・こども）／21_ヒアリング項目（こども・子育て）</t>
+        </is>
+      </c>
+      <c r="F30" s="91" t="inlineStr">
+        <is>
+          <t>こどもの担当課に何を聞くか、L3の質問を3つ選んで読み上げる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="103" t="inlineStr">
+        <is>
+          <t>B 来期</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>第8回</t>
+        </is>
+      </c>
+      <c r="C31" s="47" t="inlineStr">
+        <is>
+          <t>調査を先に、交付金とセットで</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>計画本体より調査のほうが通りやすい。ただし交付金は「対象になり得る」で止め、断定しない。</t>
+        </is>
+      </c>
+      <c r="E31" s="96" t="inlineStr">
+        <is>
+          <t>29_営業方針（B・財源）／17_深度マトリクス④⑤／18_提案ネタ台帳（財源）</t>
+        </is>
+      </c>
+      <c r="F31" s="91" t="inlineStr">
+        <is>
+          <t>担当自治体1件について、該当しうる交付金を1つ挙げ、その確認先を言う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="102" t="inlineStr">
+        <is>
+          <t>④ 運営のしかた</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="60" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B34" s="60" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C34" s="60" t="inlineStr">
+        <is>
+          <t>理由・補足</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="16" t="n"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="75" t="inlineStr">
+        <is>
+          <t>時間配分</t>
+        </is>
+      </c>
+      <c r="B35" s="47" t="inlineStr">
+        <is>
+          <t>説明3分＋演習2分</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>説明だけの5分は翌週には残らない。手や口を動かす2分を必ず入れる。</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="75" t="inlineStr">
+        <is>
+          <t>順番</t>
+        </is>
+      </c>
+      <c r="B36" s="47" t="inlineStr">
+        <is>
+          <t>A編（補正）を先に、B編（来期）を後に</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>A編は今期の期限が迫っており、10月を過ぎると使えなくなる。8〜9月にA編4回、10〜11月にB編4回を目安にする。</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="75" t="inlineStr">
+        <is>
+          <t>講師</t>
+        </is>
+      </c>
+      <c r="B37" s="47" t="inlineStr">
+        <is>
+          <t>持ち回りにする</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>教える側がいちばん学ぶ。各回のテーマに近い担当者が講師を務める。L4の「指導・組織貢献」の評価項目にそのまま紐づく。</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="75" t="inlineStr">
+        <is>
+          <t>締め方</t>
+        </is>
+      </c>
+      <c r="B38" s="47" t="inlineStr">
+        <is>
+          <t>毎回、今週やることを1つだけ指定する</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>行動を指定しない研修は聞いて終わる。翌週の冒頭で、前回指定した行動の結果を共有する。</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="75" t="inlineStr">
+        <is>
+          <t>記録</t>
+        </is>
+      </c>
+      <c r="B39" s="47" t="inlineStr">
+        <is>
+          <t>個人別チェックシートに紐づける</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>各回の演習で挙がった内容を、12_個人別チェックシートの「根拠となる実績」欄に書き足す。研修が評価と切れていると続かない。</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="78" t="inlineStr">
+        <is>
+          <t>やらないこと</t>
+        </is>
+      </c>
+      <c r="B40" s="98" t="inlineStr">
+        <is>
+          <t>資料を読み上げるだけの回にしない</t>
+        </is>
+      </c>
+      <c r="C40" s="79" t="inlineStr">
+        <is>
+          <t>読み上げなら配布で足りる。5分の場を取る以上、その場でしか起きないこと（実演・申告・点検）を必ず入れる。</t>
+        </is>
+      </c>
+      <c r="D40" s="79" t="n"/>
+      <c r="E40" s="79" t="n"/>
+      <c r="F40" s="79" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="C36:F36"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23135,821 +24656,821 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="101" t="inlineStr">
+      <c r="A1" s="104" t="inlineStr">
         <is>
           <t>エリア</t>
         </is>
       </c>
-      <c r="B1" s="101" t="inlineStr">
+      <c r="B1" s="104" t="inlineStr">
         <is>
           <t>テーマ</t>
         </is>
       </c>
-      <c r="C1" s="101" t="inlineStr">
+      <c r="C1" s="104" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
-      <c r="D1" s="101" t="inlineStr">
+      <c r="D1" s="104" t="inlineStr">
         <is>
           <t>次回アクション</t>
         </is>
       </c>
-      <c r="E1" s="101" t="inlineStr">
+      <c r="E1" s="104" t="inlineStr">
         <is>
           <t>前回策定</t>
         </is>
       </c>
-      <c r="F1" s="101" t="inlineStr">
+      <c r="F1" s="104" t="inlineStr">
         <is>
           <t>改定時期</t>
         </is>
       </c>
-      <c r="G1" s="101" t="inlineStr">
+      <c r="G1" s="104" t="inlineStr">
         <is>
           <t>アプローチ時期</t>
         </is>
       </c>
-      <c r="H1" s="101" t="inlineStr">
+      <c r="H1" s="104" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="I1" s="101" t="inlineStr">
+      <c r="I1" s="104" t="inlineStr">
         <is>
           <t>契約予定</t>
         </is>
       </c>
-      <c r="J1" s="101" t="inlineStr">
+      <c r="J1" s="104" t="inlineStr">
         <is>
           <t>温度感</t>
         </is>
       </c>
-      <c r="K1" s="101" t="inlineStr">
+      <c r="K1" s="104" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="102" t="inlineStr">
+      <c r="A2" s="105" t="inlineStr">
         <is>
           <t>北海道</t>
         </is>
       </c>
-      <c r="B2" s="102" t="inlineStr">
+      <c r="B2" s="105" t="inlineStr">
         <is>
           <t>公会計</t>
         </is>
       </c>
-      <c r="C2" s="102" t="inlineStr">
+      <c r="C2" s="105" t="inlineStr">
         <is>
           <t>見積提示</t>
         </is>
       </c>
-      <c r="D2" s="102" t="inlineStr">
+      <c r="D2" s="105" t="inlineStr">
         <is>
           <t>再アプローチ</t>
         </is>
       </c>
-      <c r="E2" s="102" t="inlineStr">
+      <c r="E2" s="105" t="inlineStr">
         <is>
           <t>委託</t>
         </is>
       </c>
-      <c r="F2" s="102" t="inlineStr">
+      <c r="F2" s="105" t="inlineStr">
         <is>
           <t>R6</t>
         </is>
       </c>
-      <c r="G2" s="102" t="inlineStr">
+      <c r="G2" s="105" t="inlineStr">
         <is>
           <t>今年度</t>
         </is>
       </c>
-      <c r="H2" s="102" t="inlineStr">
+      <c r="H2" s="105" t="inlineStr">
         <is>
           <t>初回訪問</t>
         </is>
       </c>
-      <c r="I2" s="102" t="inlineStr">
+      <c r="I2" s="105" t="inlineStr">
         <is>
           <t>入札</t>
         </is>
       </c>
-      <c r="J2" s="102" t="inlineStr">
+      <c r="J2" s="105" t="inlineStr">
         <is>
           <t>A：今年度中に動く</t>
         </is>
       </c>
-      <c r="K2" s="102" t="inlineStr">
+      <c r="K2" s="105" t="inlineStr">
         <is>
           <t>財務書類作成</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="102" t="inlineStr">
+      <c r="A3" s="105" t="inlineStr">
         <is>
           <t>青森県</t>
         </is>
       </c>
-      <c r="B3" s="102" t="inlineStr">
+      <c r="B3" s="105" t="inlineStr">
         <is>
           <t>会計支援</t>
         </is>
       </c>
-      <c r="C3" s="102" t="inlineStr">
+      <c r="C3" s="105" t="inlineStr">
         <is>
           <t>自力</t>
         </is>
       </c>
-      <c r="D3" s="102" t="inlineStr">
+      <c r="D3" s="105" t="inlineStr">
         <is>
           <t>見積提示</t>
         </is>
       </c>
-      <c r="E3" s="102" t="inlineStr">
+      <c r="E3" s="105" t="inlineStr">
         <is>
           <t>自前</t>
         </is>
       </c>
-      <c r="F3" s="102" t="inlineStr">
+      <c r="F3" s="105" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
       </c>
-      <c r="G3" s="102" t="inlineStr">
+      <c r="G3" s="105" t="inlineStr">
         <is>
           <t>来年度</t>
         </is>
       </c>
-      <c r="H3" s="102" t="inlineStr">
+      <c r="H3" s="105" t="inlineStr">
         <is>
           <t>セカンドアプローチ</t>
         </is>
       </c>
-      <c r="I3" s="102" t="inlineStr">
+      <c r="I3" s="105" t="inlineStr">
         <is>
           <t>見積合わせ</t>
         </is>
       </c>
-      <c r="J3" s="102" t="inlineStr">
+      <c r="J3" s="105" t="inlineStr">
         <is>
           <t>B：次年度予算で検討</t>
         </is>
       </c>
-      <c r="K3" s="102" t="inlineStr">
+      <c r="K3" s="105" t="inlineStr">
         <is>
           <t>台帳精緻化（全体）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="102" t="inlineStr">
+      <c r="A4" s="105" t="inlineStr">
         <is>
           <t>岩手県</t>
         </is>
       </c>
-      <c r="B4" s="102" t="inlineStr">
+      <c r="B4" s="105" t="inlineStr">
         <is>
           <t>経営戦略</t>
         </is>
       </c>
-      <c r="C4" s="102" t="inlineStr">
+      <c r="C4" s="105" t="inlineStr">
         <is>
           <t>他社随契</t>
         </is>
       </c>
-      <c r="D4" s="102" t="inlineStr">
+      <c r="D4" s="105" t="inlineStr">
         <is>
           <t>同行依頼、再訪</t>
         </is>
       </c>
-      <c r="F4" s="102" t="inlineStr">
+      <c r="F4" s="105" t="inlineStr">
         <is>
           <t>R8</t>
         </is>
       </c>
-      <c r="G4" s="102" t="inlineStr">
+      <c r="G4" s="105" t="inlineStr">
         <is>
           <t>再来年度</t>
         </is>
       </c>
-      <c r="H4" s="102" t="inlineStr">
+      <c r="H4" s="105" t="inlineStr">
         <is>
           <t>見積提示</t>
         </is>
       </c>
-      <c r="I4" s="102" t="inlineStr">
+      <c r="I4" s="105" t="inlineStr">
         <is>
           <t>随契</t>
         </is>
       </c>
-      <c r="J4" s="102" t="inlineStr">
+      <c r="J4" s="105" t="inlineStr">
         <is>
           <t>C：様子見</t>
         </is>
       </c>
-      <c r="K4" s="102" t="inlineStr">
+      <c r="K4" s="105" t="inlineStr">
         <is>
           <t>台帳精緻化（所有外管理資産）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="102" t="inlineStr">
+      <c r="A5" s="105" t="inlineStr">
         <is>
           <t>宮城県</t>
         </is>
       </c>
-      <c r="B5" s="102" t="inlineStr">
+      <c r="B5" s="105" t="inlineStr">
         <is>
           <t>経営改善</t>
         </is>
       </c>
-      <c r="C5" s="102" t="inlineStr">
+      <c r="C5" s="105" t="inlineStr">
         <is>
           <t>不在</t>
         </is>
       </c>
-      <c r="D5" s="102" t="inlineStr">
+      <c r="D5" s="105" t="inlineStr">
         <is>
           <t>再訪不要</t>
         </is>
       </c>
-      <c r="F5" s="102" t="inlineStr">
+      <c r="F5" s="105" t="inlineStr">
         <is>
           <t>R9</t>
         </is>
       </c>
-      <c r="H5" s="102" t="inlineStr">
+      <c r="H5" s="105" t="inlineStr">
         <is>
           <t>見積＋仕様書</t>
         </is>
       </c>
-      <c r="I5" s="102" t="inlineStr">
+      <c r="I5" s="105" t="inlineStr">
         <is>
           <t>プロポ</t>
         </is>
       </c>
-      <c r="J5" s="102" t="inlineStr">
+      <c r="J5" s="105" t="inlineStr">
         <is>
           <t>D：当面なし</t>
         </is>
       </c>
-      <c r="K5" s="102" t="inlineStr">
+      <c r="K5" s="105" t="inlineStr">
         <is>
           <t>公会計システム導入</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="102" t="inlineStr">
+      <c r="A6" s="105" t="inlineStr">
         <is>
           <t>秋田県</t>
         </is>
       </c>
-      <c r="B6" s="102" t="inlineStr">
+      <c r="B6" s="105" t="inlineStr">
         <is>
           <t>福祉計画</t>
         </is>
       </c>
-      <c r="C6" s="102" t="inlineStr">
+      <c r="C6" s="105" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="F6" s="102" t="inlineStr">
+      <c r="F6" s="105" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="K6" s="102" t="inlineStr">
+      <c r="K6" s="105" t="inlineStr">
         <is>
           <t>財務書類の活用支援・分析</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="102" t="inlineStr">
+      <c r="A7" s="105" t="inlineStr">
         <is>
           <t>山形県</t>
         </is>
       </c>
-      <c r="B7" s="102" t="inlineStr">
+      <c r="B7" s="105" t="inlineStr">
         <is>
           <t>公共施設マネジメント</t>
         </is>
       </c>
-      <c r="F7" s="102" t="inlineStr">
+      <c r="F7" s="105" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="K7" s="102" t="inlineStr">
+      <c r="K7" s="105" t="inlineStr">
         <is>
           <t>職員研修（公会計）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="102" t="inlineStr">
+      <c r="A8" s="105" t="inlineStr">
         <is>
           <t>福島県</t>
         </is>
       </c>
-      <c r="B8" s="102" t="inlineStr">
+      <c r="B8" s="105" t="inlineStr">
         <is>
           <t>社会生活計画</t>
         </is>
       </c>
-      <c r="F8" s="102" t="inlineStr">
+      <c r="F8" s="105" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="K8" s="102" t="inlineStr">
+      <c r="K8" s="105" t="inlineStr">
         <is>
           <t>公営企業会計 会計支援</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="102" t="inlineStr">
+      <c r="A9" s="105" t="inlineStr">
         <is>
           <t>茨城県</t>
         </is>
       </c>
-      <c r="B9" s="102" t="inlineStr">
+      <c r="B9" s="105" t="inlineStr">
         <is>
           <t>その他計画</t>
         </is>
       </c>
-      <c r="F9" s="102" t="inlineStr">
+      <c r="F9" s="105" t="inlineStr">
         <is>
           <t>R13</t>
         </is>
       </c>
-      <c r="K9" s="102" t="inlineStr">
+      <c r="K9" s="105" t="inlineStr">
         <is>
           <t>公営企業会計 適用（法適化）支援</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="102" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>栃木県</t>
         </is>
       </c>
-      <c r="F10" s="102" t="inlineStr">
+      <c r="F10" s="105" t="inlineStr">
         <is>
           <t>R14</t>
         </is>
       </c>
-      <c r="K10" s="102" t="inlineStr">
+      <c r="K10" s="105" t="inlineStr">
         <is>
           <t>決算・決算統計 作成支援</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="102" t="inlineStr">
+      <c r="A11" s="105" t="inlineStr">
         <is>
           <t>群馬県</t>
         </is>
       </c>
-      <c r="F11" s="102" t="inlineStr">
+      <c r="F11" s="105" t="inlineStr">
         <is>
           <t>R15</t>
         </is>
       </c>
-      <c r="K11" s="102" t="inlineStr">
+      <c r="K11" s="105" t="inlineStr">
         <is>
           <t>上下水道 経営戦略（策定）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="102" t="inlineStr">
+      <c r="A12" s="105" t="inlineStr">
         <is>
           <t>埼玉県</t>
         </is>
       </c>
-      <c r="F12" s="102" t="inlineStr">
+      <c r="F12" s="105" t="inlineStr">
         <is>
           <t>R16</t>
         </is>
       </c>
-      <c r="K12" s="102" t="inlineStr">
+      <c r="K12" s="105" t="inlineStr">
         <is>
           <t>上下水道 経営戦略（改定）</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="102" t="inlineStr">
+      <c r="A13" s="105" t="inlineStr">
         <is>
           <t>千葉県</t>
         </is>
       </c>
-      <c r="F13" s="102" t="inlineStr">
+      <c r="F13" s="105" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="K13" s="102" t="inlineStr">
+      <c r="K13" s="105" t="inlineStr">
         <is>
           <t>アセットマネジメント・ストックマネジメント</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="102" t="inlineStr">
+      <c r="A14" s="105" t="inlineStr">
         <is>
           <t>東京都</t>
         </is>
       </c>
-      <c r="F14" s="102" t="inlineStr">
+      <c r="F14" s="105" t="inlineStr">
         <is>
           <t>R18</t>
         </is>
       </c>
-      <c r="K14" s="102" t="inlineStr">
+      <c r="K14" s="105" t="inlineStr">
         <is>
           <t>病院事業 経営強化プラン</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="102" t="inlineStr">
+      <c r="A15" s="105" t="inlineStr">
         <is>
           <t>神奈川県</t>
         </is>
       </c>
-      <c r="F15" s="102" t="inlineStr">
+      <c r="F15" s="105" t="inlineStr">
         <is>
           <t>R19</t>
         </is>
       </c>
-      <c r="K15" s="102" t="inlineStr">
+      <c r="K15" s="105" t="inlineStr">
         <is>
           <t>料金・使用料改定</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="102" t="inlineStr">
+      <c r="A16" s="105" t="inlineStr">
         <is>
           <t>新潟県</t>
         </is>
       </c>
-      <c r="F16" s="102" t="inlineStr">
+      <c r="F16" s="105" t="inlineStr">
         <is>
           <t>R20</t>
         </is>
       </c>
-      <c r="K16" s="102" t="inlineStr">
+      <c r="K16" s="105" t="inlineStr">
         <is>
           <t>経営分析（経営比較分析表の活用）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="102" t="inlineStr">
+      <c r="A17" s="105" t="inlineStr">
         <is>
           <t>富山県</t>
         </is>
       </c>
-      <c r="K17" s="102" t="inlineStr">
+      <c r="K17" s="105" t="inlineStr">
         <is>
           <t>広域化・官民連携 検討支援</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="102" t="inlineStr">
+      <c r="A18" s="105" t="inlineStr">
         <is>
           <t>石川県</t>
         </is>
       </c>
-      <c r="K18" s="102" t="inlineStr">
+      <c r="K18" s="105" t="inlineStr">
         <is>
           <t>高齢者福祉計画・介護保険事業計画</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="102" t="inlineStr">
+      <c r="A19" s="105" t="inlineStr">
         <is>
           <t>福井県</t>
         </is>
       </c>
-      <c r="K19" s="102" t="inlineStr">
+      <c r="K19" s="105" t="inlineStr">
         <is>
           <t>障害者計画・障害福祉計画・障害児福祉計画</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="102" t="inlineStr">
+      <c r="A20" s="105" t="inlineStr">
         <is>
           <t>山梨県</t>
         </is>
       </c>
-      <c r="K20" s="102" t="inlineStr">
+      <c r="K20" s="105" t="inlineStr">
         <is>
           <t>地域福祉計画</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="102" t="inlineStr">
+      <c r="A21" s="105" t="inlineStr">
         <is>
           <t>長野県</t>
         </is>
       </c>
-      <c r="K21" s="102" t="inlineStr">
+      <c r="K21" s="105" t="inlineStr">
         <is>
           <t>こども計画</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="102" t="inlineStr">
+      <c r="A22" s="105" t="inlineStr">
         <is>
           <t>岐阜県</t>
         </is>
       </c>
-      <c r="K22" s="102" t="inlineStr">
+      <c r="K22" s="105" t="inlineStr">
         <is>
           <t>子ども子育て支援事業計画</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="102" t="inlineStr">
+      <c r="A23" s="105" t="inlineStr">
         <is>
           <t>静岡県</t>
         </is>
       </c>
-      <c r="K23" s="102" t="inlineStr">
+      <c r="K23" s="105" t="inlineStr">
         <is>
           <t>重層的支援体制整備事業 支援</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="102" t="inlineStr">
+      <c r="A24" s="105" t="inlineStr">
         <is>
           <t>愛知県</t>
         </is>
       </c>
-      <c r="K24" s="102" t="inlineStr">
+      <c r="K24" s="105" t="inlineStr">
         <is>
           <t>福祉分野 アンケート調査（単独受託）</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="102" t="inlineStr">
+      <c r="A25" s="105" t="inlineStr">
         <is>
           <t>三重県</t>
         </is>
       </c>
-      <c r="K25" s="102" t="inlineStr">
+      <c r="K25" s="105" t="inlineStr">
         <is>
           <t>公共施設等総合管理計画</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="102" t="inlineStr">
+      <c r="A26" s="105" t="inlineStr">
         <is>
           <t>滋賀県</t>
         </is>
       </c>
-      <c r="K26" s="102" t="inlineStr">
+      <c r="K26" s="105" t="inlineStr">
         <is>
           <t>個別施設計画</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="102" t="inlineStr">
+      <c r="A27" s="105" t="inlineStr">
         <is>
           <t>京都府</t>
         </is>
       </c>
-      <c r="K27" s="102" t="inlineStr">
+      <c r="K27" s="105" t="inlineStr">
         <is>
           <t>施設カルテ・施設白書</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="102" t="inlineStr">
+      <c r="A28" s="105" t="inlineStr">
         <is>
           <t>大阪府</t>
         </is>
       </c>
-      <c r="K28" s="102" t="inlineStr">
+      <c r="K28" s="105" t="inlineStr">
         <is>
           <t>公共施設 再編・適正配置検討</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="102" t="inlineStr">
+      <c r="A29" s="105" t="inlineStr">
         <is>
           <t>兵庫県</t>
         </is>
       </c>
-      <c r="K29" s="102" t="inlineStr">
+      <c r="K29" s="105" t="inlineStr">
         <is>
           <t>健康増進計画・食育推進計画</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="102" t="inlineStr">
+      <c r="A30" s="105" t="inlineStr">
         <is>
           <t>奈良県</t>
         </is>
       </c>
-      <c r="K30" s="102" t="inlineStr">
+      <c r="K30" s="105" t="inlineStr">
         <is>
           <t>自殺対策計画</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="102" t="inlineStr">
+      <c r="A31" s="105" t="inlineStr">
         <is>
           <t>和歌山県</t>
         </is>
       </c>
-      <c r="K31" s="102" t="inlineStr">
+      <c r="K31" s="105" t="inlineStr">
         <is>
           <t>男女共同参画計画</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="102" t="inlineStr">
+      <c r="A32" s="105" t="inlineStr">
         <is>
           <t>鳥取県</t>
         </is>
       </c>
-      <c r="K32" s="102" t="inlineStr">
+      <c r="K32" s="105" t="inlineStr">
         <is>
           <t>環境基本計画</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="102" t="inlineStr">
+      <c r="A33" s="105" t="inlineStr">
         <is>
           <t>島根県</t>
         </is>
       </c>
-      <c r="K33" s="102" t="inlineStr">
+      <c r="K33" s="105" t="inlineStr">
         <is>
           <t>地域公共交通計画</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="102" t="inlineStr">
+      <c r="A34" s="105" t="inlineStr">
         <is>
           <t>岡山県</t>
         </is>
       </c>
-      <c r="K34" s="102" t="inlineStr">
+      <c r="K34" s="105" t="inlineStr">
         <is>
           <t>文化財保存活用地域計画</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="102" t="inlineStr">
+      <c r="A35" s="105" t="inlineStr">
         <is>
           <t>広島県</t>
         </is>
       </c>
-      <c r="K35" s="102" t="inlineStr">
+      <c r="K35" s="105" t="inlineStr">
         <is>
           <t>総合計画</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="102" t="inlineStr">
+      <c r="A36" s="105" t="inlineStr">
         <is>
           <t>山口県</t>
         </is>
       </c>
-      <c r="K36" s="102" t="inlineStr">
+      <c r="K36" s="105" t="inlineStr">
         <is>
           <t>財政計画・中期財政推計</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="102" t="inlineStr">
+      <c r="A37" s="105" t="inlineStr">
         <is>
           <t>徳島県</t>
         </is>
       </c>
-      <c r="K37" s="102" t="inlineStr">
+      <c r="K37" s="105" t="inlineStr">
         <is>
           <t>農業振興計画・地域計画</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="102" t="inlineStr">
+      <c r="A38" s="105" t="inlineStr">
         <is>
           <t>香川県</t>
         </is>
       </c>
-      <c r="K38" s="102" t="inlineStr">
+      <c r="K38" s="105" t="inlineStr">
         <is>
           <t>国土強靱化地域計画</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="102" t="inlineStr">
+      <c r="A39" s="105" t="inlineStr">
         <is>
           <t>愛媛県</t>
         </is>
       </c>
-      <c r="K39" s="102" t="inlineStr">
+      <c r="K39" s="105" t="inlineStr">
         <is>
           <t>その他（上記以外）</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="102" t="inlineStr">
+      <c r="A40" s="105" t="inlineStr">
         <is>
           <t>高知県</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="102" t="inlineStr">
+      <c r="A41" s="105" t="inlineStr">
         <is>
           <t>福岡県</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="102" t="inlineStr">
+      <c r="A42" s="105" t="inlineStr">
         <is>
           <t>佐賀県</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="102" t="inlineStr">
+      <c r="A43" s="105" t="inlineStr">
         <is>
           <t>長崎県</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="102" t="inlineStr">
+      <c r="A44" s="105" t="inlineStr">
         <is>
           <t>熊本県</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="102" t="inlineStr">
+      <c r="A45" s="105" t="inlineStr">
         <is>
           <t>大分県</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="102" t="inlineStr">
+      <c r="A46" s="105" t="inlineStr">
         <is>
           <t>宮崎県</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="102" t="inlineStr">
+      <c r="A47" s="105" t="inlineStr">
         <is>
           <t>鹿児島県</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="102" t="inlineStr">
+      <c r="A48" s="105" t="inlineStr">
         <is>
           <t>沖縄県</t>
         </is>
